--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43418FE0-6F10-1B45-BC56-C798283ACE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC05DAE-F2D1-8D42-9860-7E7529523797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
     <sheet name="Background Music" sheetId="2" r:id="rId2"/>
-    <sheet name="Upcoming" sheetId="3" r:id="rId3"/>
+    <sheet name="Upcoming" sheetId="21" r:id="rId3"/>
     <sheet name="Highlights" sheetId="4" r:id="rId4"/>
     <sheet name="Recap" sheetId="5" r:id="rId5"/>
     <sheet name="Memory (2)" sheetId="6" r:id="rId6"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2640" uniqueCount="1912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="1915">
   <si>
     <t>date</t>
   </si>
@@ -6445,15 +6445,27 @@
     <t>https://naver.me/xhPZWDQo</t>
   </si>
   <si>
-    <t>Jungkook x Graff – New Campaign Teaser</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/p/DaPpIemMTuY/</t>
+    <t>https://www.instagram.com/p/DaPpIemMTuY/,
+https://www.instagram.com/p/DaSN324sJKp/</t>
   </si>
   <si>
     <t>IG Post: Graff | Jungkook
-Graff is defined not by a single story, but by the many facets that shape its legacy.
-Discover an icon, reimagined.</t>
+“Jung Kook is a cultural icon, known for his multifaceted talents. His performances are bold yet refined, crafted with a brilliance that is impossible to ignore. Just as we at Graff push the boundaries of what is achievable in luxury jewellery, Jungkook continually challenges creative boundaries in his work. We are delighted to welcome him as Graff’s new global ambassador,” Francois Graff, Chief Executive Officer.</t>
+  </si>
+  <si>
+    <t>Graff unveils Jung Kook as its new House ambassador</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DaT1EzxiPPA/?igsh=bXA3M2xvNDBsd3pp, https://www.instagram.com/p/DaT1E3QCY-r/?igsh=dWcyYjR3OWJtMHI=</t>
+  </si>
+  <si>
+    <t>HiteJinro Appoints BTS’s V as JINRO Ambassador</t>
+  </si>
+  <si>
+    <t>The company explained that V was chosen as its global ambassador as part of its strategy to make JINRO more widely recognized and approachable to consumers around the world while further strengthening the brand’s competitiveness. As global ambassador, V will also participate in various domestic marketing campaigns for JINRO soju and connect with consumers both in Korea and internationally.
+V is an artist whose influence extends far beyond Korea, earning worldwide recognition for his global impact. With his distinctive charm and trendsetting style, he is loved by fans across the globe.
+In particular, HiteJinro believes V naturally embodies the youthful and trendy image that the JINRO brand represents. Through his strong affinity with the brand and authentic appeal, the company expects him to build meaningful connections with consumers.
+Together with global ambassador V, HiteJinro plans to roll out a variety of JINRO marketing campaigns both in Korea and overseas. Through these efforts, the company aims to expand its reach among domestic and international consumers while further strengthening JINRO’s brand awareness and preference worldwide.</t>
   </si>
 </sst>
 </file>
@@ -59582,97 +59594,39 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DBC8E1B-7F99-D641-8142-AF4882824481}">
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="10.83203125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="50.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5" style="10" customWidth="1"/>
-    <col min="5" max="5" width="41.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="105.6640625" style="10" customWidth="1"/>
-    <col min="7" max="73" width="10.83203125" style="10" customWidth="1"/>
-    <col min="74" max="16384" width="10.83203125" style="10"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="5" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="221" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18">
-        <v>46204</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1909</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>1910</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>1911</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="18"/>
-      <c r="B5" s="20"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="18"/>
-      <c r="B6" s="20"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="20"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
+      <c r="G1" s="5"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{F23700F8-E74A-5D47-AC41-59F48DC8942D}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="10" customWidth="1"/>
@@ -59704,244 +59658,278 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="102" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="255" x14ac:dyDescent="0.2">
       <c r="A2" s="18">
-        <v>46201</v>
+        <v>46205</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>231</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1864</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>1866</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>1872</v>
+        <v>1913</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>1912</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="119" x14ac:dyDescent="0.2">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A3" s="18">
-        <v>46177</v>
+        <v>46205</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>221</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>1911</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>1909</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="102" x14ac:dyDescent="0.2">
+      <c r="A4" s="18">
+        <v>46201</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>1872</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="119" x14ac:dyDescent="0.2">
+      <c r="A5" s="18">
+        <v>46177</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>1869</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D5" s="10" t="s">
         <v>1868</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E5" s="19" t="s">
         <v>1874</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F5" s="19" t="s">
         <v>1867</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="221" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18">
+    <row r="6" spans="1:7" ht="221" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="18">
         <v>46115</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B6" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C6" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E6" s="19" t="s">
         <v>1871</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F6" s="19" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="372" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18">
+    <row r="7" spans="1:7" ht="372" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="18">
         <v>46101</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B7" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C7" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D7" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E7" s="19" t="s">
         <v>1873</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F7" s="19" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="187" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+    <row r="8" spans="1:7" ht="187" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="18">
         <v>46065</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>1870</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="187" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18">
-        <v>46003</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
-        <v>45957</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>221</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>1870</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="187" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18">
+        <v>46003</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18">
+        <v>45957</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E10" s="19" t="s">
         <v>1875</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F10" s="19" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="204" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18">
+    <row r="11" spans="1:7" ht="204" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18">
         <v>45956</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B11" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C11" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D11" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E11" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F11" s="19" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="204" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+    <row r="12" spans="1:7" ht="204" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="18">
         <v>45935</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B12" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C12" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D12" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E12" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F12" s="19" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="272" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18">
+    <row r="13" spans="1:7" ht="272" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18">
         <v>45912</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B13" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C13" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D13" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E13" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F13" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="G11" s="19"/>
-    </row>
-    <row r="12" spans="1:7" ht="238" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" spans="1:7" ht="238" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="18">
         <v>45894</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B14" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C14" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D14" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E14" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F14" s="19" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="204" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18">
+    <row r="15" spans="1:7" ht="204" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18">
         <v>45844</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B15" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C15" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D15" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E15" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F15" s="19" t="s">
         <v>250</v>
       </c>
     </row>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC05DAE-F2D1-8D42-9860-7E7529523797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A3AE96-EA22-A147-ACF0-E0FD26891B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="1915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2646" uniqueCount="1917">
   <si>
     <t>date</t>
   </si>
@@ -6445,10 +6445,6 @@
     <t>https://naver.me/xhPZWDQo</t>
   </si>
   <si>
-    <t>https://www.instagram.com/p/DaPpIemMTuY/,
-https://www.instagram.com/p/DaSN324sJKp/</t>
-  </si>
-  <si>
     <t>IG Post: Graff | Jungkook
 “Jung Kook is a cultural icon, known for his multifaceted talents. His performances are bold yet refined, crafted with a brilliance that is impossible to ignore. Just as we at Graff push the boundaries of what is achievable in luxury jewellery, Jungkook continually challenges creative boundaries in his work. We are delighted to welcome him as Graff’s new global ambassador,” Francois Graff, Chief Executive Officer.</t>
   </si>
@@ -6456,16 +6452,27 @@
     <t>Graff unveils Jung Kook as its new House ambassador</t>
   </si>
   <si>
-    <t>https://www.instagram.com/p/DaT1EzxiPPA/?igsh=bXA3M2xvNDBsd3pp, https://www.instagram.com/p/DaT1E3QCY-r/?igsh=dWcyYjR3OWJtMHI=</t>
-  </si>
-  <si>
     <t>HiteJinro Appoints BTS’s V as JINRO Ambassador</t>
   </si>
   <si>
+    <t>jinro_july2026</t>
+  </si>
+  <si>
     <t>The company explained that V was chosen as its global ambassador as part of its strategy to make JINRO more widely recognized and approachable to consumers around the world while further strengthening the brand’s competitiveness. As global ambassador, V will also participate in various domestic marketing campaigns for JINRO soju and connect with consumers both in Korea and internationally.
-V is an artist whose influence extends far beyond Korea, earning worldwide recognition for his global impact. With his distinctive charm and trendsetting style, he is loved by fans across the globe.
-In particular, HiteJinro believes V naturally embodies the youthful and trendy image that the JINRO brand represents. Through his strong affinity with the brand and authentic appeal, the company expects him to build meaningful connections with consumers.
 Together with global ambassador V, HiteJinro plans to roll out a variety of JINRO marketing campaigns both in Korea and overseas. Through these efforts, the company aims to expand its reach among domestic and international consumers while further strengthening JINRO’s brand awareness and preference worldwide.</t>
+  </si>
+  <si>
+    <t>graff_july2026</t>
+  </si>
+  <si>
+    <t>graff_JK1.webp,
+https://www.instagram.com/p/DaPpIemMTuY/,
+https://www.instagram.com/p/DaSN324sJKp/</t>
+  </si>
+  <si>
+    <t>Jinro_Tae1.webp,
+https://www.instagram.com/p/DaT1E3QCY-r,
+https://www.instagram.com/p/DaT1EzxiPPA/</t>
   </si>
 </sst>
 </file>
@@ -59658,21 +59665,24 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="255" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="136" x14ac:dyDescent="0.2">
       <c r="A2" s="18">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>231</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>1912</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F2" s="19" t="s">
         <v>1913</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>1912</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>1914</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="85" x14ac:dyDescent="0.2">
@@ -59683,13 +59693,16 @@
         <v>221</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1911</v>
+        <v>1910</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>1914</v>
       </c>
       <c r="E3" s="19" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F3" s="19" t="s">
         <v>1909</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>1910</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="102" x14ac:dyDescent="0.2">

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A3AE96-EA22-A147-ACF0-E0FD26891B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714F4C04-C828-FA4B-9919-8DA4E3E5ED1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2646" uniqueCount="1917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="1925">
   <si>
     <t>date</t>
   </si>
@@ -6474,6 +6474,30 @@
 https://www.instagram.com/p/DaT1E3QCY-r,
 https://www.instagram.com/p/DaT1EzxiPPA/</t>
   </si>
+  <si>
+    <t>https://www.instagram.com/p/DaS3cncgHA0</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DaS3s1bNID5</t>
+  </si>
+  <si>
+    <t>Jungkook’s Calvin Klein collection sells out worldwide once again</t>
+  </si>
+  <si>
+    <t>BTS Jungkook’s “Jungkook for Calvin Klein (CKJK)” collection has sold out again following its latest restock, with products selling out across multiple regions. PVH Corp. described it as the most successful collaboration in Calvin Klein’s history, driven by unprecedented global demand and Jungkook’s creative involvement.</t>
+  </si>
+  <si>
+    <t>https://naver.me/5zU7mSVf</t>
+  </si>
+  <si>
+    <t>V’s kindness and warmth in Paris moves fans and locals alike</t>
+  </si>
+  <si>
+    <t>BTS V captured attention in Paris after being seen assisting an elderly woman outside his hotel following the CELINE Men’s SS27 show, along with other moments showing his warmth toward staff and fans during his busy schedule, which were widely shared and praised online.</t>
+  </si>
+  <si>
+    <t>https://naver.me/5vJx4omO</t>
+  </si>
 </sst>
 </file>
 
@@ -6482,7 +6506,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6558,6 +6582,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6595,7 +6624,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6631,6 +6660,21 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -62176,7 +62220,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -62206,181 +62250,225 @@
         <v>434</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A2" s="9">
-        <v>46203</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:6" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A2" s="28">
+        <v>46205</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="C2" t="s">
-        <v>1877</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>1878</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>1879</v>
+      <c r="C2" s="24" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>1917</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>1923</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="9">
-        <v>46203</v>
-      </c>
-      <c r="B3" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="28">
+        <v>46206</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="C3" t="s">
-        <v>1881</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1880</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>1882</v>
+      <c r="C3" s="24" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>1920</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1884</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B4" t="s">
         <v>231</v>
       </c>
       <c r="C4" t="s">
-        <v>1886</v>
+        <v>1877</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1885</v>
+        <v>1878</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1888</v>
+        <v>1879</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1887</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B5" t="s">
         <v>221</v>
       </c>
       <c r="C5" t="s">
-        <v>1891</v>
+        <v>1881</v>
       </c>
       <c r="D5" t="s">
-        <v>1889</v>
+        <v>1880</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1890</v>
+        <v>1882</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="B6" t="s">
         <v>231</v>
       </c>
       <c r="C6" t="s">
-        <v>1893</v>
+        <v>1886</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1895</v>
+        <v>1885</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1894</v>
+        <v>1888</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="B7" t="s">
         <v>221</v>
       </c>
       <c r="C7" t="s">
-        <v>1898</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>1897</v>
+        <v>1891</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1889</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1899</v>
+        <v>1890</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1900</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="B8" t="s">
         <v>231</v>
       </c>
       <c r="C8" t="s">
-        <v>1902</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1901</v>
+        <v>1893</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1895</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
-        <v>46198</v>
+        <v>46201</v>
       </c>
       <c r="B9" t="s">
         <v>221</v>
       </c>
       <c r="C9" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A10" s="9">
+        <v>46198</v>
+      </c>
+      <c r="B10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="9">
+        <v>46198</v>
+      </c>
+      <c r="B11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" t="s">
         <v>1906</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>1905</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>1907</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>1908</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{4C165E91-B26F-0A45-88A2-06AA9774DFAE}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{7642FB96-3502-1243-90D5-20631BBFCC79}"/>
-    <hyperlink ref="D2" r:id="rId3" xr:uid="{1E0F0315-6747-884F-AA49-D6E56727920B}"/>
-    <hyperlink ref="D4" r:id="rId4" xr:uid="{8488153C-110A-4C48-965B-7630C9492F36}"/>
-    <hyperlink ref="F4" r:id="rId5" xr:uid="{BE75DA92-F980-1948-9204-01AC25600C6B}"/>
-    <hyperlink ref="F5" r:id="rId6" xr:uid="{7457B18B-86CB-6147-ADA9-A3CE56A83401}"/>
-    <hyperlink ref="D6" r:id="rId7" xr:uid="{FBAC6F67-55B1-324A-82BF-DD02FC6BBA04}"/>
-    <hyperlink ref="F6" r:id="rId8" xr:uid="{865A0475-BB84-DB47-9559-DC4649F4A676}"/>
-    <hyperlink ref="D7" r:id="rId9" xr:uid="{D9D6577F-5D20-B245-9F68-2D50BDFCA180}"/>
-    <hyperlink ref="F7" r:id="rId10" xr:uid="{21950F61-40D9-5E42-87ED-8402F010D442}"/>
-    <hyperlink ref="F8" r:id="rId11" xr:uid="{990DFC39-986D-3849-99EC-29E4E365D40A}"/>
-    <hyperlink ref="D9" r:id="rId12" xr:uid="{DE7E8DCA-2195-394F-9E1F-C6282B5AFE11}"/>
-    <hyperlink ref="F9" r:id="rId13" xr:uid="{A97FBDD3-5139-A04F-A3D7-E34D3553362F}"/>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{4C165E91-B26F-0A45-88A2-06AA9774DFAE}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{7642FB96-3502-1243-90D5-20631BBFCC79}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{1E0F0315-6747-884F-AA49-D6E56727920B}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{8488153C-110A-4C48-965B-7630C9492F36}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{BE75DA92-F980-1948-9204-01AC25600C6B}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{7457B18B-86CB-6147-ADA9-A3CE56A83401}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{FBAC6F67-55B1-324A-82BF-DD02FC6BBA04}"/>
+    <hyperlink ref="F8" r:id="rId8" xr:uid="{865A0475-BB84-DB47-9559-DC4649F4A676}"/>
+    <hyperlink ref="D9" r:id="rId9" xr:uid="{D9D6577F-5D20-B245-9F68-2D50BDFCA180}"/>
+    <hyperlink ref="F9" r:id="rId10" xr:uid="{21950F61-40D9-5E42-87ED-8402F010D442}"/>
+    <hyperlink ref="F10" r:id="rId11" xr:uid="{990DFC39-986D-3849-99EC-29E4E365D40A}"/>
+    <hyperlink ref="D11" r:id="rId12" xr:uid="{DE7E8DCA-2195-394F-9E1F-C6282B5AFE11}"/>
+    <hyperlink ref="F11" r:id="rId13" xr:uid="{A97FBDD3-5139-A04F-A3D7-E34D3553362F}"/>
+    <hyperlink ref="D2" r:id="rId14" xr:uid="{B5715535-CBF7-2F43-A872-9DF1119833A5}"/>
+    <hyperlink ref="D3" r:id="rId15" xr:uid="{4BD8C645-AD86-B644-BB86-E474C950B5C1}"/>
+    <hyperlink ref="F3" r:id="rId16" xr:uid="{E6DC40BA-2FBD-8741-8B86-BE0CB8B5DF5A}"/>
+    <hyperlink ref="F2" r:id="rId17" xr:uid="{2D25DB01-973D-C442-BAAA-A7898AECF3CB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714F4C04-C828-FA4B-9919-8DA4E3E5ED1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D566FA8-6AA4-CC41-A941-E5063460FE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="1925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2666" uniqueCount="1933">
   <si>
     <t>date</t>
   </si>
@@ -6497,6 +6497,30 @@
   </si>
   <si>
     <t>https://naver.me/5vJx4omO</t>
+  </si>
+  <si>
+    <t>Jungkook’s “Seven” continues historic Billboard and Spotify record run</t>
+  </si>
+  <si>
+    <t>BTS Jungkook’s “Seven” has extended its record-breaking run on Billboard’s Global (Excl. U.S.) chart to 154 consecutive weeks, while also reaching 155 weeks on Spotify’s Weekly Top Songs Global chart, remaining the longest-charting song by an Asian solo artist on both platforms.</t>
+  </si>
+  <si>
+    <t>https://naver.me/x7el4dXb</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DaZ2CfCtxtW/</t>
+  </si>
+  <si>
+    <t>V’s emotional fan moment in Belgium leaves lasting “core memory” for fan</t>
+  </si>
+  <si>
+    <t>BTS V created a heartfelt moment during the ARIRANG World Tour concert in Belgium after interacting with a fan with Down syndrome during “For Youth,” sharing dance and heart gestures on stage. The fan later described the experience as a “core memory unlocked.” V also comforted another emotional fan during “Into the Sun” by gifting his clothing, with the moments widely shared and praised online.</t>
+  </si>
+  <si>
+    <t>https://naver.me/FlBTH1uj</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DaZ2YjSNiXu/</t>
   </si>
 </sst>
 </file>
@@ -6624,7 +6648,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6655,26 +6679,50 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -62220,255 +62268,301 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="63.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="98.1640625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" style="27"/>
+    <col min="3" max="3" width="63.33203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="98.1640625" style="35" customWidth="1"/>
+    <col min="6" max="6" width="25.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="29" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A2" s="28">
+    <row r="2" spans="1:6" s="33" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>46208</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>1930</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="33" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>46208</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A4" s="22">
         <v>46205</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>1922</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D4" s="24" t="s">
         <v>1917</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E4" s="25" t="s">
         <v>1923</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F4" s="26" t="s">
         <v>1924</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="28">
+    <row r="5" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A5" s="22">
         <v>46206</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B5" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C5" s="23" t="s">
         <v>1919</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D5" s="24" t="s">
         <v>1918</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E5" s="25" t="s">
         <v>1920</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F5" s="24" t="s">
         <v>1921</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A4" s="9">
+    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" s="34">
         <v>46203</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" s="27" t="s">
         <v>1877</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D6" s="24" t="s">
         <v>1878</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E6" s="35" t="s">
         <v>1879</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F6" s="24" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" s="9">
+    <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A7" s="34">
         <v>46203</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" s="27" t="s">
         <v>1881</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D7" s="27" t="s">
         <v>1880</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E7" s="35" t="s">
         <v>1882</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F7" s="24" t="s">
         <v>1884</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
+    <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="34">
         <v>46202</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C8" s="27" t="s">
         <v>1886</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D8" s="24" t="s">
         <v>1885</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E8" s="35" t="s">
         <v>1888</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F8" s="24" t="s">
         <v>1887</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
+    <row r="9" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A9" s="34">
         <v>46202</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" s="27" t="s">
         <v>1891</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" s="27" t="s">
         <v>1889</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E9" s="35" t="s">
         <v>1890</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F9" s="24" t="s">
         <v>1892</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
+    <row r="10" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A10" s="34">
         <v>46201</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" s="27" t="s">
         <v>1893</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D10" s="24" t="s">
         <v>1895</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E10" s="35" t="s">
         <v>1894</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F10" s="24" t="s">
         <v>1896</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+    <row r="11" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A11" s="34">
         <v>46201</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C11" s="27" t="s">
         <v>1898</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D11" s="24" t="s">
         <v>1897</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E11" s="35" t="s">
         <v>1899</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F11" s="24" t="s">
         <v>1900</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
+    <row r="12" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A12" s="34">
         <v>46198</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C12" s="27" t="s">
         <v>1902</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D12" s="27" t="s">
         <v>1901</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E12" s="35" t="s">
         <v>1903</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F12" s="24" t="s">
         <v>1904</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+    <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" s="34">
         <v>46198</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C13" s="27" t="s">
         <v>1906</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D13" s="24" t="s">
         <v>1905</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E13" s="35" t="s">
         <v>1907</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F13" s="24" t="s">
         <v>1908</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" xr:uid="{4C165E91-B26F-0A45-88A2-06AA9774DFAE}"/>
-    <hyperlink ref="F5" r:id="rId2" xr:uid="{7642FB96-3502-1243-90D5-20631BBFCC79}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{1E0F0315-6747-884F-AA49-D6E56727920B}"/>
-    <hyperlink ref="D6" r:id="rId4" xr:uid="{8488153C-110A-4C48-965B-7630C9492F36}"/>
-    <hyperlink ref="F6" r:id="rId5" xr:uid="{BE75DA92-F980-1948-9204-01AC25600C6B}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{7457B18B-86CB-6147-ADA9-A3CE56A83401}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{FBAC6F67-55B1-324A-82BF-DD02FC6BBA04}"/>
-    <hyperlink ref="F8" r:id="rId8" xr:uid="{865A0475-BB84-DB47-9559-DC4649F4A676}"/>
-    <hyperlink ref="D9" r:id="rId9" xr:uid="{D9D6577F-5D20-B245-9F68-2D50BDFCA180}"/>
-    <hyperlink ref="F9" r:id="rId10" xr:uid="{21950F61-40D9-5E42-87ED-8402F010D442}"/>
-    <hyperlink ref="F10" r:id="rId11" xr:uid="{990DFC39-986D-3849-99EC-29E4E365D40A}"/>
-    <hyperlink ref="D11" r:id="rId12" xr:uid="{DE7E8DCA-2195-394F-9E1F-C6282B5AFE11}"/>
-    <hyperlink ref="F11" r:id="rId13" xr:uid="{A97FBDD3-5139-A04F-A3D7-E34D3553362F}"/>
-    <hyperlink ref="D2" r:id="rId14" xr:uid="{B5715535-CBF7-2F43-A872-9DF1119833A5}"/>
-    <hyperlink ref="D3" r:id="rId15" xr:uid="{4BD8C645-AD86-B644-BB86-E474C950B5C1}"/>
-    <hyperlink ref="F3" r:id="rId16" xr:uid="{E6DC40BA-2FBD-8741-8B86-BE0CB8B5DF5A}"/>
-    <hyperlink ref="F2" r:id="rId17" xr:uid="{2D25DB01-973D-C442-BAAA-A7898AECF3CB}"/>
+    <hyperlink ref="F6" r:id="rId1" xr:uid="{4C165E91-B26F-0A45-88A2-06AA9774DFAE}"/>
+    <hyperlink ref="F7" r:id="rId2" xr:uid="{7642FB96-3502-1243-90D5-20631BBFCC79}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{1E0F0315-6747-884F-AA49-D6E56727920B}"/>
+    <hyperlink ref="D8" r:id="rId4" xr:uid="{8488153C-110A-4C48-965B-7630C9492F36}"/>
+    <hyperlink ref="F8" r:id="rId5" xr:uid="{BE75DA92-F980-1948-9204-01AC25600C6B}"/>
+    <hyperlink ref="F9" r:id="rId6" xr:uid="{7457B18B-86CB-6147-ADA9-A3CE56A83401}"/>
+    <hyperlink ref="D10" r:id="rId7" xr:uid="{FBAC6F67-55B1-324A-82BF-DD02FC6BBA04}"/>
+    <hyperlink ref="F10" r:id="rId8" xr:uid="{865A0475-BB84-DB47-9559-DC4649F4A676}"/>
+    <hyperlink ref="D11" r:id="rId9" xr:uid="{D9D6577F-5D20-B245-9F68-2D50BDFCA180}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{21950F61-40D9-5E42-87ED-8402F010D442}"/>
+    <hyperlink ref="F12" r:id="rId11" xr:uid="{990DFC39-986D-3849-99EC-29E4E365D40A}"/>
+    <hyperlink ref="D13" r:id="rId12" xr:uid="{DE7E8DCA-2195-394F-9E1F-C6282B5AFE11}"/>
+    <hyperlink ref="F13" r:id="rId13" xr:uid="{A97FBDD3-5139-A04F-A3D7-E34D3553362F}"/>
+    <hyperlink ref="D4" r:id="rId14" xr:uid="{B5715535-CBF7-2F43-A872-9DF1119833A5}"/>
+    <hyperlink ref="D5" r:id="rId15" xr:uid="{4BD8C645-AD86-B644-BB86-E474C950B5C1}"/>
+    <hyperlink ref="F5" r:id="rId16" xr:uid="{E6DC40BA-2FBD-8741-8B86-BE0CB8B5DF5A}"/>
+    <hyperlink ref="F4" r:id="rId17" xr:uid="{2D25DB01-973D-C442-BAAA-A7898AECF3CB}"/>
+    <hyperlink ref="D3" r:id="rId18" xr:uid="{5EE266C8-30C3-AA49-A280-DD6ACA716BED}"/>
+    <hyperlink ref="F2" r:id="rId19" xr:uid="{406CFBE4-10DA-B54F-842C-5C37F66B6667}"/>
+    <hyperlink ref="D2" r:id="rId20" xr:uid="{51D6B607-BCF9-224D-B409-72E4FD66FF8D}"/>
+    <hyperlink ref="F3" r:id="rId21" xr:uid="{1523EF8F-C7CF-B247-84A6-D1068FDF2FC9}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D566FA8-6AA4-CC41-A941-E5063460FE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47FF321-FAF0-2D46-BD07-69567ABD47E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,10 @@
     <sheet name="Radio" sheetId="15" r:id="rId14"/>
     <sheet name="Project" sheetId="16" r:id="rId15"/>
     <sheet name="Event" sheetId="17" r:id="rId16"/>
-    <sheet name="Promotion" sheetId="18" r:id="rId17"/>
-    <sheet name="FanLetters" sheetId="19" r:id="rId18"/>
-    <sheet name="Banner" sheetId="20" r:id="rId19"/>
+    <sheet name="BrandAmbassador" sheetId="22" r:id="rId17"/>
+    <sheet name="Promotion" sheetId="18" r:id="rId18"/>
+    <sheet name="FanLetters" sheetId="19" r:id="rId19"/>
+    <sheet name="Banner" sheetId="20" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Discography!$A$1:$M$118</definedName>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2666" uniqueCount="1933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2696" uniqueCount="1946">
   <si>
     <t>date</t>
   </si>
@@ -6521,6 +6522,45 @@
   </si>
   <si>
     <t>https://www.instagram.com/p/DaZ2YjSNiXu/</t>
+  </si>
+  <si>
+    <t>CELINE</t>
+  </si>
+  <si>
+    <t>CARTIER</t>
+  </si>
+  <si>
+    <t>SIMINVEST</t>
+  </si>
+  <si>
+    <t>COMPOSE COFFEE</t>
+  </si>
+  <si>
+    <t>COCA COLA</t>
+  </si>
+  <si>
+    <t>SNOW PEAK</t>
+  </si>
+  <si>
+    <t>TIRTIR</t>
+  </si>
+  <si>
+    <t>YUNTH</t>
+  </si>
+  <si>
+    <t>CALVIN KLEIN</t>
+  </si>
+  <si>
+    <t>CHANEL</t>
+  </si>
+  <si>
+    <t>HUBLOT</t>
+  </si>
+  <si>
+    <t>HITEJINRO</t>
+  </si>
+  <si>
+    <t>media</t>
   </si>
 </sst>
 </file>
@@ -57770,12 +57810,142 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64C35039-B9B3-DA4C-95BA-F339368624DF}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>231</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -57811,7 +57981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:E169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -59182,80 +59352,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="84.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1854</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1856</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D2" s="9">
-        <v>45786</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1858</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="9">
-        <v>45820</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1859</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="9">
-        <v>45820</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C5" s="6"/>
-      <c r="D5" s="9"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1300-000001000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -59688,6 +59784,80 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="84.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D2" s="9">
+        <v>45786</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="9">
+        <v>45820</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="9">
+        <v>45820</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C5" s="6"/>
+      <c r="D5" s="9"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1300-000001000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47FF321-FAF0-2D46-BD07-69567ABD47E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C29E047-0E66-CC42-8217-9B21B6205B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2696" uniqueCount="1946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2752" uniqueCount="1982">
   <si>
     <t>date</t>
   </si>
@@ -6557,10 +6557,118 @@
     <t>HUBLOT</t>
   </si>
   <si>
+    <t>CKJK</t>
+  </si>
+  <si>
     <t>HITEJINRO</t>
   </si>
   <si>
-    <t>media</t>
+    <t>JK</t>
+  </si>
+  <si>
+    <t>https://www.calvinklein.us/en/ckjk</t>
+  </si>
+  <si>
+    <t>brandambassador</t>
+  </si>
+  <si>
+    <t>koo_calvinklein.webp</t>
+  </si>
+  <si>
+    <t>koo_ckjk.webp</t>
+  </si>
+  <si>
+    <t>koo_chanel.webp</t>
+  </si>
+  <si>
+    <t>koo_hublot.webp</t>
+  </si>
+  <si>
+    <t>koo_jk.webp</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lpvR0gjsolI</t>
+  </si>
+  <si>
+    <t>tae_celine.webp</t>
+  </si>
+  <si>
+    <t>tae_cartier.webp</t>
+  </si>
+  <si>
+    <t>tae_siminvest.webp</t>
+  </si>
+  <si>
+    <t>tae_composecoffee.webp</t>
+  </si>
+  <si>
+    <t>tae_snowpeak.webp</t>
+  </si>
+  <si>
+    <t>tae_tirtir.webp</t>
+  </si>
+  <si>
+    <t>tae_yunth.webp</t>
+  </si>
+  <si>
+    <t>tae_hitejinro.webp</t>
+  </si>
+  <si>
+    <t>PARADISE CITY</t>
+  </si>
+  <si>
+    <t>SEOUL TOURISM ORGANIZATION</t>
+  </si>
+  <si>
+    <t>tae_seoultourismorg.webp</t>
+  </si>
+  <si>
+    <t>tae_cocacola.webp</t>
+  </si>
+  <si>
+    <t>https://tirtir.global/</t>
+  </si>
+  <si>
+    <t>https://www.celine.com/</t>
+  </si>
+  <si>
+    <t>https://www.sto.or.kr/</t>
+  </si>
+  <si>
+    <t>https://www.cartier.com/</t>
+  </si>
+  <si>
+    <t>https://siminvest.id/</t>
+  </si>
+  <si>
+    <t>https://composecoffee.com/</t>
+  </si>
+  <si>
+    <t>https://www.coca-cola.com/kr/ko</t>
+  </si>
+  <si>
+    <t>https://www.snowpeakstore.co.kr/</t>
+  </si>
+  <si>
+    <t>https://yunth.jp/</t>
+  </si>
+  <si>
+    <t>https://www.p-city.com/</t>
+  </si>
+  <si>
+    <t>https://hitejinroamerica.com/</t>
+  </si>
+  <si>
+    <t>https://www.calvinklein.us/</t>
+  </si>
+  <si>
+    <t>https://www.chanel.com/</t>
+  </si>
+  <si>
+    <t>https://www.hublot.com/</t>
+  </si>
+  <si>
+    <t>tae_paradisecity.webp</t>
   </si>
 </sst>
 </file>
@@ -57811,11 +57919,13 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64C35039-B9B3-DA4C-95BA-F339368624DF}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -57829,10 +57939,10 @@
         <v>213</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>1945</v>
+        <v>150</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>149</v>
+        <v>434</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1518</v>
@@ -57845,6 +57955,18 @@
       <c r="B2" t="s">
         <v>1933</v>
       </c>
+      <c r="C2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="F2">
+        <v>2023</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -57853,6 +57975,18 @@
       <c r="B3" t="s">
         <v>1934</v>
       </c>
+      <c r="C3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F3">
+        <v>2023</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -57861,6 +57995,18 @@
       <c r="B4" t="s">
         <v>1935</v>
       </c>
+      <c r="C4" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F4">
+        <v>2023</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -57869,6 +58015,18 @@
       <c r="B5" t="s">
         <v>1936</v>
       </c>
+      <c r="C5" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F5">
+        <v>2023</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -57877,6 +58035,18 @@
       <c r="B6" t="s">
         <v>1937</v>
       </c>
+      <c r="C6" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1973</v>
+      </c>
+      <c r="F6">
+        <v>2025</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -57885,6 +58055,18 @@
       <c r="B7" t="s">
         <v>1938</v>
       </c>
+      <c r="C7" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F7">
+        <v>2025</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -57893,6 +58075,18 @@
       <c r="B8" t="s">
         <v>1939</v>
       </c>
+      <c r="C8" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1960</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F8">
+        <v>2025</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -57901,29 +58095,77 @@
       <c r="B9" t="s">
         <v>1940</v>
       </c>
+      <c r="C9" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1961</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1975</v>
+      </c>
+      <c r="F9">
+        <v>2025</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>231</v>
       </c>
       <c r="B10" t="s">
-        <v>1944</v>
+        <v>1963</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F10">
+        <v>2025</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B11" t="s">
-        <v>1941</v>
+        <v>1945</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F11">
+        <v>2026</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B12" t="s">
-        <v>1942</v>
+        <v>1964</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F12">
+        <v>2023</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -57931,10 +58173,109 @@
         <v>221</v>
       </c>
       <c r="B13" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F13">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>1978</v>
+      </c>
+      <c r="F14">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>221</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>1947</v>
+      </c>
+      <c r="F15">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>221</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1951</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>1979</v>
+      </c>
+      <c r="F16">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>221</v>
+      </c>
+      <c r="B17" t="s">
         <v>1943</v>
       </c>
+      <c r="C17" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>1980</v>
+      </c>
+      <c r="F17">
+        <v>2026</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" display="https://www.youtube.com/watch?v=0thKCJ5Pu0k&amp;t=17s" xr:uid="{41A5E872-AB16-E745-ABB7-8F73E063B69E}"/>
+    <hyperlink ref="E13" r:id="rId2" xr:uid="{BA4B1370-36D3-3A48-A4DB-1C33D850E51A}"/>
+    <hyperlink ref="E14" r:id="rId3" xr:uid="{374FF3EB-AAC2-E44C-85A5-12CD5800A2FB}"/>
+    <hyperlink ref="E16" r:id="rId4" xr:uid="{5AAE3747-957D-3845-989F-707851F55413}"/>
+    <hyperlink ref="E17" r:id="rId5" xr:uid="{EBA670F1-9C27-C94F-8055-EECE2FA9BAA1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C29E047-0E66-CC42-8217-9B21B6205B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073C1B42-D2CF-9A41-B79E-0BA7B6482113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -60373,7 +60373,7 @@
         <v>46101</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>218</v>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073C1B42-D2CF-9A41-B79E-0BA7B6482113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F00F745-58C7-F248-85EE-7E06D7B4C996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2752" uniqueCount="1982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="1985">
   <si>
     <t>date</t>
   </si>
@@ -6669,6 +6669,15 @@
   </si>
   <si>
     <t>tae_paradisecity.webp</t>
+  </si>
+  <si>
+    <t>Week of July 3, 2026</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=F___gqyFNfU</t>
+  </si>
+  <si>
+    <t>What an unforgettable week! From the incredible Brussels concerts and Taehyung turning heads in Paris for Celine, to Jungkook’s unforgettable live and dance content, their travels, Instagram updates, behind-the-scenes moments, and so many personal memories shared along the way, this week was packed from beginning to end. We truly never take these moments for granted 💜💚</t>
   </si>
 </sst>
 </file>
@@ -60557,7 +60566,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -60584,807 +60593,823 @@
     </row>
     <row r="2" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="B2" t="s">
-        <v>1861</v>
+        <v>1982</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1860</v>
+        <v>1984</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1862</v>
+        <v>1983</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>1861</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>5</v>
+        <v>1860</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>6</v>
+        <v>1862</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
-        <v>46185</v>
+        <v>46192</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
-        <v>46129</v>
+        <v>46136</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
-        <v>46115</v>
+        <v>46129</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
-        <v>46094</v>
+        <v>46115</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
-        <v>46052</v>
+        <v>46059</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
+        <v>46045</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="9">
         <v>46038</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C23" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="9">
-        <v>46031</v>
-      </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
+        <v>46031</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="9">
         <v>46024</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="9">
-        <v>46017</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
+        <v>46017</v>
+      </c>
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="9">
         <v>46010</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>71</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9">
-        <v>46003</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
-        <v>45989</v>
+        <v>45996</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G29" s="6"/>
     </row>
     <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
-        <v>45975</v>
+        <v>45982</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
+        <v>45968</v>
+      </c>
+      <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
         <v>45961</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C34" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="9">
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
         <v>45954</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C35" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D35" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="9">
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
         <v>45947</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C36" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="9">
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
         <v>45940</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>99</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C37" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9">
-        <v>45933</v>
-      </c>
-      <c r="B37" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="G37" s="6"/>
     </row>
     <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
+        <v>45933</v>
+      </c>
+      <c r="B38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
         <v>45926</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>105</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C39" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="9">
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="9">
         <v>45919</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>108</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C40" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9">
-        <v>45912</v>
-      </c>
-      <c r="B40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="G40" s="6"/>
     </row>
     <row r="41" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
+        <v>45912</v>
+      </c>
+      <c r="B41" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="9">
         <v>45905</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C42" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D42" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G41" s="6"/>
-    </row>
-    <row r="42" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9">
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="9">
         <v>45898</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C43" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D43" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="9">
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="9">
         <v>45891</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>120</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C44" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D44" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G43" s="6"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="9">
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="9">
         <v>45884</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>123</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>123</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="45" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="9">
-        <v>45877</v>
-      </c>
-      <c r="B45" t="s">
-        <v>125</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="G45" s="6"/>
     </row>
     <row r="46" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
+        <v>45877</v>
+      </c>
+      <c r="B46" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9">
         <v>45870</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>128</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D47" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="G46" s="6"/>
-    </row>
-    <row r="47" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="9">
-        <v>45863</v>
-      </c>
-      <c r="B47" t="s">
-        <v>131</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="G47" s="6"/>
     </row>
     <row r="48" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="B48" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G48" s="6"/>
     </row>
     <row r="49" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="B49" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G49" s="6"/>
     </row>
     <row r="50" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G50" s="6"/>
     </row>
     <row r="51" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
+        <v>45842</v>
+      </c>
+      <c r="B51" t="s">
+        <v>140</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G51" s="6"/>
+    </row>
+    <row r="52" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="9">
         <v>45835</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>143</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C52" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D52" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G51" s="6"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C52" s="8"/>
+      <c r="G52" s="6"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C53" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="D5" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="D6" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
-    <hyperlink ref="D7" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
-    <hyperlink ref="D8" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
-    <hyperlink ref="D9" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
-    <hyperlink ref="D11" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
-    <hyperlink ref="D13" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
-    <hyperlink ref="D14" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
-    <hyperlink ref="D15" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
-    <hyperlink ref="D16" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
-    <hyperlink ref="D17" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
-    <hyperlink ref="D18" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
-    <hyperlink ref="D19" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
-    <hyperlink ref="D20" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
-    <hyperlink ref="D21" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
-    <hyperlink ref="D22" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
-    <hyperlink ref="D23" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
-    <hyperlink ref="D24" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
-    <hyperlink ref="D25" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
-    <hyperlink ref="D26" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
-    <hyperlink ref="D27" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
-    <hyperlink ref="D28" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
-    <hyperlink ref="D29" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
-    <hyperlink ref="D30" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
-    <hyperlink ref="D31" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
-    <hyperlink ref="D32" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
-    <hyperlink ref="D33" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
-    <hyperlink ref="D34" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
-    <hyperlink ref="D35" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
-    <hyperlink ref="D36" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
-    <hyperlink ref="D37" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
-    <hyperlink ref="D38" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
-    <hyperlink ref="D39" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
-    <hyperlink ref="D40" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
-    <hyperlink ref="D41" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
-    <hyperlink ref="D42" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
-    <hyperlink ref="D43" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
-    <hyperlink ref="D44" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
-    <hyperlink ref="D45" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
-    <hyperlink ref="D46" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
-    <hyperlink ref="D47" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
-    <hyperlink ref="D48" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
-    <hyperlink ref="D49" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
-    <hyperlink ref="D50" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
-    <hyperlink ref="D51" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
-    <hyperlink ref="D3" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="D7" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="D8" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="D9" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="D10" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="D12" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="D14" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
+    <hyperlink ref="D15" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
+    <hyperlink ref="D16" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
+    <hyperlink ref="D17" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
+    <hyperlink ref="D18" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
+    <hyperlink ref="D19" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
+    <hyperlink ref="D20" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
+    <hyperlink ref="D21" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
+    <hyperlink ref="D22" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
+    <hyperlink ref="D23" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
+    <hyperlink ref="D24" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
+    <hyperlink ref="D25" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
+    <hyperlink ref="D26" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
+    <hyperlink ref="D27" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
+    <hyperlink ref="D28" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
+    <hyperlink ref="D29" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
+    <hyperlink ref="D30" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
+    <hyperlink ref="D31" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
+    <hyperlink ref="D32" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
+    <hyperlink ref="D33" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
+    <hyperlink ref="D34" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
+    <hyperlink ref="D35" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
+    <hyperlink ref="D36" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
+    <hyperlink ref="D37" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
+    <hyperlink ref="D38" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
+    <hyperlink ref="D39" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
+    <hyperlink ref="D40" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
+    <hyperlink ref="D41" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
+    <hyperlink ref="D42" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
+    <hyperlink ref="D43" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
+    <hyperlink ref="D44" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
+    <hyperlink ref="D45" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
+    <hyperlink ref="D46" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
+    <hyperlink ref="D47" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
+    <hyperlink ref="D48" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
+    <hyperlink ref="D49" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
+    <hyperlink ref="D50" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
+    <hyperlink ref="D51" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
+    <hyperlink ref="D52" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
+    <hyperlink ref="D4" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
+    <hyperlink ref="D3" r:id="rId49" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F00F745-58C7-F248-85EE-7E06D7B4C996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4493AD-3989-8946-916C-D0184D2CD3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -6471,213 +6471,212 @@
 https://www.instagram.com/p/DaSN324sJKp/</t>
   </si>
   <si>
+    <t>https://www.instagram.com/p/DaS3cncgHA0</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DaS3s1bNID5</t>
+  </si>
+  <si>
+    <t>Jungkook’s Calvin Klein collection sells out worldwide once again</t>
+  </si>
+  <si>
+    <t>BTS Jungkook’s “Jungkook for Calvin Klein (CKJK)” collection has sold out again following its latest restock, with products selling out across multiple regions. PVH Corp. described it as the most successful collaboration in Calvin Klein’s history, driven by unprecedented global demand and Jungkook’s creative involvement.</t>
+  </si>
+  <si>
+    <t>https://naver.me/5zU7mSVf</t>
+  </si>
+  <si>
+    <t>V’s kindness and warmth in Paris moves fans and locals alike</t>
+  </si>
+  <si>
+    <t>BTS V captured attention in Paris after being seen assisting an elderly woman outside his hotel following the CELINE Men’s SS27 show, along with other moments showing his warmth toward staff and fans during his busy schedule, which were widely shared and praised online.</t>
+  </si>
+  <si>
+    <t>https://naver.me/5vJx4omO</t>
+  </si>
+  <si>
+    <t>Jungkook’s “Seven” continues historic Billboard and Spotify record run</t>
+  </si>
+  <si>
+    <t>BTS Jungkook’s “Seven” has extended its record-breaking run on Billboard’s Global (Excl. U.S.) chart to 154 consecutive weeks, while also reaching 155 weeks on Spotify’s Weekly Top Songs Global chart, remaining the longest-charting song by an Asian solo artist on both platforms.</t>
+  </si>
+  <si>
+    <t>https://naver.me/x7el4dXb</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DaZ2CfCtxtW/</t>
+  </si>
+  <si>
+    <t>V’s emotional fan moment in Belgium leaves lasting “core memory” for fan</t>
+  </si>
+  <si>
+    <t>BTS V created a heartfelt moment during the ARIRANG World Tour concert in Belgium after interacting with a fan with Down syndrome during “For Youth,” sharing dance and heart gestures on stage. The fan later described the experience as a “core memory unlocked.” V also comforted another emotional fan during “Into the Sun” by gifting his clothing, with the moments widely shared and praised online.</t>
+  </si>
+  <si>
+    <t>https://naver.me/FlBTH1uj</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DaZ2YjSNiXu/</t>
+  </si>
+  <si>
+    <t>CELINE</t>
+  </si>
+  <si>
+    <t>CARTIER</t>
+  </si>
+  <si>
+    <t>SIMINVEST</t>
+  </si>
+  <si>
+    <t>COMPOSE COFFEE</t>
+  </si>
+  <si>
+    <t>COCA COLA</t>
+  </si>
+  <si>
+    <t>SNOW PEAK</t>
+  </si>
+  <si>
+    <t>TIRTIR</t>
+  </si>
+  <si>
+    <t>YUNTH</t>
+  </si>
+  <si>
+    <t>CALVIN KLEIN</t>
+  </si>
+  <si>
+    <t>CHANEL</t>
+  </si>
+  <si>
+    <t>HUBLOT</t>
+  </si>
+  <si>
+    <t>CKJK</t>
+  </si>
+  <si>
+    <t>HITEJINRO</t>
+  </si>
+  <si>
+    <t>JK</t>
+  </si>
+  <si>
+    <t>https://www.calvinklein.us/en/ckjk</t>
+  </si>
+  <si>
+    <t>brandambassador</t>
+  </si>
+  <si>
+    <t>koo_calvinklein.webp</t>
+  </si>
+  <si>
+    <t>koo_ckjk.webp</t>
+  </si>
+  <si>
+    <t>koo_chanel.webp</t>
+  </si>
+  <si>
+    <t>koo_hublot.webp</t>
+  </si>
+  <si>
+    <t>koo_jk.webp</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lpvR0gjsolI</t>
+  </si>
+  <si>
+    <t>tae_celine.webp</t>
+  </si>
+  <si>
+    <t>tae_cartier.webp</t>
+  </si>
+  <si>
+    <t>tae_siminvest.webp</t>
+  </si>
+  <si>
+    <t>tae_composecoffee.webp</t>
+  </si>
+  <si>
+    <t>tae_snowpeak.webp</t>
+  </si>
+  <si>
+    <t>tae_tirtir.webp</t>
+  </si>
+  <si>
+    <t>tae_yunth.webp</t>
+  </si>
+  <si>
+    <t>tae_hitejinro.webp</t>
+  </si>
+  <si>
+    <t>PARADISE CITY</t>
+  </si>
+  <si>
+    <t>SEOUL TOURISM ORGANIZATION</t>
+  </si>
+  <si>
+    <t>tae_seoultourismorg.webp</t>
+  </si>
+  <si>
+    <t>tae_cocacola.webp</t>
+  </si>
+  <si>
+    <t>https://tirtir.global/</t>
+  </si>
+  <si>
+    <t>https://www.celine.com/</t>
+  </si>
+  <si>
+    <t>https://www.sto.or.kr/</t>
+  </si>
+  <si>
+    <t>https://www.cartier.com/</t>
+  </si>
+  <si>
+    <t>https://siminvest.id/</t>
+  </si>
+  <si>
+    <t>https://composecoffee.com/</t>
+  </si>
+  <si>
+    <t>https://www.coca-cola.com/kr/ko</t>
+  </si>
+  <si>
+    <t>https://www.snowpeakstore.co.kr/</t>
+  </si>
+  <si>
+    <t>https://yunth.jp/</t>
+  </si>
+  <si>
+    <t>https://www.p-city.com/</t>
+  </si>
+  <si>
+    <t>https://hitejinroamerica.com/</t>
+  </si>
+  <si>
+    <t>https://www.calvinklein.us/</t>
+  </si>
+  <si>
+    <t>https://www.chanel.com/</t>
+  </si>
+  <si>
+    <t>https://www.hublot.com/</t>
+  </si>
+  <si>
+    <t>tae_paradisecity.webp</t>
+  </si>
+  <si>
+    <t>Week of July 3, 2026</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=F___gqyFNfU</t>
+  </si>
+  <si>
+    <t>What an unforgettable week! From the incredible Brussels concerts and Taehyung turning heads in Paris for Celine, to Jungkook’s unforgettable live and dance content, their travels, Instagram updates, behind-the-scenes moments, and so many personal memories shared along the way, this week was packed from beginning to end. We truly never take these moments for granted 💜💚</t>
+  </si>
+  <si>
     <t>Jinro_Tae1.webp,
-https://www.instagram.com/p/DaT1E3QCY-r,
-https://www.instagram.com/p/DaT1EzxiPPA/</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/p/DaS3cncgHA0</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/p/DaS3s1bNID5</t>
-  </si>
-  <si>
-    <t>Jungkook’s Calvin Klein collection sells out worldwide once again</t>
-  </si>
-  <si>
-    <t>BTS Jungkook’s “Jungkook for Calvin Klein (CKJK)” collection has sold out again following its latest restock, with products selling out across multiple regions. PVH Corp. described it as the most successful collaboration in Calvin Klein’s history, driven by unprecedented global demand and Jungkook’s creative involvement.</t>
-  </si>
-  <si>
-    <t>https://naver.me/5zU7mSVf</t>
-  </si>
-  <si>
-    <t>V’s kindness and warmth in Paris moves fans and locals alike</t>
-  </si>
-  <si>
-    <t>BTS V captured attention in Paris after being seen assisting an elderly woman outside his hotel following the CELINE Men’s SS27 show, along with other moments showing his warmth toward staff and fans during his busy schedule, which were widely shared and praised online.</t>
-  </si>
-  <si>
-    <t>https://naver.me/5vJx4omO</t>
-  </si>
-  <si>
-    <t>Jungkook’s “Seven” continues historic Billboard and Spotify record run</t>
-  </si>
-  <si>
-    <t>BTS Jungkook’s “Seven” has extended its record-breaking run on Billboard’s Global (Excl. U.S.) chart to 154 consecutive weeks, while also reaching 155 weeks on Spotify’s Weekly Top Songs Global chart, remaining the longest-charting song by an Asian solo artist on both platforms.</t>
-  </si>
-  <si>
-    <t>https://naver.me/x7el4dXb</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/p/DaZ2CfCtxtW/</t>
-  </si>
-  <si>
-    <t>V’s emotional fan moment in Belgium leaves lasting “core memory” for fan</t>
-  </si>
-  <si>
-    <t>BTS V created a heartfelt moment during the ARIRANG World Tour concert in Belgium after interacting with a fan with Down syndrome during “For Youth,” sharing dance and heart gestures on stage. The fan later described the experience as a “core memory unlocked.” V also comforted another emotional fan during “Into the Sun” by gifting his clothing, with the moments widely shared and praised online.</t>
-  </si>
-  <si>
-    <t>https://naver.me/FlBTH1uj</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/p/DaZ2YjSNiXu/</t>
-  </si>
-  <si>
-    <t>CELINE</t>
-  </si>
-  <si>
-    <t>CARTIER</t>
-  </si>
-  <si>
-    <t>SIMINVEST</t>
-  </si>
-  <si>
-    <t>COMPOSE COFFEE</t>
-  </si>
-  <si>
-    <t>COCA COLA</t>
-  </si>
-  <si>
-    <t>SNOW PEAK</t>
-  </si>
-  <si>
-    <t>TIRTIR</t>
-  </si>
-  <si>
-    <t>YUNTH</t>
-  </si>
-  <si>
-    <t>CALVIN KLEIN</t>
-  </si>
-  <si>
-    <t>CHANEL</t>
-  </si>
-  <si>
-    <t>HUBLOT</t>
-  </si>
-  <si>
-    <t>CKJK</t>
-  </si>
-  <si>
-    <t>HITEJINRO</t>
-  </si>
-  <si>
-    <t>JK</t>
-  </si>
-  <si>
-    <t>https://www.calvinklein.us/en/ckjk</t>
-  </si>
-  <si>
-    <t>brandambassador</t>
-  </si>
-  <si>
-    <t>koo_calvinklein.webp</t>
-  </si>
-  <si>
-    <t>koo_ckjk.webp</t>
-  </si>
-  <si>
-    <t>koo_chanel.webp</t>
-  </si>
-  <si>
-    <t>koo_hublot.webp</t>
-  </si>
-  <si>
-    <t>koo_jk.webp</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=lpvR0gjsolI</t>
-  </si>
-  <si>
-    <t>tae_celine.webp</t>
-  </si>
-  <si>
-    <t>tae_cartier.webp</t>
-  </si>
-  <si>
-    <t>tae_siminvest.webp</t>
-  </si>
-  <si>
-    <t>tae_composecoffee.webp</t>
-  </si>
-  <si>
-    <t>tae_snowpeak.webp</t>
-  </si>
-  <si>
-    <t>tae_tirtir.webp</t>
-  </si>
-  <si>
-    <t>tae_yunth.webp</t>
-  </si>
-  <si>
-    <t>tae_hitejinro.webp</t>
-  </si>
-  <si>
-    <t>PARADISE CITY</t>
-  </si>
-  <si>
-    <t>SEOUL TOURISM ORGANIZATION</t>
-  </si>
-  <si>
-    <t>tae_seoultourismorg.webp</t>
-  </si>
-  <si>
-    <t>tae_cocacola.webp</t>
-  </si>
-  <si>
-    <t>https://tirtir.global/</t>
-  </si>
-  <si>
-    <t>https://www.celine.com/</t>
-  </si>
-  <si>
-    <t>https://www.sto.or.kr/</t>
-  </si>
-  <si>
-    <t>https://www.cartier.com/</t>
-  </si>
-  <si>
-    <t>https://siminvest.id/</t>
-  </si>
-  <si>
-    <t>https://composecoffee.com/</t>
-  </si>
-  <si>
-    <t>https://www.coca-cola.com/kr/ko</t>
-  </si>
-  <si>
-    <t>https://www.snowpeakstore.co.kr/</t>
-  </si>
-  <si>
-    <t>https://yunth.jp/</t>
-  </si>
-  <si>
-    <t>https://www.p-city.com/</t>
-  </si>
-  <si>
-    <t>https://hitejinroamerica.com/</t>
-  </si>
-  <si>
-    <t>https://www.calvinklein.us/</t>
-  </si>
-  <si>
-    <t>https://www.chanel.com/</t>
-  </si>
-  <si>
-    <t>https://www.hublot.com/</t>
-  </si>
-  <si>
-    <t>tae_paradisecity.webp</t>
-  </si>
-  <si>
-    <t>Week of July 3, 2026</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=F___gqyFNfU</t>
-  </si>
-  <si>
-    <t>What an unforgettable week! From the incredible Brussels concerts and Taehyung turning heads in Paris for Celine, to Jungkook’s unforgettable live and dance content, their travels, Instagram updates, behind-the-scenes moments, and so many personal memories shared along the way, this week was packed from beginning to end. We truly never take these moments for granted 💜💚</t>
+https://x.com/jinrojapan/status/2072832695143649746?s=20</t>
   </si>
 </sst>
 </file>
@@ -6805,7 +6804,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6854,32 +6853,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -57962,16 +57946,16 @@
         <v>231</v>
       </c>
       <c r="B2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="C2" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D2" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="E2" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="F2">
         <v>2023</v>
@@ -57982,16 +57966,16 @@
         <v>231</v>
       </c>
       <c r="B3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="C3" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D3" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="E3" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="F3">
         <v>2023</v>
@@ -58002,16 +57986,16 @@
         <v>231</v>
       </c>
       <c r="B4" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="C4" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D4" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="F4">
         <v>2023</v>
@@ -58022,16 +58006,16 @@
         <v>231</v>
       </c>
       <c r="B5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="C5" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D5" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="E5" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="F5">
         <v>2023</v>
@@ -58042,16 +58026,16 @@
         <v>231</v>
       </c>
       <c r="B6" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="C6" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D6" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="E6" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="F6">
         <v>2025</v>
@@ -58062,16 +58046,16 @@
         <v>231</v>
       </c>
       <c r="B7" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="C7" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D7" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="E7" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="F7">
         <v>2025</v>
@@ -58082,16 +58066,16 @@
         <v>231</v>
       </c>
       <c r="B8" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="C8" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D8" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="E8" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="F8">
         <v>2025</v>
@@ -58102,16 +58086,16 @@
         <v>231</v>
       </c>
       <c r="B9" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="C9" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D9" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="E9" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="F9">
         <v>2025</v>
@@ -58122,16 +58106,16 @@
         <v>231</v>
       </c>
       <c r="B10" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C10" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D10" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E10" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="F10">
         <v>2025</v>
@@ -58142,16 +58126,16 @@
         <v>231</v>
       </c>
       <c r="B11" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="C11" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D11" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="E11" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="F11">
         <v>2026</v>
@@ -58162,16 +58146,16 @@
         <v>231</v>
       </c>
       <c r="B12" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D12" t="s">
         <v>1964</v>
       </c>
-      <c r="C12" t="s">
-        <v>1948</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1965</v>
-      </c>
       <c r="E12" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F12">
         <v>2023</v>
@@ -58182,16 +58166,16 @@
         <v>221</v>
       </c>
       <c r="B13" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="C13" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D13" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>1953</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>1954</v>
       </c>
       <c r="F13">
         <v>2023</v>
@@ -58202,16 +58186,16 @@
         <v>221</v>
       </c>
       <c r="B14" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="C14" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D14" t="s">
         <v>1948</v>
       </c>
-      <c r="D14" t="s">
-        <v>1949</v>
-      </c>
       <c r="E14" s="6" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F14">
         <v>2023</v>
@@ -58222,16 +58206,16 @@
         <v>221</v>
       </c>
       <c r="B15" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="C15" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D15" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="F15">
         <v>2026</v>
@@ -58242,16 +58226,16 @@
         <v>221</v>
       </c>
       <c r="B16" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="C16" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D16" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="F16">
         <v>2025</v>
@@ -58262,16 +58246,16 @@
         <v>221</v>
       </c>
       <c r="B17" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="C17" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="D17" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="F17">
         <v>2026</v>
@@ -60279,7 +60263,7 @@
     </row>
     <row r="2" spans="1:7" ht="136" x14ac:dyDescent="0.2">
       <c r="A2" s="18">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>231</v>
@@ -60291,7 +60275,7 @@
         <v>1912</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>1916</v>
+        <v>1984</v>
       </c>
       <c r="F2" s="19" t="s">
         <v>1913</v>
@@ -60596,13 +60580,13 @@
         <v>46206</v>
       </c>
       <c r="B2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>1982</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>1984</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>1983</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -62811,69 +62795,69 @@
     <col min="2" max="2" width="8.83203125" style="27"/>
     <col min="3" max="3" width="63.33203125" style="27" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="98.1640625" style="35" customWidth="1"/>
+    <col min="5" max="5" width="98.1640625" style="31" customWidth="1"/>
     <col min="6" max="6" width="25.5" style="27" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.83203125" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="28" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="33" customFormat="1" ht="68" x14ac:dyDescent="0.2">
-      <c r="A2" s="31">
+    <row r="2" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A2" s="22">
         <v>46208</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="23" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>1931</v>
+      </c>
+      <c r="E2" s="25" t="s">
         <v>1929</v>
       </c>
-      <c r="D2" s="36" t="s">
-        <v>1932</v>
-      </c>
-      <c r="E2" s="32" t="s">
+      <c r="F2" s="24" t="s">
         <v>1930</v>
       </c>
-      <c r="F2" s="36" t="s">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="33" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="31">
+    </row>
+    <row r="3" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="22">
         <v>46208</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="23" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>1925</v>
       </c>
-      <c r="D3" s="36" t="s">
-        <v>1928</v>
-      </c>
-      <c r="E3" s="32" t="s">
+      <c r="F3" s="24" t="s">
         <v>1926</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>1927</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -62884,16 +62868,16 @@
         <v>231</v>
       </c>
       <c r="C4" s="23" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>1916</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>1922</v>
       </c>
-      <c r="D4" s="24" t="s">
-        <v>1917</v>
-      </c>
-      <c r="E4" s="25" t="s">
+      <c r="F4" s="26" t="s">
         <v>1923</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>1924</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -62904,20 +62888,20 @@
         <v>221</v>
       </c>
       <c r="C5" s="23" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>1917</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>1919</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>1918</v>
-      </c>
-      <c r="E5" s="25" t="s">
+      <c r="F5" s="24" t="s">
         <v>1920</v>
       </c>
-      <c r="F5" s="24" t="s">
-        <v>1921</v>
-      </c>
     </row>
     <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A6" s="34">
+      <c r="A6" s="30">
         <v>46203</v>
       </c>
       <c r="B6" s="27" t="s">
@@ -62929,7 +62913,7 @@
       <c r="D6" s="24" t="s">
         <v>1878</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="31" t="s">
         <v>1879</v>
       </c>
       <c r="F6" s="24" t="s">
@@ -62937,7 +62921,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" s="34">
+      <c r="A7" s="30">
         <v>46203</v>
       </c>
       <c r="B7" s="27" t="s">
@@ -62949,7 +62933,7 @@
       <c r="D7" s="27" t="s">
         <v>1880</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="31" t="s">
         <v>1882</v>
       </c>
       <c r="F7" s="24" t="s">
@@ -62957,7 +62941,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A8" s="34">
+      <c r="A8" s="30">
         <v>46202</v>
       </c>
       <c r="B8" s="27" t="s">
@@ -62969,7 +62953,7 @@
       <c r="D8" s="24" t="s">
         <v>1885</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="31" t="s">
         <v>1888</v>
       </c>
       <c r="F8" s="24" t="s">
@@ -62977,7 +62961,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A9" s="34">
+      <c r="A9" s="30">
         <v>46202</v>
       </c>
       <c r="B9" s="27" t="s">
@@ -62989,7 +62973,7 @@
       <c r="D9" s="27" t="s">
         <v>1889</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="31" t="s">
         <v>1890</v>
       </c>
       <c r="F9" s="24" t="s">
@@ -62997,7 +62981,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A10" s="34">
+      <c r="A10" s="30">
         <v>46201</v>
       </c>
       <c r="B10" s="27" t="s">
@@ -63009,7 +62993,7 @@
       <c r="D10" s="24" t="s">
         <v>1895</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="31" t="s">
         <v>1894</v>
       </c>
       <c r="F10" s="24" t="s">
@@ -63017,7 +63001,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A11" s="34">
+      <c r="A11" s="30">
         <v>46201</v>
       </c>
       <c r="B11" s="27" t="s">
@@ -63029,7 +63013,7 @@
       <c r="D11" s="24" t="s">
         <v>1897</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="31" t="s">
         <v>1899</v>
       </c>
       <c r="F11" s="24" t="s">
@@ -63037,7 +63021,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A12" s="34">
+      <c r="A12" s="30">
         <v>46198</v>
       </c>
       <c r="B12" s="27" t="s">
@@ -63049,7 +63033,7 @@
       <c r="D12" s="27" t="s">
         <v>1901</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="31" t="s">
         <v>1903</v>
       </c>
       <c r="F12" s="24" t="s">
@@ -63057,7 +63041,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="34">
+      <c r="A13" s="30">
         <v>46198</v>
       </c>
       <c r="B13" s="27" t="s">
@@ -63069,7 +63053,7 @@
       <c r="D13" s="24" t="s">
         <v>1905</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="31" t="s">
         <v>1907</v>
       </c>
       <c r="F13" s="24" t="s">

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295C4507-3176-5B4E-9AB5-4AC940A57D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4795518E-4797-8A48-96E0-F3F60A47A400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1200" windowWidth="38400" windowHeight="20980" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="1947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2723" uniqueCount="1954">
   <si>
     <t>date</t>
   </si>
@@ -6586,6 +6586,27 @@
 https://x.com/tetekoofm/status/1782399409365582153,
 https://x.com/tetekoofm/status/1804189689894834240</t>
   </si>
+  <si>
+    <t>https://www.tiktok.com/@taekookusa</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@uktaekook</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@taekookargentina2</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@thetkglobal</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@tk_honduras9597</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@tk_mexico</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@taekook0912vk</t>
+  </si>
 </sst>
 </file>
 
@@ -6594,7 +6615,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6681,6 +6702,12 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6718,7 +6745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6781,6 +6808,7 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -27972,10 +28000,11 @@
     <col min="7" max="7" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="52.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="40" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.83203125" customWidth="1"/>
+    <col min="10" max="10" width="39.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="35.83203125" customWidth="1"/>
     <col min="12" max="12" width="37.83203125" customWidth="1"/>
     <col min="14" max="14" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
@@ -28146,7 +28175,9 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="2"/>
+      <c r="J4" s="6" t="s">
+        <v>1950</v>
+      </c>
       <c r="K4" s="2"/>
       <c r="L4" s="6"/>
       <c r="M4" s="2"/>
@@ -28224,7 +28255,9 @@
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="J6" s="6" t="s">
+        <v>1947</v>
+      </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -28270,7 +28303,9 @@
       <c r="I7" s="6" t="s">
         <v>1144</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="J7" s="6" t="s">
+        <v>1948</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="6" t="s">
         <v>1145</v>
@@ -28548,7 +28583,9 @@
       <c r="I14" s="6" t="s">
         <v>1177</v>
       </c>
-      <c r="J14" s="2"/>
+      <c r="J14" s="6" t="s">
+        <v>1953</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -28588,7 +28625,9 @@
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="J15" s="6" t="s">
+        <v>1952</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -28666,7 +28705,9 @@
       <c r="G17" s="6"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+      <c r="J17" s="6" t="s">
+        <v>1949</v>
+      </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -28706,7 +28747,9 @@
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="J18" s="6" t="s">
+        <v>1951</v>
+      </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -56381,6 +56424,13 @@
     <hyperlink ref="G18" r:id="rId36" xr:uid="{00000000-0004-0000-0C00-000024000000}"/>
     <hyperlink ref="F19" r:id="rId37" xr:uid="{00000000-0004-0000-0C00-000025000000}"/>
     <hyperlink ref="F4" r:id="rId38" xr:uid="{00000000-0004-0000-0C00-000008000000}"/>
+    <hyperlink ref="J6" r:id="rId39" xr:uid="{B8410E49-79F3-8644-8AB1-87D554AAD302}"/>
+    <hyperlink ref="J7" r:id="rId40" xr:uid="{AC97C96B-4996-FF4B-985D-FD0C4E44443B}"/>
+    <hyperlink ref="J17" r:id="rId41" xr:uid="{2896CF42-B64B-3E4F-B71B-6E5B094A2EE0}"/>
+    <hyperlink ref="J4" r:id="rId42" xr:uid="{5F249AE3-6D67-5E45-BFD7-95CA4D18E411}"/>
+    <hyperlink ref="J18" r:id="rId43" xr:uid="{A8AE5879-0F45-A74B-BBCE-1BF8DDDA6AF3}"/>
+    <hyperlink ref="J15" r:id="rId44" xr:uid="{221BBD68-77E4-0D49-BFFE-E7A6AA61D37A}"/>
+    <hyperlink ref="J14" r:id="rId45" xr:uid="{E735862C-A075-144E-B1B8-C643F4A6F4F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -59476,7 +59526,7 @@
     <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -59656,10 +59706,10 @@
         <v>176</v>
       </c>
       <c r="P9" s="33">
-        <v>1137011531</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1137205471</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>188</v>
       </c>
@@ -59669,11 +59719,11 @@
       <c r="F10" t="s">
         <v>172</v>
       </c>
-      <c r="P10" s="32">
-        <v>379431964</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="33">
+        <v>379548571</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>189</v>
       </c>
@@ -59683,11 +59733,11 @@
       <c r="F11" t="s">
         <v>176</v>
       </c>
-      <c r="P11" s="32">
-        <v>172018007</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P11" s="34">
+        <v>172090822</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>190</v>
       </c>
@@ -59697,11 +59747,11 @@
       <c r="F12" t="s">
         <v>168</v>
       </c>
-      <c r="P12" s="32">
-        <v>585106166</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="33">
+        <v>585285626</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>191</v>
       </c>
@@ -59711,11 +59761,11 @@
       <c r="F13" t="s">
         <v>176</v>
       </c>
-      <c r="P13" s="32">
-        <v>178623619</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="33">
+        <v>178700934</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>192</v>
       </c>
@@ -59725,8 +59775,8 @@
       <c r="F14" t="s">
         <v>172</v>
       </c>
-      <c r="P14" s="32">
-        <v>147435232</v>
+      <c r="P14" s="33">
+        <v>147468974</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
@@ -59741,7 +59791,7 @@
       </c>
       <c r="P15" s="32">
         <f>SUM(P9:P14)</f>
-        <v>2599626519</v>
+        <v>2600300398</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -60359,6 +60409,7 @@
     <col min="3" max="3" width="122.83203125" customWidth="1"/>
     <col min="4" max="4" width="49.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CBE17C-330D-EF4A-94C2-19C8A06BD722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8300AB41-9473-1041-B028-C83C472DDC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="1942">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2710" uniqueCount="1945">
   <si>
     <t>date</t>
   </si>
@@ -6570,6 +6570,15 @@
   </si>
   <si>
     <t>https://www.threads.com/@uktaekook</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OgfK5_Jtpj4</t>
+  </si>
+  <si>
+    <t>Week of July 10, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two EPIC nights in London 🇬🇧, where our amazing TKUK admin got to see Taehyung and Jungkook live! Add in exciting new brand ambassador content, behind-the-scenes moments, personal updates, and more, and it was another unforgettable week for TaeKook! 💜💚 </t>
   </si>
 </sst>
 </file>
@@ -61246,7 +61255,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -61274,823 +61283,839 @@
     </row>
     <row r="2" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B2" t="s">
-        <v>1890</v>
+        <v>1943</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1892</v>
+        <v>1944</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1891</v>
+        <v>1942</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="B3" t="s">
-        <v>1771</v>
+        <v>1890</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1770</v>
+        <v>1892</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1772</v>
+        <v>1891</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>1771</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>5</v>
+        <v>1770</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>6</v>
+        <v>1772</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
-        <v>46185</v>
+        <v>46192</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
-        <v>46129</v>
+        <v>46136</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
-        <v>46115</v>
+        <v>46129</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
-        <v>46094</v>
+        <v>46115</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
-        <v>46052</v>
+        <v>46059</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
+        <v>46045</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="9">
         <v>46038</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C24" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D24" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9">
-        <v>46031</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
+        <v>46031</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="9">
         <v>46024</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C26" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="9">
-        <v>46017</v>
-      </c>
-      <c r="B26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
+        <v>46017</v>
+      </c>
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="9">
         <v>46010</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>71</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D28" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9">
-        <v>46003</v>
-      </c>
-      <c r="B28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
-        <v>45989</v>
+        <v>45996</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
-        <v>45975</v>
+        <v>45982</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G33" s="6"/>
     </row>
     <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
+        <v>45968</v>
+      </c>
+      <c r="B34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
         <v>45961</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C35" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D35" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="9">
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
         <v>45954</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C36" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="9">
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
         <v>45947</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C37" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9">
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
         <v>45940</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C38" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D38" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="9">
-        <v>45933</v>
-      </c>
-      <c r="B38" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="G38" s="6"/>
     </row>
     <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
+        <v>45933</v>
+      </c>
+      <c r="B39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="9">
         <v>45926</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C40" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9">
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="9">
         <v>45919</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>108</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C41" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D41" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="G40" s="6"/>
-    </row>
-    <row r="41" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="9">
-        <v>45912</v>
-      </c>
-      <c r="B41" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="G41" s="6"/>
     </row>
     <row r="42" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
+        <v>45912</v>
+      </c>
+      <c r="B42" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="9">
         <v>45905</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>114</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C43" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D43" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="9">
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="9">
         <v>45898</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C44" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D44" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G43" s="6"/>
-    </row>
-    <row r="44" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="9">
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="9">
         <v>45891</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C45" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="9">
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="9">
         <v>45884</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>123</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C46" t="s">
         <v>123</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="G45" s="6"/>
-    </row>
-    <row r="46" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="9">
-        <v>45877</v>
-      </c>
-      <c r="B46" t="s">
-        <v>125</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="G46" s="6"/>
     </row>
     <row r="47" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
+        <v>45877</v>
+      </c>
+      <c r="B47" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G47" s="6"/>
+    </row>
+    <row r="48" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="9">
         <v>45870</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>128</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D48" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="G47" s="6"/>
-    </row>
-    <row r="48" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="9">
-        <v>45863</v>
-      </c>
-      <c r="B48" t="s">
-        <v>131</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="G48" s="6"/>
     </row>
     <row r="49" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G49" s="6"/>
     </row>
     <row r="50" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="B50" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G50" s="6"/>
     </row>
     <row r="51" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="B51" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G51" s="6"/>
     </row>
     <row r="52" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
+        <v>45842</v>
+      </c>
+      <c r="B52" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G52" s="6"/>
+    </row>
+    <row r="53" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="9">
         <v>45835</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
         <v>143</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C53" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D53" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G52" s="6"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C53" s="8"/>
+      <c r="G53" s="6"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C54" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="D5" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="D7" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
-    <hyperlink ref="D8" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
-    <hyperlink ref="D9" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
-    <hyperlink ref="D10" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
-    <hyperlink ref="D12" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
-    <hyperlink ref="D14" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
-    <hyperlink ref="D15" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
-    <hyperlink ref="D16" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
-    <hyperlink ref="D17" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
-    <hyperlink ref="D18" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
-    <hyperlink ref="D19" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
-    <hyperlink ref="D20" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
-    <hyperlink ref="D21" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
-    <hyperlink ref="D22" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
-    <hyperlink ref="D23" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
-    <hyperlink ref="D24" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
-    <hyperlink ref="D25" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
-    <hyperlink ref="D26" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
-    <hyperlink ref="D27" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
-    <hyperlink ref="D28" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
-    <hyperlink ref="D29" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
-    <hyperlink ref="D30" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
-    <hyperlink ref="D31" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
-    <hyperlink ref="D32" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
-    <hyperlink ref="D33" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
-    <hyperlink ref="D34" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
-    <hyperlink ref="D35" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
-    <hyperlink ref="D36" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
-    <hyperlink ref="D37" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
-    <hyperlink ref="D38" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
-    <hyperlink ref="D39" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
-    <hyperlink ref="D40" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
-    <hyperlink ref="D41" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
-    <hyperlink ref="D42" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
-    <hyperlink ref="D43" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
-    <hyperlink ref="D44" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
-    <hyperlink ref="D45" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
-    <hyperlink ref="D46" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
-    <hyperlink ref="D47" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
-    <hyperlink ref="D48" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
-    <hyperlink ref="D49" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
-    <hyperlink ref="D50" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
-    <hyperlink ref="D51" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
-    <hyperlink ref="D52" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
-    <hyperlink ref="D4" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
-    <hyperlink ref="D3" r:id="rId49" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
+    <hyperlink ref="D6" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="D8" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="D9" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="D10" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="D11" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="D13" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="D15" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
+    <hyperlink ref="D16" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
+    <hyperlink ref="D17" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
+    <hyperlink ref="D18" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
+    <hyperlink ref="D19" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
+    <hyperlink ref="D20" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
+    <hyperlink ref="D21" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
+    <hyperlink ref="D22" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
+    <hyperlink ref="D23" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
+    <hyperlink ref="D24" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
+    <hyperlink ref="D25" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
+    <hyperlink ref="D26" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
+    <hyperlink ref="D27" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
+    <hyperlink ref="D28" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
+    <hyperlink ref="D29" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
+    <hyperlink ref="D30" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
+    <hyperlink ref="D31" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
+    <hyperlink ref="D32" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
+    <hyperlink ref="D33" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
+    <hyperlink ref="D34" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
+    <hyperlink ref="D35" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
+    <hyperlink ref="D36" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
+    <hyperlink ref="D37" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
+    <hyperlink ref="D38" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
+    <hyperlink ref="D39" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
+    <hyperlink ref="D40" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
+    <hyperlink ref="D41" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
+    <hyperlink ref="D42" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
+    <hyperlink ref="D43" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
+    <hyperlink ref="D44" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
+    <hyperlink ref="D45" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
+    <hyperlink ref="D46" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
+    <hyperlink ref="D47" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
+    <hyperlink ref="D48" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
+    <hyperlink ref="D49" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
+    <hyperlink ref="D50" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
+    <hyperlink ref="D51" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
+    <hyperlink ref="D52" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
+    <hyperlink ref="D53" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
+    <hyperlink ref="D5" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
+    <hyperlink ref="D4" r:id="rId49" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
+    <hyperlink ref="D3" r:id="rId50" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C39F6E2-9A35-BA4B-9F65-56BEB0442282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C99AA1-45FA-A34E-B243-BC5D56F6E316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="1947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="1949">
   <si>
     <t>date</t>
   </si>
@@ -6585,6 +6585,13 @@
   </si>
   <si>
     <t>donations</t>
+  </si>
+  <si>
+    <t>Munich. Paris. More unforgettable moments. 💜💚
+From two incredible concerts in Munich and an unforgettable night in Paris to more content celebrating Taehyung and Jungkook’s work with the brands they represent, plus some of the sweetest personal moments they’ve chosen to share with us, this week gave us so much to celebrate.</t>
+  </si>
+  <si>
+    <t>Week of July 17, 2026</t>
   </si>
 </sst>
 </file>
@@ -61267,7 +61274,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -61295,13 +61302,13 @@
     </row>
     <row r="2" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="B2" t="s">
-        <v>1942</v>
+        <v>1948</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1943</v>
+        <v>1947</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>1941</v>
@@ -61310,824 +61317,840 @@
     </row>
     <row r="3" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B3" t="s">
-        <v>1889</v>
+        <v>1942</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1891</v>
+        <v>1943</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1890</v>
+        <v>1941</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="B4" t="s">
-        <v>1770</v>
+        <v>1889</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1769</v>
+        <v>1891</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1771</v>
+        <v>1890</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>1770</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>5</v>
+        <v>1769</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>6</v>
+        <v>1771</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
-        <v>46185</v>
+        <v>46192</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
-        <v>46129</v>
+        <v>46136</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
-        <v>46115</v>
+        <v>46129</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
-        <v>46094</v>
+        <v>46115</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
-        <v>46052</v>
+        <v>46059</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
+        <v>46045</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="9">
         <v>46038</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9">
-        <v>46031</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
+        <v>46031</v>
+      </c>
+      <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9">
         <v>46024</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C27" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="9">
-        <v>46017</v>
-      </c>
-      <c r="B27" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
+        <v>46017</v>
+      </c>
+      <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="5"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="9">
         <v>46010</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>71</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="9">
-        <v>46003</v>
-      </c>
-      <c r="B29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G30" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
-        <v>45989</v>
+        <v>45996</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
-        <v>45975</v>
+        <v>45982</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G33" s="6"/>
     </row>
     <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
+        <v>45968</v>
+      </c>
+      <c r="B35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
         <v>45961</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>90</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C36" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="9">
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
         <v>45954</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C37" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9">
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
         <v>45947</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C38" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D38" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="9">
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
         <v>45940</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>99</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C39" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="9">
-        <v>45933</v>
-      </c>
-      <c r="B39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="G39" s="6"/>
     </row>
     <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
+        <v>45933</v>
+      </c>
+      <c r="B40" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="9">
         <v>45926</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C41" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D41" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G40" s="6"/>
-    </row>
-    <row r="41" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="9">
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="9">
         <v>45919</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>108</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C42" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D42" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="G41" s="6"/>
-    </row>
-    <row r="42" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9">
-        <v>45912</v>
-      </c>
-      <c r="B42" t="s">
-        <v>111</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="G42" s="6"/>
     </row>
     <row r="43" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
+        <v>45912</v>
+      </c>
+      <c r="B43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="9">
         <v>45905</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C44" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D44" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G43" s="6"/>
-    </row>
-    <row r="44" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="9">
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="9">
         <v>45898</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>117</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C45" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="45" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="9">
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="9">
         <v>45891</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C46" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G45" s="6"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="9">
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="9">
         <v>45884</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>123</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>123</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D47" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="G46" s="6"/>
-    </row>
-    <row r="47" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="9">
-        <v>45877</v>
-      </c>
-      <c r="B47" t="s">
-        <v>125</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="G47" s="6"/>
     </row>
     <row r="48" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
+        <v>45877</v>
+      </c>
+      <c r="B48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" s="6"/>
+    </row>
+    <row r="49" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="9">
         <v>45870</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>128</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C49" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D49" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="G48" s="6"/>
-    </row>
-    <row r="49" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="9">
-        <v>45863</v>
-      </c>
-      <c r="B49" t="s">
-        <v>131</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="G49" s="6"/>
     </row>
     <row r="50" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G50" s="6"/>
     </row>
     <row r="51" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="B51" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G51" s="6"/>
     </row>
     <row r="52" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G52" s="6"/>
     </row>
     <row r="53" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
+        <v>45842</v>
+      </c>
+      <c r="B53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G53" s="6"/>
+    </row>
+    <row r="54" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="9">
         <v>45835</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B54" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C54" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D54" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G53" s="6"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C54" s="8"/>
+      <c r="G54" s="6"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C55" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="D6" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="D8" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
-    <hyperlink ref="D9" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
-    <hyperlink ref="D10" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
-    <hyperlink ref="D11" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
-    <hyperlink ref="D13" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
-    <hyperlink ref="D15" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
-    <hyperlink ref="D16" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
-    <hyperlink ref="D17" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
-    <hyperlink ref="D18" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
-    <hyperlink ref="D19" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
-    <hyperlink ref="D20" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
-    <hyperlink ref="D21" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
-    <hyperlink ref="D22" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
-    <hyperlink ref="D23" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
-    <hyperlink ref="D24" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
-    <hyperlink ref="D25" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
-    <hyperlink ref="D26" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
-    <hyperlink ref="D27" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
-    <hyperlink ref="D28" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
-    <hyperlink ref="D29" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
-    <hyperlink ref="D30" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
-    <hyperlink ref="D31" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
-    <hyperlink ref="D32" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
-    <hyperlink ref="D33" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
-    <hyperlink ref="D34" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
-    <hyperlink ref="D35" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
-    <hyperlink ref="D36" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
-    <hyperlink ref="D37" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
-    <hyperlink ref="D38" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
-    <hyperlink ref="D39" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
-    <hyperlink ref="D40" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
-    <hyperlink ref="D41" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
-    <hyperlink ref="D42" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
-    <hyperlink ref="D43" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
-    <hyperlink ref="D44" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
-    <hyperlink ref="D45" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
-    <hyperlink ref="D46" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
-    <hyperlink ref="D47" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
-    <hyperlink ref="D48" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
-    <hyperlink ref="D49" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
-    <hyperlink ref="D50" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
-    <hyperlink ref="D51" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
-    <hyperlink ref="D52" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
-    <hyperlink ref="D53" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
-    <hyperlink ref="D5" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
-    <hyperlink ref="D4" r:id="rId49" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
-    <hyperlink ref="D3" r:id="rId50" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
+    <hyperlink ref="D7" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="D8" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="D9" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="D10" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="D11" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="D12" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="D14" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="D16" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
+    <hyperlink ref="D17" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
+    <hyperlink ref="D18" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
+    <hyperlink ref="D19" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
+    <hyperlink ref="D20" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
+    <hyperlink ref="D21" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
+    <hyperlink ref="D22" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
+    <hyperlink ref="D23" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
+    <hyperlink ref="D24" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
+    <hyperlink ref="D25" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
+    <hyperlink ref="D26" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
+    <hyperlink ref="D27" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
+    <hyperlink ref="D28" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
+    <hyperlink ref="D29" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
+    <hyperlink ref="D30" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
+    <hyperlink ref="D31" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
+    <hyperlink ref="D32" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
+    <hyperlink ref="D33" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
+    <hyperlink ref="D34" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
+    <hyperlink ref="D35" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
+    <hyperlink ref="D36" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
+    <hyperlink ref="D37" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
+    <hyperlink ref="D38" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
+    <hyperlink ref="D39" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
+    <hyperlink ref="D40" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
+    <hyperlink ref="D41" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
+    <hyperlink ref="D42" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
+    <hyperlink ref="D43" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
+    <hyperlink ref="D44" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
+    <hyperlink ref="D45" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
+    <hyperlink ref="D46" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
+    <hyperlink ref="D47" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
+    <hyperlink ref="D48" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
+    <hyperlink ref="D49" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
+    <hyperlink ref="D50" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
+    <hyperlink ref="D51" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
+    <hyperlink ref="D52" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
+    <hyperlink ref="D53" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
+    <hyperlink ref="D54" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
+    <hyperlink ref="D6" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
+    <hyperlink ref="D5" r:id="rId49" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
+    <hyperlink ref="D4" r:id="rId50" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
+    <hyperlink ref="D3" r:id="rId51" xr:uid="{8E240BDD-02FF-CA47-B5D9-FD7E9FCA5AEA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C99AA1-45FA-A34E-B243-BC5D56F6E316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5271CD62-649B-1943-ABF7-2AA4D1A2CB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="1949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2790" uniqueCount="2008">
   <si>
     <t>date</t>
   </si>
@@ -6592,6 +6592,192 @@
   </si>
   <si>
     <t>Week of July 17, 2026</t>
+  </si>
+  <si>
+    <t>http://www.youtube.com/watch?v=grZTqTvCapE</t>
+  </si>
+  <si>
+    <t>V becomes first K-pop male solo artist to reach 75M Instagram followers</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DafF8IwtmgI/</t>
+  </si>
+  <si>
+    <t>BTS V has surpassed 75 million Instagram followers, becoming the first K-pop male solo artist to reach the milestone. He gained an additional 5 million followers in just six months after reaching 70 million, making him the sixth male musician in the world to surpass 75 million followers.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DamppOFNdq1/</t>
+  </si>
+  <si>
+    <t>Jungkook’s “Seven” extends historic Spotify record to 155 weeks</t>
+  </si>
+  <si>
+    <t>BTS Jungkook’s debut solo single “Seven” has now spent 155 consecutive weeks on Spotify’s Weekly Top Songs Global chart, extending its record as the first and longest-charting song by an Asian solo artist. The song has also surpassed 3.01 billion Spotify streams, setting another milestone for an Asian artist.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DamqUoxtvWk/</t>
+  </si>
+  <si>
+    <t>V makes first appearance as JINRO’s global ambassador</t>
+  </si>
+  <si>
+    <t>BTS V has made his first official appearance as JINRO’s first-ever global brand ambassador, with HiteJinro unveiling a teaser for its new global campaign. The company said V best represents JINRO’s brand values and will help strengthen its presence with consumers in Korea and around the world.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DauEcbLN2tJ/</t>
+  </si>
+  <si>
+    <t>Taekook | Weverse Magazine | BTS “ARIRANG” world tour report</t>
+  </si>
+  <si>
+    <t>🐰 Jung Kook has been filming and editing his own vlogs on the road, despite the tour’s packed schedule, and posting them to his Instagram, calling to mind the Golden Closet Film series he used to upload to BTS’s YouTube channel. “It reminded me of when I used to film things every once in a while, back in the day,” the idol said when asked what prompted him to start vlogging. “Keeping a record of everything not just with photos but with video makes it easier to remember exactly what things were like at a given time, so I thought it’d be nice to build a habit of documenting my day for ARMY every now and then!”
+🐯 V, too, has found the surprise segment to be an energetic, emotional experience. “When an old song comes on, the memories from back then suddenly come clearly into view,” he said. “I guess I just can’t forget that period of time, so those memories come rushing back, and my body starts moving on its own. Maybe it’s because I’m so happy and excited, but I start dancing without even knowing it. Honestly, there’s some songs I practiced so much back then that they’re just there in my body. I don’t think I could forget them if I tried.”</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DauYErFtc1t/</t>
+  </si>
+  <si>
+    <t>Drake follows Jungkook on Instagram, sparking collaboration speculation</t>
+  </si>
+  <si>
+    <t>Canadian rapper Drake has followed BTS Jungkook’s personal Instagram account, making Jungkook the only BTS member he follows. The news has drawn attention from international media and fueled fan speculation about a possible future collaboration.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DauZRfDtsJ6/</t>
+  </si>
+  <si>
+    <t>FC Bayern Munich declares V as its favorite BTS member</t>
+  </si>
+  <si>
+    <t>FC Bayern Munich showed its support for BTS during the group’s sold-out concerts at Allianz Arena, once again declaring “Tae” as its favorite member and sharing multiple posts of V across its official social media accounts throughout the concert weekend.</t>
+  </si>
+  <si>
+    <t>naver.me/xQJzqNeo</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DazhLpnNq4y/</t>
+  </si>
+  <si>
+    <t>V’s soulful vocals earn praise from GQ Germany</t>
+  </si>
+  <si>
+    <t>BTS V received praise from GQ Germany for his emotional vocals during BTS’s sold-out Munich concerts, with the magazine describing his voice as “like a spoonful of warm honey.” It also highlighted “Into the Sun” and V’s tribute to local fans by wearing a special FC Bayern Munich jersey on stage.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DazjFgQNKQj/</t>
+  </si>
+  <si>
+    <t>Jungkook wins over German fans with local hit “Gut Genug”</t>
+  </si>
+  <si>
+    <t>BTS Jungkook performed the German hit “Gut Genug” during both nights of BTS’s Munich concerts, delighting local fans by singing in German. The performance fulfilled an idea he previously shared of performing popular local songs during overseas tours, with fans and the original artist praising the heartfelt gesture.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Da3rhZ4tE2v/</t>
+  </si>
+  <si>
+    <t>Q: Something that stands out about this tour is how there are no subunit or solo songs, instead focusing on the seven of you being all together. The concerts really drive home how BTS is one unified group._x000B_
+🐰 You hit the nail on the head with our intention. It’s pretty unusual for a group to fill an entire concert exclusively with group songs from start to finish anymore. We wanted to remind everyone what BTS is like as a group, and since it’s been so long since our last tour, we tried to focus on the kind of energy we have when we’re all together. Obviously that makes things harder, but we wanted to immerse the audience in that feeling of all seven of us putting on the show together, all the way through.
+🐯 We all felt that we should be focusing on the group rather than subunit or solo songs. I think that is the core of this tour. Having the seven of us back together after all this time feels special, and it’s also our way of saying we want to keep doing this together.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Da3siJqtAYi/</t>
+  </si>
+  <si>
+    <t>Taekook | Weverse Magazine 2</t>
+  </si>
+  <si>
+    <t>Taekook | Weverse Magazine 1</t>
+  </si>
+  <si>
+    <t>Q: The part where Jung Kook catches the drone during “Run BTS” got a lot of attention. He looks so natural doing it that some people thought it was improvised at first. What’s the story behind that?
+🐰 That part was very deliberately orchestrated. We ended up trying it out based on an idea the director had. The drone actually crashed into the floor by accident when we were rehearsing. I’m always worried I’m going to miss it. (laughs)
+Q: That’s another big part of what makes this tour special—those spontaneous moments you share with ARMY, like V in Mexico City eating a hot dog or making a toast with them, or Jin asking for confetti to rain down over his head or blowing his signature kiss. Every show ends up with its own special moment.
+🐯 Umm, how do I say this? I just like seeing ARMY happy, so if some idea pops into my head suddenly, I guess I just go with it. I want to make them laugh. (laughs) Even when I’m talking with the crowd, I try not to get too serious about it. I’d rather just chat about everyday stuff and keep it light. I feel like that gets more laughs out of them anyway.</t>
+  </si>
+  <si>
+    <t>Taekook | Weverse Magazine 3</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Da3ttJOt7Im/</t>
+  </si>
+  <si>
+    <t>Q: This tour has BTS’s past and present coexisting side by side. The setlist is built around “ARIRANG” for the most part, but there’s also time set aside to connect with ARMY through songs from your earlier days. How do you feel when you sing those older songs with ARMY now?
+🐰 It makes me happy. Sometimes I get nostalgic and look up old videos of our performances, too. Obviously I can’t do all the choreography from back then exactly the same, but there’s a very different hit of nostalgia when I’m actually performing it live instead of just watching a video of it, and I wanted to let ARMY experience the same thing.
+Q: And on that note, it seems like V’s been putting in a lot of effort to help create even more memories with the group throughout the tour. Jin even called him the “culture master” on Weverse LIVE on May 3. What’s been driving this hunt for little pockets of joy in every city, like the pizza V told ARMY was great at Stanford Stadium?
+🐯 We’d talked about wanting to make the most of our time together offstage, too, and I wanted to keep everyone’s energy up so no one got too worn out over the tour, so I ended up being among a few of us who comes up with ideas, like restaurants and pickleball, and I kept nagging the others to come along. (laughs) I’ve come to realize that creating little pockets of happiness like that can make the whole tour a better experience for all of us.</t>
+  </si>
+  <si>
+    <t>Jungkook shines in new Graff campaign as global ambassador</t>
+  </si>
+  <si>
+    <t>BTS Jungkook captivated fans with a new Graff campaign featuring behind-the-scenes footage and photos from his first collection as the brand’s first-ever global ambassador. Graff praised Jungkook as a cultural icon whose creativity and brilliance reflect the brand’s values.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Da7XiB7tpYD/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Da7X8oKNq_I/</t>
+  </si>
+  <si>
+    <t>V’s cinematic Paris dance video goes viral on TikTok</t>
+  </si>
+  <si>
+    <t>BTS V shared a cinematic dance video filmed in Paris on TikTok, drawing millions of views within hours. The video also caught Jungkook’s attention, who commented, “When did you film this? Hahahaha,” as fans around the world praised V’s choreography, creativity, and performance.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Da94309tP6y/</t>
+  </si>
+  <si>
+    <t>BTS Jungkook’s “Seven” has reached 156 consecutive weeks on both Billboard’s Global (Excl. U.S.) chart and Spotify’s Weekly Top Songs Global chart, extending its record as the first and longest-charting song by an Asian solo artist. The song has also surpassed 3.02 billion Spotify streams.</t>
+  </si>
+  <si>
+    <t>Jungkook’s “Seven” extends historic Billboard and Spotify run to 156 weeks</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Da95lzENogb/</t>
+  </si>
+  <si>
+    <t>V captivates Paris with his charm and heartfelt French message</t>
+  </si>
+  <si>
+    <t>BTS V drew praise during BTS’s final European concerts in Paris, wearing custom CELINE outfits and ending the show with a heartfelt message in French. His sincere words to fans and confident French pronunciation earned admiration from both attendees and French journalist Hugo Travers.</t>
+  </si>
+  <si>
+    <t>https://naver.me/56Xv0EkO</t>
+  </si>
+  <si>
+    <t>https://naver.me/FBMztib2</t>
+  </si>
+  <si>
+    <t>https://naver.me/5Z1laYeO</t>
+  </si>
+  <si>
+    <t>https://naver.me/FFqr34i4</t>
+  </si>
+  <si>
+    <t>https://magazine.weverse.io/article/view/1903?lang=en</t>
+  </si>
+  <si>
+    <t>https://naver.me/Fx2xcm3z</t>
+  </si>
+  <si>
+    <t>https://naver.me/5fdUJ73Y</t>
+  </si>
+  <si>
+    <t>https://naver.me/FAAXyB6Y</t>
+  </si>
+  <si>
+    <t>https://magazine.weverse.io/article/view/1899?lang=en</t>
+  </si>
+  <si>
+    <t>https://naver.me/5o01tWe9</t>
+  </si>
+  <si>
+    <t>https://naver.me/xtN0Iu2Q</t>
+  </si>
+  <si>
+    <t>https://naver.me/F053XVrF</t>
   </si>
 </sst>
 </file>
@@ -6731,7 +6917,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6762,32 +6948,14 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6795,6 +6963,18 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -60572,7 +60752,7 @@
       <c r="F9" t="s">
         <v>176</v>
       </c>
-      <c r="P9" s="33">
+      <c r="P9" s="27">
         <v>1137205471</v>
       </c>
     </row>
@@ -60586,7 +60766,7 @@
       <c r="F10" t="s">
         <v>172</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10" s="27">
         <v>379548571</v>
       </c>
     </row>
@@ -60600,7 +60780,7 @@
       <c r="F11" t="s">
         <v>176</v>
       </c>
-      <c r="P11" s="34">
+      <c r="P11" s="28">
         <v>172090822</v>
       </c>
     </row>
@@ -60614,7 +60794,7 @@
       <c r="F12" t="s">
         <v>168</v>
       </c>
-      <c r="P12" s="33">
+      <c r="P12" s="27">
         <v>585285626</v>
       </c>
     </row>
@@ -60628,7 +60808,7 @@
       <c r="F13" t="s">
         <v>176</v>
       </c>
-      <c r="P13" s="33">
+      <c r="P13" s="27">
         <v>178700934</v>
       </c>
     </row>
@@ -60642,7 +60822,7 @@
       <c r="F14" t="s">
         <v>172</v>
       </c>
-      <c r="P14" s="33">
+      <c r="P14" s="27">
         <v>147468974</v>
       </c>
     </row>
@@ -60656,7 +60836,7 @@
       <c r="F15" t="s">
         <v>168</v>
       </c>
-      <c r="P15" s="32">
+      <c r="P15" s="26">
         <f>SUM(P9:P14)</f>
         <v>2600300398</v>
       </c>
@@ -61311,7 +61491,7 @@
         <v>1947</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1941</v>
+        <v>1949</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -63545,301 +63725,630 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" style="27"/>
-    <col min="3" max="3" width="63.33203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="98.1640625" style="31" customWidth="1"/>
-    <col min="6" max="6" width="25.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="27"/>
+    <col min="1" max="1" width="10.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" style="25"/>
+    <col min="3" max="3" width="54" style="25" customWidth="1"/>
+    <col min="4" max="4" width="40.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="88.33203125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" style="25" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="24" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A2" s="22">
+    <row r="2" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A2" s="31">
+        <v>46222</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>1995</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="31">
+        <v>46222</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>1990</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>1991</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A4" s="31">
+        <v>46219</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>1989</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>46219</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="289" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>46218</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>1983</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="238" x14ac:dyDescent="0.2">
+      <c r="A7" s="31">
+        <v>46218</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>1980</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="204" x14ac:dyDescent="0.2">
+      <c r="A8" s="31">
+        <v>46218</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>1975</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A9" s="31">
+        <v>46217</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A10" s="31">
+        <v>46217</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>1970</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="31">
+        <v>46216</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A12" s="31">
+        <v>46216</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="238" x14ac:dyDescent="0.2">
+      <c r="A13" s="31">
+        <v>46215</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>1961</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A14" s="31">
+        <v>46213</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>1958</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A15" s="31">
+        <v>46213</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>1955</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A16" s="31">
+        <v>46210</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>1951</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1952</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A17" s="31">
         <v>46208</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B17" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C17" s="22" t="s">
         <v>1836</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D17" s="29" t="s">
         <v>1839</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E17" s="22" t="s">
         <v>1837</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F17" s="6" t="s">
         <v>1838</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="22">
+    <row r="18" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A18" s="31">
         <v>46208</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B18" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C18" s="22" t="s">
         <v>1832</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D18" s="29" t="s">
         <v>1835</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E18" s="22" t="s">
         <v>1833</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F18" s="29" t="s">
         <v>1834</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A4" s="22">
+    <row r="19" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A19" s="31">
         <v>46205</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B19" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C19" s="22" t="s">
         <v>1829</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D19" s="29" t="s">
         <v>1824</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E19" s="22" t="s">
         <v>1830</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F19" s="30" t="s">
         <v>1831</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" s="22">
+    <row r="20" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A20" s="31">
         <v>46206</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B20" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C20" s="22" t="s">
         <v>1826</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D20" s="29" t="s">
         <v>1825</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E20" s="22" t="s">
         <v>1827</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F20" s="29" t="s">
         <v>1828</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A6" s="30">
+    <row r="21" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A21" s="32">
         <v>46203</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B21" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C21" s="25" t="s">
         <v>1785</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D21" s="29" t="s">
         <v>1786</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E21" s="25" t="s">
         <v>1787</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F21" s="29" t="s">
         <v>1791</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" s="30">
+    <row r="22" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A22" s="32">
         <v>46203</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B22" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C22" s="25" t="s">
         <v>1789</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D22" s="25" t="s">
         <v>1788</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E22" s="25" t="s">
         <v>1790</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F22" s="29" t="s">
         <v>1792</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A8" s="30">
+    <row r="23" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A23" s="32">
         <v>46202</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B23" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C23" s="25" t="s">
         <v>1794</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D23" s="29" t="s">
         <v>1793</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E23" s="25" t="s">
         <v>1796</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F23" s="29" t="s">
         <v>1795</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A9" s="30">
+    <row r="24" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A24" s="32">
         <v>46202</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B24" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C24" s="25" t="s">
         <v>1799</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D24" s="25" t="s">
         <v>1797</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E24" s="25" t="s">
         <v>1798</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F24" s="29" t="s">
         <v>1800</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A10" s="30">
+    <row r="25" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A25" s="32">
         <v>46201</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B25" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C25" s="25" t="s">
         <v>1801</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D25" s="29" t="s">
         <v>1803</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E25" s="25" t="s">
         <v>1802</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F25" s="29" t="s">
         <v>1804</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A11" s="30">
+    <row r="26" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A26" s="32">
         <v>46201</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B26" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C26" s="25" t="s">
         <v>1806</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D26" s="29" t="s">
         <v>1805</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E26" s="25" t="s">
         <v>1807</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F26" s="29" t="s">
         <v>1808</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A12" s="30">
+    <row r="27" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A27" s="32">
         <v>46198</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B27" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C27" s="25" t="s">
         <v>1810</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D27" s="25" t="s">
         <v>1809</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E27" s="25" t="s">
         <v>1811</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F27" s="29" t="s">
         <v>1812</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="30">
+    <row r="28" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A28" s="32">
         <v>46198</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B28" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C28" s="25" t="s">
         <v>1814</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D28" s="29" t="s">
         <v>1813</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E28" s="25" t="s">
         <v>1815</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F28" s="29" t="s">
         <v>1816</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1" xr:uid="{4C165E91-B26F-0A45-88A2-06AA9774DFAE}"/>
-    <hyperlink ref="F7" r:id="rId2" xr:uid="{7642FB96-3502-1243-90D5-20631BBFCC79}"/>
-    <hyperlink ref="D6" r:id="rId3" xr:uid="{1E0F0315-6747-884F-AA49-D6E56727920B}"/>
-    <hyperlink ref="D8" r:id="rId4" xr:uid="{8488153C-110A-4C48-965B-7630C9492F36}"/>
-    <hyperlink ref="F8" r:id="rId5" xr:uid="{BE75DA92-F980-1948-9204-01AC25600C6B}"/>
-    <hyperlink ref="F9" r:id="rId6" xr:uid="{7457B18B-86CB-6147-ADA9-A3CE56A83401}"/>
-    <hyperlink ref="D10" r:id="rId7" xr:uid="{FBAC6F67-55B1-324A-82BF-DD02FC6BBA04}"/>
-    <hyperlink ref="F10" r:id="rId8" xr:uid="{865A0475-BB84-DB47-9559-DC4649F4A676}"/>
-    <hyperlink ref="D11" r:id="rId9" xr:uid="{D9D6577F-5D20-B245-9F68-2D50BDFCA180}"/>
-    <hyperlink ref="F11" r:id="rId10" xr:uid="{21950F61-40D9-5E42-87ED-8402F010D442}"/>
-    <hyperlink ref="F12" r:id="rId11" xr:uid="{990DFC39-986D-3849-99EC-29E4E365D40A}"/>
-    <hyperlink ref="D13" r:id="rId12" xr:uid="{DE7E8DCA-2195-394F-9E1F-C6282B5AFE11}"/>
-    <hyperlink ref="F13" r:id="rId13" xr:uid="{A97FBDD3-5139-A04F-A3D7-E34D3553362F}"/>
-    <hyperlink ref="D4" r:id="rId14" xr:uid="{B5715535-CBF7-2F43-A872-9DF1119833A5}"/>
-    <hyperlink ref="D5" r:id="rId15" xr:uid="{4BD8C645-AD86-B644-BB86-E474C950B5C1}"/>
-    <hyperlink ref="F5" r:id="rId16" xr:uid="{E6DC40BA-2FBD-8741-8B86-BE0CB8B5DF5A}"/>
-    <hyperlink ref="F4" r:id="rId17" xr:uid="{2D25DB01-973D-C442-BAAA-A7898AECF3CB}"/>
-    <hyperlink ref="D3" r:id="rId18" xr:uid="{5EE266C8-30C3-AA49-A280-DD6ACA716BED}"/>
-    <hyperlink ref="F2" r:id="rId19" xr:uid="{406CFBE4-10DA-B54F-842C-5C37F66B6667}"/>
-    <hyperlink ref="D2" r:id="rId20" xr:uid="{51D6B607-BCF9-224D-B409-72E4FD66FF8D}"/>
-    <hyperlink ref="F3" r:id="rId21" xr:uid="{1523EF8F-C7CF-B247-84A6-D1068FDF2FC9}"/>
+    <hyperlink ref="F21" r:id="rId1" xr:uid="{4C165E91-B26F-0A45-88A2-06AA9774DFAE}"/>
+    <hyperlink ref="F22" r:id="rId2" xr:uid="{7642FB96-3502-1243-90D5-20631BBFCC79}"/>
+    <hyperlink ref="D21" r:id="rId3" xr:uid="{1E0F0315-6747-884F-AA49-D6E56727920B}"/>
+    <hyperlink ref="D23" r:id="rId4" xr:uid="{8488153C-110A-4C48-965B-7630C9492F36}"/>
+    <hyperlink ref="F23" r:id="rId5" xr:uid="{BE75DA92-F980-1948-9204-01AC25600C6B}"/>
+    <hyperlink ref="F24" r:id="rId6" xr:uid="{7457B18B-86CB-6147-ADA9-A3CE56A83401}"/>
+    <hyperlink ref="D25" r:id="rId7" xr:uid="{FBAC6F67-55B1-324A-82BF-DD02FC6BBA04}"/>
+    <hyperlink ref="F25" r:id="rId8" xr:uid="{865A0475-BB84-DB47-9559-DC4649F4A676}"/>
+    <hyperlink ref="D26" r:id="rId9" xr:uid="{D9D6577F-5D20-B245-9F68-2D50BDFCA180}"/>
+    <hyperlink ref="F26" r:id="rId10" xr:uid="{21950F61-40D9-5E42-87ED-8402F010D442}"/>
+    <hyperlink ref="F27" r:id="rId11" xr:uid="{990DFC39-986D-3849-99EC-29E4E365D40A}"/>
+    <hyperlink ref="D28" r:id="rId12" xr:uid="{DE7E8DCA-2195-394F-9E1F-C6282B5AFE11}"/>
+    <hyperlink ref="F28" r:id="rId13" xr:uid="{A97FBDD3-5139-A04F-A3D7-E34D3553362F}"/>
+    <hyperlink ref="D19" r:id="rId14" xr:uid="{B5715535-CBF7-2F43-A872-9DF1119833A5}"/>
+    <hyperlink ref="D20" r:id="rId15" xr:uid="{4BD8C645-AD86-B644-BB86-E474C950B5C1}"/>
+    <hyperlink ref="F20" r:id="rId16" xr:uid="{E6DC40BA-2FBD-8741-8B86-BE0CB8B5DF5A}"/>
+    <hyperlink ref="F19" r:id="rId17" xr:uid="{2D25DB01-973D-C442-BAAA-A7898AECF3CB}"/>
+    <hyperlink ref="D18" r:id="rId18" xr:uid="{5EE266C8-30C3-AA49-A280-DD6ACA716BED}"/>
+    <hyperlink ref="F18" r:id="rId19" xr:uid="{1523EF8F-C7CF-B247-84A6-D1068FDF2FC9}"/>
+    <hyperlink ref="F17" r:id="rId20" xr:uid="{5344D85B-DBA1-7F4D-A437-9ADA0A6F25E7}"/>
+    <hyperlink ref="D17" r:id="rId21" xr:uid="{82E8603F-6B68-A849-9DB1-A6D7D62BC5C3}"/>
+    <hyperlink ref="D16" r:id="rId22" xr:uid="{C4B7F07F-C7EF-A445-BA36-79AFD111A13A}"/>
+    <hyperlink ref="D15" r:id="rId23" xr:uid="{28DE8988-3557-EF48-BB75-91D97971DC4D}"/>
+    <hyperlink ref="D14" r:id="rId24" xr:uid="{0B7C9678-BFED-1B4C-9FF2-DCCCE6ED62A7}"/>
+    <hyperlink ref="D13" r:id="rId25" xr:uid="{F69DCD8B-5576-A945-A1C0-850B8C57018F}"/>
+    <hyperlink ref="D12" r:id="rId26" xr:uid="{5CC655C1-5F71-CA47-90F1-336EB32A4376}"/>
+    <hyperlink ref="D11" r:id="rId27" xr:uid="{435469A8-0A82-1B46-ADC7-2BD93F4F0AD8}"/>
+    <hyperlink ref="D10" r:id="rId28" xr:uid="{C3AD3B54-C7D7-D14E-9805-9AEFCD3B56FC}"/>
+    <hyperlink ref="D9" r:id="rId29" xr:uid="{0FC6BD88-2D04-304E-AA6D-D0FC8F78BCA3}"/>
+    <hyperlink ref="D8" r:id="rId30" xr:uid="{9D70D003-ECDB-EC41-8AC7-5169C0795E15}"/>
+    <hyperlink ref="D7" r:id="rId31" xr:uid="{95972599-A68F-6141-8993-0C512EA7EB77}"/>
+    <hyperlink ref="D6" r:id="rId32" xr:uid="{325C9583-A49B-764F-9858-1A1870FCBF90}"/>
+    <hyperlink ref="D5" r:id="rId33" xr:uid="{841ECEF8-4ED6-B84D-8372-B8844DAD23B5}"/>
+    <hyperlink ref="D4" r:id="rId34" xr:uid="{3F93FFDC-C232-DD42-9509-5E6EC6ECC7D3}"/>
+    <hyperlink ref="D3" r:id="rId35" xr:uid="{1C3439D8-0793-DA4B-991C-E5E37FAAC840}"/>
+    <hyperlink ref="D2" r:id="rId36" xr:uid="{51A6409E-8F94-AF44-B60C-08D0EDDC3758}"/>
+    <hyperlink ref="F2" r:id="rId37" xr:uid="{7F3D42E2-43F6-3548-BB2F-32CAD36E6170}"/>
+    <hyperlink ref="F3" r:id="rId38" xr:uid="{BDC3FD63-F436-E94D-A22F-05D357586E92}"/>
+    <hyperlink ref="F4" r:id="rId39" xr:uid="{0D035AE3-AAB0-254A-8010-E546387524A5}"/>
+    <hyperlink ref="F5" r:id="rId40" xr:uid="{2BCDC745-7256-214E-85A3-5FD239BA2A2F}"/>
+    <hyperlink ref="F6" r:id="rId41" xr:uid="{646B607C-75D4-0A47-8DED-0FDED514E2D3}"/>
+    <hyperlink ref="F7" r:id="rId42" xr:uid="{B9D307B7-2704-6E46-A670-B2DF92C7BC6F}"/>
+    <hyperlink ref="F8" r:id="rId43" xr:uid="{AE106E88-F04C-8744-B97B-68010273A3BF}"/>
+    <hyperlink ref="F9" r:id="rId44" xr:uid="{E5B27231-C944-BC4D-8025-6C163578708B}"/>
+    <hyperlink ref="F10" r:id="rId45" xr:uid="{4394F2F6-3518-9346-9D09-3496D3A48ABE}"/>
+    <hyperlink ref="F12" r:id="rId46" xr:uid="{C243C78A-1717-6C4E-9BE0-5AB19A56F3AB}"/>
+    <hyperlink ref="F13" r:id="rId47" xr:uid="{95FB7936-E26F-434D-AF06-44A9337A976E}"/>
+    <hyperlink ref="F14" r:id="rId48" xr:uid="{DFDB01C1-AE39-EB47-8DEA-A691B1A13FFF}"/>
+    <hyperlink ref="F15" r:id="rId49" xr:uid="{D57E7D52-6454-0149-87FF-11C129D8632B}"/>
+    <hyperlink ref="F16" r:id="rId50" xr:uid="{CD3A77F8-468B-EB42-BC45-17DABC164DD2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5271CD62-649B-1943-ABF7-2AA4D1A2CB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445D6E5B-3311-2945-8044-FB5DCC1D69ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="1360" windowWidth="29560" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -60752,9 +60752,7 @@
       <c r="F9" t="s">
         <v>176</v>
       </c>
-      <c r="P9" s="27">
-        <v>1137205471</v>
-      </c>
+      <c r="P9" s="27"/>
     </row>
     <row r="10" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -60766,9 +60764,7 @@
       <c r="F10" t="s">
         <v>172</v>
       </c>
-      <c r="P10" s="27">
-        <v>379548571</v>
-      </c>
+      <c r="P10" s="27"/>
     </row>
     <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -60780,9 +60776,7 @@
       <c r="F11" t="s">
         <v>176</v>
       </c>
-      <c r="P11" s="28">
-        <v>172090822</v>
-      </c>
+      <c r="P11" s="28"/>
     </row>
     <row r="12" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -60794,9 +60788,7 @@
       <c r="F12" t="s">
         <v>168</v>
       </c>
-      <c r="P12" s="27">
-        <v>585285626</v>
-      </c>
+      <c r="P12" s="27"/>
     </row>
     <row r="13" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -60808,9 +60800,7 @@
       <c r="F13" t="s">
         <v>176</v>
       </c>
-      <c r="P13" s="27">
-        <v>178700934</v>
-      </c>
+      <c r="P13" s="27"/>
     </row>
     <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -60822,9 +60812,7 @@
       <c r="F14" t="s">
         <v>172</v>
       </c>
-      <c r="P14" s="27">
-        <v>147468974</v>
-      </c>
+      <c r="P14" s="27"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -60836,10 +60824,7 @@
       <c r="F15" t="s">
         <v>168</v>
       </c>
-      <c r="P15" s="26">
-        <f>SUM(P9:P14)</f>
-        <v>2600300398</v>
-      </c>
+      <c r="P15" s="26"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E601E3D-9039-6B48-B75A-702D0E2740CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE21B68-6A58-544F-A186-C8E6C1974E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4760" yWindow="620" windowWidth="29560" windowHeight="21000" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="1180" windowWidth="38400" windowHeight="21000" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="2020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="2024">
   <si>
     <t>date</t>
   </si>
@@ -7062,6 +7062,19 @@
 (Fly with me fly with me)
 You make me begin
 You made me again</t>
+  </si>
+  <si>
+    <t>3D</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GGlFJYH1wsQ</t>
+  </si>
+  <si>
+    <t>Week of July 24, 2026</t>
+  </si>
+  <si>
+    <t>From an unforgettable second night in Paris and the personal memories they chose to share, to a week full of NORMAL content, including the Live video, behind-the-scenes moments, and more, it’s been another beautiful week with Taehyung and Jungkook.
+Now they’re safely back home in Korea for a well-earned break before the tour resumes in August. 💜</t>
   </si>
 </sst>
 </file>
@@ -7201,7 +7214,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -7259,6 +7272,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7662,9 +7676,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D78C016-D6BB-C949-90F3-825A9275A28A}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
     <col min="5" max="5" width="32.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="43" customWidth="1"/>
     <col min="7" max="7" width="45.33203125" customWidth="1"/>
@@ -7696,7 +7711,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>230</v>
       </c>
@@ -7719,7 +7734,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>220</v>
       </c>
@@ -7742,20 +7757,423 @@
         <v>2019</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" t="s">
+        <v>797</v>
+      </c>
+      <c r="C4" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>610</v>
+      </c>
+    </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C6" s="5"/>
+      <c r="A6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C7" s="5"/>
+      <c r="A7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" t="s">
+        <v>885</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C8" s="5"/>
+      <c r="A8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" t="s">
+        <v>937</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C9" s="5"/>
+      <c r="A9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" t="s">
+        <v>615</v>
+      </c>
+      <c r="C9" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C10" s="5"/>
+      <c r="A10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" t="s">
+        <v>615</v>
+      </c>
+      <c r="C10" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B11" t="s">
+        <v>816</v>
+      </c>
+      <c r="C11" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" t="s">
+        <v>757</v>
+      </c>
+      <c r="C12" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" t="s">
+        <v>900</v>
+      </c>
+      <c r="C13" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" t="s">
+        <v>876</v>
+      </c>
+      <c r="C14" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" t="s">
+        <v>752</v>
+      </c>
+      <c r="C15" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" t="s">
+        <v>627</v>
+      </c>
+      <c r="C16" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" t="s">
+        <v>602</v>
+      </c>
+      <c r="C17" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>220</v>
+      </c>
+      <c r="B18" t="s">
+        <v>510</v>
+      </c>
+      <c r="C18" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" t="s">
+        <v>640</v>
+      </c>
+      <c r="C19" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B20" t="s">
+        <v>823</v>
+      </c>
+      <c r="C20" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" t="s">
+        <v>823</v>
+      </c>
+      <c r="C21" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" t="s">
+        <v>823</v>
+      </c>
+      <c r="C22" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>230</v>
+      </c>
+      <c r="B23" t="s">
+        <v>823</v>
+      </c>
+      <c r="C23" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B24" t="s">
+        <v>823</v>
+      </c>
+      <c r="C24" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>220</v>
+      </c>
+      <c r="B25" t="s">
+        <v>462</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>220</v>
+      </c>
+      <c r="B26" t="s">
+        <v>762</v>
+      </c>
+      <c r="C26" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>220</v>
+      </c>
+      <c r="B27" t="s">
+        <v>526</v>
+      </c>
+      <c r="C27" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>220</v>
+      </c>
+      <c r="B28" t="s">
+        <v>526</v>
+      </c>
+      <c r="C28" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>220</v>
+      </c>
+      <c r="B29" t="s">
+        <v>526</v>
+      </c>
+      <c r="C29" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>220</v>
+      </c>
+      <c r="B30" t="s">
+        <v>526</v>
+      </c>
+      <c r="C30" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>220</v>
+      </c>
+      <c r="B31" t="s">
+        <v>526</v>
+      </c>
+      <c r="C31" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" t="s">
+        <v>526</v>
+      </c>
+      <c r="C32" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>220</v>
+      </c>
+      <c r="B33" t="s">
+        <v>526</v>
+      </c>
+      <c r="C33" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>220</v>
+      </c>
+      <c r="B34" t="s">
+        <v>526</v>
+      </c>
+      <c r="C34" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>220</v>
+      </c>
+      <c r="B35" t="s">
+        <v>715</v>
+      </c>
+      <c r="C35" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>230</v>
+      </c>
+      <c r="B36" t="s">
+        <v>910</v>
+      </c>
+      <c r="C36" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>230</v>
+      </c>
+      <c r="B37" t="s">
+        <v>771</v>
+      </c>
+      <c r="C37" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" t="s">
+        <v>573</v>
+      </c>
+      <c r="C38" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>220</v>
+      </c>
+      <c r="B39" t="s">
+        <v>632</v>
+      </c>
+      <c r="C39" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>230</v>
+      </c>
+      <c r="B40" t="s">
+        <v>942</v>
+      </c>
+      <c r="C40" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>230</v>
+      </c>
+      <c r="B41" t="s">
+        <v>964</v>
+      </c>
+      <c r="C41" t="s">
+        <v>964</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -61825,7 +62243,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -61853,855 +62271,871 @@
     </row>
     <row r="2" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B2" t="s">
-        <v>1944</v>
+        <v>2022</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1943</v>
+        <v>2023</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1945</v>
+        <v>2021</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="B3" t="s">
-        <v>1938</v>
+        <v>1944</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1937</v>
+        <v>1945</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B4" t="s">
-        <v>1885</v>
+        <v>1938</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1887</v>
+        <v>1939</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1886</v>
+        <v>1937</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="B5" t="s">
-        <v>1766</v>
+        <v>1885</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1765</v>
+        <v>1887</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1767</v>
+        <v>1886</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>1766</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>5</v>
+        <v>1765</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>6</v>
+        <v>1767</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
-        <v>46185</v>
+        <v>46192</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
-        <v>46129</v>
+        <v>46136</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
-        <v>46115</v>
+        <v>46129</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
-        <v>46094</v>
+        <v>46115</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
-        <v>46052</v>
+        <v>46059</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
+        <v>46045</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="9">
         <v>46038</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C26" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="9">
-        <v>46031</v>
-      </c>
-      <c r="B26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
+        <v>46031</v>
+      </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="9">
         <v>46024</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C28" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D28" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="9">
-        <v>46017</v>
-      </c>
-      <c r="B28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
+        <v>46017</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
         <v>46010</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>71</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D30" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9">
-        <v>46003</v>
-      </c>
-      <c r="B30" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G31" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
-        <v>45989</v>
+        <v>45996</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G33" s="6"/>
     </row>
     <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
-        <v>45975</v>
+        <v>45982</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G35" s="6"/>
     </row>
     <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
+        <v>45968</v>
+      </c>
+      <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
         <v>45961</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>90</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C37" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9">
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
         <v>45954</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>93</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C38" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D38" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="9">
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
         <v>45947</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>96</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C39" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="9">
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="9">
         <v>45940</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C40" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9">
-        <v>45933</v>
-      </c>
-      <c r="B40" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="G40" s="6"/>
     </row>
     <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
+        <v>45933</v>
+      </c>
+      <c r="B41" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="9">
         <v>45926</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>105</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C42" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D42" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G41" s="6"/>
-    </row>
-    <row r="42" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9">
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="9">
         <v>45919</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C43" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D43" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="9">
-        <v>45912</v>
-      </c>
-      <c r="B43" t="s">
-        <v>111</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="G43" s="6"/>
     </row>
     <row r="44" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
+        <v>45912</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="9">
         <v>45905</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C45" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="45" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="9">
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="9">
         <v>45898</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>117</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C46" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G45" s="6"/>
-    </row>
-    <row r="46" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="9">
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9">
         <v>45891</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>120</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D47" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G46" s="6"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="9">
+      <c r="G47" s="6"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="9">
         <v>45884</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>123</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>123</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D48" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="G47" s="6"/>
-    </row>
-    <row r="48" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="9">
-        <v>45877</v>
-      </c>
-      <c r="B48" t="s">
-        <v>125</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="G48" s="6"/>
     </row>
     <row r="49" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
+        <v>45877</v>
+      </c>
+      <c r="B49" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G49" s="6"/>
+    </row>
+    <row r="50" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="9">
         <v>45870</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>128</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C50" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D50" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="G49" s="6"/>
-    </row>
-    <row r="50" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="9">
-        <v>45863</v>
-      </c>
-      <c r="B50" t="s">
-        <v>131</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="G50" s="6"/>
     </row>
     <row r="51" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="B51" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G51" s="6"/>
     </row>
     <row r="52" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="B52" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G52" s="6"/>
     </row>
     <row r="53" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="B53" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G53" s="6"/>
     </row>
     <row r="54" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
+        <v>45842</v>
+      </c>
+      <c r="B54" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G54" s="6"/>
+    </row>
+    <row r="55" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="9">
         <v>45835</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
         <v>143</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C55" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D55" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G54" s="6"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C55" s="8"/>
+      <c r="G55" s="6"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C56" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="D7" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="D8" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="D9" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
-    <hyperlink ref="D10" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
-    <hyperlink ref="D11" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
-    <hyperlink ref="D12" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
-    <hyperlink ref="D14" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
-    <hyperlink ref="D16" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
-    <hyperlink ref="D17" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
-    <hyperlink ref="D18" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
-    <hyperlink ref="D19" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
-    <hyperlink ref="D20" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
-    <hyperlink ref="D21" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
-    <hyperlink ref="D22" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
-    <hyperlink ref="D23" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
-    <hyperlink ref="D24" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
-    <hyperlink ref="D25" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
-    <hyperlink ref="D26" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
-    <hyperlink ref="D27" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
-    <hyperlink ref="D28" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
-    <hyperlink ref="D29" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
-    <hyperlink ref="D30" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
-    <hyperlink ref="D31" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
-    <hyperlink ref="D32" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
-    <hyperlink ref="D33" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
-    <hyperlink ref="D34" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
-    <hyperlink ref="D35" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
-    <hyperlink ref="D36" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
-    <hyperlink ref="D37" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
-    <hyperlink ref="D38" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
-    <hyperlink ref="D39" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
-    <hyperlink ref="D40" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
-    <hyperlink ref="D41" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
-    <hyperlink ref="D42" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
-    <hyperlink ref="D43" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
-    <hyperlink ref="D44" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
-    <hyperlink ref="D45" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
-    <hyperlink ref="D46" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
-    <hyperlink ref="D47" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
-    <hyperlink ref="D48" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
-    <hyperlink ref="D49" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
-    <hyperlink ref="D50" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
-    <hyperlink ref="D51" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
-    <hyperlink ref="D52" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
-    <hyperlink ref="D53" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
-    <hyperlink ref="D54" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
-    <hyperlink ref="D6" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
-    <hyperlink ref="D5" r:id="rId49" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
-    <hyperlink ref="D4" r:id="rId50" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
-    <hyperlink ref="D3" r:id="rId51" xr:uid="{8E240BDD-02FF-CA47-B5D9-FD7E9FCA5AEA}"/>
+    <hyperlink ref="D8" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="D9" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="D10" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="D11" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="D12" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="D13" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="D15" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="D17" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
+    <hyperlink ref="D18" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
+    <hyperlink ref="D19" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
+    <hyperlink ref="D20" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
+    <hyperlink ref="D21" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
+    <hyperlink ref="D22" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
+    <hyperlink ref="D23" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
+    <hyperlink ref="D24" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
+    <hyperlink ref="D25" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
+    <hyperlink ref="D26" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
+    <hyperlink ref="D27" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
+    <hyperlink ref="D28" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
+    <hyperlink ref="D29" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
+    <hyperlink ref="D30" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
+    <hyperlink ref="D31" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
+    <hyperlink ref="D32" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
+    <hyperlink ref="D33" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
+    <hyperlink ref="D34" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
+    <hyperlink ref="D35" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
+    <hyperlink ref="D36" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
+    <hyperlink ref="D37" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
+    <hyperlink ref="D38" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
+    <hyperlink ref="D39" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
+    <hyperlink ref="D40" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
+    <hyperlink ref="D41" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
+    <hyperlink ref="D42" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
+    <hyperlink ref="D43" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
+    <hyperlink ref="D44" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
+    <hyperlink ref="D45" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
+    <hyperlink ref="D46" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
+    <hyperlink ref="D47" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
+    <hyperlink ref="D48" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
+    <hyperlink ref="D49" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
+    <hyperlink ref="D50" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
+    <hyperlink ref="D51" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
+    <hyperlink ref="D52" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
+    <hyperlink ref="D53" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
+    <hyperlink ref="D54" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
+    <hyperlink ref="D55" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
+    <hyperlink ref="D7" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
+    <hyperlink ref="D6" r:id="rId49" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
+    <hyperlink ref="D5" r:id="rId50" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
+    <hyperlink ref="D4" r:id="rId51" xr:uid="{8E240BDD-02FF-CA47-B5D9-FD7E9FCA5AEA}"/>
+    <hyperlink ref="D3" r:id="rId52" xr:uid="{77C8CFB5-83B9-D448-AFCE-DD617D9A359D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017227C9-EB0F-494B-9D5B-815D7D7034A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD96B3D-0BD5-3343-976C-23B997B5F4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31520" yWindow="1560" windowWidth="29580" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31520" yWindow="1560" windowWidth="29560" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -41,6 +41,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Lyrics!$A$1:$H$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Memory!$A$1:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Memory (2)'!$A$1:$E$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TKURadio!$A$1:$M$86</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3956" uniqueCount="2430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3901" uniqueCount="2486">
   <si>
     <t>date</t>
   </si>
@@ -7022,6 +7023,15 @@
   </si>
   <si>
     <t>3D</t>
+  </si>
+  <si>
+    <t>3D (Instrumental)</t>
+  </si>
+  <si>
+    <t>3D (Slowed Down)</t>
+  </si>
+  <si>
+    <t>3D (Sped Up)</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=GGlFJYH1wsQ</t>
@@ -11926,9 +11936,6 @@
     <t>20 min</t>
   </si>
   <si>
-    <t>egg_toastie.png</t>
-  </si>
-  <si>
     <t>bulguri_ramen.png</t>
   </si>
   <si>
@@ -11977,18 +11984,12 @@
     <t>Jungkook explained that pasta cooked only in plain water does not absorb enough seasoning. He intentionally keeps the sauce less salty because the pasta water already contains salt.&lt;br&gt;He focused on getting the sauce consistency right before combining it with the pasta.</t>
   </si>
   <si>
-    <t>3D (ft. Jack Harlow)</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=mHNCM-YALSA</t>
   </si>
   <si>
     <t>mHNCM-YALSA</t>
   </si>
   <si>
-    <t>GOLDEN_HOUR</t>
-  </si>
-  <si>
     <t>Official MV</t>
   </si>
   <si>
@@ -12001,9 +12002,6 @@
     <t>Z3x9i7njCCo</t>
   </si>
   <si>
-    <t>Live Performance</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=XpDEEnZQxNU</t>
   </si>
   <si>
@@ -12043,18 +12041,6 @@
     <t>album</t>
   </si>
   <si>
-    <t>era</t>
-  </si>
-  <si>
-    <t>channel</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>version_type</t>
-  </si>
-  <si>
     <t>cover_image</t>
   </si>
   <si>
@@ -12115,9 +12101,6 @@
     <t>B-side</t>
   </si>
   <si>
-    <t>Seven (ft. Latto)</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=QU9c0053UAU</t>
   </si>
   <si>
@@ -12139,18 +12122,12 @@
     <t>_v3r20mr_B0</t>
   </si>
   <si>
-    <t>Seven - Island Mix Visualizer</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=BlVSe_5cbFE</t>
   </si>
   <si>
     <t>BlVSe_5cbFE</t>
   </si>
   <si>
-    <t>Seven Remix</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=lu8dy2MPWCI</t>
   </si>
   <si>
@@ -12181,9 +12158,6 @@
     <t>GMHu94pRLmY</t>
   </si>
   <si>
-    <t>Seven - David Guetta Remix Extended</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=o6Q-PC7dRaE</t>
   </si>
   <si>
@@ -12211,9 +12185,6 @@
     <t>nlkQE38k-UY</t>
   </si>
   <si>
-    <t>Standing Next to You Remix</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=8AZmf23NgZ0</t>
   </si>
   <si>
@@ -12286,15 +12257,6 @@
     <t>J_n4Ysi5iUM</t>
   </si>
   <si>
-    <t>Solo</t>
-  </si>
-  <si>
-    <t>NEVER_LET_GO</t>
-  </si>
-  <si>
-    <t>Birthday/Fan Song</t>
-  </si>
-  <si>
     <t>/static/images/songs/never_let_go.jpg</t>
   </si>
   <si>
@@ -12304,12 +12266,6 @@
     <t>m5_J7xuYxzs</t>
   </si>
   <si>
-    <t>BTS Era</t>
-  </si>
-  <si>
-    <t>PURPLE_UNIVERSE</t>
-  </si>
-  <si>
     <t>Solo Track</t>
   </si>
   <si>
@@ -12379,12 +12335,6 @@
     <t>IwzkfMmNMpM</t>
   </si>
   <si>
-    <t>DREAMERS_SPECIAL</t>
-  </si>
-  <si>
-    <t>World Cup Song</t>
-  </si>
-  <si>
     <t>/static/images/songs/dreamers.jpg</t>
   </si>
   <si>
@@ -12415,9 +12365,6 @@
     <t>62peQdQv4uo</t>
   </si>
   <si>
-    <t>FRIENDS_ZONE</t>
-  </si>
-  <si>
     <t>/static/images/songs/friends.jpg</t>
   </si>
   <si>
@@ -12436,9 +12383,6 @@
     <t>Xh0YXPrIyFk</t>
   </si>
   <si>
-    <t>wherever u r Remix</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=qJa6xrcCLII</t>
   </si>
   <si>
@@ -12460,9 +12404,6 @@
     <t>yTsINmrAK4I</t>
   </si>
   <si>
-    <t>LAYOVER_LOUNGE</t>
-  </si>
-  <si>
     <t>/static/images/songs/layover.jpg</t>
   </si>
   <si>
@@ -12523,9 +12464,6 @@
     <t>lj8TV9q59P4</t>
   </si>
   <si>
-    <t>WINTER_SPECIAL</t>
-  </si>
-  <si>
     <t>/static/images/songs/christmas_tree.jpg</t>
   </si>
   <si>
@@ -12601,9 +12539,6 @@
     <t>/static/images/songs/hwarang.jpg</t>
   </si>
   <si>
-    <t>It's Definitely You Instrumental</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=kDv1T0bnLwU</t>
   </si>
   <si>
@@ -12616,12 +12551,6 @@
     <t>9a87uoVqTrs</t>
   </si>
   <si>
-    <t>Slow Dancing Remix</t>
-  </si>
-  <si>
-    <t>Slow Dancing (CC Remix)</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=JRrx_Y0RMys</t>
   </si>
   <si>
@@ -12637,9 +12566,6 @@
     <t>/static/images/songs/white_christmas.jpg</t>
   </si>
   <si>
-    <t>White Christmas (with V of BTS) Audio</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=e3AN0-t_uQU</t>
   </si>
   <si>
@@ -12670,12 +12596,6 @@
     <t>HAWYOuMGkK0</t>
   </si>
   <si>
-    <t>Winter Ahead (with Park Hyoshin)</t>
-  </si>
-  <si>
-    <t>WINTER_AHEAD</t>
-  </si>
-  <si>
     <t>/static/images/songs/winter_ahead.jpg</t>
   </si>
   <si>
@@ -12685,9 +12605,6 @@
     <t>J-fQEhHAorE</t>
   </si>
   <si>
-    <t>Trio Version</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=dCZj7X8MooE</t>
   </si>
   <si>
@@ -12703,9 +12620,6 @@
     <t>4tsn6xlomNI</t>
   </si>
   <si>
-    <t>SWIM (MV)</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=b4iVv91Z6lY</t>
   </si>
   <si>
@@ -12727,9 +12641,6 @@
     <t>h-Y97xErGL8</t>
   </si>
   <si>
-    <t>SWIM (JK Acoustic Lofi Remix)</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=pW4ZWvzxcQk</t>
   </si>
   <si>
@@ -12743,6 +12654,264 @@
   </si>
   <si>
     <t>JRTlsT2L38I</t>
+  </si>
+  <si>
+    <t>https://weverse.io/bts/live/3-215169045</t>
+  </si>
+  <si>
+    <t>media</t>
+  </si>
+  <si>
+    <t>playlist_group</t>
+  </si>
+  <si>
+    <t>play_order</t>
+  </si>
+  <si>
+    <t>track_type</t>
+  </si>
+  <si>
+    <t>3D (BangtanTV Live Performance)</t>
+  </si>
+  <si>
+    <t>Live</t>
+  </si>
+  <si>
+    <t>3D (BangtanTV Choreography)</t>
+  </si>
+  <si>
+    <t>3D (Alternative Version)</t>
+  </si>
+  <si>
+    <t>3D (A.G. Cook Remix Visualizer)</t>
+  </si>
+  <si>
+    <t>A.G. Cook Remix</t>
+  </si>
+  <si>
+    <t>3D (Clean Version Visualizer)</t>
+  </si>
+  <si>
+    <t>Clean Version</t>
+  </si>
+  <si>
+    <t>Justin Timberlake Remix</t>
+  </si>
+  <si>
+    <t>MK Remix</t>
+  </si>
+  <si>
+    <t>Seven (Instrumental)</t>
+  </si>
+  <si>
+    <t>Seven Remixes</t>
+  </si>
+  <si>
+    <t>Seven (Island Mix)</t>
+  </si>
+  <si>
+    <t>Island Mix</t>
+  </si>
+  <si>
+    <t>Seven (Nightfall Mix)</t>
+  </si>
+  <si>
+    <t>Nightfall Mix</t>
+  </si>
+  <si>
+    <t>Seven (Festival Mix)</t>
+  </si>
+  <si>
+    <t>Festival Mix</t>
+  </si>
+  <si>
+    <t>Seven (Lo-Fi Mix)</t>
+  </si>
+  <si>
+    <t>Seven (Summer Mix)</t>
+  </si>
+  <si>
+    <t>Summer Mix</t>
+  </si>
+  <si>
+    <t>Seven (Band Version)</t>
+  </si>
+  <si>
+    <t>David Guetta Remix</t>
+  </si>
+  <si>
+    <t>Seven (David Guetta Extended Remix)</t>
+  </si>
+  <si>
+    <t>David Guetta Extended Remix</t>
+  </si>
+  <si>
+    <t>Standing Next to You (BangtanTV Choreography)</t>
+  </si>
+  <si>
+    <t>Standing Next to You Remixes</t>
+  </si>
+  <si>
+    <t>Slow Jam Remix</t>
+  </si>
+  <si>
+    <t>PBR&amp;B Remix</t>
+  </si>
+  <si>
+    <t>Latin Trap Remix</t>
+  </si>
+  <si>
+    <t>Holiday Remix</t>
+  </si>
+  <si>
+    <t>Future Funk Remix</t>
+  </si>
+  <si>
+    <t>USHER Remix</t>
+  </si>
+  <si>
+    <t>The Kid LAROI, Central Cee &amp; Jung Kook</t>
+  </si>
+  <si>
+    <t>FIFA World Cup 2022</t>
+  </si>
+  <si>
+    <t>Left and Right (feat. Jung Kook)</t>
+  </si>
+  <si>
+    <t>Charlie Puth collaboration</t>
+  </si>
+  <si>
+    <t>wherever u r (feat. V)</t>
+  </si>
+  <si>
+    <t>with UMI</t>
+  </si>
+  <si>
+    <t>wherever u r (Lullaby Remix)</t>
+  </si>
+  <si>
+    <t>wherever u r Remixes</t>
+  </si>
+  <si>
+    <t>V-Ron Mix</t>
+  </si>
+  <si>
+    <t>wherever u r (Instrumental)</t>
+  </si>
+  <si>
+    <t>wherever u r (Meditation Version)</t>
+  </si>
+  <si>
+    <t>Slow Dancing (Piano Version)</t>
+  </si>
+  <si>
+    <t>Duet with Jin</t>
+  </si>
+  <si>
+    <t>It's Definitely You (Instrumental)</t>
+  </si>
+  <si>
+    <t>Slow Dancing Remixes</t>
+  </si>
+  <si>
+    <t>FRNK Remix</t>
+  </si>
+  <si>
+    <t>CC Remix</t>
+  </si>
+  <si>
+    <t>White Christmas (Official MV)</t>
+  </si>
+  <si>
+    <t>with Bing Crosby</t>
+  </si>
+  <si>
+    <t>White Christmas (Audio)</t>
+  </si>
+  <si>
+    <t>White Christmas (Lyric Video)</t>
+  </si>
+  <si>
+    <t>Winter Ahead (Official MV)</t>
+  </si>
+  <si>
+    <t>with Park Hyoshin</t>
+  </si>
+  <si>
+    <t>Winter Ahead (Yunseokcheol Trio Version)</t>
+  </si>
+  <si>
+    <t>Winter Ahead (Cinematic Version)</t>
+  </si>
+  <si>
+    <t>Winter Ahead (Yunseokcheol Trio Visualizer)</t>
+  </si>
+  <si>
+    <t>SWIM (Official MV)</t>
+  </si>
+  <si>
+    <t>SWIM (JK Acoustic Lo-fi Remix)</t>
+  </si>
+  <si>
+    <t>Arirang Remixes</t>
+  </si>
+  <si>
+    <t>Fan Remix</t>
+  </si>
+  <si>
+    <t>Yunseokcheol Trio Version</t>
+  </si>
+  <si>
+    <t>GOLDEN_ALBUM,TKU_LIBRARY,KOOKIE_VIBES</t>
+  </si>
+  <si>
+    <t>LIVE_STAGE,TKU_LIBRARY,KOOKIE_VIBES</t>
+  </si>
+  <si>
+    <t>REMIXES,TKU_LIBRARY,KOOKIE_VIBES</t>
+  </si>
+  <si>
+    <t>INSTRUMENTALS,TKU_LIBRARY,KOOKIE_VIBES</t>
+  </si>
+  <si>
+    <t>KOOKIE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>COLLABS,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>TETE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>COLLABS,TETE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>REMIXES,COLLABS,TETE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>INSTRUMENTALS,COLLABS,TETE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>LAYOVER_ALBUM,TETE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>WINTER_SPECIAL,TETE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>INSTRUMENTALS,WINTER_SPECIAL,TETE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>INSTRUMENTALS,TETE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>REMIXES,TETE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>LIVE_STAGE,COLLABS,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>REMIXES,COLLABS,KOOKIE_VIBES,TKU_LIBRARY</t>
   </si>
 </sst>
 </file>
@@ -13263,51 +13432,52 @@
     <col min="2" max="2" width="33.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="7" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1" t="s">
         <v>2192</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2193</v>
       </c>
       <c r="C1" t="s">
         <v>439</v>
       </c>
       <c r="D1" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="E1" t="s">
         <v>198</v>
       </c>
       <c r="F1" t="s">
+        <v>2194</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>2191</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>2402</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2403</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2404</v>
+      </c>
+      <c r="K1" t="s">
         <v>2195</v>
       </c>
-      <c r="G1" t="s">
-        <v>2196</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2197</v>
-      </c>
-      <c r="I1" t="s">
-        <v>2198</v>
-      </c>
-      <c r="J1" t="s">
-        <v>2199</v>
-      </c>
-      <c r="K1" t="s">
-        <v>2200</v>
-      </c>
       <c r="L1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="M1" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -13315,25 +13485,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2174</v>
+        <v>449</v>
       </c>
       <c r="C2" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="D2" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="E2" t="s">
         <v>423</v>
       </c>
       <c r="F2" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>2177</v>
+        <v>2469</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -13353,7 +13523,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>966</v>
+        <v>2405</v>
       </c>
       <c r="C3" t="s">
         <v>2180</v>
@@ -13365,16 +13535,19 @@
         <v>423</v>
       </c>
       <c r="F3" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G3" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>2177</v>
+        <v>2470</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
       </c>
       <c r="J3" t="s">
-        <v>2182</v>
+        <v>2406</v>
       </c>
       <c r="K3" t="s">
         <v>2179</v>
@@ -13388,28 +13561,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>968</v>
+        <v>2407</v>
       </c>
       <c r="C4" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D4" t="s">
         <v>2183</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2184</v>
       </c>
       <c r="E4" t="s">
         <v>423</v>
       </c>
       <c r="F4" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G4" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>2177</v>
+        <v>2470</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>2201</v>
+        <v>2196</v>
       </c>
       <c r="K4" t="s">
         <v>2179</v>
@@ -13423,34 +13599,40 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>970</v>
+        <v>2408</v>
       </c>
       <c r="C5" t="s">
+        <v>2184</v>
+      </c>
+      <c r="D5" t="s">
         <v>2185</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2186</v>
       </c>
       <c r="E5" t="s">
         <v>423</v>
       </c>
       <c r="F5" t="s">
+        <v>2186</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2471</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
         <v>2187</v>
-      </c>
-      <c r="G5" t="s">
-        <v>2060</v>
-      </c>
-      <c r="H5" t="s">
-        <v>2177</v>
-      </c>
-      <c r="J5" t="s">
-        <v>2188</v>
       </c>
       <c r="K5" t="s">
         <v>2179</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>2327</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -13458,28 +13640,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>972</v>
+        <v>2006</v>
       </c>
       <c r="C6" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D6" t="s">
         <v>2189</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2190</v>
       </c>
       <c r="E6" t="s">
         <v>423</v>
       </c>
       <c r="F6" t="s">
-        <v>2187</v>
-      </c>
-      <c r="G6" t="s">
-        <v>2060</v>
+        <v>2186</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>2177</v>
+        <v>2472</v>
+      </c>
+      <c r="I6">
+        <v>30</v>
       </c>
       <c r="J6" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="K6" t="s">
         <v>2179</v>
@@ -13493,34 +13678,40 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>974</v>
+        <v>2409</v>
       </c>
       <c r="C7" t="s">
-        <v>2202</v>
+        <v>2197</v>
       </c>
       <c r="D7" t="s">
-        <v>2203</v>
+        <v>2198</v>
       </c>
       <c r="E7" t="s">
         <v>423</v>
       </c>
       <c r="F7" t="s">
-        <v>2187</v>
-      </c>
-      <c r="G7" t="s">
-        <v>2060</v>
+        <v>2186</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>2204</v>
+        <v>2199</v>
       </c>
       <c r="K7" t="s">
         <v>2179</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>2410</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -13528,34 +13719,40 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>976</v>
+        <v>2411</v>
       </c>
       <c r="C8" t="s">
-        <v>2205</v>
+        <v>2200</v>
       </c>
       <c r="D8" t="s">
-        <v>2206</v>
+        <v>2201</v>
       </c>
       <c r="E8" t="s">
         <v>423</v>
       </c>
       <c r="F8" t="s">
-        <v>2187</v>
-      </c>
-      <c r="G8" t="s">
-        <v>2060</v>
+        <v>2186</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I8">
+        <v>22</v>
       </c>
       <c r="J8" t="s">
-        <v>2204</v>
+        <v>2199</v>
       </c>
       <c r="K8" t="s">
         <v>2179</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>2412</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -13563,28 +13760,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>978</v>
+        <v>2008</v>
       </c>
       <c r="C9" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="D9" t="s">
-        <v>2208</v>
+        <v>2203</v>
       </c>
       <c r="E9" t="s">
         <v>423</v>
       </c>
       <c r="F9" t="s">
-        <v>2187</v>
-      </c>
-      <c r="G9" t="s">
-        <v>2060</v>
+        <v>2186</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>2209</v>
+        <v>2204</v>
       </c>
       <c r="K9" t="s">
         <v>2179</v>
@@ -13598,28 +13798,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>980</v>
+        <v>2007</v>
       </c>
       <c r="C10" t="s">
-        <v>2210</v>
+        <v>2205</v>
       </c>
       <c r="D10" t="s">
-        <v>2211</v>
+        <v>2206</v>
       </c>
       <c r="E10" t="s">
         <v>423</v>
       </c>
       <c r="F10" t="s">
-        <v>2187</v>
-      </c>
-      <c r="G10" t="s">
-        <v>2060</v>
+        <v>2186</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I10">
+        <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>2212</v>
+        <v>2207</v>
       </c>
       <c r="K10" t="s">
         <v>2179</v>
@@ -13636,31 +13839,37 @@
         <v>492</v>
       </c>
       <c r="C11" t="s">
-        <v>2213</v>
+        <v>2208</v>
       </c>
       <c r="D11" t="s">
-        <v>2214</v>
+        <v>2209</v>
       </c>
       <c r="E11" t="s">
         <v>423</v>
       </c>
       <c r="F11" t="s">
+        <v>2186</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
+        <v>2471</v>
+      </c>
+      <c r="I11">
+        <v>25</v>
+      </c>
+      <c r="J11" t="s">
         <v>2187</v>
-      </c>
-      <c r="G11" t="s">
-        <v>2060</v>
-      </c>
-      <c r="H11" t="s">
-        <v>2177</v>
-      </c>
-      <c r="J11" t="s">
-        <v>2188</v>
       </c>
       <c r="K11" t="s">
         <v>2179</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>2413</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
@@ -13671,31 +13880,37 @@
         <v>983</v>
       </c>
       <c r="C12" t="s">
-        <v>2215</v>
+        <v>2210</v>
       </c>
       <c r="D12" t="s">
-        <v>2216</v>
+        <v>2211</v>
       </c>
       <c r="E12" t="s">
         <v>423</v>
       </c>
       <c r="F12" t="s">
+        <v>2186</v>
+      </c>
+      <c r="G12">
+        <v>11</v>
+      </c>
+      <c r="H12" t="s">
+        <v>2471</v>
+      </c>
+      <c r="I12">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
         <v>2187</v>
-      </c>
-      <c r="G12" t="s">
-        <v>2060</v>
-      </c>
-      <c r="H12" t="s">
-        <v>2177</v>
-      </c>
-      <c r="J12" t="s">
-        <v>2188</v>
       </c>
       <c r="K12" t="s">
         <v>2179</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -13706,25 +13921,28 @@
         <v>516</v>
       </c>
       <c r="C13" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D13" t="s">
-        <v>2218</v>
+        <v>2213</v>
       </c>
       <c r="E13" t="s">
         <v>423</v>
       </c>
       <c r="F13" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G13" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G13">
+        <v>12</v>
       </c>
       <c r="H13" t="s">
-        <v>2177</v>
+        <v>2469</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
       </c>
       <c r="J13" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="K13" t="s">
         <v>2179</v>
@@ -13738,25 +13956,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>2220</v>
+        <v>626</v>
       </c>
       <c r="C14" t="s">
-        <v>2221</v>
+        <v>2215</v>
       </c>
       <c r="D14" t="s">
-        <v>2222</v>
+        <v>2216</v>
       </c>
       <c r="E14" t="s">
         <v>423</v>
       </c>
       <c r="F14" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G14" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G14">
+        <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>2177</v>
+        <v>2469</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -13779,25 +13997,28 @@
         <v>987</v>
       </c>
       <c r="C15" t="s">
-        <v>2223</v>
+        <v>2217</v>
       </c>
       <c r="D15" t="s">
-        <v>2224</v>
+        <v>2218</v>
       </c>
       <c r="E15" t="s">
         <v>423</v>
       </c>
       <c r="F15" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G15" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G15">
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>2177</v>
+        <v>2470</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
       </c>
       <c r="J15" t="s">
-        <v>2225</v>
+        <v>2219</v>
       </c>
       <c r="K15" t="s">
         <v>2179</v>
@@ -13811,28 +14032,31 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>989</v>
+        <v>2415</v>
       </c>
       <c r="C16" t="s">
-        <v>2226</v>
+        <v>2220</v>
       </c>
       <c r="D16" t="s">
-        <v>2227</v>
+        <v>2221</v>
       </c>
       <c r="E16" t="s">
         <v>423</v>
       </c>
       <c r="F16" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G16" t="s">
-        <v>2060</v>
+        <v>2416</v>
+      </c>
+      <c r="G16">
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>2177</v>
+        <v>2472</v>
+      </c>
+      <c r="I16">
+        <v>30</v>
       </c>
       <c r="J16" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="K16" t="s">
         <v>2179</v>
@@ -13841,33 +14065,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>2228</v>
+        <v>2417</v>
       </c>
       <c r="C17" t="s">
-        <v>2229</v>
+        <v>2222</v>
       </c>
       <c r="D17" t="s">
-        <v>2230</v>
+        <v>2223</v>
       </c>
       <c r="E17" t="s">
         <v>423</v>
       </c>
       <c r="F17" t="s">
-        <v>2231</v>
-      </c>
-      <c r="G17" t="s">
-        <v>2060</v>
+        <v>2416</v>
+      </c>
+      <c r="G17">
+        <v>16</v>
       </c>
       <c r="H17" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I17">
+        <v>20</v>
       </c>
       <c r="J17" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K17" t="s">
         <v>2179</v>
@@ -13875,34 +14102,40 @@
       <c r="L17" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M17" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>993</v>
+        <v>2419</v>
       </c>
       <c r="C18" t="s">
-        <v>2232</v>
+        <v>2224</v>
       </c>
       <c r="D18" t="s">
-        <v>2233</v>
+        <v>2225</v>
       </c>
       <c r="E18" t="s">
         <v>423</v>
       </c>
       <c r="F18" t="s">
-        <v>2231</v>
-      </c>
-      <c r="G18" t="s">
-        <v>2060</v>
+        <v>2416</v>
+      </c>
+      <c r="G18">
+        <v>17</v>
       </c>
       <c r="H18" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I18">
+        <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K18" t="s">
         <v>2179</v>
@@ -13910,34 +14143,40 @@
       <c r="L18" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M18" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>995</v>
+        <v>2421</v>
       </c>
       <c r="C19" t="s">
-        <v>2232</v>
+        <v>2224</v>
       </c>
       <c r="D19" t="s">
-        <v>2233</v>
+        <v>2225</v>
       </c>
       <c r="E19" t="s">
         <v>423</v>
       </c>
       <c r="F19" t="s">
-        <v>2231</v>
-      </c>
-      <c r="G19" t="s">
-        <v>2060</v>
+        <v>2416</v>
+      </c>
+      <c r="G19">
+        <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I19">
+        <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K19" t="s">
         <v>2179</v>
@@ -13945,34 +14184,40 @@
       <c r="L19" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M19" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>997</v>
+        <v>2423</v>
       </c>
       <c r="C20" t="s">
-        <v>2234</v>
+        <v>2226</v>
       </c>
       <c r="D20" t="s">
-        <v>2235</v>
+        <v>2227</v>
       </c>
       <c r="E20" t="s">
         <v>423</v>
       </c>
       <c r="F20" t="s">
-        <v>2231</v>
-      </c>
-      <c r="G20" t="s">
-        <v>2060</v>
+        <v>2416</v>
+      </c>
+      <c r="G20">
+        <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I20">
+        <v>23</v>
       </c>
       <c r="J20" t="s">
-        <v>2236</v>
+        <v>2228</v>
       </c>
       <c r="K20" t="s">
         <v>2179</v>
@@ -13981,33 +14226,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>999</v>
+        <v>2424</v>
       </c>
       <c r="C21" t="s">
-        <v>2237</v>
+        <v>2229</v>
       </c>
       <c r="D21" t="s">
-        <v>2238</v>
+        <v>2230</v>
       </c>
       <c r="E21" t="s">
         <v>423</v>
       </c>
       <c r="F21" t="s">
-        <v>2231</v>
-      </c>
-      <c r="G21" t="s">
-        <v>2060</v>
+        <v>2416</v>
+      </c>
+      <c r="G21">
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I21">
+        <v>24</v>
       </c>
       <c r="J21" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K21" t="s">
         <v>2179</v>
@@ -14015,34 +14263,40 @@
       <c r="L21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M21" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>1001</v>
+        <v>2426</v>
       </c>
       <c r="C22" t="s">
-        <v>2237</v>
+        <v>2229</v>
       </c>
       <c r="D22" t="s">
-        <v>2238</v>
+        <v>2230</v>
       </c>
       <c r="E22" t="s">
         <v>423</v>
       </c>
       <c r="F22" t="s">
+        <v>2416</v>
+      </c>
+      <c r="G22">
+        <v>21</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2471</v>
+      </c>
+      <c r="I22">
+        <v>25</v>
+      </c>
+      <c r="J22" t="s">
         <v>2231</v>
-      </c>
-      <c r="G22" t="s">
-        <v>2060</v>
-      </c>
-      <c r="H22" t="s">
-        <v>2177</v>
-      </c>
-      <c r="J22" t="s">
-        <v>2239</v>
       </c>
       <c r="K22" t="s">
         <v>2179</v>
@@ -14051,33 +14305,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>1002</v>
+        <v>656</v>
       </c>
       <c r="C23" t="s">
-        <v>2240</v>
+        <v>2232</v>
       </c>
       <c r="D23" t="s">
-        <v>2241</v>
+        <v>2233</v>
       </c>
       <c r="E23" t="s">
         <v>423</v>
       </c>
       <c r="F23" t="s">
-        <v>2231</v>
-      </c>
-      <c r="G23" t="s">
-        <v>2060</v>
+        <v>2416</v>
+      </c>
+      <c r="G23">
+        <v>22</v>
       </c>
       <c r="H23" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I23">
+        <v>26</v>
       </c>
       <c r="J23" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K23" t="s">
         <v>2179</v>
@@ -14085,34 +14342,40 @@
       <c r="L23" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M23" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>2242</v>
+        <v>2428</v>
       </c>
       <c r="C24" t="s">
-        <v>2243</v>
+        <v>2234</v>
       </c>
       <c r="D24" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="E24" t="s">
         <v>423</v>
       </c>
       <c r="F24" t="s">
-        <v>2231</v>
-      </c>
-      <c r="G24" t="s">
-        <v>2060</v>
+        <v>2416</v>
+      </c>
+      <c r="G24">
+        <v>23</v>
       </c>
       <c r="H24" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I24">
+        <v>27</v>
       </c>
       <c r="J24" t="s">
-        <v>2245</v>
+        <v>2236</v>
       </c>
       <c r="K24" t="s">
         <v>2179</v>
@@ -14120,8 +14383,11 @@
       <c r="L24" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M24" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -14129,22 +14395,22 @@
         <v>544</v>
       </c>
       <c r="C25" t="s">
-        <v>2246</v>
+        <v>2237</v>
       </c>
       <c r="D25" t="s">
-        <v>2247</v>
+        <v>2238</v>
       </c>
       <c r="E25" t="s">
         <v>423</v>
       </c>
       <c r="F25" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G25" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G25">
+        <v>24</v>
       </c>
       <c r="H25" t="s">
-        <v>2177</v>
+        <v>2469</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -14159,33 +14425,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>1006</v>
+        <v>2430</v>
       </c>
       <c r="C26" t="s">
-        <v>2248</v>
+        <v>2239</v>
       </c>
       <c r="D26" t="s">
-        <v>2249</v>
+        <v>2240</v>
       </c>
       <c r="E26" t="s">
         <v>423</v>
       </c>
       <c r="F26" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G26" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>2177</v>
+        <v>2470</v>
+      </c>
+      <c r="I26">
+        <v>5</v>
       </c>
       <c r="J26" t="s">
-        <v>2201</v>
+        <v>2196</v>
       </c>
       <c r="K26" t="s">
         <v>2179</v>
@@ -14194,33 +14463,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>1008</v>
+        <v>717</v>
       </c>
       <c r="C27" t="s">
-        <v>2250</v>
+        <v>2241</v>
       </c>
       <c r="D27" t="s">
-        <v>2251</v>
+        <v>2242</v>
       </c>
       <c r="E27" t="s">
         <v>423</v>
       </c>
       <c r="F27" t="s">
-        <v>2252</v>
-      </c>
-      <c r="G27" t="s">
-        <v>2060</v>
+        <v>2431</v>
+      </c>
+      <c r="G27">
+        <v>26</v>
       </c>
       <c r="H27" t="s">
-        <v>2177</v>
+        <v>2472</v>
+      </c>
+      <c r="I27">
+        <v>30</v>
       </c>
       <c r="J27" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="K27" t="s">
         <v>2179</v>
@@ -14229,33 +14501,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>1010</v>
+        <v>728</v>
       </c>
       <c r="C28" t="s">
-        <v>2253</v>
+        <v>2243</v>
       </c>
       <c r="D28" t="s">
-        <v>2254</v>
+        <v>2244</v>
       </c>
       <c r="E28" t="s">
         <v>423</v>
       </c>
       <c r="F28" t="s">
-        <v>2252</v>
-      </c>
-      <c r="G28" t="s">
-        <v>2060</v>
+        <v>2431</v>
+      </c>
+      <c r="G28">
+        <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I28">
+        <v>20</v>
       </c>
       <c r="J28" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K28" t="s">
         <v>2179</v>
@@ -14263,34 +14538,40 @@
       <c r="L28" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M28" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>1012</v>
+        <v>725</v>
       </c>
       <c r="C29" t="s">
-        <v>2253</v>
+        <v>2243</v>
       </c>
       <c r="D29" t="s">
-        <v>2254</v>
+        <v>2244</v>
       </c>
       <c r="E29" t="s">
         <v>423</v>
       </c>
       <c r="F29" t="s">
-        <v>2252</v>
-      </c>
-      <c r="G29" t="s">
-        <v>2060</v>
+        <v>2431</v>
+      </c>
+      <c r="G29">
+        <v>28</v>
       </c>
       <c r="H29" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I29">
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K29" t="s">
         <v>2179</v>
@@ -14298,34 +14579,40 @@
       <c r="L29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M29" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>1013</v>
+        <v>721</v>
       </c>
       <c r="C30" t="s">
-        <v>2255</v>
+        <v>2245</v>
       </c>
       <c r="D30" t="s">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="E30" t="s">
         <v>423</v>
       </c>
       <c r="F30" t="s">
-        <v>2252</v>
-      </c>
-      <c r="G30" t="s">
-        <v>2060</v>
+        <v>2431</v>
+      </c>
+      <c r="G30">
+        <v>29</v>
       </c>
       <c r="H30" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I30">
+        <v>22</v>
       </c>
       <c r="J30" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K30" t="s">
         <v>2179</v>
@@ -14333,34 +14620,40 @@
       <c r="L30" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M30" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>1015</v>
+        <v>713</v>
       </c>
       <c r="C31" t="s">
-        <v>2257</v>
+        <v>2247</v>
       </c>
       <c r="D31" t="s">
-        <v>2258</v>
+        <v>2248</v>
       </c>
       <c r="E31" t="s">
         <v>423</v>
       </c>
       <c r="F31" t="s">
-        <v>2252</v>
-      </c>
-      <c r="G31" t="s">
-        <v>2060</v>
+        <v>2431</v>
+      </c>
+      <c r="G31">
+        <v>30</v>
       </c>
       <c r="H31" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I31">
+        <v>23</v>
       </c>
       <c r="J31" t="s">
-        <v>2259</v>
+        <v>2249</v>
       </c>
       <c r="K31" t="s">
         <v>2179</v>
@@ -14368,34 +14661,40 @@
       <c r="L31" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M31" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>1017</v>
+        <v>709</v>
       </c>
       <c r="C32" t="s">
-        <v>2260</v>
+        <v>2250</v>
       </c>
       <c r="D32" t="s">
-        <v>2261</v>
+        <v>2251</v>
       </c>
       <c r="E32" t="s">
         <v>423</v>
       </c>
       <c r="F32" t="s">
-        <v>2252</v>
-      </c>
-      <c r="G32" t="s">
-        <v>2060</v>
+        <v>2431</v>
+      </c>
+      <c r="G32">
+        <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I32">
+        <v>24</v>
       </c>
       <c r="J32" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K32" t="s">
         <v>2179</v>
@@ -14403,8 +14702,11 @@
       <c r="L32" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M32" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -14412,25 +14714,28 @@
         <v>733</v>
       </c>
       <c r="C33" t="s">
-        <v>2262</v>
+        <v>2252</v>
       </c>
       <c r="D33" t="s">
-        <v>2263</v>
+        <v>2253</v>
       </c>
       <c r="E33" t="s">
         <v>423</v>
       </c>
       <c r="F33" t="s">
-        <v>2252</v>
-      </c>
-      <c r="G33" t="s">
-        <v>2060</v>
+        <v>2431</v>
+      </c>
+      <c r="G33">
+        <v>32</v>
       </c>
       <c r="H33" t="s">
-        <v>2177</v>
+        <v>2471</v>
+      </c>
+      <c r="I33">
+        <v>25</v>
       </c>
       <c r="J33" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K33" t="s">
         <v>2179</v>
@@ -14438,8 +14743,11 @@
       <c r="L33" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M33" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -14447,25 +14755,28 @@
         <v>555</v>
       </c>
       <c r="C34" t="s">
-        <v>2264</v>
+        <v>2254</v>
       </c>
       <c r="D34" t="s">
-        <v>2265</v>
+        <v>2255</v>
       </c>
       <c r="E34" t="s">
         <v>423</v>
       </c>
       <c r="F34" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G34" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G34">
+        <v>33</v>
       </c>
       <c r="H34" t="s">
-        <v>2177</v>
+        <v>2469</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
       </c>
       <c r="J34" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="K34" t="s">
         <v>2179</v>
@@ -14474,7 +14785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -14482,25 +14793,28 @@
         <v>524</v>
       </c>
       <c r="C35" t="s">
-        <v>2266</v>
+        <v>2256</v>
       </c>
       <c r="D35" t="s">
-        <v>2267</v>
+        <v>2257</v>
       </c>
       <c r="E35" t="s">
         <v>423</v>
       </c>
       <c r="F35" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G35" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G35">
+        <v>34</v>
       </c>
       <c r="H35" t="s">
-        <v>2177</v>
+        <v>2469</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
       </c>
       <c r="J35" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="K35" t="s">
         <v>2179</v>
@@ -14509,7 +14823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -14517,25 +14831,28 @@
         <v>520</v>
       </c>
       <c r="C36" t="s">
-        <v>2268</v>
+        <v>2258</v>
       </c>
       <c r="D36" t="s">
-        <v>2269</v>
+        <v>2259</v>
       </c>
       <c r="E36" t="s">
         <v>423</v>
       </c>
       <c r="F36" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G36" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G36">
+        <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>2177</v>
+        <v>2469</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
       </c>
       <c r="J36" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="K36" t="s">
         <v>2179</v>
@@ -14544,7 +14861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -14552,25 +14869,28 @@
         <v>540</v>
       </c>
       <c r="C37" t="s">
-        <v>2270</v>
+        <v>2260</v>
       </c>
       <c r="D37" t="s">
-        <v>2271</v>
+        <v>2261</v>
       </c>
       <c r="E37" t="s">
         <v>423</v>
       </c>
       <c r="F37" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G37" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G37">
+        <v>36</v>
       </c>
       <c r="H37" t="s">
-        <v>2177</v>
+        <v>2469</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
       </c>
       <c r="J37" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="K37" t="s">
         <v>2179</v>
@@ -14579,7 +14899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -14587,25 +14907,28 @@
         <v>551</v>
       </c>
       <c r="C38" t="s">
-        <v>2272</v>
+        <v>2262</v>
       </c>
       <c r="D38" t="s">
-        <v>2273</v>
+        <v>2263</v>
       </c>
       <c r="E38" t="s">
         <v>423</v>
       </c>
       <c r="F38" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G38" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G38">
+        <v>37</v>
       </c>
       <c r="H38" t="s">
-        <v>2177</v>
+        <v>2469</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
       </c>
       <c r="J38" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="K38" t="s">
         <v>2179</v>
@@ -14614,7 +14937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -14622,25 +14945,28 @@
         <v>536</v>
       </c>
       <c r="C39" t="s">
-        <v>2274</v>
+        <v>2264</v>
       </c>
       <c r="D39" t="s">
-        <v>2275</v>
+        <v>2265</v>
       </c>
       <c r="E39" t="s">
         <v>423</v>
       </c>
       <c r="F39" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G39" t="s">
-        <v>2060</v>
+        <v>2063</v>
+      </c>
+      <c r="G39">
+        <v>38</v>
       </c>
       <c r="H39" t="s">
-        <v>2177</v>
+        <v>2469</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
       </c>
       <c r="J39" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="K39" t="s">
         <v>2179</v>
@@ -14649,7 +14975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -14660,7 +14986,7 @@
         <v>621</v>
       </c>
       <c r="D40" t="s">
-        <v>2276</v>
+        <v>2266</v>
       </c>
       <c r="E40" t="s">
         <v>423</v>
@@ -14668,23 +14994,26 @@
       <c r="F40" t="s">
         <v>618</v>
       </c>
-      <c r="G40" t="s">
-        <v>2277</v>
+      <c r="G40">
+        <v>39</v>
       </c>
       <c r="H40" t="s">
-        <v>2278</v>
+        <v>2473</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>2279</v>
+        <v>2299</v>
       </c>
       <c r="K40" t="s">
-        <v>2280</v>
+        <v>2267</v>
       </c>
       <c r="L40" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -14692,10 +15021,10 @@
         <v>752</v>
       </c>
       <c r="C41" t="s">
-        <v>2281</v>
+        <v>2268</v>
       </c>
       <c r="D41" t="s">
-        <v>2282</v>
+        <v>2269</v>
       </c>
       <c r="E41" t="s">
         <v>423</v>
@@ -14703,23 +15032,26 @@
       <c r="F41" t="s">
         <v>916</v>
       </c>
-      <c r="G41" t="s">
-        <v>2283</v>
+      <c r="G41">
+        <v>40</v>
       </c>
       <c r="H41" t="s">
-        <v>2284</v>
+        <v>2473</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>2285</v>
+        <v>2270</v>
       </c>
       <c r="K41" t="s">
-        <v>2286</v>
+        <v>2271</v>
       </c>
       <c r="L41" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -14727,10 +15059,10 @@
         <v>602</v>
       </c>
       <c r="C42" t="s">
-        <v>2287</v>
+        <v>2272</v>
       </c>
       <c r="D42" t="s">
-        <v>2288</v>
+        <v>2273</v>
       </c>
       <c r="E42" t="s">
         <v>423</v>
@@ -14738,23 +15070,26 @@
       <c r="F42" t="s">
         <v>601</v>
       </c>
-      <c r="G42" t="s">
-        <v>2283</v>
+      <c r="G42">
+        <v>41</v>
       </c>
       <c r="H42" t="s">
-        <v>2284</v>
+        <v>2473</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
       </c>
       <c r="J42" t="s">
-        <v>2285</v>
+        <v>2270</v>
       </c>
       <c r="K42" t="s">
-        <v>2289</v>
+        <v>2274</v>
       </c>
       <c r="L42" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -14762,10 +15097,10 @@
         <v>743</v>
       </c>
       <c r="C43" t="s">
-        <v>2290</v>
+        <v>2275</v>
       </c>
       <c r="D43" t="s">
-        <v>2291</v>
+        <v>2276</v>
       </c>
       <c r="E43" t="s">
         <v>423</v>
@@ -14773,23 +15108,26 @@
       <c r="F43" t="s">
         <v>743</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43">
+        <v>42</v>
+      </c>
+      <c r="H43" t="s">
+        <v>2473</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43" t="s">
         <v>2277</v>
       </c>
-      <c r="H43" t="s">
+      <c r="K43" t="s">
         <v>2278</v>
-      </c>
-      <c r="J43" t="s">
-        <v>2292</v>
-      </c>
-      <c r="K43" t="s">
-        <v>2293</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -14797,10 +15135,10 @@
         <v>1028</v>
       </c>
       <c r="C44" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="D44" t="s">
-        <v>2295</v>
+        <v>2280</v>
       </c>
       <c r="E44" t="s">
         <v>423</v>
@@ -14808,23 +15146,26 @@
       <c r="F44" t="s">
         <v>1028</v>
       </c>
-      <c r="G44" t="s">
-        <v>2277</v>
+      <c r="G44">
+        <v>43</v>
       </c>
       <c r="H44" t="s">
-        <v>2284</v>
+        <v>2473</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
       </c>
       <c r="J44" t="s">
-        <v>2296</v>
+        <v>2281</v>
       </c>
       <c r="K44" t="s">
-        <v>2297</v>
+        <v>2282</v>
       </c>
       <c r="L44" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -14832,34 +15173,37 @@
         <v>597</v>
       </c>
       <c r="C45" t="s">
-        <v>2298</v>
+        <v>2283</v>
       </c>
       <c r="D45" t="s">
-        <v>2299</v>
+        <v>2284</v>
       </c>
       <c r="E45" t="s">
         <v>423</v>
       </c>
       <c r="F45" t="s">
-        <v>2300</v>
-      </c>
-      <c r="G45" t="s">
-        <v>2283</v>
+        <v>2285</v>
+      </c>
+      <c r="G45">
+        <v>44</v>
       </c>
       <c r="H45" t="s">
-        <v>2284</v>
+        <v>2473</v>
+      </c>
+      <c r="I45">
+        <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>2285</v>
+        <v>2270</v>
       </c>
       <c r="K45" t="s">
-        <v>2301</v>
+        <v>2286</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -14867,10 +15211,10 @@
         <v>748</v>
       </c>
       <c r="C46" t="s">
-        <v>2302</v>
+        <v>2287</v>
       </c>
       <c r="D46" t="s">
-        <v>2303</v>
+        <v>2288</v>
       </c>
       <c r="E46" t="s">
         <v>423</v>
@@ -14878,23 +15222,29 @@
       <c r="F46" t="s">
         <v>748</v>
       </c>
-      <c r="G46" t="s">
-        <v>2277</v>
+      <c r="G46">
+        <v>45</v>
       </c>
       <c r="H46" t="s">
-        <v>2284</v>
+        <v>2474</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>2304</v>
+        <v>2289</v>
       </c>
       <c r="K46" t="s">
-        <v>2305</v>
+        <v>2290</v>
       </c>
       <c r="L46" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M46" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -14902,10 +15252,10 @@
         <v>498</v>
       </c>
       <c r="C47" t="s">
-        <v>2306</v>
+        <v>2291</v>
       </c>
       <c r="D47" t="s">
-        <v>2307</v>
+        <v>2292</v>
       </c>
       <c r="E47" t="s">
         <v>423</v>
@@ -14913,61 +15263,70 @@
       <c r="F47" t="s">
         <v>498</v>
       </c>
-      <c r="G47" t="s">
-        <v>2277</v>
+      <c r="G47">
+        <v>46</v>
       </c>
       <c r="H47" t="s">
-        <v>2308</v>
+        <v>2474</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="s">
-        <v>2309</v>
+        <v>2178</v>
       </c>
       <c r="K47" t="s">
-        <v>2310</v>
+        <v>2293</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M47" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>566</v>
+        <v>2440</v>
       </c>
       <c r="C48" t="s">
-        <v>2311</v>
+        <v>2294</v>
       </c>
       <c r="D48" t="s">
-        <v>2312</v>
+        <v>2295</v>
       </c>
       <c r="E48" t="s">
         <v>423</v>
       </c>
       <c r="F48" t="s">
-        <v>2062</v>
-      </c>
-      <c r="G48" t="s">
-        <v>2277</v>
+        <v>2065</v>
+      </c>
+      <c r="G48">
+        <v>47</v>
       </c>
       <c r="H48" t="s">
-        <v>2284</v>
+        <v>2474</v>
+      </c>
+      <c r="I48">
+        <v>3</v>
       </c>
       <c r="J48" t="s">
-        <v>2304</v>
+        <v>2289</v>
       </c>
       <c r="K48" t="s">
-        <v>2313</v>
+        <v>2296</v>
       </c>
       <c r="L48" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M48" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -14975,10 +15334,10 @@
         <v>613</v>
       </c>
       <c r="C49" t="s">
-        <v>2314</v>
+        <v>2297</v>
       </c>
       <c r="D49" t="s">
-        <v>2315</v>
+        <v>2298</v>
       </c>
       <c r="E49" t="s">
         <v>423</v>
@@ -14986,23 +15345,26 @@
       <c r="F49" t="s">
         <v>613</v>
       </c>
-      <c r="G49" t="s">
-        <v>2277</v>
+      <c r="G49">
+        <v>48</v>
       </c>
       <c r="H49" t="s">
-        <v>2278</v>
+        <v>2473</v>
+      </c>
+      <c r="I49">
+        <v>3</v>
       </c>
       <c r="J49" t="s">
-        <v>2316</v>
+        <v>2299</v>
       </c>
       <c r="K49" t="s">
-        <v>2317</v>
+        <v>2300</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -15010,10 +15372,10 @@
         <v>757</v>
       </c>
       <c r="C50" t="s">
-        <v>2318</v>
+        <v>2301</v>
       </c>
       <c r="D50" t="s">
-        <v>2319</v>
+        <v>2302</v>
       </c>
       <c r="E50" t="s">
         <v>421</v>
@@ -15021,11 +15383,11 @@
       <c r="F50" t="s">
         <v>757</v>
       </c>
-      <c r="G50" t="s">
-        <v>2277</v>
+      <c r="G50">
+        <v>49</v>
       </c>
       <c r="H50" t="s">
-        <v>2320</v>
+        <v>2475</v>
       </c>
       <c r="I50">
         <v>1</v>
@@ -15034,153 +15396,171 @@
         <v>2178</v>
       </c>
       <c r="K50" t="s">
-        <v>2321</v>
+        <v>2303</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>895</v>
+        <v>2442</v>
       </c>
       <c r="C51" t="s">
-        <v>2322</v>
+        <v>2304</v>
       </c>
       <c r="D51" t="s">
-        <v>2323</v>
+        <v>2305</v>
       </c>
       <c r="E51" t="s">
         <v>421</v>
       </c>
       <c r="F51" t="s">
-        <v>2066</v>
-      </c>
-      <c r="G51" t="s">
-        <v>2277</v>
+        <v>2069</v>
+      </c>
+      <c r="G51">
+        <v>50</v>
       </c>
       <c r="H51" t="s">
-        <v>2320</v>
+        <v>2476</v>
+      </c>
+      <c r="I51">
+        <v>4</v>
       </c>
       <c r="J51" t="s">
-        <v>2304</v>
+        <v>2289</v>
       </c>
       <c r="K51" t="s">
-        <v>2324</v>
+        <v>2306</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M51" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>1033</v>
+        <v>2444</v>
       </c>
       <c r="C52" t="s">
-        <v>2325</v>
+        <v>2307</v>
       </c>
       <c r="D52" t="s">
-        <v>2326</v>
+        <v>2308</v>
       </c>
       <c r="E52" t="s">
         <v>421</v>
       </c>
       <c r="F52" t="s">
-        <v>2327</v>
-      </c>
-      <c r="G52" t="s">
-        <v>2277</v>
+        <v>2445</v>
+      </c>
+      <c r="G52">
+        <v>51</v>
       </c>
       <c r="H52" t="s">
-        <v>2320</v>
+        <v>2477</v>
+      </c>
+      <c r="I52">
+        <v>20</v>
       </c>
       <c r="J52" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K52" t="s">
-        <v>2324</v>
+        <v>2306</v>
       </c>
       <c r="L52" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M52" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>1035</v>
+        <v>2447</v>
       </c>
       <c r="C53" t="s">
-        <v>2328</v>
+        <v>2309</v>
       </c>
       <c r="D53" t="s">
-        <v>2329</v>
+        <v>2310</v>
       </c>
       <c r="E53" t="s">
         <v>421</v>
       </c>
       <c r="F53" t="s">
-        <v>2327</v>
-      </c>
-      <c r="G53" t="s">
-        <v>2277</v>
+        <v>2445</v>
+      </c>
+      <c r="G53">
+        <v>52</v>
       </c>
       <c r="H53" t="s">
-        <v>2320</v>
+        <v>2478</v>
+      </c>
+      <c r="I53">
+        <v>30</v>
       </c>
       <c r="J53" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="K53" t="s">
-        <v>2324</v>
+        <v>2306</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>1037</v>
+        <v>2448</v>
       </c>
       <c r="C54" t="s">
-        <v>2330</v>
+        <v>2311</v>
       </c>
       <c r="D54" t="s">
-        <v>2331</v>
+        <v>2312</v>
       </c>
       <c r="E54" t="s">
         <v>421</v>
       </c>
       <c r="F54" t="s">
-        <v>2327</v>
-      </c>
-      <c r="G54" t="s">
-        <v>2277</v>
+        <v>2445</v>
+      </c>
+      <c r="G54">
+        <v>53</v>
       </c>
       <c r="H54" t="s">
-        <v>2320</v>
+        <v>2477</v>
+      </c>
+      <c r="I54">
+        <v>21</v>
       </c>
       <c r="J54" t="s">
-        <v>2332</v>
+        <v>2313</v>
       </c>
       <c r="K54" t="s">
-        <v>2324</v>
+        <v>2306</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -15188,10 +15568,10 @@
         <v>825</v>
       </c>
       <c r="C55" t="s">
-        <v>2333</v>
+        <v>2314</v>
       </c>
       <c r="D55" t="s">
-        <v>2334</v>
+        <v>2315</v>
       </c>
       <c r="E55" t="s">
         <v>421</v>
@@ -15199,23 +15579,26 @@
       <c r="F55" t="s">
         <v>809</v>
       </c>
-      <c r="G55" t="s">
-        <v>809</v>
+      <c r="G55">
+        <v>54</v>
       </c>
       <c r="H55" t="s">
-        <v>2335</v>
+        <v>2479</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
       </c>
       <c r="J55" t="s">
         <v>2178</v>
       </c>
       <c r="K55" t="s">
-        <v>2336</v>
+        <v>2316</v>
       </c>
       <c r="L55" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -15223,10 +15606,10 @@
         <v>810</v>
       </c>
       <c r="C56" t="s">
-        <v>2337</v>
+        <v>2317</v>
       </c>
       <c r="D56" t="s">
-        <v>2338</v>
+        <v>2318</v>
       </c>
       <c r="E56" t="s">
         <v>421</v>
@@ -15234,23 +15617,26 @@
       <c r="F56" t="s">
         <v>809</v>
       </c>
-      <c r="G56" t="s">
-        <v>809</v>
+      <c r="G56">
+        <v>55</v>
       </c>
       <c r="H56" t="s">
-        <v>2335</v>
+        <v>2479</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
       </c>
       <c r="J56" t="s">
         <v>2178</v>
       </c>
       <c r="K56" t="s">
-        <v>2336</v>
+        <v>2316</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -15258,10 +15644,10 @@
         <v>818</v>
       </c>
       <c r="C57" t="s">
-        <v>2339</v>
+        <v>2319</v>
       </c>
       <c r="D57" t="s">
-        <v>2340</v>
+        <v>2320</v>
       </c>
       <c r="E57" t="s">
         <v>421</v>
@@ -15269,26 +15655,26 @@
       <c r="F57" t="s">
         <v>809</v>
       </c>
-      <c r="G57" t="s">
-        <v>809</v>
+      <c r="G57">
+        <v>56</v>
       </c>
       <c r="H57" t="s">
-        <v>2335</v>
+        <v>2479</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J57" t="s">
         <v>2178</v>
       </c>
       <c r="K57" t="s">
-        <v>2336</v>
+        <v>2316</v>
       </c>
       <c r="L57" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -15296,10 +15682,10 @@
         <v>829</v>
       </c>
       <c r="C58" t="s">
-        <v>2341</v>
+        <v>2321</v>
       </c>
       <c r="D58" t="s">
-        <v>2342</v>
+        <v>2322</v>
       </c>
       <c r="E58" t="s">
         <v>421</v>
@@ -15307,26 +15693,26 @@
       <c r="F58" t="s">
         <v>809</v>
       </c>
-      <c r="G58" t="s">
-        <v>809</v>
+      <c r="G58">
+        <v>57</v>
       </c>
       <c r="H58" t="s">
-        <v>2335</v>
+        <v>2479</v>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J58" t="s">
         <v>2178</v>
       </c>
       <c r="K58" t="s">
-        <v>2336</v>
+        <v>2316</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -15334,10 +15720,10 @@
         <v>814</v>
       </c>
       <c r="C59" t="s">
-        <v>2343</v>
+        <v>2323</v>
       </c>
       <c r="D59" t="s">
-        <v>2344</v>
+        <v>2324</v>
       </c>
       <c r="E59" t="s">
         <v>421</v>
@@ -15345,34 +15731,37 @@
       <c r="F59" t="s">
         <v>809</v>
       </c>
-      <c r="G59" t="s">
-        <v>809</v>
+      <c r="G59">
+        <v>58</v>
       </c>
       <c r="H59" t="s">
-        <v>2335</v>
+        <v>2479</v>
+      </c>
+      <c r="I59">
+        <v>5</v>
       </c>
       <c r="J59" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="K59" t="s">
-        <v>2336</v>
+        <v>2316</v>
       </c>
       <c r="L59" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>836</v>
+        <v>2449</v>
       </c>
       <c r="C60" t="s">
-        <v>2345</v>
+        <v>2325</v>
       </c>
       <c r="D60" t="s">
-        <v>2346</v>
+        <v>2326</v>
       </c>
       <c r="E60" t="s">
         <v>421</v>
@@ -15380,23 +15769,26 @@
       <c r="F60" t="s">
         <v>809</v>
       </c>
-      <c r="G60" t="s">
-        <v>809</v>
+      <c r="G60">
+        <v>59</v>
       </c>
       <c r="H60" t="s">
-        <v>2335</v>
+        <v>2479</v>
+      </c>
+      <c r="I60">
+        <v>6</v>
       </c>
       <c r="J60" t="s">
-        <v>2347</v>
+        <v>2327</v>
       </c>
       <c r="K60" t="s">
-        <v>2336</v>
+        <v>2316</v>
       </c>
       <c r="L60" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -15404,10 +15796,10 @@
         <v>917</v>
       </c>
       <c r="C61" t="s">
-        <v>2348</v>
+        <v>2328</v>
       </c>
       <c r="D61" t="s">
-        <v>2349</v>
+        <v>2329</v>
       </c>
       <c r="E61" t="s">
         <v>421</v>
@@ -15415,23 +15807,26 @@
       <c r="F61" t="s">
         <v>916</v>
       </c>
-      <c r="G61" t="s">
-        <v>2283</v>
+      <c r="G61">
+        <v>60</v>
       </c>
       <c r="H61" t="s">
-        <v>2284</v>
+        <v>2475</v>
+      </c>
+      <c r="I61">
+        <v>5</v>
       </c>
       <c r="J61" t="s">
-        <v>2285</v>
+        <v>2270</v>
       </c>
       <c r="K61" t="s">
-        <v>2286</v>
+        <v>2271</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -15439,34 +15834,37 @@
         <v>846</v>
       </c>
       <c r="C62" t="s">
-        <v>2350</v>
+        <v>2330</v>
       </c>
       <c r="D62" t="s">
-        <v>2351</v>
+        <v>2331</v>
       </c>
       <c r="E62" t="s">
         <v>421</v>
       </c>
       <c r="F62" t="s">
-        <v>2300</v>
-      </c>
-      <c r="G62" t="s">
-        <v>2283</v>
+        <v>2285</v>
+      </c>
+      <c r="G62">
+        <v>61</v>
       </c>
       <c r="H62" t="s">
-        <v>2284</v>
+        <v>2475</v>
+      </c>
+      <c r="I62">
+        <v>6</v>
       </c>
       <c r="J62" t="s">
-        <v>2285</v>
+        <v>2270</v>
       </c>
       <c r="K62" t="s">
-        <v>2301</v>
+        <v>2286</v>
       </c>
       <c r="L62" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -15474,10 +15872,10 @@
         <v>850</v>
       </c>
       <c r="C63" t="s">
-        <v>2352</v>
+        <v>2332</v>
       </c>
       <c r="D63" t="s">
-        <v>2353</v>
+        <v>2333</v>
       </c>
       <c r="E63" t="s">
         <v>421</v>
@@ -15485,23 +15883,26 @@
       <c r="F63" t="s">
         <v>601</v>
       </c>
-      <c r="G63" t="s">
-        <v>2283</v>
+      <c r="G63">
+        <v>62</v>
       </c>
       <c r="H63" t="s">
-        <v>2284</v>
+        <v>2475</v>
+      </c>
+      <c r="I63">
+        <v>7</v>
       </c>
       <c r="J63" t="s">
-        <v>2285</v>
+        <v>2270</v>
       </c>
       <c r="K63" t="s">
-        <v>2289</v>
+        <v>2274</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -15509,69 +15910,75 @@
         <v>856</v>
       </c>
       <c r="C64" t="s">
-        <v>2354</v>
+        <v>2334</v>
       </c>
       <c r="D64" t="s">
-        <v>2355</v>
+        <v>2335</v>
       </c>
       <c r="E64" t="s">
         <v>421</v>
       </c>
       <c r="F64" t="s">
-        <v>2058</v>
-      </c>
-      <c r="G64" t="s">
-        <v>2296</v>
+        <v>2061</v>
+      </c>
+      <c r="G64">
+        <v>63</v>
       </c>
       <c r="H64" t="s">
-        <v>2356</v>
+        <v>2480</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>2296</v>
+        <v>2281</v>
       </c>
       <c r="K64" t="s">
-        <v>2357</v>
+        <v>2336</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>2358</v>
+        <v>2337</v>
       </c>
       <c r="C65" t="s">
-        <v>2359</v>
+        <v>2338</v>
       </c>
       <c r="D65" t="s">
-        <v>2360</v>
+        <v>2339</v>
       </c>
       <c r="E65" t="s">
         <v>421</v>
       </c>
       <c r="F65" t="s">
-        <v>2058</v>
-      </c>
-      <c r="G65" t="s">
-        <v>2296</v>
+        <v>2061</v>
+      </c>
+      <c r="G65">
+        <v>64</v>
       </c>
       <c r="H65" t="s">
-        <v>2356</v>
+        <v>2481</v>
+      </c>
+      <c r="I65">
+        <v>30</v>
       </c>
       <c r="J65" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="K65" t="s">
-        <v>2357</v>
+        <v>2336</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -15579,34 +15986,37 @@
         <v>885</v>
       </c>
       <c r="C66" t="s">
-        <v>2361</v>
+        <v>2340</v>
       </c>
       <c r="D66" t="s">
-        <v>2362</v>
+        <v>2341</v>
       </c>
       <c r="E66" t="s">
         <v>421</v>
       </c>
       <c r="F66" t="s">
-        <v>2061</v>
-      </c>
-      <c r="G66" t="s">
-        <v>2277</v>
+        <v>2064</v>
+      </c>
+      <c r="G66">
+        <v>65</v>
       </c>
       <c r="H66" t="s">
-        <v>2356</v>
+        <v>2480</v>
+      </c>
+      <c r="I66">
+        <v>2</v>
       </c>
       <c r="J66" t="s">
-        <v>2363</v>
+        <v>2342</v>
       </c>
       <c r="K66" t="s">
-        <v>2364</v>
+        <v>2343</v>
       </c>
       <c r="L66" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -15614,69 +16024,75 @@
         <v>793</v>
       </c>
       <c r="C67" t="s">
-        <v>2365</v>
+        <v>2344</v>
       </c>
       <c r="D67" t="s">
-        <v>2366</v>
+        <v>2345</v>
       </c>
       <c r="E67" t="s">
         <v>421</v>
       </c>
       <c r="F67" t="s">
-        <v>2367</v>
-      </c>
-      <c r="G67" t="s">
-        <v>2296</v>
+        <v>2346</v>
+      </c>
+      <c r="G67">
+        <v>66</v>
       </c>
       <c r="H67" t="s">
-        <v>2284</v>
+        <v>2475</v>
+      </c>
+      <c r="I67">
+        <v>8</v>
       </c>
       <c r="J67" t="s">
-        <v>2296</v>
+        <v>2281</v>
       </c>
       <c r="K67" t="s">
-        <v>2368</v>
+        <v>2347</v>
       </c>
       <c r="L67" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>2369</v>
+        <v>2348</v>
       </c>
       <c r="C68" t="s">
-        <v>2370</v>
+        <v>2349</v>
       </c>
       <c r="D68" t="s">
-        <v>2371</v>
+        <v>2350</v>
       </c>
       <c r="E68" t="s">
         <v>421</v>
       </c>
       <c r="F68" t="s">
-        <v>2367</v>
-      </c>
-      <c r="G68" t="s">
-        <v>2296</v>
+        <v>2346</v>
+      </c>
+      <c r="G68">
+        <v>67</v>
       </c>
       <c r="H68" t="s">
-        <v>2284</v>
+        <v>2482</v>
+      </c>
+      <c r="I68">
+        <v>31</v>
       </c>
       <c r="J68" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="K68" t="s">
-        <v>2368</v>
+        <v>2347</v>
       </c>
       <c r="L68" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -15684,10 +16100,10 @@
         <v>922</v>
       </c>
       <c r="C69" t="s">
-        <v>2372</v>
+        <v>2351</v>
       </c>
       <c r="D69" t="s">
-        <v>2373</v>
+        <v>2352</v>
       </c>
       <c r="E69" t="s">
         <v>421</v>
@@ -15695,23 +16111,26 @@
       <c r="F69" t="s">
         <v>922</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69">
+        <v>68</v>
+      </c>
+      <c r="H69" t="s">
+        <v>2475</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69" t="s">
         <v>2277</v>
       </c>
-      <c r="H69" t="s">
-        <v>2284</v>
-      </c>
-      <c r="J69" t="s">
-        <v>2292</v>
-      </c>
       <c r="K69" t="s">
-        <v>2374</v>
+        <v>2353</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -15719,10 +16138,10 @@
         <v>870</v>
       </c>
       <c r="C70" t="s">
-        <v>2375</v>
+        <v>2354</v>
       </c>
       <c r="D70" t="s">
-        <v>2376</v>
+        <v>2355</v>
       </c>
       <c r="E70" t="s">
         <v>421</v>
@@ -15730,23 +16149,26 @@
       <c r="F70" t="s">
         <v>870</v>
       </c>
-      <c r="G70" t="s">
+      <c r="G70">
+        <v>69</v>
+      </c>
+      <c r="H70" t="s">
+        <v>2475</v>
+      </c>
+      <c r="I70">
+        <v>3</v>
+      </c>
+      <c r="J70" t="s">
         <v>2277</v>
       </c>
-      <c r="H70" t="s">
-        <v>2284</v>
-      </c>
-      <c r="J70" t="s">
-        <v>2292</v>
-      </c>
       <c r="K70" t="s">
-        <v>2377</v>
+        <v>2356</v>
       </c>
       <c r="L70" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -15754,69 +16176,78 @@
         <v>778</v>
       </c>
       <c r="C71" t="s">
-        <v>2378</v>
+        <v>2357</v>
       </c>
       <c r="D71" t="s">
-        <v>2379</v>
+        <v>2358</v>
       </c>
       <c r="E71" t="s">
         <v>421</v>
       </c>
       <c r="F71" t="s">
-        <v>2380</v>
-      </c>
-      <c r="G71" t="s">
-        <v>2296</v>
+        <v>2359</v>
+      </c>
+      <c r="G71">
+        <v>70</v>
       </c>
       <c r="H71" t="s">
-        <v>2284</v>
+        <v>2476</v>
+      </c>
+      <c r="I71">
+        <v>5</v>
       </c>
       <c r="J71" t="s">
-        <v>2296</v>
+        <v>2281</v>
       </c>
       <c r="K71" t="s">
-        <v>2381</v>
+        <v>2360</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M71" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>2382</v>
+        <v>2451</v>
       </c>
       <c r="C72" t="s">
-        <v>2383</v>
+        <v>2361</v>
       </c>
       <c r="D72" t="s">
-        <v>2384</v>
+        <v>2362</v>
       </c>
       <c r="E72" t="s">
         <v>421</v>
       </c>
       <c r="F72" t="s">
-        <v>2380</v>
-      </c>
-      <c r="G72" t="s">
-        <v>2296</v>
+        <v>2359</v>
+      </c>
+      <c r="G72">
+        <v>71</v>
       </c>
       <c r="H72" t="s">
-        <v>2284</v>
+        <v>2478</v>
+      </c>
+      <c r="I72">
+        <v>32</v>
       </c>
       <c r="J72" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="K72" t="s">
-        <v>2381</v>
+        <v>2360</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -15824,80 +16255,92 @@
         <v>880</v>
       </c>
       <c r="C73" t="s">
-        <v>2385</v>
+        <v>2363</v>
       </c>
       <c r="D73" t="s">
-        <v>2386</v>
+        <v>2364</v>
       </c>
       <c r="E73" t="s">
         <v>421</v>
       </c>
       <c r="F73" t="s">
-        <v>2387</v>
-      </c>
-      <c r="G73" t="s">
-        <v>809</v>
+        <v>2452</v>
+      </c>
+      <c r="G73">
+        <v>72</v>
       </c>
       <c r="H73" t="s">
-        <v>2335</v>
+        <v>2483</v>
+      </c>
+      <c r="I73">
+        <v>20</v>
       </c>
       <c r="J73" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K73" t="s">
-        <v>2336</v>
+        <v>2316</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M73" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>2388</v>
+        <v>876</v>
       </c>
       <c r="C74" t="s">
-        <v>2389</v>
+        <v>2365</v>
       </c>
       <c r="D74" t="s">
-        <v>2390</v>
+        <v>2366</v>
       </c>
       <c r="E74" t="s">
         <v>421</v>
       </c>
       <c r="F74" t="s">
-        <v>2387</v>
-      </c>
-      <c r="G74" t="s">
-        <v>809</v>
+        <v>2452</v>
+      </c>
+      <c r="G74">
+        <v>73</v>
       </c>
       <c r="H74" t="s">
-        <v>2335</v>
+        <v>2483</v>
+      </c>
+      <c r="I74">
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K74" t="s">
-        <v>2336</v>
+        <v>2316</v>
       </c>
       <c r="L74" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M74" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>1057</v>
+        <v>2455</v>
       </c>
       <c r="C75" t="s">
-        <v>2391</v>
+        <v>2367</v>
       </c>
       <c r="D75" t="s">
-        <v>2392</v>
+        <v>2368</v>
       </c>
       <c r="E75" t="s">
         <v>421</v>
@@ -15905,34 +16348,40 @@
       <c r="F75" t="s">
         <v>949</v>
       </c>
-      <c r="G75" t="s">
-        <v>2356</v>
+      <c r="G75">
+        <v>74</v>
       </c>
       <c r="H75" t="s">
-        <v>2356</v>
+        <v>2480</v>
+      </c>
+      <c r="I75">
+        <v>3</v>
       </c>
       <c r="J75" t="s">
         <v>2178</v>
       </c>
       <c r="K75" t="s">
-        <v>2393</v>
+        <v>2369</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M75" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>2394</v>
+        <v>2457</v>
       </c>
       <c r="C76" t="s">
-        <v>2395</v>
+        <v>2370</v>
       </c>
       <c r="D76" t="s">
-        <v>2396</v>
+        <v>2371</v>
       </c>
       <c r="E76" t="s">
         <v>421</v>
@@ -15940,23 +16389,26 @@
       <c r="F76" t="s">
         <v>949</v>
       </c>
-      <c r="G76" t="s">
-        <v>2356</v>
+      <c r="G76">
+        <v>75</v>
       </c>
       <c r="H76" t="s">
-        <v>2356</v>
+        <v>2480</v>
+      </c>
+      <c r="I76">
+        <v>4</v>
       </c>
       <c r="J76" t="s">
-        <v>2397</v>
+        <v>2372</v>
       </c>
       <c r="K76" t="s">
-        <v>2393</v>
+        <v>2369</v>
       </c>
       <c r="L76" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -15964,10 +16416,10 @@
         <v>1061</v>
       </c>
       <c r="C77" t="s">
-        <v>2398</v>
+        <v>2373</v>
       </c>
       <c r="D77" t="s">
-        <v>2399</v>
+        <v>2374</v>
       </c>
       <c r="E77" t="s">
         <v>421</v>
@@ -15975,34 +16427,37 @@
       <c r="F77" t="s">
         <v>949</v>
       </c>
-      <c r="G77" t="s">
-        <v>2356</v>
+      <c r="G77">
+        <v>76</v>
       </c>
       <c r="H77" t="s">
-        <v>2356</v>
+        <v>2481</v>
+      </c>
+      <c r="I77">
+        <v>33</v>
       </c>
       <c r="J77" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="K77" t="s">
-        <v>2393</v>
+        <v>2369</v>
       </c>
       <c r="L77" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>1063</v>
+        <v>2458</v>
       </c>
       <c r="C78" t="s">
-        <v>2400</v>
+        <v>2375</v>
       </c>
       <c r="D78" t="s">
-        <v>2401</v>
+        <v>2376</v>
       </c>
       <c r="E78" t="s">
         <v>421</v>
@@ -16010,306 +16465,343 @@
       <c r="F78" t="s">
         <v>949</v>
       </c>
-      <c r="G78" t="s">
-        <v>2356</v>
+      <c r="G78">
+        <v>77</v>
       </c>
       <c r="H78" t="s">
-        <v>2356</v>
+        <v>2480</v>
+      </c>
+      <c r="I78">
+        <v>5</v>
       </c>
       <c r="J78" t="s">
-        <v>2402</v>
+        <v>2377</v>
       </c>
       <c r="K78" t="s">
-        <v>2393</v>
+        <v>2369</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>1065</v>
+        <v>2459</v>
       </c>
       <c r="C79" t="s">
-        <v>2403</v>
+        <v>2378</v>
       </c>
       <c r="D79" t="s">
-        <v>2404</v>
+        <v>2379</v>
       </c>
       <c r="E79" t="s">
         <v>421</v>
       </c>
       <c r="F79" t="s">
-        <v>2405</v>
-      </c>
-      <c r="G79" t="s">
-        <v>2406</v>
+        <v>927</v>
+      </c>
+      <c r="G79">
+        <v>78</v>
       </c>
       <c r="H79" t="s">
-        <v>2356</v>
+        <v>2480</v>
       </c>
       <c r="I79">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J79" t="s">
         <v>2178</v>
       </c>
       <c r="K79" t="s">
-        <v>2407</v>
+        <v>2380</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M79" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>1066</v>
+        <v>2461</v>
       </c>
       <c r="C80" t="s">
-        <v>2408</v>
+        <v>2381</v>
       </c>
       <c r="D80" t="s">
-        <v>2409</v>
+        <v>2382</v>
       </c>
       <c r="E80" t="s">
         <v>421</v>
       </c>
       <c r="F80" t="s">
-        <v>2405</v>
-      </c>
-      <c r="G80" t="s">
-        <v>2406</v>
+        <v>927</v>
+      </c>
+      <c r="G80">
+        <v>79</v>
       </c>
       <c r="H80" t="s">
-        <v>2356</v>
+        <v>2480</v>
+      </c>
+      <c r="I80">
+        <v>7</v>
       </c>
       <c r="J80" t="s">
-        <v>2410</v>
+        <v>2327</v>
       </c>
       <c r="K80" t="s">
-        <v>2407</v>
+        <v>2380</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M80" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>1068</v>
+        <v>2462</v>
       </c>
       <c r="C81" t="s">
-        <v>2411</v>
+        <v>2383</v>
       </c>
       <c r="D81" t="s">
-        <v>2412</v>
+        <v>2384</v>
       </c>
       <c r="E81" t="s">
         <v>421</v>
       </c>
       <c r="F81" t="s">
-        <v>2405</v>
-      </c>
-      <c r="G81" t="s">
-        <v>2406</v>
+        <v>927</v>
+      </c>
+      <c r="G81">
+        <v>80</v>
       </c>
       <c r="H81" t="s">
-        <v>2356</v>
+        <v>2480</v>
+      </c>
+      <c r="I81">
+        <v>8</v>
       </c>
       <c r="J81" t="s">
-        <v>2413</v>
+        <v>2385</v>
       </c>
       <c r="K81" t="s">
-        <v>2407</v>
+        <v>2380</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>1070</v>
+        <v>2463</v>
       </c>
       <c r="C82" t="s">
-        <v>2414</v>
+        <v>2386</v>
       </c>
       <c r="D82" t="s">
-        <v>2415</v>
+        <v>2387</v>
       </c>
       <c r="E82" t="s">
         <v>421</v>
       </c>
       <c r="F82" t="s">
-        <v>2405</v>
-      </c>
-      <c r="G82" t="s">
-        <v>2406</v>
+        <v>927</v>
+      </c>
+      <c r="G82">
+        <v>81</v>
       </c>
       <c r="H82" t="s">
-        <v>2356</v>
+        <v>2480</v>
+      </c>
+      <c r="I82">
+        <v>9</v>
       </c>
       <c r="J82" t="s">
-        <v>2204</v>
+        <v>2199</v>
       </c>
       <c r="K82" t="s">
-        <v>2407</v>
+        <v>2380</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>2416</v>
+        <v>2464</v>
       </c>
       <c r="C83" t="s">
-        <v>2417</v>
+        <v>2388</v>
       </c>
       <c r="D83" t="s">
-        <v>2418</v>
+        <v>2389</v>
       </c>
       <c r="E83" t="s">
         <v>200</v>
       </c>
       <c r="F83" t="s">
-        <v>2419</v>
-      </c>
-      <c r="G83" t="s">
-        <v>2283</v>
+        <v>2390</v>
+      </c>
+      <c r="G83">
+        <v>82</v>
       </c>
       <c r="H83" t="s">
-        <v>2284</v>
+        <v>2474</v>
+      </c>
+      <c r="I83">
+        <v>6</v>
       </c>
       <c r="J83" t="s">
         <v>2178</v>
       </c>
       <c r="K83" t="s">
-        <v>2420</v>
+        <v>2391</v>
       </c>
       <c r="L83" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>2421</v>
+        <v>2392</v>
       </c>
       <c r="C84" t="s">
-        <v>2422</v>
+        <v>2393</v>
       </c>
       <c r="D84" t="s">
-        <v>2423</v>
+        <v>2394</v>
       </c>
       <c r="E84" t="s">
         <v>200</v>
       </c>
       <c r="F84" t="s">
-        <v>2419</v>
-      </c>
-      <c r="G84" t="s">
-        <v>2283</v>
+        <v>2390</v>
+      </c>
+      <c r="G84">
+        <v>83</v>
       </c>
       <c r="H84" t="s">
-        <v>2284</v>
+        <v>2484</v>
+      </c>
+      <c r="I84">
+        <v>6</v>
       </c>
       <c r="J84" t="s">
-        <v>2225</v>
+        <v>2219</v>
       </c>
       <c r="K84" t="s">
-        <v>2420</v>
+        <v>2391</v>
       </c>
       <c r="L84" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>2424</v>
+        <v>2465</v>
       </c>
       <c r="C85" t="s">
-        <v>2425</v>
+        <v>2395</v>
       </c>
       <c r="D85" t="s">
-        <v>2426</v>
+        <v>2396</v>
       </c>
       <c r="E85" t="s">
         <v>423</v>
       </c>
       <c r="F85" t="s">
-        <v>2419</v>
-      </c>
-      <c r="G85" t="s">
-        <v>2283</v>
+        <v>2466</v>
+      </c>
+      <c r="G85">
+        <v>84</v>
       </c>
       <c r="H85" t="s">
-        <v>2284</v>
+        <v>2485</v>
+      </c>
+      <c r="I85">
+        <v>22</v>
       </c>
       <c r="J85" t="s">
-        <v>2188</v>
+        <v>2228</v>
       </c>
       <c r="K85" t="s">
-        <v>2420</v>
+        <v>2391</v>
       </c>
       <c r="L85" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M85" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>2427</v>
+        <v>2397</v>
       </c>
       <c r="C86" t="s">
-        <v>2428</v>
+        <v>2398</v>
       </c>
       <c r="D86" t="s">
-        <v>2429</v>
+        <v>2399</v>
       </c>
       <c r="E86" t="s">
         <v>421</v>
       </c>
       <c r="F86" t="s">
-        <v>2419</v>
-      </c>
-      <c r="G86" t="s">
-        <v>2283</v>
+        <v>2466</v>
+      </c>
+      <c r="G86">
+        <v>85</v>
       </c>
       <c r="H86" t="s">
-        <v>2284</v>
+        <v>2477</v>
+      </c>
+      <c r="I86">
+        <v>23</v>
       </c>
       <c r="J86" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="K86" t="s">
-        <v>2420</v>
+        <v>2391</v>
       </c>
       <c r="L86" t="b">
         <v>1</v>
       </c>
+      <c r="M86" t="s">
+        <v>2467</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M86" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16378,7 +16870,7 @@
         <v>1999</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -16404,7 +16896,7 @@
         <v>2004</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -16418,19 +16910,19 @@
         <v>778</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>2096</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -16447,16 +16939,16 @@
         <v>596</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>2097</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -16473,16 +16965,16 @@
         <v>596</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -16496,19 +16988,19 @@
         <v>870</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>2099</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -16522,19 +17014,19 @@
         <v>922</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -16542,7 +17034,7 @@
         <v>207</v>
       </c>
       <c r="B9" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="C9" t="s">
         <v>602</v>
@@ -16551,16 +17043,16 @@
         <v>601</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -16568,7 +17060,7 @@
         <v>217</v>
       </c>
       <c r="B10" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="C10" t="s">
         <v>850</v>
@@ -16577,16 +17069,16 @@
         <v>601</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -16600,19 +17092,19 @@
         <v>793</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -16626,19 +17118,19 @@
         <v>743</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>2102</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -16649,22 +17141,22 @@
         <v>884</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -16678,19 +17170,19 @@
         <v>856</v>
       </c>
       <c r="D14" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -16704,19 +17196,19 @@
         <v>1028</v>
       </c>
       <c r="D15" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -16730,19 +17222,19 @@
         <v>613</v>
       </c>
       <c r="D16" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>2055</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>2052</v>
-      </c>
       <c r="F16" s="8" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -16753,22 +17245,22 @@
         <v>565</v>
       </c>
       <c r="C17" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="D17" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -16785,16 +17277,16 @@
         <v>498</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -16805,22 +17297,22 @@
         <v>512</v>
       </c>
       <c r="C19" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="D19" t="s">
         <v>513</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -16837,16 +17329,16 @@
         <v>809</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -16863,16 +17355,16 @@
         <v>809</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -16889,16 +17381,16 @@
         <v>809</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -16915,16 +17407,16 @@
         <v>809</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -16941,16 +17433,16 @@
         <v>809</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -16967,16 +17459,16 @@
         <v>513</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -16990,19 +17482,19 @@
         <v>748</v>
       </c>
       <c r="D26" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="F26" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G26" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17013,22 +17505,22 @@
         <v>512</v>
       </c>
       <c r="C27" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="D27" t="s">
         <v>513</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="F27" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G27" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -17045,16 +17537,16 @@
         <v>513</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="F28" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G28" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -17065,22 +17557,22 @@
         <v>512</v>
       </c>
       <c r="C29" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="D29" t="s">
         <v>513</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="F29" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G29" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17097,16 +17589,16 @@
         <v>513</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
       <c r="F30" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G30" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17123,16 +17615,16 @@
         <v>513</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="F31" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G31" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -17149,16 +17641,16 @@
         <v>513</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="F32" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G32" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -17175,16 +17667,16 @@
         <v>513</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="F33" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G33" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -17201,13 +17693,13 @@
         <v>513</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
       <c r="F34" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G34" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -17224,16 +17716,16 @@
         <v>513</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="F35" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G35" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17244,22 +17736,22 @@
         <v>894</v>
       </c>
       <c r="C36" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="D36" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="F36" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G36" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -17273,19 +17765,19 @@
         <v>757</v>
       </c>
       <c r="D37" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="F37" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G37" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17296,22 +17788,22 @@
         <v>559</v>
       </c>
       <c r="C38" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="D38" t="s">
         <v>560</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17325,19 +17817,19 @@
         <v>618</v>
       </c>
       <c r="D39" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="F39" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G39" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.2">
@@ -17351,19 +17843,19 @@
         <v>927</v>
       </c>
       <c r="D40" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="F40" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G40" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.2">
@@ -17377,19 +17869,19 @@
         <v>949</v>
       </c>
       <c r="D41" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="F41" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="G41" s="33" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
   </sheetData>
@@ -18806,7 +19298,7 @@
         <v>207</v>
       </c>
       <c r="B37" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>601</v>
@@ -20089,7 +20581,7 @@
         <v>737</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>738</v>
@@ -21014,7 +21506,7 @@
         <v>217</v>
       </c>
       <c r="B95" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>601</v>
@@ -38175,7 +38667,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55941987-30AF-6648-9A85-31A79E0640F5}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
@@ -38194,72 +38686,72 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="B1" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
       <c r="C1" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="D1" t="s">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="E1" t="s">
-        <v>147</v>
+        <v>2401</v>
       </c>
       <c r="F1" t="s">
         <v>146</v>
       </c>
       <c r="G1" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="H1" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="I1" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J1" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="K1" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
       <c r="L1" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="B2" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="C2" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="D2" t="s">
-        <v>2153</v>
-      </c>
-      <c r="E2" t="s">
-        <v>2157</v>
+        <v>2156</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>2400</v>
       </c>
       <c r="F2" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="G2" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="H2" t="s">
-        <v>2123</v>
+        <v>2126</v>
       </c>
       <c r="J2" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="K2" t="s">
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -38267,34 +38759,34 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C3" t="s">
         <v>2149</v>
       </c>
-      <c r="B3" t="s">
-        <v>2163</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2146</v>
-      </c>
       <c r="D3" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="E3" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="F3" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="G3" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="H3" t="s">
-        <v>2128</v>
+        <v>2131</v>
       </c>
       <c r="J3" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="K3" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -38302,34 +38794,34 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C4" t="s">
         <v>2150</v>
       </c>
-      <c r="B4" t="s">
-        <v>2163</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2147</v>
-      </c>
       <c r="D4" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="E4" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="F4" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="G4" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="H4" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="J4" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="K4" t="s">
-        <v>2135</v>
+        <v>2138</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -38337,34 +38829,34 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="B5" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="C5" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="D5" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="E5" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="F5" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="G5" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="H5" t="s">
-        <v>2138</v>
+        <v>2141</v>
       </c>
       <c r="J5" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="K5" t="s">
-        <v>2140</v>
+        <v>2143</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -38372,34 +38864,34 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="B6" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="C6" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2159</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2145</v>
+      </c>
+      <c r="H6" t="s">
         <v>2146</v>
       </c>
-      <c r="D6" t="s">
-        <v>2156</v>
-      </c>
-      <c r="E6" t="s">
-        <v>2161</v>
-      </c>
-      <c r="F6" t="s">
-        <v>2141</v>
-      </c>
-      <c r="G6" t="s">
-        <v>2142</v>
-      </c>
-      <c r="H6" t="s">
-        <v>2143</v>
-      </c>
       <c r="J6" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="K6" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -38407,43 +38899,49 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B7" t="s">
         <v>2165</v>
       </c>
-      <c r="B7" t="s">
-        <v>2163</v>
-      </c>
       <c r="C7" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="D7" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="E7" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="F7" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="G7" t="s">
+        <v>2173</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I7" t="s">
+        <v>2175</v>
+      </c>
+      <c r="J7" t="s">
         <v>2171</v>
       </c>
-      <c r="H7" t="s">
+      <c r="K7" t="s">
         <v>2172</v>
-      </c>
-      <c r="I7" t="s">
-        <v>2173</v>
-      </c>
-      <c r="J7" t="s">
-        <v>2169</v>
-      </c>
-      <c r="K7" t="s">
-        <v>2170</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E11" s="6"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{DB08D9B6-F3C8-E84F-AFA0-CD1E52770AC7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -71766,13 +72264,13 @@
         <v>46227</v>
       </c>
       <c r="B2" t="s">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="G2" s="5"/>
     </row>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD96B3D-0BD5-3343-976C-23B997B5F4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C524A6-9005-DC47-9396-6D0CF9F31B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31520" yWindow="1560" windowWidth="29560" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31520" yWindow="1180" windowWidth="29560" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Lyrics!$A$1:$H$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Memory!$A$1:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Memory (2)'!$A$1:$E$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TKURadio!$A$1:$M$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TKURadio!$A$1:$K$89</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3901" uniqueCount="2486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3924" uniqueCount="2473">
   <si>
     <t>date</t>
   </si>
@@ -11993,9 +11993,6 @@
     <t>Official MV</t>
   </si>
   <si>
-    <t>/static/images/songs/golden.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=Z3x9i7njCCo</t>
   </si>
   <si>
@@ -12257,9 +12254,6 @@
     <t>J_n4Ysi5iUM</t>
   </si>
   <si>
-    <t>/static/images/songs/never_let_go.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=m5_J7xuYxzs</t>
   </si>
   <si>
@@ -12269,18 +12263,12 @@
     <t>Solo Track</t>
   </si>
   <si>
-    <t>/static/images/songs/wings.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=a_zk4JFK43g</t>
   </si>
   <si>
     <t>a_zk4JFK43g</t>
   </si>
   <si>
-    <t>/static/images/songs/mots7.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=BksBNbTIoPE</t>
   </si>
   <si>
@@ -12290,9 +12278,6 @@
     <t>Solo Song</t>
   </si>
   <si>
-    <t>/static/images/songs/still_with_you.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=yzjTpCgfIII</t>
   </si>
   <si>
@@ -12302,9 +12287,6 @@
     <t>OST</t>
   </si>
   <si>
-    <t>/static/images/songs/stay_alive.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=kX0vO4vlJuU</t>
   </si>
   <si>
@@ -12314,9 +12296,6 @@
     <t>Love Yourself: Answer</t>
   </si>
   <si>
-    <t>/static/images/songs/love_yourself.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=83Lv790h79k</t>
   </si>
   <si>
@@ -12326,27 +12305,18 @@
     <t>Collaboration</t>
   </si>
   <si>
-    <t>/static/images/songs/too_much.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=IwzkfMmNMpM</t>
   </si>
   <si>
     <t>IwzkfMmNMpM</t>
   </si>
   <si>
-    <t>/static/images/songs/dreamers.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=a7GITgqwDVg</t>
   </si>
   <si>
     <t>a7GITgqwDVg</t>
   </si>
   <si>
-    <t>/static/images/songs/left_and_right.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=_yTP_L8fC-k</t>
   </si>
   <si>
@@ -12356,27 +12326,18 @@
     <t>Fan Song</t>
   </si>
   <si>
-    <t>/static/images/songs/my_you.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=62peQdQv4uo</t>
   </si>
   <si>
     <t>62peQdQv4uo</t>
   </si>
   <si>
-    <t>/static/images/songs/friends.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=LEdNCS8luWE</t>
   </si>
   <si>
     <t>LEdNCS8luWE</t>
   </si>
   <si>
-    <t>/static/images/songs/wherever_u_r.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=Xh0YXPrIyFk</t>
   </si>
   <si>
@@ -12404,9 +12365,6 @@
     <t>yTsINmrAK4I</t>
   </si>
   <si>
-    <t>/static/images/songs/layover.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=sIh9_cNCwPc</t>
   </si>
   <si>
@@ -12464,9 +12422,6 @@
     <t>lj8TV9q59P4</t>
   </si>
   <si>
-    <t>/static/images/songs/christmas_tree.jpg</t>
-  </si>
-  <si>
     <t>Christmas Tree (Instrumental)</t>
   </si>
   <si>
@@ -12485,9 +12440,6 @@
     <t>Seasonal Song</t>
   </si>
   <si>
-    <t>/static/images/songs/snow_flower.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=_pC6o6H3CmY</t>
   </si>
   <si>
@@ -12497,9 +12449,6 @@
     <t>Itaewon Class OST</t>
   </si>
   <si>
-    <t>/static/images/songs/sweet_night.jpg</t>
-  </si>
-  <si>
     <t>Sweet Night (Instrumental)</t>
   </si>
   <si>
@@ -12515,18 +12464,12 @@
     <t>pk7ESz6vtyA</t>
   </si>
   <si>
-    <t>/static/images/songs/winter_bear.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=xe2r_KG2XdA</t>
   </si>
   <si>
     <t>xe2r_KG2XdA</t>
   </si>
   <si>
-    <t>/static/images/songs/scenery.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=uLfLbtulKZc</t>
   </si>
   <si>
@@ -12536,9 +12479,6 @@
     <t>Hwarang OST</t>
   </si>
   <si>
-    <t>/static/images/songs/hwarang.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=kDv1T0bnLwU</t>
   </si>
   <si>
@@ -12563,9 +12503,6 @@
     <t>r3QP1SxW1_I</t>
   </si>
   <si>
-    <t>/static/images/songs/white_christmas.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=e3AN0-t_uQU</t>
   </si>
   <si>
@@ -12596,9 +12533,6 @@
     <t>HAWYOuMGkK0</t>
   </si>
   <si>
-    <t>/static/images/songs/winter_ahead.jpg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=J-fQEhHAorE</t>
   </si>
   <si>
@@ -12629,9 +12563,6 @@
     <t>Arirang</t>
   </si>
   <si>
-    <t>/static/images/songs/arirang.jpg</t>
-  </si>
-  <si>
     <t>SWIM (Performance Video)</t>
   </si>
   <si>
@@ -12665,9 +12596,6 @@
     <t>playlist_group</t>
   </si>
   <si>
-    <t>play_order</t>
-  </si>
-  <si>
     <t>track_type</t>
   </si>
   <si>
@@ -12866,9 +12794,6 @@
     <t>GOLDEN_ALBUM,TKU_LIBRARY,KOOKIE_VIBES</t>
   </si>
   <si>
-    <t>LIVE_STAGE,TKU_LIBRARY,KOOKIE_VIBES</t>
-  </si>
-  <si>
     <t>REMIXES,TKU_LIBRARY,KOOKIE_VIBES</t>
   </si>
   <si>
@@ -12908,10 +12833,46 @@
     <t>REMIXES,TETE_VIBES,TKU_LIBRARY</t>
   </si>
   <si>
-    <t>LIVE_STAGE,COLLABS,TKU_LIBRARY</t>
-  </si>
-  <si>
     <t>REMIXES,COLLABS,KOOKIE_VIBES,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>Hooligan (Official MV)</t>
+  </si>
+  <si>
+    <t>2.0 (Official MV)</t>
+  </si>
+  <si>
+    <t>Normal (Official MV)</t>
+  </si>
+  <si>
+    <t>_gyultVTesk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_gyultVTesk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Zv6JKobJyFY</t>
+  </si>
+  <si>
+    <t>Zv6JKobJyFY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GEk4jHwfFTA</t>
+  </si>
+  <si>
+    <t>GEk4jHwfFTA</t>
+  </si>
+  <si>
+    <t>arirang.webp</t>
+  </si>
+  <si>
+    <t>PERFORMANCE,TKU_LIBRARY,KOOKIE_VIBES</t>
+  </si>
+  <si>
+    <t>PERFORMANCE,COLLABS,TKU_LIBRARY</t>
+  </si>
+  <si>
+    <t>Winter_Ahead_with_PARK_HYO_SHIN_YUNSEOKCHEOL_TRIO_.webp</t>
   </si>
 </sst>
 </file>
@@ -13051,7 +13012,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -13109,7 +13070,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -13425,62 +13385,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.33203125" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="7" width="16.5" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1" t="s">
         <v>2191</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2192</v>
       </c>
       <c r="C1" t="s">
         <v>439</v>
       </c>
       <c r="D1" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="E1" t="s">
         <v>198</v>
       </c>
       <c r="F1" t="s">
+        <v>2193</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2379</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2380</v>
+      </c>
+      <c r="I1" t="s">
         <v>2194</v>
       </c>
-      <c r="G1" s="33" t="s">
-        <v>2191</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>2402</v>
-      </c>
-      <c r="I1" t="s">
-        <v>2403</v>
-      </c>
       <c r="J1" t="s">
-        <v>2404</v>
+        <v>2123</v>
       </c>
       <c r="K1" t="s">
-        <v>2195</v>
-      </c>
-      <c r="L1" t="s">
-        <v>2123</v>
-      </c>
-      <c r="M1" t="s">
         <v>2122</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -13499,37 +13453,31 @@
       <c r="F2" t="s">
         <v>2063</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="s">
+        <v>2445</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I2" t="s">
+        <v>512</v>
+      </c>
+      <c r="J2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>2178</v>
-      </c>
-      <c r="K2" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2405</v>
+        <v>2381</v>
       </c>
       <c r="C3" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D3" t="s">
         <v>2180</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2181</v>
       </c>
       <c r="E3" t="s">
         <v>423</v>
@@ -13537,37 +13485,31 @@
       <c r="F3" t="s">
         <v>2063</v>
       </c>
-      <c r="G3">
-        <v>2</v>
+      <c r="G3" t="s">
+        <v>2470</v>
       </c>
       <c r="H3" t="s">
-        <v>2470</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2406</v>
-      </c>
-      <c r="K3" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L3" t="b">
+        <v>2382</v>
+      </c>
+      <c r="I3" t="s">
+        <v>512</v>
+      </c>
+      <c r="J3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2407</v>
+        <v>2383</v>
       </c>
       <c r="C4" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D4" t="s">
         <v>2182</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2183</v>
       </c>
       <c r="E4" t="s">
         <v>423</v>
@@ -13575,67 +13517,55 @@
       <c r="F4" t="s">
         <v>2063</v>
       </c>
-      <c r="G4">
-        <v>3</v>
+      <c r="G4" t="s">
+        <v>2470</v>
       </c>
       <c r="H4" t="s">
-        <v>2470</v>
-      </c>
-      <c r="I4">
-        <v>5</v>
-      </c>
-      <c r="J4" t="s">
-        <v>2196</v>
-      </c>
-      <c r="K4" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L4" t="b">
+        <v>2195</v>
+      </c>
+      <c r="I4" t="s">
+        <v>512</v>
+      </c>
+      <c r="J4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2408</v>
+        <v>2384</v>
       </c>
       <c r="C5" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D5" t="s">
         <v>2184</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2185</v>
       </c>
       <c r="E5" t="s">
         <v>423</v>
       </c>
       <c r="F5" t="s">
+        <v>2185</v>
+      </c>
+      <c r="G5" t="s">
+        <v>2446</v>
+      </c>
+      <c r="H5" t="s">
         <v>2186</v>
       </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>2187</v>
+      <c r="I5" t="s">
+        <v>443</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>2327</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -13643,119 +13573,101 @@
         <v>2006</v>
       </c>
       <c r="C6" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D6" t="s">
         <v>2188</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2189</v>
       </c>
       <c r="E6" t="s">
         <v>423</v>
       </c>
       <c r="F6" t="s">
-        <v>2186</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
+        <v>2185</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2447</v>
       </c>
       <c r="H6" t="s">
-        <v>2472</v>
-      </c>
-      <c r="I6">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s">
-        <v>2190</v>
-      </c>
-      <c r="K6" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L6" t="b">
+        <v>2189</v>
+      </c>
+      <c r="I6" t="s">
+        <v>443</v>
+      </c>
+      <c r="J6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2409</v>
+        <v>2385</v>
       </c>
       <c r="C7" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D7" t="s">
         <v>2197</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2198</v>
       </c>
       <c r="E7" t="s">
         <v>423</v>
       </c>
       <c r="F7" t="s">
-        <v>2186</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
+        <v>2185</v>
+      </c>
+      <c r="G7" t="s">
+        <v>2446</v>
       </c>
       <c r="H7" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I7">
-        <v>21</v>
-      </c>
-      <c r="J7" t="s">
-        <v>2199</v>
+        <v>2198</v>
+      </c>
+      <c r="I7" t="s">
+        <v>443</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>2410</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2411</v>
+        <v>2387</v>
       </c>
       <c r="C8" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D8" t="s">
         <v>2200</v>
-      </c>
-      <c r="D8" t="s">
-        <v>2201</v>
       </c>
       <c r="E8" t="s">
         <v>423</v>
       </c>
       <c r="F8" t="s">
-        <v>2186</v>
-      </c>
-      <c r="G8">
-        <v>7</v>
+        <v>2185</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2446</v>
       </c>
       <c r="H8" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I8">
-        <v>22</v>
-      </c>
-      <c r="J8" t="s">
-        <v>2199</v>
+        <v>2198</v>
+      </c>
+      <c r="I8" t="s">
+        <v>443</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>2412</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -13763,37 +13675,31 @@
         <v>2008</v>
       </c>
       <c r="C9" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D9" t="s">
         <v>2202</v>
-      </c>
-      <c r="D9" t="s">
-        <v>2203</v>
       </c>
       <c r="E9" t="s">
         <v>423</v>
       </c>
       <c r="F9" t="s">
-        <v>2186</v>
-      </c>
-      <c r="G9">
-        <v>8</v>
+        <v>2185</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2446</v>
       </c>
       <c r="H9" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I9">
-        <v>23</v>
-      </c>
-      <c r="J9" t="s">
-        <v>2204</v>
-      </c>
-      <c r="K9" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L9" t="b">
+        <v>2203</v>
+      </c>
+      <c r="I9" t="s">
+        <v>443</v>
+      </c>
+      <c r="J9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -13801,37 +13707,31 @@
         <v>2007</v>
       </c>
       <c r="C10" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D10" t="s">
         <v>2205</v>
-      </c>
-      <c r="D10" t="s">
-        <v>2206</v>
       </c>
       <c r="E10" t="s">
         <v>423</v>
       </c>
       <c r="F10" t="s">
-        <v>2186</v>
-      </c>
-      <c r="G10">
-        <v>9</v>
+        <v>2185</v>
+      </c>
+      <c r="G10" t="s">
+        <v>2446</v>
       </c>
       <c r="H10" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I10">
-        <v>24</v>
-      </c>
-      <c r="J10" t="s">
-        <v>2207</v>
-      </c>
-      <c r="K10" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L10" t="b">
+        <v>2206</v>
+      </c>
+      <c r="I10" t="s">
+        <v>443</v>
+      </c>
+      <c r="J10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -13839,40 +13739,34 @@
         <v>492</v>
       </c>
       <c r="C11" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D11" t="s">
         <v>2208</v>
-      </c>
-      <c r="D11" t="s">
-        <v>2209</v>
       </c>
       <c r="E11" t="s">
         <v>423</v>
       </c>
       <c r="F11" t="s">
+        <v>2185</v>
+      </c>
+      <c r="G11" t="s">
+        <v>2446</v>
+      </c>
+      <c r="H11" t="s">
         <v>2186</v>
       </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I11">
-        <v>25</v>
-      </c>
-      <c r="J11" t="s">
-        <v>2187</v>
+      <c r="I11" t="s">
+        <v>491</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" t="s">
-        <v>2413</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -13880,40 +13774,34 @@
         <v>983</v>
       </c>
       <c r="C12" t="s">
+        <v>2209</v>
+      </c>
+      <c r="D12" t="s">
         <v>2210</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2211</v>
       </c>
       <c r="E12" t="s">
         <v>423</v>
       </c>
       <c r="F12" t="s">
+        <v>2185</v>
+      </c>
+      <c r="G12" t="s">
+        <v>2446</v>
+      </c>
+      <c r="H12" t="s">
         <v>2186</v>
       </c>
-      <c r="G12">
-        <v>11</v>
-      </c>
-      <c r="H12" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I12">
-        <v>26</v>
-      </c>
-      <c r="J12" t="s">
-        <v>2187</v>
+      <c r="I12" t="s">
+        <v>486</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" t="s">
-        <v>2414</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -13921,10 +13809,10 @@
         <v>516</v>
       </c>
       <c r="C13" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D13" t="s">
         <v>2212</v>
-      </c>
-      <c r="D13" t="s">
-        <v>2213</v>
       </c>
       <c r="E13" t="s">
         <v>423</v>
@@ -13932,26 +13820,20 @@
       <c r="F13" t="s">
         <v>2063</v>
       </c>
-      <c r="G13">
-        <v>12</v>
+      <c r="G13" t="s">
+        <v>2445</v>
       </c>
       <c r="H13" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-      <c r="J13" t="s">
-        <v>2214</v>
-      </c>
-      <c r="K13" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L13" t="b">
+        <v>2213</v>
+      </c>
+      <c r="I13" t="s">
+        <v>512</v>
+      </c>
+      <c r="J13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -13959,10 +13841,10 @@
         <v>626</v>
       </c>
       <c r="C14" t="s">
+        <v>2214</v>
+      </c>
+      <c r="D14" t="s">
         <v>2215</v>
-      </c>
-      <c r="D14" t="s">
-        <v>2216</v>
       </c>
       <c r="E14" t="s">
         <v>423</v>
@@ -13970,26 +13852,20 @@
       <c r="F14" t="s">
         <v>2063</v>
       </c>
-      <c r="G14">
-        <v>13</v>
+      <c r="G14" t="s">
+        <v>2445</v>
       </c>
       <c r="H14" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I14">
+        <v>2178</v>
+      </c>
+      <c r="I14" t="s">
+        <v>512</v>
+      </c>
+      <c r="J14" t="b">
         <v>1</v>
       </c>
-      <c r="J14" t="s">
-        <v>2178</v>
-      </c>
-      <c r="K14" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -13997,10 +13873,10 @@
         <v>987</v>
       </c>
       <c r="C15" t="s">
+        <v>2216</v>
+      </c>
+      <c r="D15" t="s">
         <v>2217</v>
-      </c>
-      <c r="D15" t="s">
-        <v>2218</v>
       </c>
       <c r="E15" t="s">
         <v>423</v>
@@ -14008,304 +13884,256 @@
       <c r="F15" t="s">
         <v>2063</v>
       </c>
-      <c r="G15">
-        <v>14</v>
+      <c r="G15" t="s">
+        <v>2470</v>
       </c>
       <c r="H15" t="s">
-        <v>2470</v>
-      </c>
-      <c r="I15">
-        <v>3</v>
-      </c>
-      <c r="J15" t="s">
-        <v>2219</v>
-      </c>
-      <c r="K15" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L15" t="b">
+        <v>2218</v>
+      </c>
+      <c r="I15" t="s">
+        <v>512</v>
+      </c>
+      <c r="J15" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>2415</v>
+        <v>2391</v>
       </c>
       <c r="C16" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D16" t="s">
         <v>2220</v>
-      </c>
-      <c r="D16" t="s">
-        <v>2221</v>
       </c>
       <c r="E16" t="s">
         <v>423</v>
       </c>
       <c r="F16" t="s">
-        <v>2416</v>
-      </c>
-      <c r="G16">
-        <v>15</v>
+        <v>2392</v>
+      </c>
+      <c r="G16" t="s">
+        <v>2447</v>
       </c>
       <c r="H16" t="s">
-        <v>2472</v>
-      </c>
-      <c r="I16">
-        <v>30</v>
-      </c>
-      <c r="J16" t="s">
-        <v>2190</v>
-      </c>
-      <c r="K16" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L16" t="b">
+        <v>2189</v>
+      </c>
+      <c r="I16" t="s">
+        <v>625</v>
+      </c>
+      <c r="J16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>2417</v>
+        <v>2393</v>
       </c>
       <c r="C17" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D17" t="s">
         <v>2222</v>
-      </c>
-      <c r="D17" t="s">
-        <v>2223</v>
       </c>
       <c r="E17" t="s">
         <v>423</v>
       </c>
       <c r="F17" t="s">
-        <v>2416</v>
-      </c>
-      <c r="G17">
-        <v>16</v>
+        <v>2392</v>
+      </c>
+      <c r="G17" t="s">
+        <v>2446</v>
       </c>
       <c r="H17" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I17">
-        <v>20</v>
-      </c>
-      <c r="J17" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I17" t="s">
+        <v>676</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" t="s">
-        <v>2418</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>2419</v>
+        <v>2395</v>
       </c>
       <c r="C18" t="s">
+        <v>2223</v>
+      </c>
+      <c r="D18" t="s">
         <v>2224</v>
-      </c>
-      <c r="D18" t="s">
-        <v>2225</v>
       </c>
       <c r="E18" t="s">
         <v>423</v>
       </c>
       <c r="F18" t="s">
-        <v>2416</v>
-      </c>
-      <c r="G18">
-        <v>17</v>
+        <v>2392</v>
+      </c>
+      <c r="G18" t="s">
+        <v>2446</v>
       </c>
       <c r="H18" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I18">
-        <v>21</v>
-      </c>
-      <c r="J18" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I18" t="s">
+        <v>676</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" t="s">
-        <v>2420</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>2421</v>
+        <v>2397</v>
       </c>
       <c r="C19" t="s">
+        <v>2223</v>
+      </c>
+      <c r="D19" t="s">
         <v>2224</v>
-      </c>
-      <c r="D19" t="s">
-        <v>2225</v>
       </c>
       <c r="E19" t="s">
         <v>423</v>
       </c>
       <c r="F19" t="s">
-        <v>2416</v>
-      </c>
-      <c r="G19">
-        <v>18</v>
+        <v>2392</v>
+      </c>
+      <c r="G19" t="s">
+        <v>2446</v>
       </c>
       <c r="H19" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I19">
-        <v>22</v>
-      </c>
-      <c r="J19" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I19" t="s">
+        <v>676</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L19" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" t="s">
-        <v>2422</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>2423</v>
+        <v>2399</v>
       </c>
       <c r="C20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="D20" t="s">
         <v>2226</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2227</v>
       </c>
       <c r="E20" t="s">
         <v>423</v>
       </c>
       <c r="F20" t="s">
-        <v>2416</v>
-      </c>
-      <c r="G20">
-        <v>19</v>
+        <v>2392</v>
+      </c>
+      <c r="G20" t="s">
+        <v>2446</v>
       </c>
       <c r="H20" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I20">
-        <v>23</v>
-      </c>
-      <c r="J20" t="s">
-        <v>2228</v>
-      </c>
-      <c r="K20" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L20" t="b">
+        <v>2227</v>
+      </c>
+      <c r="I20" t="s">
+        <v>676</v>
+      </c>
+      <c r="J20" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>2424</v>
+        <v>2400</v>
       </c>
       <c r="C21" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D21" t="s">
         <v>2229</v>
-      </c>
-      <c r="D21" t="s">
-        <v>2230</v>
       </c>
       <c r="E21" t="s">
         <v>423</v>
       </c>
       <c r="F21" t="s">
-        <v>2416</v>
-      </c>
-      <c r="G21">
-        <v>20</v>
+        <v>2392</v>
+      </c>
+      <c r="G21" t="s">
+        <v>2446</v>
       </c>
       <c r="H21" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I21">
-        <v>24</v>
-      </c>
-      <c r="J21" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I21" t="s">
+        <v>661</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L21" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" t="s">
-        <v>2425</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>2426</v>
+        <v>2402</v>
       </c>
       <c r="C22" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D22" t="s">
         <v>2229</v>
-      </c>
-      <c r="D22" t="s">
-        <v>2230</v>
       </c>
       <c r="E22" t="s">
         <v>423</v>
       </c>
       <c r="F22" t="s">
-        <v>2416</v>
-      </c>
-      <c r="G22">
-        <v>21</v>
+        <v>2392</v>
+      </c>
+      <c r="G22" t="s">
+        <v>2446</v>
       </c>
       <c r="H22" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I22">
-        <v>25</v>
-      </c>
-      <c r="J22" t="s">
-        <v>2231</v>
-      </c>
-      <c r="K22" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L22" t="b">
+        <v>2230</v>
+      </c>
+      <c r="I22" t="s">
+        <v>661</v>
+      </c>
+      <c r="J22" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -14313,81 +14141,69 @@
         <v>656</v>
       </c>
       <c r="C23" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D23" t="s">
         <v>2232</v>
-      </c>
-      <c r="D23" t="s">
-        <v>2233</v>
       </c>
       <c r="E23" t="s">
         <v>423</v>
       </c>
       <c r="F23" t="s">
-        <v>2416</v>
-      </c>
-      <c r="G23">
-        <v>22</v>
+        <v>2392</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2446</v>
       </c>
       <c r="H23" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I23">
-        <v>26</v>
-      </c>
-      <c r="J23" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I23" t="s">
+        <v>650</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L23" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" t="s">
-        <v>2427</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>2428</v>
+        <v>2404</v>
       </c>
       <c r="C24" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D24" t="s">
         <v>2234</v>
-      </c>
-      <c r="D24" t="s">
-        <v>2235</v>
       </c>
       <c r="E24" t="s">
         <v>423</v>
       </c>
       <c r="F24" t="s">
-        <v>2416</v>
-      </c>
-      <c r="G24">
-        <v>23</v>
+        <v>2392</v>
+      </c>
+      <c r="G24" t="s">
+        <v>2446</v>
       </c>
       <c r="H24" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I24">
-        <v>27</v>
-      </c>
-      <c r="J24" t="s">
-        <v>2236</v>
+        <v>2235</v>
+      </c>
+      <c r="I24" t="s">
+        <v>650</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L24" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" t="s">
-        <v>2429</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -14395,10 +14211,10 @@
         <v>544</v>
       </c>
       <c r="C25" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D25" t="s">
         <v>2237</v>
-      </c>
-      <c r="D25" t="s">
-        <v>2238</v>
       </c>
       <c r="E25" t="s">
         <v>423</v>
@@ -14406,37 +14222,31 @@
       <c r="F25" t="s">
         <v>2063</v>
       </c>
-      <c r="G25">
-        <v>24</v>
+      <c r="G25" t="s">
+        <v>2445</v>
       </c>
       <c r="H25" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I25">
+        <v>2178</v>
+      </c>
+      <c r="I25" t="s">
+        <v>512</v>
+      </c>
+      <c r="J25" t="b">
         <v>1</v>
       </c>
-      <c r="J25" t="s">
-        <v>2178</v>
-      </c>
-      <c r="K25" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>2430</v>
+        <v>2406</v>
       </c>
       <c r="C26" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D26" t="s">
         <v>2239</v>
-      </c>
-      <c r="D26" t="s">
-        <v>2240</v>
       </c>
       <c r="E26" t="s">
         <v>423</v>
@@ -14444,26 +14254,20 @@
       <c r="F26" t="s">
         <v>2063</v>
       </c>
-      <c r="G26">
-        <v>25</v>
+      <c r="G26" t="s">
+        <v>2470</v>
       </c>
       <c r="H26" t="s">
-        <v>2470</v>
-      </c>
-      <c r="I26">
-        <v>5</v>
-      </c>
-      <c r="J26" t="s">
-        <v>2196</v>
-      </c>
-      <c r="K26" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L26" t="b">
+        <v>2195</v>
+      </c>
+      <c r="I26" t="s">
+        <v>512</v>
+      </c>
+      <c r="J26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -14471,37 +14275,31 @@
         <v>717</v>
       </c>
       <c r="C27" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D27" t="s">
         <v>2241</v>
-      </c>
-      <c r="D27" t="s">
-        <v>2242</v>
       </c>
       <c r="E27" t="s">
         <v>423</v>
       </c>
       <c r="F27" t="s">
-        <v>2431</v>
-      </c>
-      <c r="G27">
-        <v>26</v>
+        <v>2407</v>
+      </c>
+      <c r="G27" t="s">
+        <v>2447</v>
       </c>
       <c r="H27" t="s">
-        <v>2472</v>
-      </c>
-      <c r="I27">
-        <v>30</v>
-      </c>
-      <c r="J27" t="s">
-        <v>2190</v>
-      </c>
-      <c r="K27" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L27" t="b">
+        <v>2189</v>
+      </c>
+      <c r="I27" t="s">
+        <v>704</v>
+      </c>
+      <c r="J27" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -14509,40 +14307,34 @@
         <v>728</v>
       </c>
       <c r="C28" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D28" t="s">
         <v>2243</v>
-      </c>
-      <c r="D28" t="s">
-        <v>2244</v>
       </c>
       <c r="E28" t="s">
         <v>423</v>
       </c>
       <c r="F28" t="s">
-        <v>2431</v>
-      </c>
-      <c r="G28">
-        <v>27</v>
+        <v>2407</v>
+      </c>
+      <c r="G28" t="s">
+        <v>2446</v>
       </c>
       <c r="H28" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I28">
-        <v>20</v>
-      </c>
-      <c r="J28" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I28" t="s">
+        <v>704</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L28" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" t="s">
-        <v>2432</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -14550,40 +14342,34 @@
         <v>725</v>
       </c>
       <c r="C29" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D29" t="s">
         <v>2243</v>
-      </c>
-      <c r="D29" t="s">
-        <v>2244</v>
       </c>
       <c r="E29" t="s">
         <v>423</v>
       </c>
       <c r="F29" t="s">
-        <v>2431</v>
-      </c>
-      <c r="G29">
-        <v>28</v>
+        <v>2407</v>
+      </c>
+      <c r="G29" t="s">
+        <v>2446</v>
       </c>
       <c r="H29" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I29">
-        <v>21</v>
-      </c>
-      <c r="J29" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I29" t="s">
+        <v>704</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M29" t="s">
-        <v>2433</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -14591,40 +14377,34 @@
         <v>721</v>
       </c>
       <c r="C30" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D30" t="s">
         <v>2245</v>
-      </c>
-      <c r="D30" t="s">
-        <v>2246</v>
       </c>
       <c r="E30" t="s">
         <v>423</v>
       </c>
       <c r="F30" t="s">
-        <v>2431</v>
-      </c>
-      <c r="G30">
-        <v>29</v>
+        <v>2407</v>
+      </c>
+      <c r="G30" t="s">
+        <v>2446</v>
       </c>
       <c r="H30" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I30">
-        <v>22</v>
-      </c>
-      <c r="J30" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I30" t="s">
+        <v>704</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L30" t="b">
-        <v>1</v>
-      </c>
-      <c r="M30" t="s">
-        <v>2434</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -14632,40 +14412,34 @@
         <v>713</v>
       </c>
       <c r="C31" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D31" t="s">
         <v>2247</v>
-      </c>
-      <c r="D31" t="s">
-        <v>2248</v>
       </c>
       <c r="E31" t="s">
         <v>423</v>
       </c>
       <c r="F31" t="s">
-        <v>2431</v>
-      </c>
-      <c r="G31">
-        <v>30</v>
+        <v>2407</v>
+      </c>
+      <c r="G31" t="s">
+        <v>2446</v>
       </c>
       <c r="H31" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I31">
-        <v>23</v>
-      </c>
-      <c r="J31" t="s">
-        <v>2249</v>
+        <v>2248</v>
+      </c>
+      <c r="I31" t="s">
+        <v>704</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M31" t="s">
-        <v>2435</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -14673,40 +14447,34 @@
         <v>709</v>
       </c>
       <c r="C32" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D32" t="s">
         <v>2250</v>
-      </c>
-      <c r="D32" t="s">
-        <v>2251</v>
       </c>
       <c r="E32" t="s">
         <v>423</v>
       </c>
       <c r="F32" t="s">
-        <v>2431</v>
-      </c>
-      <c r="G32">
-        <v>31</v>
+        <v>2407</v>
+      </c>
+      <c r="G32" t="s">
+        <v>2446</v>
       </c>
       <c r="H32" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I32">
-        <v>24</v>
-      </c>
-      <c r="J32" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I32" t="s">
+        <v>704</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L32" t="b">
-        <v>1</v>
-      </c>
-      <c r="M32" t="s">
-        <v>2436</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -14714,40 +14482,34 @@
         <v>733</v>
       </c>
       <c r="C33" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D33" t="s">
         <v>2252</v>
-      </c>
-      <c r="D33" t="s">
-        <v>2253</v>
       </c>
       <c r="E33" t="s">
         <v>423</v>
       </c>
       <c r="F33" t="s">
-        <v>2431</v>
-      </c>
-      <c r="G33">
-        <v>32</v>
+        <v>2407</v>
+      </c>
+      <c r="G33" t="s">
+        <v>2446</v>
       </c>
       <c r="H33" t="s">
-        <v>2471</v>
-      </c>
-      <c r="I33">
-        <v>25</v>
-      </c>
-      <c r="J33" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I33" t="s">
+        <v>732</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L33" t="b">
-        <v>1</v>
-      </c>
-      <c r="M33" t="s">
-        <v>2437</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -14755,10 +14517,10 @@
         <v>555</v>
       </c>
       <c r="C34" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D34" t="s">
         <v>2254</v>
-      </c>
-      <c r="D34" t="s">
-        <v>2255</v>
       </c>
       <c r="E34" t="s">
         <v>423</v>
@@ -14766,26 +14528,20 @@
       <c r="F34" t="s">
         <v>2063</v>
       </c>
-      <c r="G34">
-        <v>33</v>
+      <c r="G34" t="s">
+        <v>2445</v>
       </c>
       <c r="H34" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I34">
-        <v>2</v>
-      </c>
-      <c r="J34" t="s">
-        <v>2214</v>
-      </c>
-      <c r="K34" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L34" t="b">
+        <v>2213</v>
+      </c>
+      <c r="I34" t="s">
+        <v>512</v>
+      </c>
+      <c r="J34" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -14793,10 +14549,10 @@
         <v>524</v>
       </c>
       <c r="C35" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D35" t="s">
         <v>2256</v>
-      </c>
-      <c r="D35" t="s">
-        <v>2257</v>
       </c>
       <c r="E35" t="s">
         <v>423</v>
@@ -14804,26 +14560,20 @@
       <c r="F35" t="s">
         <v>2063</v>
       </c>
-      <c r="G35">
-        <v>34</v>
+      <c r="G35" t="s">
+        <v>2445</v>
       </c>
       <c r="H35" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I35">
-        <v>2</v>
-      </c>
-      <c r="J35" t="s">
-        <v>2214</v>
-      </c>
-      <c r="K35" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L35" t="b">
+        <v>2213</v>
+      </c>
+      <c r="I35" t="s">
+        <v>512</v>
+      </c>
+      <c r="J35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -14831,10 +14581,10 @@
         <v>520</v>
       </c>
       <c r="C36" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D36" t="s">
         <v>2258</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2259</v>
       </c>
       <c r="E36" t="s">
         <v>423</v>
@@ -14842,26 +14592,20 @@
       <c r="F36" t="s">
         <v>2063</v>
       </c>
-      <c r="G36">
-        <v>35</v>
+      <c r="G36" t="s">
+        <v>2445</v>
       </c>
       <c r="H36" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I36">
-        <v>2</v>
-      </c>
-      <c r="J36" t="s">
-        <v>2214</v>
-      </c>
-      <c r="K36" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L36" t="b">
+        <v>2213</v>
+      </c>
+      <c r="I36" t="s">
+        <v>512</v>
+      </c>
+      <c r="J36" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -14869,10 +14613,10 @@
         <v>540</v>
       </c>
       <c r="C37" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D37" t="s">
         <v>2260</v>
-      </c>
-      <c r="D37" t="s">
-        <v>2261</v>
       </c>
       <c r="E37" t="s">
         <v>423</v>
@@ -14880,26 +14624,20 @@
       <c r="F37" t="s">
         <v>2063</v>
       </c>
-      <c r="G37">
-        <v>36</v>
+      <c r="G37" t="s">
+        <v>2445</v>
       </c>
       <c r="H37" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I37">
-        <v>2</v>
-      </c>
-      <c r="J37" t="s">
-        <v>2214</v>
-      </c>
-      <c r="K37" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L37" t="b">
+        <v>2213</v>
+      </c>
+      <c r="I37" t="s">
+        <v>512</v>
+      </c>
+      <c r="J37" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -14907,10 +14645,10 @@
         <v>551</v>
       </c>
       <c r="C38" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D38" t="s">
         <v>2262</v>
-      </c>
-      <c r="D38" t="s">
-        <v>2263</v>
       </c>
       <c r="E38" t="s">
         <v>423</v>
@@ -14918,26 +14656,20 @@
       <c r="F38" t="s">
         <v>2063</v>
       </c>
-      <c r="G38">
-        <v>37</v>
+      <c r="G38" t="s">
+        <v>2445</v>
       </c>
       <c r="H38" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I38">
-        <v>2</v>
-      </c>
-      <c r="J38" t="s">
-        <v>2214</v>
-      </c>
-      <c r="K38" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L38" t="b">
+        <v>2213</v>
+      </c>
+      <c r="I38" t="s">
+        <v>512</v>
+      </c>
+      <c r="J38" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -14945,10 +14677,10 @@
         <v>536</v>
       </c>
       <c r="C39" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D39" t="s">
         <v>2264</v>
-      </c>
-      <c r="D39" t="s">
-        <v>2265</v>
       </c>
       <c r="E39" t="s">
         <v>423</v>
@@ -14956,26 +14688,20 @@
       <c r="F39" t="s">
         <v>2063</v>
       </c>
-      <c r="G39">
-        <v>38</v>
+      <c r="G39" t="s">
+        <v>2445</v>
       </c>
       <c r="H39" t="s">
-        <v>2469</v>
-      </c>
-      <c r="I39">
-        <v>2</v>
-      </c>
-      <c r="J39" t="s">
-        <v>2214</v>
-      </c>
-      <c r="K39" t="s">
-        <v>2179</v>
-      </c>
-      <c r="L39" t="b">
+        <v>2213</v>
+      </c>
+      <c r="I39" t="s">
+        <v>512</v>
+      </c>
+      <c r="J39" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -14986,7 +14712,7 @@
         <v>621</v>
       </c>
       <c r="D40" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="E40" t="s">
         <v>423</v>
@@ -14994,26 +14720,20 @@
       <c r="F40" t="s">
         <v>618</v>
       </c>
-      <c r="G40">
-        <v>39</v>
+      <c r="G40" t="s">
+        <v>2448</v>
       </c>
       <c r="H40" t="s">
-        <v>2473</v>
-      </c>
-      <c r="I40">
+        <v>2289</v>
+      </c>
+      <c r="I40" t="s">
+        <v>617</v>
+      </c>
+      <c r="J40" t="b">
         <v>1</v>
       </c>
-      <c r="J40" t="s">
-        <v>2299</v>
-      </c>
-      <c r="K40" t="s">
-        <v>2267</v>
-      </c>
-      <c r="L40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -15021,10 +14741,10 @@
         <v>752</v>
       </c>
       <c r="C41" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="D41" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="E41" t="s">
         <v>423</v>
@@ -15032,26 +14752,20 @@
       <c r="F41" t="s">
         <v>916</v>
       </c>
-      <c r="G41">
-        <v>40</v>
+      <c r="G41" t="s">
+        <v>2448</v>
       </c>
       <c r="H41" t="s">
-        <v>2473</v>
-      </c>
-      <c r="I41">
+        <v>2268</v>
+      </c>
+      <c r="I41" t="s">
+        <v>2000</v>
+      </c>
+      <c r="J41" t="b">
         <v>1</v>
       </c>
-      <c r="J41" t="s">
-        <v>2270</v>
-      </c>
-      <c r="K41" t="s">
-        <v>2271</v>
-      </c>
-      <c r="L41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -15059,10 +14773,10 @@
         <v>602</v>
       </c>
       <c r="C42" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="D42" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="E42" t="s">
         <v>423</v>
@@ -15070,26 +14784,20 @@
       <c r="F42" t="s">
         <v>601</v>
       </c>
-      <c r="G42">
-        <v>41</v>
+      <c r="G42" t="s">
+        <v>2448</v>
       </c>
       <c r="H42" t="s">
-        <v>2473</v>
-      </c>
-      <c r="I42">
-        <v>2</v>
-      </c>
-      <c r="J42" t="s">
-        <v>2270</v>
-      </c>
-      <c r="K42" t="s">
-        <v>2274</v>
-      </c>
-      <c r="L42" t="b">
+        <v>2268</v>
+      </c>
+      <c r="I42" t="s">
+        <v>2059</v>
+      </c>
+      <c r="J42" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -15097,10 +14805,10 @@
         <v>743</v>
       </c>
       <c r="C43" t="s">
-        <v>2275</v>
+        <v>2271</v>
       </c>
       <c r="D43" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="E43" t="s">
         <v>423</v>
@@ -15108,26 +14816,20 @@
       <c r="F43" t="s">
         <v>743</v>
       </c>
-      <c r="G43">
-        <v>42</v>
+      <c r="G43" t="s">
+        <v>2448</v>
       </c>
       <c r="H43" t="s">
-        <v>2473</v>
-      </c>
-      <c r="I43">
-        <v>2</v>
-      </c>
-      <c r="J43" t="s">
-        <v>2277</v>
-      </c>
-      <c r="K43" t="s">
-        <v>2278</v>
-      </c>
-      <c r="L43" t="b">
+        <v>2273</v>
+      </c>
+      <c r="I43" t="s">
+        <v>742</v>
+      </c>
+      <c r="J43" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -15135,10 +14837,10 @@
         <v>1028</v>
       </c>
       <c r="C44" t="s">
-        <v>2279</v>
+        <v>2274</v>
       </c>
       <c r="D44" t="s">
-        <v>2280</v>
+        <v>2275</v>
       </c>
       <c r="E44" t="s">
         <v>423</v>
@@ -15146,26 +14848,20 @@
       <c r="F44" t="s">
         <v>1028</v>
       </c>
-      <c r="G44">
-        <v>43</v>
+      <c r="G44" t="s">
+        <v>2448</v>
       </c>
       <c r="H44" t="s">
-        <v>2473</v>
-      </c>
-      <c r="I44">
-        <v>3</v>
-      </c>
-      <c r="J44" t="s">
-        <v>2281</v>
-      </c>
-      <c r="K44" t="s">
-        <v>2282</v>
-      </c>
-      <c r="L44" t="b">
+        <v>2276</v>
+      </c>
+      <c r="I44" t="s">
+        <v>737</v>
+      </c>
+      <c r="J44" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -15173,37 +14869,31 @@
         <v>597</v>
       </c>
       <c r="C45" t="s">
-        <v>2283</v>
+        <v>2277</v>
       </c>
       <c r="D45" t="s">
-        <v>2284</v>
+        <v>2278</v>
       </c>
       <c r="E45" t="s">
         <v>423</v>
       </c>
       <c r="F45" t="s">
-        <v>2285</v>
-      </c>
-      <c r="G45">
-        <v>44</v>
+        <v>2279</v>
+      </c>
+      <c r="G45" t="s">
+        <v>2448</v>
       </c>
       <c r="H45" t="s">
-        <v>2473</v>
-      </c>
-      <c r="I45">
-        <v>4</v>
-      </c>
-      <c r="J45" t="s">
-        <v>2270</v>
-      </c>
-      <c r="K45" t="s">
-        <v>2286</v>
-      </c>
-      <c r="L45" t="b">
+        <v>2268</v>
+      </c>
+      <c r="I45" t="s">
+        <v>2001</v>
+      </c>
+      <c r="J45" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -15211,10 +14901,10 @@
         <v>748</v>
       </c>
       <c r="C46" t="s">
-        <v>2287</v>
+        <v>2280</v>
       </c>
       <c r="D46" t="s">
-        <v>2288</v>
+        <v>2281</v>
       </c>
       <c r="E46" t="s">
         <v>423</v>
@@ -15222,29 +14912,23 @@
       <c r="F46" t="s">
         <v>748</v>
       </c>
-      <c r="G46">
-        <v>45</v>
+      <c r="G46" t="s">
+        <v>2449</v>
       </c>
       <c r="H46" t="s">
-        <v>2474</v>
-      </c>
-      <c r="I46">
+        <v>2282</v>
+      </c>
+      <c r="I46" t="s">
+        <v>747</v>
+      </c>
+      <c r="J46" t="b">
         <v>1</v>
       </c>
-      <c r="J46" t="s">
-        <v>2289</v>
-      </c>
       <c r="K46" t="s">
-        <v>2290</v>
-      </c>
-      <c r="L46" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" t="s">
-        <v>2438</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -15252,10 +14936,10 @@
         <v>498</v>
       </c>
       <c r="C47" t="s">
-        <v>2291</v>
+        <v>2283</v>
       </c>
       <c r="D47" t="s">
-        <v>2292</v>
+        <v>2284</v>
       </c>
       <c r="E47" t="s">
         <v>423</v>
@@ -15263,40 +14947,34 @@
       <c r="F47" t="s">
         <v>498</v>
       </c>
-      <c r="G47">
-        <v>46</v>
+      <c r="G47" t="s">
+        <v>2449</v>
       </c>
       <c r="H47" t="s">
-        <v>2474</v>
-      </c>
-      <c r="I47">
-        <v>2</v>
-      </c>
-      <c r="J47" t="s">
         <v>2178</v>
       </c>
+      <c r="I47" t="s">
+        <v>496</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
       <c r="K47" t="s">
-        <v>2293</v>
-      </c>
-      <c r="L47" t="b">
-        <v>1</v>
-      </c>
-      <c r="M47" t="s">
-        <v>2439</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>2440</v>
+        <v>2416</v>
       </c>
       <c r="C48" t="s">
-        <v>2294</v>
+        <v>2285</v>
       </c>
       <c r="D48" t="s">
-        <v>2295</v>
+        <v>2286</v>
       </c>
       <c r="E48" t="s">
         <v>423</v>
@@ -15304,29 +14982,23 @@
       <c r="F48" t="s">
         <v>2065</v>
       </c>
-      <c r="G48">
-        <v>47</v>
+      <c r="G48" t="s">
+        <v>2449</v>
       </c>
       <c r="H48" t="s">
-        <v>2474</v>
-      </c>
-      <c r="I48">
-        <v>3</v>
-      </c>
-      <c r="J48" t="s">
-        <v>2289</v>
+        <v>2282</v>
+      </c>
+      <c r="I48" t="s">
+        <v>565</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>2296</v>
-      </c>
-      <c r="L48" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" t="s">
-        <v>2441</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -15334,10 +15006,10 @@
         <v>613</v>
       </c>
       <c r="C49" t="s">
-        <v>2297</v>
+        <v>2287</v>
       </c>
       <c r="D49" t="s">
-        <v>2298</v>
+        <v>2288</v>
       </c>
       <c r="E49" t="s">
         <v>423</v>
@@ -15345,26 +15017,20 @@
       <c r="F49" t="s">
         <v>613</v>
       </c>
-      <c r="G49">
-        <v>48</v>
+      <c r="G49" t="s">
+        <v>2448</v>
       </c>
       <c r="H49" t="s">
-        <v>2473</v>
-      </c>
-      <c r="I49">
-        <v>3</v>
-      </c>
-      <c r="J49" t="s">
-        <v>2299</v>
-      </c>
-      <c r="K49" t="s">
-        <v>2300</v>
-      </c>
-      <c r="L49" t="b">
+        <v>2289</v>
+      </c>
+      <c r="I49" t="s">
+        <v>612</v>
+      </c>
+      <c r="J49" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -15372,10 +15038,10 @@
         <v>757</v>
       </c>
       <c r="C50" t="s">
-        <v>2301</v>
+        <v>2290</v>
       </c>
       <c r="D50" t="s">
-        <v>2302</v>
+        <v>2291</v>
       </c>
       <c r="E50" t="s">
         <v>421</v>
@@ -15383,37 +15049,31 @@
       <c r="F50" t="s">
         <v>757</v>
       </c>
-      <c r="G50">
-        <v>49</v>
+      <c r="G50" t="s">
+        <v>2450</v>
       </c>
       <c r="H50" t="s">
-        <v>2475</v>
-      </c>
-      <c r="I50">
+        <v>2178</v>
+      </c>
+      <c r="I50" t="s">
+        <v>756</v>
+      </c>
+      <c r="J50" t="b">
         <v>1</v>
       </c>
-      <c r="J50" t="s">
-        <v>2178</v>
-      </c>
-      <c r="K50" t="s">
-        <v>2303</v>
-      </c>
-      <c r="L50" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>2442</v>
+        <v>2418</v>
       </c>
       <c r="C51" t="s">
-        <v>2304</v>
+        <v>2292</v>
       </c>
       <c r="D51" t="s">
-        <v>2305</v>
+        <v>2293</v>
       </c>
       <c r="E51" t="s">
         <v>421</v>
@@ -15421,146 +15081,122 @@
       <c r="F51" t="s">
         <v>2069</v>
       </c>
-      <c r="G51">
-        <v>50</v>
+      <c r="G51" t="s">
+        <v>2451</v>
       </c>
       <c r="H51" t="s">
-        <v>2476</v>
-      </c>
-      <c r="I51">
-        <v>4</v>
-      </c>
-      <c r="J51" t="s">
-        <v>2289</v>
+        <v>2282</v>
+      </c>
+      <c r="I51" t="s">
+        <v>894</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>2306</v>
-      </c>
-      <c r="L51" t="b">
-        <v>1</v>
-      </c>
-      <c r="M51" t="s">
-        <v>2443</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>2444</v>
+        <v>2420</v>
       </c>
       <c r="C52" t="s">
-        <v>2307</v>
+        <v>2294</v>
       </c>
       <c r="D52" t="s">
-        <v>2308</v>
+        <v>2295</v>
       </c>
       <c r="E52" t="s">
         <v>421</v>
       </c>
       <c r="F52" t="s">
-        <v>2445</v>
-      </c>
-      <c r="G52">
-        <v>51</v>
+        <v>2421</v>
+      </c>
+      <c r="G52" t="s">
+        <v>2452</v>
       </c>
       <c r="H52" t="s">
-        <v>2477</v>
-      </c>
-      <c r="I52">
-        <v>20</v>
-      </c>
-      <c r="J52" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I52" t="s">
+        <v>894</v>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>2306</v>
-      </c>
-      <c r="L52" t="b">
-        <v>1</v>
-      </c>
-      <c r="M52" t="s">
-        <v>2446</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>2447</v>
+        <v>2423</v>
       </c>
       <c r="C53" t="s">
-        <v>2309</v>
+        <v>2296</v>
       </c>
       <c r="D53" t="s">
-        <v>2310</v>
+        <v>2297</v>
       </c>
       <c r="E53" t="s">
         <v>421</v>
       </c>
       <c r="F53" t="s">
-        <v>2445</v>
-      </c>
-      <c r="G53">
-        <v>52</v>
+        <v>2421</v>
+      </c>
+      <c r="G53" t="s">
+        <v>2453</v>
       </c>
       <c r="H53" t="s">
-        <v>2478</v>
-      </c>
-      <c r="I53">
-        <v>30</v>
-      </c>
-      <c r="J53" t="s">
-        <v>2190</v>
-      </c>
-      <c r="K53" t="s">
-        <v>2306</v>
-      </c>
-      <c r="L53" t="b">
+        <v>2189</v>
+      </c>
+      <c r="I53" t="s">
+        <v>894</v>
+      </c>
+      <c r="J53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>2448</v>
+        <v>2424</v>
       </c>
       <c r="C54" t="s">
-        <v>2311</v>
+        <v>2298</v>
       </c>
       <c r="D54" t="s">
-        <v>2312</v>
+        <v>2299</v>
       </c>
       <c r="E54" t="s">
         <v>421</v>
       </c>
       <c r="F54" t="s">
-        <v>2445</v>
-      </c>
-      <c r="G54">
-        <v>53</v>
+        <v>2421</v>
+      </c>
+      <c r="G54" t="s">
+        <v>2452</v>
       </c>
       <c r="H54" t="s">
-        <v>2477</v>
-      </c>
-      <c r="I54">
-        <v>21</v>
-      </c>
-      <c r="J54" t="s">
-        <v>2313</v>
-      </c>
-      <c r="K54" t="s">
-        <v>2306</v>
-      </c>
-      <c r="L54" t="b">
+        <v>2300</v>
+      </c>
+      <c r="I54" t="s">
+        <v>894</v>
+      </c>
+      <c r="J54" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -15568,10 +15204,10 @@
         <v>825</v>
       </c>
       <c r="C55" t="s">
-        <v>2314</v>
+        <v>2301</v>
       </c>
       <c r="D55" t="s">
-        <v>2315</v>
+        <v>2302</v>
       </c>
       <c r="E55" t="s">
         <v>421</v>
@@ -15579,26 +15215,20 @@
       <c r="F55" t="s">
         <v>809</v>
       </c>
-      <c r="G55">
-        <v>54</v>
+      <c r="G55" t="s">
+        <v>2454</v>
       </c>
       <c r="H55" t="s">
-        <v>2479</v>
-      </c>
-      <c r="I55">
+        <v>2178</v>
+      </c>
+      <c r="I55" t="s">
+        <v>808</v>
+      </c>
+      <c r="J55" t="b">
         <v>1</v>
       </c>
-      <c r="J55" t="s">
-        <v>2178</v>
-      </c>
-      <c r="K55" t="s">
-        <v>2316</v>
-      </c>
-      <c r="L55" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -15606,10 +15236,10 @@
         <v>810</v>
       </c>
       <c r="C56" t="s">
-        <v>2317</v>
+        <v>2303</v>
       </c>
       <c r="D56" t="s">
-        <v>2318</v>
+        <v>2304</v>
       </c>
       <c r="E56" t="s">
         <v>421</v>
@@ -15617,26 +15247,20 @@
       <c r="F56" t="s">
         <v>809</v>
       </c>
-      <c r="G56">
-        <v>55</v>
+      <c r="G56" t="s">
+        <v>2454</v>
       </c>
       <c r="H56" t="s">
-        <v>2479</v>
-      </c>
-      <c r="I56">
-        <v>2</v>
-      </c>
-      <c r="J56" t="s">
         <v>2178</v>
       </c>
-      <c r="K56" t="s">
-        <v>2316</v>
-      </c>
-      <c r="L56" t="b">
+      <c r="I56" t="s">
+        <v>808</v>
+      </c>
+      <c r="J56" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -15644,10 +15268,10 @@
         <v>818</v>
       </c>
       <c r="C57" t="s">
-        <v>2319</v>
+        <v>2305</v>
       </c>
       <c r="D57" t="s">
-        <v>2320</v>
+        <v>2306</v>
       </c>
       <c r="E57" t="s">
         <v>421</v>
@@ -15655,26 +15279,20 @@
       <c r="F57" t="s">
         <v>809</v>
       </c>
-      <c r="G57">
-        <v>56</v>
+      <c r="G57" t="s">
+        <v>2454</v>
       </c>
       <c r="H57" t="s">
-        <v>2479</v>
-      </c>
-      <c r="I57">
-        <v>3</v>
-      </c>
-      <c r="J57" t="s">
         <v>2178</v>
       </c>
-      <c r="K57" t="s">
-        <v>2316</v>
-      </c>
-      <c r="L57" t="b">
+      <c r="I57" t="s">
+        <v>808</v>
+      </c>
+      <c r="J57" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -15682,10 +15300,10 @@
         <v>829</v>
       </c>
       <c r="C58" t="s">
-        <v>2321</v>
+        <v>2307</v>
       </c>
       <c r="D58" t="s">
-        <v>2322</v>
+        <v>2308</v>
       </c>
       <c r="E58" t="s">
         <v>421</v>
@@ -15693,26 +15311,20 @@
       <c r="F58" t="s">
         <v>809</v>
       </c>
-      <c r="G58">
-        <v>57</v>
+      <c r="G58" t="s">
+        <v>2454</v>
       </c>
       <c r="H58" t="s">
-        <v>2479</v>
-      </c>
-      <c r="I58">
-        <v>4</v>
-      </c>
-      <c r="J58" t="s">
         <v>2178</v>
       </c>
-      <c r="K58" t="s">
-        <v>2316</v>
-      </c>
-      <c r="L58" t="b">
+      <c r="I58" t="s">
+        <v>808</v>
+      </c>
+      <c r="J58" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -15720,10 +15332,10 @@
         <v>814</v>
       </c>
       <c r="C59" t="s">
-        <v>2323</v>
+        <v>2309</v>
       </c>
       <c r="D59" t="s">
-        <v>2324</v>
+        <v>2310</v>
       </c>
       <c r="E59" t="s">
         <v>421</v>
@@ -15731,37 +15343,31 @@
       <c r="F59" t="s">
         <v>809</v>
       </c>
-      <c r="G59">
-        <v>58</v>
+      <c r="G59" t="s">
+        <v>2454</v>
       </c>
       <c r="H59" t="s">
-        <v>2479</v>
-      </c>
-      <c r="I59">
-        <v>5</v>
-      </c>
-      <c r="J59" t="s">
-        <v>2214</v>
-      </c>
-      <c r="K59" t="s">
-        <v>2316</v>
-      </c>
-      <c r="L59" t="b">
+        <v>2213</v>
+      </c>
+      <c r="I59" t="s">
+        <v>808</v>
+      </c>
+      <c r="J59" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>2449</v>
+        <v>2425</v>
       </c>
       <c r="C60" t="s">
-        <v>2325</v>
+        <v>2311</v>
       </c>
       <c r="D60" t="s">
-        <v>2326</v>
+        <v>2312</v>
       </c>
       <c r="E60" t="s">
         <v>421</v>
@@ -15769,26 +15375,20 @@
       <c r="F60" t="s">
         <v>809</v>
       </c>
-      <c r="G60">
-        <v>59</v>
+      <c r="G60" t="s">
+        <v>2454</v>
       </c>
       <c r="H60" t="s">
-        <v>2479</v>
-      </c>
-      <c r="I60">
-        <v>6</v>
-      </c>
-      <c r="J60" t="s">
-        <v>2327</v>
-      </c>
-      <c r="K60" t="s">
-        <v>2316</v>
-      </c>
-      <c r="L60" t="b">
+        <v>2313</v>
+      </c>
+      <c r="I60" t="s">
+        <v>808</v>
+      </c>
+      <c r="J60" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -15796,10 +15396,10 @@
         <v>917</v>
       </c>
       <c r="C61" t="s">
-        <v>2328</v>
+        <v>2314</v>
       </c>
       <c r="D61" t="s">
-        <v>2329</v>
+        <v>2315</v>
       </c>
       <c r="E61" t="s">
         <v>421</v>
@@ -15807,26 +15407,20 @@
       <c r="F61" t="s">
         <v>916</v>
       </c>
-      <c r="G61">
-        <v>60</v>
+      <c r="G61" t="s">
+        <v>2450</v>
       </c>
       <c r="H61" t="s">
-        <v>2475</v>
-      </c>
-      <c r="I61">
-        <v>5</v>
-      </c>
-      <c r="J61" t="s">
-        <v>2270</v>
-      </c>
-      <c r="K61" t="s">
-        <v>2271</v>
-      </c>
-      <c r="L61" t="b">
+        <v>2268</v>
+      </c>
+      <c r="I61" t="s">
+        <v>2000</v>
+      </c>
+      <c r="J61" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -15834,37 +15428,31 @@
         <v>846</v>
       </c>
       <c r="C62" t="s">
-        <v>2330</v>
+        <v>2316</v>
       </c>
       <c r="D62" t="s">
-        <v>2331</v>
+        <v>2317</v>
       </c>
       <c r="E62" t="s">
         <v>421</v>
       </c>
       <c r="F62" t="s">
-        <v>2285</v>
-      </c>
-      <c r="G62">
-        <v>61</v>
+        <v>2279</v>
+      </c>
+      <c r="G62" t="s">
+        <v>2450</v>
       </c>
       <c r="H62" t="s">
-        <v>2475</v>
-      </c>
-      <c r="I62">
-        <v>6</v>
-      </c>
-      <c r="J62" t="s">
-        <v>2270</v>
-      </c>
-      <c r="K62" t="s">
-        <v>2286</v>
-      </c>
-      <c r="L62" t="b">
+        <v>2268</v>
+      </c>
+      <c r="I62" t="s">
+        <v>2001</v>
+      </c>
+      <c r="J62" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -15872,10 +15460,10 @@
         <v>850</v>
       </c>
       <c r="C63" t="s">
-        <v>2332</v>
+        <v>2318</v>
       </c>
       <c r="D63" t="s">
-        <v>2333</v>
+        <v>2319</v>
       </c>
       <c r="E63" t="s">
         <v>421</v>
@@ -15883,26 +15471,20 @@
       <c r="F63" t="s">
         <v>601</v>
       </c>
-      <c r="G63">
-        <v>62</v>
+      <c r="G63" t="s">
+        <v>2450</v>
       </c>
       <c r="H63" t="s">
-        <v>2475</v>
-      </c>
-      <c r="I63">
-        <v>7</v>
-      </c>
-      <c r="J63" t="s">
-        <v>2270</v>
-      </c>
-      <c r="K63" t="s">
-        <v>2274</v>
-      </c>
-      <c r="L63" t="b">
+        <v>2268</v>
+      </c>
+      <c r="I63" t="s">
+        <v>2059</v>
+      </c>
+      <c r="J63" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -15910,10 +15492,10 @@
         <v>856</v>
       </c>
       <c r="C64" t="s">
-        <v>2334</v>
+        <v>2320</v>
       </c>
       <c r="D64" t="s">
-        <v>2335</v>
+        <v>2321</v>
       </c>
       <c r="E64" t="s">
         <v>421</v>
@@ -15921,37 +15503,31 @@
       <c r="F64" t="s">
         <v>2061</v>
       </c>
-      <c r="G64">
-        <v>63</v>
+      <c r="G64" t="s">
+        <v>2455</v>
       </c>
       <c r="H64" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I64">
+        <v>2276</v>
+      </c>
+      <c r="I64" t="s">
+        <v>860</v>
+      </c>
+      <c r="J64" t="b">
         <v>1</v>
       </c>
-      <c r="J64" t="s">
-        <v>2281</v>
-      </c>
-      <c r="K64" t="s">
-        <v>2336</v>
-      </c>
-      <c r="L64" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>2337</v>
+        <v>2322</v>
       </c>
       <c r="C65" t="s">
-        <v>2338</v>
+        <v>2323</v>
       </c>
       <c r="D65" t="s">
-        <v>2339</v>
+        <v>2324</v>
       </c>
       <c r="E65" t="s">
         <v>421</v>
@@ -15959,26 +15535,20 @@
       <c r="F65" t="s">
         <v>2061</v>
       </c>
-      <c r="G65">
-        <v>64</v>
+      <c r="G65" t="s">
+        <v>2456</v>
       </c>
       <c r="H65" t="s">
-        <v>2481</v>
-      </c>
-      <c r="I65">
-        <v>30</v>
-      </c>
-      <c r="J65" t="s">
-        <v>2190</v>
-      </c>
-      <c r="K65" t="s">
-        <v>2336</v>
-      </c>
-      <c r="L65" t="b">
+        <v>2189</v>
+      </c>
+      <c r="I65" t="s">
+        <v>860</v>
+      </c>
+      <c r="J65" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -15986,10 +15556,10 @@
         <v>885</v>
       </c>
       <c r="C66" t="s">
-        <v>2340</v>
+        <v>2325</v>
       </c>
       <c r="D66" t="s">
-        <v>2341</v>
+        <v>2326</v>
       </c>
       <c r="E66" t="s">
         <v>421</v>
@@ -15997,26 +15567,20 @@
       <c r="F66" t="s">
         <v>2064</v>
       </c>
-      <c r="G66">
-        <v>65</v>
+      <c r="G66" t="s">
+        <v>2455</v>
       </c>
       <c r="H66" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I66">
-        <v>2</v>
-      </c>
-      <c r="J66" t="s">
-        <v>2342</v>
-      </c>
-      <c r="K66" t="s">
-        <v>2343</v>
-      </c>
-      <c r="L66" t="b">
+        <v>2327</v>
+      </c>
+      <c r="I66" t="s">
+        <v>884</v>
+      </c>
+      <c r="J66" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -16024,75 +15588,63 @@
         <v>793</v>
       </c>
       <c r="C67" t="s">
-        <v>2344</v>
+        <v>2328</v>
       </c>
       <c r="D67" t="s">
-        <v>2345</v>
+        <v>2329</v>
       </c>
       <c r="E67" t="s">
         <v>421</v>
       </c>
       <c r="F67" t="s">
-        <v>2346</v>
-      </c>
-      <c r="G67">
-        <v>66</v>
+        <v>2330</v>
+      </c>
+      <c r="G67" t="s">
+        <v>2450</v>
       </c>
       <c r="H67" t="s">
-        <v>2475</v>
-      </c>
-      <c r="I67">
-        <v>8</v>
-      </c>
-      <c r="J67" t="s">
-        <v>2281</v>
-      </c>
-      <c r="K67" t="s">
-        <v>2347</v>
-      </c>
-      <c r="L67" t="b">
+        <v>2276</v>
+      </c>
+      <c r="I67" t="s">
+        <v>791</v>
+      </c>
+      <c r="J67" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>2348</v>
+        <v>2331</v>
       </c>
       <c r="C68" t="s">
-        <v>2349</v>
+        <v>2332</v>
       </c>
       <c r="D68" t="s">
-        <v>2350</v>
+        <v>2333</v>
       </c>
       <c r="E68" t="s">
         <v>421</v>
       </c>
       <c r="F68" t="s">
-        <v>2346</v>
-      </c>
-      <c r="G68">
-        <v>67</v>
+        <v>2330</v>
+      </c>
+      <c r="G68" t="s">
+        <v>2457</v>
       </c>
       <c r="H68" t="s">
-        <v>2482</v>
-      </c>
-      <c r="I68">
-        <v>31</v>
-      </c>
-      <c r="J68" t="s">
-        <v>2190</v>
-      </c>
-      <c r="K68" t="s">
-        <v>2347</v>
-      </c>
-      <c r="L68" t="b">
+        <v>2189</v>
+      </c>
+      <c r="I68" t="s">
+        <v>791</v>
+      </c>
+      <c r="J68" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -16100,10 +15652,10 @@
         <v>922</v>
       </c>
       <c r="C69" t="s">
-        <v>2351</v>
+        <v>2334</v>
       </c>
       <c r="D69" t="s">
-        <v>2352</v>
+        <v>2335</v>
       </c>
       <c r="E69" t="s">
         <v>421</v>
@@ -16111,26 +15663,20 @@
       <c r="F69" t="s">
         <v>922</v>
       </c>
-      <c r="G69">
-        <v>68</v>
+      <c r="G69" t="s">
+        <v>2450</v>
       </c>
       <c r="H69" t="s">
-        <v>2475</v>
-      </c>
-      <c r="I69">
-        <v>2</v>
-      </c>
-      <c r="J69" t="s">
-        <v>2277</v>
-      </c>
-      <c r="K69" t="s">
-        <v>2353</v>
-      </c>
-      <c r="L69" t="b">
+        <v>2273</v>
+      </c>
+      <c r="I69" t="s">
+        <v>921</v>
+      </c>
+      <c r="J69" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -16138,10 +15684,10 @@
         <v>870</v>
       </c>
       <c r="C70" t="s">
-        <v>2354</v>
+        <v>2336</v>
       </c>
       <c r="D70" t="s">
-        <v>2355</v>
+        <v>2337</v>
       </c>
       <c r="E70" t="s">
         <v>421</v>
@@ -16149,26 +15695,20 @@
       <c r="F70" t="s">
         <v>870</v>
       </c>
-      <c r="G70">
-        <v>69</v>
+      <c r="G70" t="s">
+        <v>2450</v>
       </c>
       <c r="H70" t="s">
-        <v>2475</v>
-      </c>
-      <c r="I70">
-        <v>3</v>
-      </c>
-      <c r="J70" t="s">
-        <v>2277</v>
-      </c>
-      <c r="K70" t="s">
-        <v>2356</v>
-      </c>
-      <c r="L70" t="b">
+        <v>2273</v>
+      </c>
+      <c r="I70" t="s">
+        <v>869</v>
+      </c>
+      <c r="J70" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -16176,78 +15716,66 @@
         <v>778</v>
       </c>
       <c r="C71" t="s">
-        <v>2357</v>
+        <v>2338</v>
       </c>
       <c r="D71" t="s">
-        <v>2358</v>
+        <v>2339</v>
       </c>
       <c r="E71" t="s">
         <v>421</v>
       </c>
       <c r="F71" t="s">
-        <v>2359</v>
-      </c>
-      <c r="G71">
-        <v>70</v>
+        <v>2340</v>
+      </c>
+      <c r="G71" t="s">
+        <v>2451</v>
       </c>
       <c r="H71" t="s">
-        <v>2476</v>
-      </c>
-      <c r="I71">
-        <v>5</v>
-      </c>
-      <c r="J71" t="s">
-        <v>2281</v>
+        <v>2276</v>
+      </c>
+      <c r="I71" t="s">
+        <v>782</v>
+      </c>
+      <c r="J71" t="b">
+        <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>2360</v>
-      </c>
-      <c r="L71" t="b">
-        <v>1</v>
-      </c>
-      <c r="M71" t="s">
-        <v>2450</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>2451</v>
+        <v>2427</v>
       </c>
       <c r="C72" t="s">
-        <v>2361</v>
+        <v>2341</v>
       </c>
       <c r="D72" t="s">
-        <v>2362</v>
+        <v>2342</v>
       </c>
       <c r="E72" t="s">
         <v>421</v>
       </c>
       <c r="F72" t="s">
-        <v>2359</v>
-      </c>
-      <c r="G72">
-        <v>71</v>
+        <v>2340</v>
+      </c>
+      <c r="G72" t="s">
+        <v>2453</v>
       </c>
       <c r="H72" t="s">
-        <v>2478</v>
-      </c>
-      <c r="I72">
-        <v>32</v>
-      </c>
-      <c r="J72" t="s">
-        <v>2190</v>
-      </c>
-      <c r="K72" t="s">
-        <v>2360</v>
-      </c>
-      <c r="L72" t="b">
+        <v>2189</v>
+      </c>
+      <c r="I72" t="s">
+        <v>782</v>
+      </c>
+      <c r="J72" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -16255,40 +15783,34 @@
         <v>880</v>
       </c>
       <c r="C73" t="s">
-        <v>2363</v>
+        <v>2343</v>
       </c>
       <c r="D73" t="s">
-        <v>2364</v>
+        <v>2344</v>
       </c>
       <c r="E73" t="s">
         <v>421</v>
       </c>
       <c r="F73" t="s">
-        <v>2452</v>
-      </c>
-      <c r="G73">
-        <v>72</v>
+        <v>2428</v>
+      </c>
+      <c r="G73" t="s">
+        <v>2458</v>
       </c>
       <c r="H73" t="s">
-        <v>2483</v>
-      </c>
-      <c r="I73">
-        <v>20</v>
-      </c>
-      <c r="J73" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I73" t="s">
+        <v>874</v>
+      </c>
+      <c r="J73" t="b">
+        <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>2316</v>
-      </c>
-      <c r="L73" t="b">
-        <v>1</v>
-      </c>
-      <c r="M73" t="s">
-        <v>2453</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -16296,51 +15818,45 @@
         <v>876</v>
       </c>
       <c r="C74" t="s">
-        <v>2365</v>
+        <v>2345</v>
       </c>
       <c r="D74" t="s">
-        <v>2366</v>
+        <v>2346</v>
       </c>
       <c r="E74" t="s">
         <v>421</v>
       </c>
       <c r="F74" t="s">
-        <v>2452</v>
-      </c>
-      <c r="G74">
-        <v>73</v>
+        <v>2428</v>
+      </c>
+      <c r="G74" t="s">
+        <v>2458</v>
       </c>
       <c r="H74" t="s">
-        <v>2483</v>
-      </c>
-      <c r="I74">
-        <v>21</v>
-      </c>
-      <c r="J74" t="s">
-        <v>2187</v>
+        <v>2186</v>
+      </c>
+      <c r="I74" t="s">
+        <v>874</v>
+      </c>
+      <c r="J74" t="b">
+        <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>2316</v>
-      </c>
-      <c r="L74" t="b">
-        <v>1</v>
-      </c>
-      <c r="M74" t="s">
-        <v>2454</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>2455</v>
+        <v>2431</v>
       </c>
       <c r="C75" t="s">
-        <v>2367</v>
+        <v>2347</v>
       </c>
       <c r="D75" t="s">
-        <v>2368</v>
+        <v>2348</v>
       </c>
       <c r="E75" t="s">
         <v>421</v>
@@ -16348,40 +15864,34 @@
       <c r="F75" t="s">
         <v>949</v>
       </c>
-      <c r="G75">
-        <v>74</v>
+      <c r="G75" t="s">
+        <v>2455</v>
       </c>
       <c r="H75" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I75">
-        <v>3</v>
-      </c>
-      <c r="J75" t="s">
         <v>2178</v>
       </c>
+      <c r="I75" t="s">
+        <v>947</v>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
+      </c>
       <c r="K75" t="s">
-        <v>2369</v>
-      </c>
-      <c r="L75" t="b">
-        <v>1</v>
-      </c>
-      <c r="M75" t="s">
-        <v>2456</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>2457</v>
+        <v>2433</v>
       </c>
       <c r="C76" t="s">
-        <v>2370</v>
+        <v>2349</v>
       </c>
       <c r="D76" t="s">
-        <v>2371</v>
+        <v>2350</v>
       </c>
       <c r="E76" t="s">
         <v>421</v>
@@ -16389,26 +15899,20 @@
       <c r="F76" t="s">
         <v>949</v>
       </c>
-      <c r="G76">
-        <v>75</v>
+      <c r="G76" t="s">
+        <v>2455</v>
       </c>
       <c r="H76" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I76">
-        <v>4</v>
-      </c>
-      <c r="J76" t="s">
-        <v>2372</v>
-      </c>
-      <c r="K76" t="s">
-        <v>2369</v>
-      </c>
-      <c r="L76" t="b">
+        <v>2351</v>
+      </c>
+      <c r="I76" t="s">
+        <v>947</v>
+      </c>
+      <c r="J76" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -16416,10 +15920,10 @@
         <v>1061</v>
       </c>
       <c r="C77" t="s">
-        <v>2373</v>
+        <v>2352</v>
       </c>
       <c r="D77" t="s">
-        <v>2374</v>
+        <v>2353</v>
       </c>
       <c r="E77" t="s">
         <v>421</v>
@@ -16427,37 +15931,31 @@
       <c r="F77" t="s">
         <v>949</v>
       </c>
-      <c r="G77">
-        <v>76</v>
+      <c r="G77" t="s">
+        <v>2456</v>
       </c>
       <c r="H77" t="s">
-        <v>2481</v>
-      </c>
-      <c r="I77">
-        <v>33</v>
-      </c>
-      <c r="J77" t="s">
-        <v>2190</v>
-      </c>
-      <c r="K77" t="s">
-        <v>2369</v>
-      </c>
-      <c r="L77" t="b">
+        <v>2189</v>
+      </c>
+      <c r="I77" t="s">
+        <v>947</v>
+      </c>
+      <c r="J77" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>2458</v>
+        <v>2434</v>
       </c>
       <c r="C78" t="s">
-        <v>2375</v>
+        <v>2354</v>
       </c>
       <c r="D78" t="s">
-        <v>2376</v>
+        <v>2355</v>
       </c>
       <c r="E78" t="s">
         <v>421</v>
@@ -16465,37 +15963,31 @@
       <c r="F78" t="s">
         <v>949</v>
       </c>
-      <c r="G78">
-        <v>77</v>
+      <c r="G78" t="s">
+        <v>2455</v>
       </c>
       <c r="H78" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I78">
-        <v>5</v>
-      </c>
-      <c r="J78" t="s">
-        <v>2377</v>
-      </c>
-      <c r="K78" t="s">
-        <v>2369</v>
-      </c>
-      <c r="L78" t="b">
+        <v>2356</v>
+      </c>
+      <c r="I78" t="s">
+        <v>947</v>
+      </c>
+      <c r="J78" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>2459</v>
+        <v>2435</v>
       </c>
       <c r="C79" t="s">
-        <v>2378</v>
+        <v>2357</v>
       </c>
       <c r="D79" t="s">
-        <v>2379</v>
+        <v>2358</v>
       </c>
       <c r="E79" t="s">
         <v>421</v>
@@ -16503,40 +15995,34 @@
       <c r="F79" t="s">
         <v>927</v>
       </c>
-      <c r="G79">
-        <v>78</v>
+      <c r="G79" t="s">
+        <v>2455</v>
       </c>
       <c r="H79" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I79">
-        <v>6</v>
-      </c>
-      <c r="J79" t="s">
         <v>2178</v>
       </c>
+      <c r="I79" t="s">
+        <v>926</v>
+      </c>
+      <c r="J79" t="b">
+        <v>1</v>
+      </c>
       <c r="K79" t="s">
-        <v>2380</v>
-      </c>
-      <c r="L79" t="b">
-        <v>1</v>
-      </c>
-      <c r="M79" t="s">
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>2461</v>
+        <v>2437</v>
       </c>
       <c r="C80" t="s">
-        <v>2381</v>
+        <v>2359</v>
       </c>
       <c r="D80" t="s">
-        <v>2382</v>
+        <v>2360</v>
       </c>
       <c r="E80" t="s">
         <v>421</v>
@@ -16544,40 +16030,34 @@
       <c r="F80" t="s">
         <v>927</v>
       </c>
-      <c r="G80">
-        <v>79</v>
+      <c r="G80" t="s">
+        <v>2455</v>
       </c>
       <c r="H80" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I80">
-        <v>7</v>
-      </c>
-      <c r="J80" t="s">
-        <v>2327</v>
+        <v>2313</v>
+      </c>
+      <c r="I80" t="s">
+        <v>2472</v>
+      </c>
+      <c r="J80" t="b">
+        <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>2380</v>
-      </c>
-      <c r="L80" t="b">
-        <v>1</v>
-      </c>
-      <c r="M80" t="s">
-        <v>2468</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>2462</v>
+        <v>2438</v>
       </c>
       <c r="C81" t="s">
-        <v>2383</v>
+        <v>2361</v>
       </c>
       <c r="D81" t="s">
-        <v>2384</v>
+        <v>2362</v>
       </c>
       <c r="E81" t="s">
         <v>421</v>
@@ -16585,37 +16065,31 @@
       <c r="F81" t="s">
         <v>927</v>
       </c>
-      <c r="G81">
-        <v>80</v>
+      <c r="G81" t="s">
+        <v>2455</v>
       </c>
       <c r="H81" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I81">
-        <v>8</v>
-      </c>
-      <c r="J81" t="s">
-        <v>2385</v>
-      </c>
-      <c r="K81" t="s">
-        <v>2380</v>
-      </c>
-      <c r="L81" t="b">
+        <v>2363</v>
+      </c>
+      <c r="I81" t="s">
+        <v>926</v>
+      </c>
+      <c r="J81" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>2463</v>
+        <v>2439</v>
       </c>
       <c r="C82" t="s">
-        <v>2386</v>
+        <v>2364</v>
       </c>
       <c r="D82" t="s">
-        <v>2387</v>
+        <v>2365</v>
       </c>
       <c r="E82" t="s">
         <v>421</v>
@@ -16623,185 +16097,251 @@
       <c r="F82" t="s">
         <v>927</v>
       </c>
-      <c r="G82">
-        <v>81</v>
+      <c r="G82" t="s">
+        <v>2455</v>
       </c>
       <c r="H82" t="s">
-        <v>2480</v>
-      </c>
-      <c r="I82">
-        <v>9</v>
-      </c>
-      <c r="J82" t="s">
-        <v>2199</v>
-      </c>
-      <c r="K82" t="s">
-        <v>2380</v>
-      </c>
-      <c r="L82" t="b">
+        <v>2198</v>
+      </c>
+      <c r="I82" t="s">
+        <v>2472</v>
+      </c>
+      <c r="J82" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>2464</v>
+        <v>2440</v>
       </c>
       <c r="C83" t="s">
-        <v>2388</v>
+        <v>2366</v>
       </c>
       <c r="D83" t="s">
-        <v>2389</v>
+        <v>2367</v>
       </c>
       <c r="E83" t="s">
         <v>200</v>
       </c>
       <c r="F83" t="s">
-        <v>2390</v>
-      </c>
-      <c r="G83">
-        <v>82</v>
+        <v>2368</v>
+      </c>
+      <c r="G83" t="s">
+        <v>2449</v>
       </c>
       <c r="H83" t="s">
-        <v>2474</v>
-      </c>
-      <c r="I83">
-        <v>6</v>
-      </c>
-      <c r="J83" t="s">
         <v>2178</v>
       </c>
-      <c r="K83" t="s">
-        <v>2391</v>
-      </c>
-      <c r="L83" t="b">
+      <c r="I83" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J83" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>2392</v>
+        <v>2369</v>
       </c>
       <c r="C84" t="s">
-        <v>2393</v>
+        <v>2370</v>
       </c>
       <c r="D84" t="s">
-        <v>2394</v>
+        <v>2371</v>
       </c>
       <c r="E84" t="s">
         <v>200</v>
       </c>
       <c r="F84" t="s">
-        <v>2390</v>
-      </c>
-      <c r="G84">
-        <v>83</v>
+        <v>2368</v>
+      </c>
+      <c r="G84" t="s">
+        <v>2471</v>
       </c>
       <c r="H84" t="s">
-        <v>2484</v>
-      </c>
-      <c r="I84">
-        <v>6</v>
-      </c>
-      <c r="J84" t="s">
-        <v>2219</v>
-      </c>
-      <c r="K84" t="s">
-        <v>2391</v>
-      </c>
-      <c r="L84" t="b">
+        <v>2218</v>
+      </c>
+      <c r="I84" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J84" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>2465</v>
+        <v>2441</v>
       </c>
       <c r="C85" t="s">
-        <v>2395</v>
+        <v>2372</v>
       </c>
       <c r="D85" t="s">
-        <v>2396</v>
+        <v>2373</v>
       </c>
       <c r="E85" t="s">
         <v>423</v>
       </c>
       <c r="F85" t="s">
-        <v>2466</v>
-      </c>
-      <c r="G85">
-        <v>84</v>
+        <v>2442</v>
+      </c>
+      <c r="G85" t="s">
+        <v>2459</v>
       </c>
       <c r="H85" t="s">
-        <v>2485</v>
-      </c>
-      <c r="I85">
-        <v>22</v>
-      </c>
-      <c r="J85" t="s">
-        <v>2228</v>
+        <v>2227</v>
+      </c>
+      <c r="I85" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J85" t="b">
+        <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>2391</v>
-      </c>
-      <c r="L85" t="b">
-        <v>1</v>
-      </c>
-      <c r="M85" t="s">
-        <v>2467</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>2397</v>
+        <v>2374</v>
       </c>
       <c r="C86" t="s">
-        <v>2398</v>
+        <v>2375</v>
       </c>
       <c r="D86" t="s">
-        <v>2399</v>
+        <v>2376</v>
       </c>
       <c r="E86" t="s">
         <v>421</v>
       </c>
       <c r="F86" t="s">
+        <v>2442</v>
+      </c>
+      <c r="G86" t="s">
+        <v>2452</v>
+      </c>
+      <c r="H86" t="s">
+        <v>2186</v>
+      </c>
+      <c r="I86" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J86" t="b">
+        <v>1</v>
+      </c>
+      <c r="K86" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D87" t="s">
         <v>2466</v>
       </c>
-      <c r="G86">
-        <v>85</v>
-      </c>
-      <c r="H86" t="s">
-        <v>2477</v>
-      </c>
-      <c r="I86">
-        <v>23</v>
-      </c>
-      <c r="J86" t="s">
-        <v>2187</v>
-      </c>
-      <c r="K86" t="s">
-        <v>2391</v>
-      </c>
-      <c r="L86" t="b">
+      <c r="E87" t="s">
+        <v>200</v>
+      </c>
+      <c r="F87" t="s">
+        <v>2368</v>
+      </c>
+      <c r="G87" t="s">
+        <v>2449</v>
+      </c>
+      <c r="H87" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I87" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J87" t="b">
         <v>1</v>
       </c>
-      <c r="M86" t="s">
+    </row>
+    <row r="88" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>2461</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2464</v>
+      </c>
+      <c r="D88" t="s">
+        <v>2463</v>
+      </c>
+      <c r="E88" t="s">
+        <v>200</v>
+      </c>
+      <c r="F88" t="s">
+        <v>2368</v>
+      </c>
+      <c r="G88" t="s">
+        <v>2449</v>
+      </c>
+      <c r="H88" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I88" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J88" t="b">
+        <v>1</v>
+      </c>
+      <c r="K88"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C89" t="s">
         <v>2467</v>
       </c>
+      <c r="D89" t="s">
+        <v>2468</v>
+      </c>
+      <c r="E89" t="s">
+        <v>200</v>
+      </c>
+      <c r="F89" t="s">
+        <v>2368</v>
+      </c>
+      <c r="G89" t="s">
+        <v>2449</v>
+      </c>
+      <c r="H89" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I89" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J89" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M86" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16900,16 +16440,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="33" t="s">
+      <c r="A4" t="s">
         <v>217</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" t="s">
         <v>782</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" t="s">
         <v>778</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" t="s">
         <v>2018</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -16932,7 +16472,7 @@
       <c r="B5" t="s">
         <v>2001</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" t="s">
         <v>597</v>
       </c>
       <c r="D5" t="s">
@@ -16958,7 +16498,7 @@
       <c r="B6" t="s">
         <v>2001</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" t="s">
         <v>846</v>
       </c>
       <c r="D6" t="s">
@@ -16978,16 +16518,16 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="33" t="s">
+      <c r="A7" t="s">
         <v>217</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" t="s">
         <v>869</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" t="s">
         <v>870</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" t="s">
         <v>2058</v>
       </c>
       <c r="E7" s="8" t="s">
@@ -17004,25 +16544,25 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="33" t="s">
+      <c r="A8" t="s">
         <v>217</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" t="s">
         <v>921</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" t="s">
         <v>922</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" t="s">
         <v>2058</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>2045</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" t="s">
         <v>2095</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" t="s">
         <v>2095</v>
       </c>
       <c r="H8" s="8" t="s">
@@ -17082,25 +16622,25 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="33" t="s">
+      <c r="A11" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" t="s">
         <v>791</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" t="s">
         <v>793</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" t="s">
         <v>2060</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>2046</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="F11" t="s">
         <v>2095</v>
       </c>
-      <c r="G11" s="33" t="s">
+      <c r="G11" t="s">
         <v>2095</v>
       </c>
       <c r="H11" s="8" t="s">
@@ -17108,16 +16648,16 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="33" t="s">
+      <c r="A12" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" t="s">
         <v>742</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" t="s">
         <v>743</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" t="s">
         <v>2058</v>
       </c>
       <c r="E12" s="8" t="s">
@@ -17134,16 +16674,16 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="33" t="s">
+      <c r="A13" t="s">
         <v>217</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" t="s">
         <v>884</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" t="s">
         <v>2064</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" t="s">
         <v>2058</v>
       </c>
       <c r="E13" s="8" t="s">
@@ -17253,10 +16793,10 @@
       <c r="E17" s="8" t="s">
         <v>2025</v>
       </c>
-      <c r="F17" s="33" t="s">
+      <c r="F17" t="s">
         <v>2095</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" t="s">
         <v>2095</v>
       </c>
       <c r="H17" s="8" t="s">
@@ -17279,10 +16819,10 @@
       <c r="E18" s="8" t="s">
         <v>2071</v>
       </c>
-      <c r="F18" s="33" t="s">
+      <c r="F18" t="s">
         <v>2095</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" t="s">
         <v>2095</v>
       </c>
       <c r="H18" s="8" t="s">
@@ -17305,10 +16845,10 @@
       <c r="E19" s="8" t="s">
         <v>2034</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="F19" t="s">
         <v>2095</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" t="s">
         <v>2095</v>
       </c>
       <c r="H19" s="8" t="s">
@@ -17409,10 +16949,10 @@
       <c r="E23" s="8" t="s">
         <v>2075</v>
       </c>
-      <c r="F23" s="33" t="s">
+      <c r="F23" t="s">
         <v>2095</v>
       </c>
-      <c r="G23" s="33" t="s">
+      <c r="G23" t="s">
         <v>2095</v>
       </c>
       <c r="H23" s="8" t="s">
@@ -17461,10 +17001,10 @@
       <c r="E25" s="8" t="s">
         <v>2032</v>
       </c>
-      <c r="F25" s="33" t="s">
+      <c r="F25" t="s">
         <v>2095</v>
       </c>
-      <c r="G25" s="33" t="s">
+      <c r="G25" t="s">
         <v>2095</v>
       </c>
       <c r="H25" s="8" t="s">
@@ -17487,10 +17027,10 @@
       <c r="E26" s="8" t="s">
         <v>2079</v>
       </c>
-      <c r="F26" s="33" t="s">
+      <c r="F26" t="s">
         <v>2095</v>
       </c>
-      <c r="G26" s="33" t="s">
+      <c r="G26" t="s">
         <v>2095</v>
       </c>
       <c r="H26" s="8" t="s">
@@ -17513,10 +17053,10 @@
       <c r="E27" s="8" t="s">
         <v>2033</v>
       </c>
-      <c r="F27" s="33" t="s">
+      <c r="F27" t="s">
         <v>2095</v>
       </c>
-      <c r="G27" s="33" t="s">
+      <c r="G27" t="s">
         <v>2095</v>
       </c>
       <c r="H27" s="8" t="s">
@@ -17539,10 +17079,10 @@
       <c r="E28" s="8" t="s">
         <v>2080</v>
       </c>
-      <c r="F28" s="33" t="s">
+      <c r="F28" t="s">
         <v>2095</v>
       </c>
-      <c r="G28" s="33" t="s">
+      <c r="G28" t="s">
         <v>2095</v>
       </c>
       <c r="H28" s="8" t="s">
@@ -17565,10 +17105,10 @@
       <c r="E29" s="8" t="s">
         <v>2081</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="F29" t="s">
         <v>2095</v>
       </c>
-      <c r="G29" s="33" t="s">
+      <c r="G29" t="s">
         <v>2095</v>
       </c>
       <c r="H29" s="8" t="s">
@@ -17591,10 +17131,10 @@
       <c r="E30" s="8" t="s">
         <v>2082</v>
       </c>
-      <c r="F30" s="33" t="s">
+      <c r="F30" t="s">
         <v>2095</v>
       </c>
-      <c r="G30" s="33" t="s">
+      <c r="G30" t="s">
         <v>2095</v>
       </c>
       <c r="H30" s="8" t="s">
@@ -17617,10 +17157,10 @@
       <c r="E31" s="8" t="s">
         <v>2083</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="F31" t="s">
         <v>2095</v>
       </c>
-      <c r="G31" s="33" t="s">
+      <c r="G31" t="s">
         <v>2095</v>
       </c>
       <c r="H31" s="8" t="s">
@@ -17643,10 +17183,10 @@
       <c r="E32" s="8" t="s">
         <v>2035</v>
       </c>
-      <c r="F32" s="33" t="s">
+      <c r="F32" t="s">
         <v>2095</v>
       </c>
-      <c r="G32" s="33" t="s">
+      <c r="G32" t="s">
         <v>2095</v>
       </c>
       <c r="H32" s="8" t="s">
@@ -17669,10 +17209,10 @@
       <c r="E33" s="8" t="s">
         <v>2084</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="F33" t="s">
         <v>2095</v>
       </c>
-      <c r="G33" s="33" t="s">
+      <c r="G33" t="s">
         <v>2095</v>
       </c>
       <c r="H33" s="8" t="s">
@@ -17695,10 +17235,10 @@
       <c r="E34" s="8" t="s">
         <v>2085</v>
       </c>
-      <c r="F34" s="33" t="s">
+      <c r="F34" t="s">
         <v>2095</v>
       </c>
-      <c r="G34" s="33" t="s">
+      <c r="G34" t="s">
         <v>2095</v>
       </c>
     </row>
@@ -17718,10 +17258,10 @@
       <c r="E35" s="8" t="s">
         <v>2086</v>
       </c>
-      <c r="F35" s="33" t="s">
+      <c r="F35" t="s">
         <v>2095</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" t="s">
         <v>2095</v>
       </c>
       <c r="H35" s="8" t="s">
@@ -17744,10 +17284,10 @@
       <c r="E36" s="8" t="s">
         <v>2087</v>
       </c>
-      <c r="F36" s="33" t="s">
+      <c r="F36" t="s">
         <v>2095</v>
       </c>
-      <c r="G36" s="33" t="s">
+      <c r="G36" t="s">
         <v>2095</v>
       </c>
       <c r="H36" s="8" t="s">
@@ -17770,10 +17310,10 @@
       <c r="E37" s="8" t="s">
         <v>2088</v>
       </c>
-      <c r="F37" s="33" t="s">
+      <c r="F37" t="s">
         <v>2095</v>
       </c>
-      <c r="G37" s="33" t="s">
+      <c r="G37" t="s">
         <v>2095</v>
       </c>
       <c r="H37" s="8" t="s">
@@ -17822,10 +17362,10 @@
       <c r="E39" s="8" t="s">
         <v>2092</v>
       </c>
-      <c r="F39" s="33" t="s">
+      <c r="F39" t="s">
         <v>2095</v>
       </c>
-      <c r="G39" s="33" t="s">
+      <c r="G39" t="s">
         <v>2095</v>
       </c>
       <c r="H39" s="8" t="s">
@@ -17848,10 +17388,10 @@
       <c r="E40" s="8" t="s">
         <v>2093</v>
       </c>
-      <c r="F40" s="33" t="s">
+      <c r="F40" t="s">
         <v>2095</v>
       </c>
-      <c r="G40" s="33" t="s">
+      <c r="G40" t="s">
         <v>2095</v>
       </c>
       <c r="H40" s="8" t="s">
@@ -17874,10 +17414,10 @@
       <c r="E41" s="8" t="s">
         <v>2094</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" t="s">
         <v>2095</v>
       </c>
-      <c r="G41" s="33" t="s">
+      <c r="G41" t="s">
         <v>2095</v>
       </c>
       <c r="H41" s="8" t="s">
@@ -38667,24 +38207,25 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55941987-30AF-6648-9A85-31A79E0640F5}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="62.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="66.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="88.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="88.33203125" customWidth="1"/>
-    <col min="10" max="10" width="53.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="62.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="66.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="88.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="88.33203125" customWidth="1"/>
+    <col min="11" max="11" width="53.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2115</v>
       </c>
@@ -38698,31 +38239,34 @@
         <v>2118</v>
       </c>
       <c r="E1" t="s">
-        <v>2401</v>
+        <v>0</v>
       </c>
       <c r="F1" t="s">
+        <v>2378</v>
+      </c>
+      <c r="G1" t="s">
         <v>146</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>2119</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>2120</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>2166</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>2121</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>2122</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>2123</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2151</v>
       </c>
@@ -38735,29 +38279,29 @@
       <c r="D2" t="s">
         <v>2156</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>2400</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="F2" s="6" t="s">
+        <v>2377</v>
+      </c>
+      <c r="G2" t="s">
         <v>2124</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>2125</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>2126</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>2127</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>2128</v>
       </c>
-      <c r="L2" t="b">
+      <c r="M2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2152</v>
       </c>
@@ -38770,29 +38314,29 @@
       <c r="D3" t="s">
         <v>2156</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>2160</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>2129</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>2130</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>2131</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>2132</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>2133</v>
       </c>
-      <c r="L3" t="b">
+      <c r="M3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2153</v>
       </c>
@@ -38805,29 +38349,29 @@
       <c r="D4" t="s">
         <v>2157</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>2161</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>2134</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>2135</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>2136</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>2137</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>2138</v>
       </c>
-      <c r="L4" t="b">
+      <c r="M4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2154</v>
       </c>
@@ -38840,29 +38384,29 @@
       <c r="D5" t="s">
         <v>2158</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>2162</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>2139</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>2140</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>2141</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>2142</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>2143</v>
       </c>
-      <c r="L5" t="b">
+      <c r="M5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2155</v>
       </c>
@@ -38875,29 +38419,29 @@
       <c r="D6" t="s">
         <v>2159</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>2163</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>2144</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>2145</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>2146</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>2147</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>2148</v>
       </c>
-      <c r="L6" t="b">
+      <c r="M6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>2167</v>
       </c>
@@ -38910,37 +38454,37 @@
       <c r="D7" t="s">
         <v>2168</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>2169</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>2170</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>2173</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>2174</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>2175</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>2171</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>2172</v>
       </c>
-      <c r="L7" t="b">
+      <c r="M7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E11" s="6"/>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F8" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{DB08D9B6-F3C8-E84F-AFA0-CD1E52770AC7}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{DB08D9B6-F3C8-E84F-AFA0-CD1E52770AC7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C524A6-9005-DC47-9396-6D0CF9F31B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EF5D34-B49C-BB42-A21F-49901975B1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31520" yWindow="1180" windowWidth="29560" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31520" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3924" uniqueCount="2473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3940" uniqueCount="2485">
   <si>
     <t>date</t>
   </si>
@@ -12590,9 +12590,6 @@
     <t>https://weverse.io/bts/live/3-215169045</t>
   </si>
   <si>
-    <t>media</t>
-  </si>
-  <si>
     <t>playlist_group</t>
   </si>
   <si>
@@ -12873,6 +12870,106 @@
   </si>
   <si>
     <t>Winter_Ahead_with_PARK_HYO_SHIN_YUNSEOKCHEOL_TRIO_.webp</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rJqlnCywaBc</t>
+  </si>
+  <si>
+    <t>Week of August 1, 2026</t>
+  </si>
+  <si>
+    <t>Even without a concert, Taehyung and Jungkook still gave us tons of content to enjoy and celebrate. From brand content, behind-the-scenes moments from the “Normal” MV shoot, to personal updates and JK Live, twice, we had another full week!💜</t>
+  </si>
+  <si>
+    <t>Doenjang Curry Pasta</t>
+  </si>
+  <si>
+    <t>35 min</t>
+  </si>
+  <si>
+    <t>doenjang_curry_pasta.png</t>
+  </si>
+  <si>
+    <t>During his December 3, 2025 Weverse Live, Jungkook experimented with creating a completely original pasta recipe using doenjang and Golden Curry. Although he enjoyed the finished dish, he concluded that the flavorful sauce paired even better with rice, showcasing his love for comforting home-style meals and playful experimentation in the kitchen.</t>
+  </si>
+  <si>
+    <t>video</t>
+  </si>
+  <si>
+    <t>Bring a pot of salted water to a boil and cook the pasta until al dente (about 8–10 minutes). Reserve some pasta water before draining.
+Dice the potato into very small cubes. Thinly slice the bacon. Julienne the onion.
+Heat olive oil over low heat and slowly sauté the bacon until lightly crisp.
+Transfer the bacon and its flavorful oil to a plate.
+Add butter (or a little more olive oil) to the pan.
+Add the onion and sauté until softened.
+Stir in the diced potatoes.
+Season with salt and black pepper.
+Cook until the potatoes begin to soften.
+Add ½ teaspoon doenjang (soybean paste) and stir until dissolved.
+Return about half of the cooked bacon together with its reserved oil.
+Pour in a splash of water.
+Add ½ teaspoon Golden Curry and stir until fully dissolved.
+Add a pinch of sugar.
+Stir in 1 tablespoon heavy cream.
+Add more water if the sauce becomes too thick.
+Bring everything to a gentle simmer.
+Add the cooked pasta.
+Add a little pasta water if needed and toss everything together.
+Cook for about 3 minutes, allowing the sauce to fully coat the noodles.
+Add red pepper flakes to taste.
+Stir in chopped parsley.
+Jungkook added about 3 more spoonfuls of water before performing mantecare—vigorously tossing the pasta until the sauce became smooth and glossy.
+Plate the pasta.
+Top with the remaining bacon and garnish with more parsley and red pepper flakes.</t>
+  </si>
+  <si>
+    <t>This was one of Jungkook's own original recipe tryouts, and throughout the live, he was skeptical about how the dish would turn out. His childhood friend from Busan was with him, and Jungkook joked that if the pasta turned out badly, they would simply order delivery afterward.
+While the curry was almost ready, he showed us the output and specified that the color looked like Danhobak-juk (Sweet Pumpkin Porridge) because of its warm golden-orange color. 
+He also mentioned several times that the sauce would probably be delicious with udon noodles.
+While eating, he said that he could have done Risotto with it. He even asked his house helper ("Emo"—a respectful Korean term meaning "Auntie") for a bowl of cooked rice, mixed it into the remaining sauce, and happily ate it. After trying it with rice, he felt the sauce actually paired better with rice than pasta.</t>
+  </si>
+  <si>
+    <t>Pasta (about 200 g)*
+1 potato, finely diced
+1 onion, julienned
+Bacon (quantity not specified)
+Olive oil (amount not specified)
+Butter (amount not specified)
+Doenjang (about ½ tsp)*
+Golden Curry (about ½ cube)*
+Heavy cream (about 1 tbsp)*
+Sugar (a pinch, as shown)
+Salt
+Black pepper
+Water
+Pasta water
+Red pepper flakes
+Parsley</t>
+  </si>
+  <si>
+    <t>A rich and creamy fusion pasta created by Jungkook, combining Korean doenjang with Japanese Golden Curry for a unique blend of savory, umami flavors.</t>
+  </si>
+  <si>
+    <t>Dice the potatoes very small so they soften quickly and naturally thicken the sauce.
+Finely sliced onions release moisture faster and develop more sweetness.
+The starch from the potatoes creates a naturally creamy texture.
+Because both doenjang and curry already contain salt, Jungkook intentionally used less pasta water than he normally would.
+The recipe also works well with udon noodles.
+The sauce can easily be transformed into a risotto by stirring cooked rice into it.
+In Korea, it's common to mix leftover rice into a flavorful soup or sauce (국물, gukmul) after finishing the noodles.
+*Estimated measurements are based on observing the livestream.
+---
+🌏 Cultural Notes
+Doenjang (된장)
+Traditional Korean fermented soybean paste with a deep, salty, umami flavor.
+Golden Curry
+A Japanese curry roux commonly sold in cube form.
+Danhobak-juk (단호박죽)
+Korean sweet pumpkin porridge.
+Mantecare
+An Italian cooking technique of vigorously tossing pasta with sauce to create a smooth, emulsified texture.
+Jjigae (찌개)
+A Korean stew, such as kimchi-jjigae.</t>
   </si>
 </sst>
 </file>
@@ -13419,10 +13516,10 @@
         <v>2193</v>
       </c>
       <c r="G1" t="s">
+        <v>2378</v>
+      </c>
+      <c r="H1" t="s">
         <v>2379</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2380</v>
       </c>
       <c r="I1" t="s">
         <v>2194</v>
@@ -13454,7 +13551,7 @@
         <v>2063</v>
       </c>
       <c r="G2" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="H2" t="s">
         <v>2178</v>
@@ -13471,7 +13568,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="C3" t="s">
         <v>2179</v>
@@ -13486,10 +13583,10 @@
         <v>2063</v>
       </c>
       <c r="G3" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="H3" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="I3" t="s">
         <v>512</v>
@@ -13503,7 +13600,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="C4" t="s">
         <v>2181</v>
@@ -13518,7 +13615,7 @@
         <v>2063</v>
       </c>
       <c r="G4" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="H4" t="s">
         <v>2195</v>
@@ -13535,7 +13632,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="C5" t="s">
         <v>2183</v>
@@ -13550,7 +13647,7 @@
         <v>2185</v>
       </c>
       <c r="G5" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H5" t="s">
         <v>2186</v>
@@ -13585,7 +13682,7 @@
         <v>2185</v>
       </c>
       <c r="G6" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="H6" t="s">
         <v>2189</v>
@@ -13602,7 +13699,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="C7" t="s">
         <v>2196</v>
@@ -13617,7 +13714,7 @@
         <v>2185</v>
       </c>
       <c r="G7" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H7" t="s">
         <v>2198</v>
@@ -13629,7 +13726,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -13637,7 +13734,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="C8" t="s">
         <v>2199</v>
@@ -13652,7 +13749,7 @@
         <v>2185</v>
       </c>
       <c r="G8" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H8" t="s">
         <v>2198</v>
@@ -13664,7 +13761,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -13687,7 +13784,7 @@
         <v>2185</v>
       </c>
       <c r="G9" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H9" t="s">
         <v>2203</v>
@@ -13719,7 +13816,7 @@
         <v>2185</v>
       </c>
       <c r="G10" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H10" t="s">
         <v>2206</v>
@@ -13751,7 +13848,7 @@
         <v>2185</v>
       </c>
       <c r="G11" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H11" t="s">
         <v>2186</v>
@@ -13763,7 +13860,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -13786,7 +13883,7 @@
         <v>2185</v>
       </c>
       <c r="G12" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H12" t="s">
         <v>2186</v>
@@ -13798,7 +13895,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -13821,7 +13918,7 @@
         <v>2063</v>
       </c>
       <c r="G13" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="H13" t="s">
         <v>2213</v>
@@ -13853,7 +13950,7 @@
         <v>2063</v>
       </c>
       <c r="G14" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="H14" t="s">
         <v>2178</v>
@@ -13885,7 +13982,7 @@
         <v>2063</v>
       </c>
       <c r="G15" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="H15" t="s">
         <v>2218</v>
@@ -13902,7 +13999,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="C16" t="s">
         <v>2219</v>
@@ -13914,10 +14011,10 @@
         <v>423</v>
       </c>
       <c r="F16" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="G16" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="H16" t="s">
         <v>2189</v>
@@ -13934,7 +14031,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="C17" t="s">
         <v>2221</v>
@@ -13946,10 +14043,10 @@
         <v>423</v>
       </c>
       <c r="F17" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="G17" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H17" t="s">
         <v>2186</v>
@@ -13961,7 +14058,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -13969,7 +14066,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="C18" t="s">
         <v>2223</v>
@@ -13981,10 +14078,10 @@
         <v>423</v>
       </c>
       <c r="F18" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="G18" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H18" t="s">
         <v>2186</v>
@@ -13996,7 +14093,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -14004,7 +14101,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="C19" t="s">
         <v>2223</v>
@@ -14016,10 +14113,10 @@
         <v>423</v>
       </c>
       <c r="F19" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="G19" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H19" t="s">
         <v>2186</v>
@@ -14031,7 +14128,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -14039,7 +14136,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="C20" t="s">
         <v>2225</v>
@@ -14051,10 +14148,10 @@
         <v>423</v>
       </c>
       <c r="F20" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="G20" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H20" t="s">
         <v>2227</v>
@@ -14071,7 +14168,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="C21" t="s">
         <v>2228</v>
@@ -14083,10 +14180,10 @@
         <v>423</v>
       </c>
       <c r="F21" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="G21" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H21" t="s">
         <v>2186</v>
@@ -14098,7 +14195,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -14106,7 +14203,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="C22" t="s">
         <v>2228</v>
@@ -14118,10 +14215,10 @@
         <v>423</v>
       </c>
       <c r="F22" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="G22" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H22" t="s">
         <v>2230</v>
@@ -14150,10 +14247,10 @@
         <v>423</v>
       </c>
       <c r="F23" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="G23" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H23" t="s">
         <v>2186</v>
@@ -14165,7 +14262,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -14173,7 +14270,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="C24" t="s">
         <v>2233</v>
@@ -14185,10 +14282,10 @@
         <v>423</v>
       </c>
       <c r="F24" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="G24" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H24" t="s">
         <v>2235</v>
@@ -14200,7 +14297,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -14223,7 +14320,7 @@
         <v>2063</v>
       </c>
       <c r="G25" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="H25" t="s">
         <v>2178</v>
@@ -14240,7 +14337,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="C26" t="s">
         <v>2238</v>
@@ -14255,7 +14352,7 @@
         <v>2063</v>
       </c>
       <c r="G26" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="H26" t="s">
         <v>2195</v>
@@ -14284,10 +14381,10 @@
         <v>423</v>
       </c>
       <c r="F27" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="G27" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="H27" t="s">
         <v>2189</v>
@@ -14316,10 +14413,10 @@
         <v>423</v>
       </c>
       <c r="F28" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="G28" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H28" t="s">
         <v>2186</v>
@@ -14331,7 +14428,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -14351,10 +14448,10 @@
         <v>423</v>
       </c>
       <c r="F29" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="G29" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H29" t="s">
         <v>2186</v>
@@ -14366,7 +14463,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -14386,10 +14483,10 @@
         <v>423</v>
       </c>
       <c r="F30" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="G30" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H30" t="s">
         <v>2186</v>
@@ -14401,7 +14498,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -14421,10 +14518,10 @@
         <v>423</v>
       </c>
       <c r="F31" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="G31" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H31" t="s">
         <v>2248</v>
@@ -14436,7 +14533,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -14456,10 +14553,10 @@
         <v>423</v>
       </c>
       <c r="F32" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="G32" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H32" t="s">
         <v>2186</v>
@@ -14471,7 +14568,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -14491,10 +14588,10 @@
         <v>423</v>
       </c>
       <c r="F33" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="G33" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H33" t="s">
         <v>2186</v>
@@ -14506,7 +14603,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -14529,7 +14626,7 @@
         <v>2063</v>
       </c>
       <c r="G34" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="H34" t="s">
         <v>2213</v>
@@ -14561,7 +14658,7 @@
         <v>2063</v>
       </c>
       <c r="G35" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="H35" t="s">
         <v>2213</v>
@@ -14593,7 +14690,7 @@
         <v>2063</v>
       </c>
       <c r="G36" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="H36" t="s">
         <v>2213</v>
@@ -14625,7 +14722,7 @@
         <v>2063</v>
       </c>
       <c r="G37" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="H37" t="s">
         <v>2213</v>
@@ -14657,7 +14754,7 @@
         <v>2063</v>
       </c>
       <c r="G38" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="H38" t="s">
         <v>2213</v>
@@ -14689,7 +14786,7 @@
         <v>2063</v>
       </c>
       <c r="G39" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="H39" t="s">
         <v>2213</v>
@@ -14721,7 +14818,7 @@
         <v>618</v>
       </c>
       <c r="G40" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="H40" t="s">
         <v>2289</v>
@@ -14753,7 +14850,7 @@
         <v>916</v>
       </c>
       <c r="G41" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="H41" t="s">
         <v>2268</v>
@@ -14785,7 +14882,7 @@
         <v>601</v>
       </c>
       <c r="G42" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="H42" t="s">
         <v>2268</v>
@@ -14817,7 +14914,7 @@
         <v>743</v>
       </c>
       <c r="G43" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="H43" t="s">
         <v>2273</v>
@@ -14849,7 +14946,7 @@
         <v>1028</v>
       </c>
       <c r="G44" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="H44" t="s">
         <v>2276</v>
@@ -14881,7 +14978,7 @@
         <v>2279</v>
       </c>
       <c r="G45" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="H45" t="s">
         <v>2268</v>
@@ -14913,7 +15010,7 @@
         <v>748</v>
       </c>
       <c r="G46" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="H46" t="s">
         <v>2282</v>
@@ -14925,7 +15022,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -14948,7 +15045,7 @@
         <v>498</v>
       </c>
       <c r="G47" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="H47" t="s">
         <v>2178</v>
@@ -14960,7 +15057,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -14968,7 +15065,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="C48" t="s">
         <v>2285</v>
@@ -14983,7 +15080,7 @@
         <v>2065</v>
       </c>
       <c r="G48" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="H48" t="s">
         <v>2282</v>
@@ -14995,7 +15092,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -15018,7 +15115,7 @@
         <v>613</v>
       </c>
       <c r="G49" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="H49" t="s">
         <v>2289</v>
@@ -15050,7 +15147,7 @@
         <v>757</v>
       </c>
       <c r="G50" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="H50" t="s">
         <v>2178</v>
@@ -15067,7 +15164,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="C51" t="s">
         <v>2292</v>
@@ -15082,7 +15179,7 @@
         <v>2069</v>
       </c>
       <c r="G51" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="H51" t="s">
         <v>2282</v>
@@ -15094,7 +15191,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -15102,7 +15199,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="C52" t="s">
         <v>2294</v>
@@ -15114,10 +15211,10 @@
         <v>421</v>
       </c>
       <c r="F52" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="G52" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="H52" t="s">
         <v>2186</v>
@@ -15129,7 +15226,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -15137,7 +15234,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="C53" t="s">
         <v>2296</v>
@@ -15149,10 +15246,10 @@
         <v>421</v>
       </c>
       <c r="F53" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="G53" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="H53" t="s">
         <v>2189</v>
@@ -15169,7 +15266,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="C54" t="s">
         <v>2298</v>
@@ -15181,10 +15278,10 @@
         <v>421</v>
       </c>
       <c r="F54" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="G54" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="H54" t="s">
         <v>2300</v>
@@ -15216,7 +15313,7 @@
         <v>809</v>
       </c>
       <c r="G55" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="H55" t="s">
         <v>2178</v>
@@ -15248,7 +15345,7 @@
         <v>809</v>
       </c>
       <c r="G56" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="H56" t="s">
         <v>2178</v>
@@ -15280,7 +15377,7 @@
         <v>809</v>
       </c>
       <c r="G57" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="H57" t="s">
         <v>2178</v>
@@ -15312,7 +15409,7 @@
         <v>809</v>
       </c>
       <c r="G58" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="H58" t="s">
         <v>2178</v>
@@ -15344,7 +15441,7 @@
         <v>809</v>
       </c>
       <c r="G59" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="H59" t="s">
         <v>2213</v>
@@ -15361,7 +15458,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="C60" t="s">
         <v>2311</v>
@@ -15376,7 +15473,7 @@
         <v>809</v>
       </c>
       <c r="G60" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="H60" t="s">
         <v>2313</v>
@@ -15408,7 +15505,7 @@
         <v>916</v>
       </c>
       <c r="G61" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="H61" t="s">
         <v>2268</v>
@@ -15440,7 +15537,7 @@
         <v>2279</v>
       </c>
       <c r="G62" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="H62" t="s">
         <v>2268</v>
@@ -15472,7 +15569,7 @@
         <v>601</v>
       </c>
       <c r="G63" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="H63" t="s">
         <v>2268</v>
@@ -15504,7 +15601,7 @@
         <v>2061</v>
       </c>
       <c r="G64" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="H64" t="s">
         <v>2276</v>
@@ -15536,7 +15633,7 @@
         <v>2061</v>
       </c>
       <c r="G65" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="H65" t="s">
         <v>2189</v>
@@ -15568,7 +15665,7 @@
         <v>2064</v>
       </c>
       <c r="G66" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="H66" t="s">
         <v>2327</v>
@@ -15600,7 +15697,7 @@
         <v>2330</v>
       </c>
       <c r="G67" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="H67" t="s">
         <v>2276</v>
@@ -15632,7 +15729,7 @@
         <v>2330</v>
       </c>
       <c r="G68" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="H68" t="s">
         <v>2189</v>
@@ -15664,7 +15761,7 @@
         <v>922</v>
       </c>
       <c r="G69" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="H69" t="s">
         <v>2273</v>
@@ -15696,7 +15793,7 @@
         <v>870</v>
       </c>
       <c r="G70" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="H70" t="s">
         <v>2273</v>
@@ -15728,7 +15825,7 @@
         <v>2340</v>
       </c>
       <c r="G71" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="H71" t="s">
         <v>2276</v>
@@ -15740,7 +15837,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
@@ -15748,7 +15845,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="C72" t="s">
         <v>2341</v>
@@ -15763,7 +15860,7 @@
         <v>2340</v>
       </c>
       <c r="G72" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="H72" t="s">
         <v>2189</v>
@@ -15792,10 +15889,10 @@
         <v>421</v>
       </c>
       <c r="F73" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="G73" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H73" t="s">
         <v>2186</v>
@@ -15807,7 +15904,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
@@ -15827,10 +15924,10 @@
         <v>421</v>
       </c>
       <c r="F74" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="G74" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H74" t="s">
         <v>2186</v>
@@ -15842,7 +15939,7 @@
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
@@ -15850,7 +15947,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="C75" t="s">
         <v>2347</v>
@@ -15865,7 +15962,7 @@
         <v>949</v>
       </c>
       <c r="G75" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="H75" t="s">
         <v>2178</v>
@@ -15877,7 +15974,7 @@
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
@@ -15885,7 +15982,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="C76" t="s">
         <v>2349</v>
@@ -15900,7 +15997,7 @@
         <v>949</v>
       </c>
       <c r="G76" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="H76" t="s">
         <v>2351</v>
@@ -15932,7 +16029,7 @@
         <v>949</v>
       </c>
       <c r="G77" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="H77" t="s">
         <v>2189</v>
@@ -15949,7 +16046,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="C78" t="s">
         <v>2354</v>
@@ -15964,7 +16061,7 @@
         <v>949</v>
       </c>
       <c r="G78" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="H78" t="s">
         <v>2356</v>
@@ -15981,7 +16078,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="C79" t="s">
         <v>2357</v>
@@ -15996,7 +16093,7 @@
         <v>927</v>
       </c>
       <c r="G79" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="H79" t="s">
         <v>2178</v>
@@ -16008,7 +16105,7 @@
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
@@ -16016,7 +16113,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="C80" t="s">
         <v>2359</v>
@@ -16031,19 +16128,19 @@
         <v>927</v>
       </c>
       <c r="G80" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="H80" t="s">
         <v>2313</v>
       </c>
       <c r="I80" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
@@ -16051,7 +16148,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="C81" t="s">
         <v>2361</v>
@@ -16066,7 +16163,7 @@
         <v>927</v>
       </c>
       <c r="G81" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="H81" t="s">
         <v>2363</v>
@@ -16083,7 +16180,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="C82" t="s">
         <v>2364</v>
@@ -16098,13 +16195,13 @@
         <v>927</v>
       </c>
       <c r="G82" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="H82" t="s">
         <v>2198</v>
       </c>
       <c r="I82" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
@@ -16115,7 +16212,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="C83" t="s">
         <v>2366</v>
@@ -16130,13 +16227,13 @@
         <v>2368</v>
       </c>
       <c r="G83" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="H83" t="s">
         <v>2178</v>
       </c>
       <c r="I83" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
@@ -16162,13 +16259,13 @@
         <v>2368</v>
       </c>
       <c r="G84" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="H84" t="s">
         <v>2218</v>
       </c>
       <c r="I84" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
@@ -16179,7 +16276,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="C85" t="s">
         <v>2372</v>
@@ -16191,22 +16288,22 @@
         <v>423</v>
       </c>
       <c r="F85" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="G85" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="H85" t="s">
         <v>2227</v>
       </c>
       <c r="I85" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -16226,22 +16323,22 @@
         <v>421</v>
       </c>
       <c r="F86" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="G86" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="H86" t="s">
         <v>2186</v>
       </c>
       <c r="I86" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
@@ -16249,13 +16346,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="C87" t="s">
+        <v>2464</v>
+      </c>
+      <c r="D87" t="s">
         <v>2465</v>
-      </c>
-      <c r="D87" t="s">
-        <v>2466</v>
       </c>
       <c r="E87" t="s">
         <v>200</v>
@@ -16264,13 +16361,13 @@
         <v>2368</v>
       </c>
       <c r="G87" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="H87" t="s">
         <v>2178</v>
       </c>
       <c r="I87" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
@@ -16281,13 +16378,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="C88" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="D88" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="E88" t="s">
         <v>200</v>
@@ -16296,13 +16393,13 @@
         <v>2368</v>
       </c>
       <c r="G88" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="H88" t="s">
         <v>2178</v>
       </c>
       <c r="I88" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
@@ -16314,13 +16411,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="C89" t="s">
+        <v>2466</v>
+      </c>
+      <c r="D89" t="s">
         <v>2467</v>
-      </c>
-      <c r="D89" t="s">
-        <v>2468</v>
       </c>
       <c r="E89" t="s">
         <v>200</v>
@@ -16329,13 +16426,13 @@
         <v>2368</v>
       </c>
       <c r="G89" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="H89" t="s">
         <v>2178</v>
       </c>
       <c r="I89" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
@@ -38207,7 +38304,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55941987-30AF-6648-9A85-31A79E0640F5}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
@@ -38216,16 +38313,17 @@
     <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" customWidth="1"/>
     <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="62.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="66.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="88.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="88.33203125" customWidth="1"/>
-    <col min="11" max="11" width="53.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="36.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.5" customWidth="1"/>
+    <col min="8" max="8" width="62.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="66.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" customWidth="1"/>
+    <col min="11" max="11" width="90.83203125" customWidth="1"/>
+    <col min="12" max="12" width="62.5" customWidth="1"/>
+    <col min="13" max="13" width="74.1640625" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2115</v>
       </c>
@@ -38242,31 +38340,34 @@
         <v>0</v>
       </c>
       <c r="F1" t="s">
-        <v>2378</v>
+        <v>147</v>
       </c>
       <c r="G1" t="s">
+        <v>2479</v>
+      </c>
+      <c r="H1" t="s">
         <v>146</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>2119</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>2120</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>2166</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>2121</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>2122</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>2123</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2151</v>
       </c>
@@ -38279,29 +38380,30 @@
       <c r="D2" t="s">
         <v>2156</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="6"/>
+      <c r="G2" s="6" t="s">
         <v>2377</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>2124</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>2125</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>2126</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>2127</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>2128</v>
       </c>
-      <c r="M2" t="b">
+      <c r="N2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2152</v>
       </c>
@@ -38317,26 +38419,26 @@
       <c r="F3" t="s">
         <v>2160</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>2129</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>2130</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>2131</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>2132</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>2133</v>
       </c>
-      <c r="M3" t="b">
+      <c r="N3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2153</v>
       </c>
@@ -38352,26 +38454,26 @@
       <c r="F4" t="s">
         <v>2161</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>2134</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>2135</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>2136</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>2137</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>2138</v>
       </c>
-      <c r="M4" t="b">
+      <c r="N4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2154</v>
       </c>
@@ -38387,26 +38489,26 @@
       <c r="F5" t="s">
         <v>2162</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>2139</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>2140</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>2141</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>2142</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>2143</v>
       </c>
-      <c r="M5" t="b">
+      <c r="N5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2155</v>
       </c>
@@ -38419,29 +38521,30 @@
       <c r="D6" t="s">
         <v>2159</v>
       </c>
+      <c r="E6" s="9"/>
       <c r="F6" t="s">
         <v>2163</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>2144</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>2145</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>2146</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>2147</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>2148</v>
       </c>
-      <c r="M6" t="b">
+      <c r="N6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>2167</v>
       </c>
@@ -38457,34 +38560,76 @@
       <c r="F7" t="s">
         <v>2169</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>2170</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>2173</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>2174</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>2175</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>2171</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" s="8" t="s">
         <v>2172</v>
       </c>
-      <c r="M7" t="b">
+      <c r="N7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="F8" s="6"/>
+    <row r="8" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2150</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2476</v>
+      </c>
+      <c r="E8" s="9">
+        <v>45994</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2477</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>2377</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>2483</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>2482</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>2480</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>2481</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>2484</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{DB08D9B6-F3C8-E84F-AFA0-CD1E52770AC7}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{0D225B07-4494-C44D-997D-1695264A8219}"/>
+    <hyperlink ref="G8" r:id="rId2" xr:uid="{F237ABC7-87F1-A443-83D7-225DCF79C51C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -71777,7 +71922,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" bestFit="1" customWidth="1"/>
@@ -71803,873 +71948,889 @@
       </c>
       <c r="G1" s="5"/>
     </row>
-    <row r="2" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
-        <v>46227</v>
+        <v>46235</v>
       </c>
       <c r="B2" t="s">
-        <v>2010</v>
+        <v>2473</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>2011</v>
+        <v>2474</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2009</v>
+        <v>2472</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B3" t="s">
-        <v>1929</v>
+        <v>2010</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1928</v>
+        <v>2011</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1930</v>
+        <v>2009</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="B4" t="s">
-        <v>1923</v>
+        <v>1929</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1924</v>
+        <v>1928</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1922</v>
+        <v>1930</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B5" t="s">
-        <v>1870</v>
+        <v>1923</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1872</v>
+        <v>1924</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1871</v>
+        <v>1922</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="B6" t="s">
-        <v>1751</v>
+        <v>1870</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1750</v>
+        <v>1872</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1752</v>
+        <v>1871</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>1751</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>5</v>
+        <v>1750</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>6</v>
+        <v>1752</v>
       </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
-        <v>46185</v>
+        <v>46192</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
-        <v>46129</v>
+        <v>46136</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
-        <v>46115</v>
+        <v>46129</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
-        <v>46094</v>
+        <v>46115</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
-        <v>46052</v>
+        <v>46059</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
+        <v>46045</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9">
         <v>46038</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C27" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9">
-        <v>46031</v>
-      </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
+        <v>46031</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" s="5"/>
+    </row>
+    <row r="29" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="9">
         <v>46024</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C29" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="9">
-        <v>46017</v>
-      </c>
-      <c r="B29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
+        <v>46017</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="5"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
         <v>46010</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>71</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D31" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="G30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9">
-        <v>46003</v>
-      </c>
-      <c r="B31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G32" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="G32" s="5"/>
     </row>
     <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
-        <v>45989</v>
+        <v>45996</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G33" s="6"/>
     </row>
     <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
-        <v>45975</v>
+        <v>45982</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G35" s="6"/>
     </row>
     <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G36" s="6"/>
     </row>
     <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
+        <v>45968</v>
+      </c>
+      <c r="B37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
         <v>45961</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C38" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D38" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="9">
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
         <v>45954</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C39" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D39" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="9">
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="9">
         <v>45947</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>96</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C40" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9">
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="9">
         <v>45940</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C41" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D41" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="G40" s="6"/>
-    </row>
-    <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="9">
-        <v>45933</v>
-      </c>
-      <c r="B41" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="G41" s="6"/>
     </row>
     <row r="42" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
+        <v>45933</v>
+      </c>
+      <c r="B42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="9">
         <v>45926</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>105</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C43" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D43" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="9">
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="9">
         <v>45919</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>108</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C44" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D44" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="G43" s="6"/>
-    </row>
-    <row r="44" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="9">
-        <v>45912</v>
-      </c>
-      <c r="B44" t="s">
-        <v>111</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="G44" s="6"/>
     </row>
     <row r="45" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
+        <v>45912</v>
+      </c>
+      <c r="B45" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="9">
         <v>45905</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C46" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G45" s="6"/>
-    </row>
-    <row r="46" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="9">
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9">
         <v>45898</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>117</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D47" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G46" s="6"/>
-    </row>
-    <row r="47" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="9">
+      <c r="G47" s="6"/>
+    </row>
+    <row r="48" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="9">
         <v>45891</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>120</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D48" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G47" s="6"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="9">
+      <c r="G48" s="6"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="9">
         <v>45884</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>123</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>123</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D49" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="G48" s="6"/>
-    </row>
-    <row r="49" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="9">
-        <v>45877</v>
-      </c>
-      <c r="B49" t="s">
-        <v>125</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="G49" s="6"/>
     </row>
     <row r="50" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
+        <v>45877</v>
+      </c>
+      <c r="B50" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G50" s="6"/>
+    </row>
+    <row r="51" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="9">
         <v>45870</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>128</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C51" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D51" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="G50" s="6"/>
-    </row>
-    <row r="51" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="9">
-        <v>45863</v>
-      </c>
-      <c r="B51" t="s">
-        <v>131</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="G51" s="6"/>
     </row>
     <row r="52" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="B52" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G52" s="6"/>
     </row>
     <row r="53" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G53" s="6"/>
     </row>
     <row r="54" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="B54" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G54" s="6"/>
     </row>
     <row r="55" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
+        <v>45842</v>
+      </c>
+      <c r="B55" t="s">
+        <v>140</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G55" s="6"/>
+    </row>
+    <row r="56" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="9">
         <v>45835</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B56" t="s">
         <v>143</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C56" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D56" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G55" s="6"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C56" s="8"/>
+      <c r="G56" s="6"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C57" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="D8" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="D9" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="D10" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
-    <hyperlink ref="D11" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
-    <hyperlink ref="D12" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
-    <hyperlink ref="D13" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
-    <hyperlink ref="D15" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
-    <hyperlink ref="D17" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
-    <hyperlink ref="D18" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
-    <hyperlink ref="D19" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
-    <hyperlink ref="D20" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
-    <hyperlink ref="D21" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
-    <hyperlink ref="D22" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
-    <hyperlink ref="D23" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
-    <hyperlink ref="D24" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
-    <hyperlink ref="D25" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
-    <hyperlink ref="D26" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
-    <hyperlink ref="D27" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
-    <hyperlink ref="D28" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
-    <hyperlink ref="D29" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
-    <hyperlink ref="D30" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
-    <hyperlink ref="D31" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
-    <hyperlink ref="D32" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
-    <hyperlink ref="D33" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
-    <hyperlink ref="D34" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
-    <hyperlink ref="D35" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
-    <hyperlink ref="D36" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
-    <hyperlink ref="D37" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
-    <hyperlink ref="D38" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
-    <hyperlink ref="D39" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
-    <hyperlink ref="D40" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
-    <hyperlink ref="D41" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
-    <hyperlink ref="D42" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
-    <hyperlink ref="D43" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
-    <hyperlink ref="D44" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
-    <hyperlink ref="D45" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
-    <hyperlink ref="D46" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
-    <hyperlink ref="D47" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
-    <hyperlink ref="D48" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
-    <hyperlink ref="D49" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
-    <hyperlink ref="D50" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
-    <hyperlink ref="D51" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
-    <hyperlink ref="D52" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
-    <hyperlink ref="D53" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
-    <hyperlink ref="D54" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
-    <hyperlink ref="D55" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
-    <hyperlink ref="D7" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
-    <hyperlink ref="D6" r:id="rId49" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
-    <hyperlink ref="D5" r:id="rId50" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
-    <hyperlink ref="D4" r:id="rId51" xr:uid="{8E240BDD-02FF-CA47-B5D9-FD7E9FCA5AEA}"/>
-    <hyperlink ref="D3" r:id="rId52" xr:uid="{77C8CFB5-83B9-D448-AFCE-DD617D9A359D}"/>
+    <hyperlink ref="D9" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="D10" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="D11" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="D12" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="D13" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="D14" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="D16" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="D18" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
+    <hyperlink ref="D19" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
+    <hyperlink ref="D20" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
+    <hyperlink ref="D21" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
+    <hyperlink ref="D22" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
+    <hyperlink ref="D23" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
+    <hyperlink ref="D24" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
+    <hyperlink ref="D25" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
+    <hyperlink ref="D26" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
+    <hyperlink ref="D27" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
+    <hyperlink ref="D28" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
+    <hyperlink ref="D29" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
+    <hyperlink ref="D30" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
+    <hyperlink ref="D31" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
+    <hyperlink ref="D32" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
+    <hyperlink ref="D33" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
+    <hyperlink ref="D34" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
+    <hyperlink ref="D35" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
+    <hyperlink ref="D36" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
+    <hyperlink ref="D37" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
+    <hyperlink ref="D38" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
+    <hyperlink ref="D39" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
+    <hyperlink ref="D40" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
+    <hyperlink ref="D41" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
+    <hyperlink ref="D42" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
+    <hyperlink ref="D43" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
+    <hyperlink ref="D44" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
+    <hyperlink ref="D45" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
+    <hyperlink ref="D46" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
+    <hyperlink ref="D47" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
+    <hyperlink ref="D48" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
+    <hyperlink ref="D49" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
+    <hyperlink ref="D50" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
+    <hyperlink ref="D51" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
+    <hyperlink ref="D52" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
+    <hyperlink ref="D53" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
+    <hyperlink ref="D54" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
+    <hyperlink ref="D55" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
+    <hyperlink ref="D56" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
+    <hyperlink ref="D8" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
+    <hyperlink ref="D7" r:id="rId49" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
+    <hyperlink ref="D6" r:id="rId50" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
+    <hyperlink ref="D5" r:id="rId51" xr:uid="{8E240BDD-02FF-CA47-B5D9-FD7E9FCA5AEA}"/>
+    <hyperlink ref="D4" r:id="rId52" xr:uid="{77C8CFB5-83B9-D448-AFCE-DD617D9A359D}"/>
+    <hyperlink ref="D3" r:id="rId53" xr:uid="{7282EB94-FBFF-C64E-9C65-3E4E1C662EA7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EF5D34-B49C-BB42-A21F-49901975B1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEA9C0D-4B2D-0048-884C-3BF8659E4A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31520" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12890,9 +12890,6 @@
     <t>doenjang_curry_pasta.png</t>
   </si>
   <si>
-    <t>During his December 3, 2025 Weverse Live, Jungkook experimented with creating a completely original pasta recipe using doenjang and Golden Curry. Although he enjoyed the finished dish, he concluded that the flavorful sauce paired even better with rice, showcasing his love for comforting home-style meals and playful experimentation in the kitchen.</t>
-  </si>
-  <si>
     <t>video</t>
   </si>
   <si>
@@ -12950,24 +12947,32 @@
     <t>A rich and creamy fusion pasta created by Jungkook, combining Korean doenjang with Japanese Golden Curry for a unique blend of savory, umami flavors.</t>
   </si>
   <si>
+    <t>Throughout the live, he playfully doubted the outcome, making viewers laugh with his reactions. Although he enjoyed the final dish, he ultimately decided the rich curry-doenjang sauce paired even better with rice than pasta.</t>
+  </si>
+  <si>
     <t>Dice the potatoes very small so they soften quickly and naturally thicken the sauce.
 Finely sliced onions release moisture faster and develop more sweetness.
 The starch from the potatoes creates a naturally creamy texture.
 Because both doenjang and curry already contain salt, Jungkook intentionally used less pasta water than he normally would.
 The recipe also works well with udon noodles.
 The sauce can easily be transformed into a risotto by stirring cooked rice into it.
-In Korea, it's common to mix leftover rice into a flavorful soup or sauce (국물, gukmul) after finishing the noodles.
+In Korea, it's common to mix rice into a flavorful soup or sauce (국물, gukmul) after finishing the noodles.
+After finishing the pasta, Jungkook jokingly mentioned that he was still hungry and suggested to his friend that they should eat kimchi-jjigae afterward.
 *Estimated measurements are based on observing the livestream.
 ---
 🌏 Cultural Notes
 Doenjang (된장)
 Traditional Korean fermented soybean paste with a deep, salty, umami flavor.
+Miso Doenjang
+A soybean paste similar to Japanese miso. While related to doenjang, miso and doenjang are distinct fermented soybean products from different culinary traditions.
 Golden Curry
 A Japanese curry roux commonly sold in cube form.
 Danhobak-juk (단호박죽)
 Korean sweet pumpkin porridge.
 Mantecare
 An Italian cooking technique of vigorously tossing pasta with sauce to create a smooth, emulsified texture.
+Gukmul (국물)
+The flavorful liquid portion of a dish, which can refer to broth, soup, or sauce depending on the context.
 Jjigae (찌개)
 A Korean stew, such as kimchi-jjigae.</t>
   </si>
@@ -38343,7 +38348,7 @@
         <v>147</v>
       </c>
       <c r="G1" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="H1" t="s">
         <v>146</v>
@@ -38605,19 +38610,19 @@
         <v>2377</v>
       </c>
       <c r="H8" s="8" t="s">
+        <v>2482</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>2481</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>2479</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>2480</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>2483</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>2482</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>2480</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>2481</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>2478</v>
       </c>
       <c r="M8" s="8" t="s">
         <v>2484</v>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEA9C0D-4B2D-0048-884C-3BF8659E4A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F785142-A355-B543-B7EE-DD6313B9C333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31520" yWindow="1180" windowWidth="29560" windowHeight="21000" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-33320" yWindow="2920" windowWidth="29560" windowHeight="19060" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3940" uniqueCount="2485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3942" uniqueCount="2486">
   <si>
     <t>date</t>
   </si>
@@ -11957,33 +11957,6 @@
     <t>jk_corner</t>
   </si>
   <si>
-    <t>Jungkook's Carbonara Buldak Pasta</t>
-  </si>
-  <si>
-    <t>Not specified</t>
-  </si>
-  <si>
-    <t>carbonara_buldak_pasta.png</t>
-  </si>
-  <si>
-    <t>A creamy and spicy pasta creation made by Jungkook and Jimin, combining Carbonara Buldak sauce with pasta, vegetables, and a rich homemade sauce.</t>
-  </si>
-  <si>
-    <t>A fun cooking collaboration between Jungkook and Jimin filled with experimentation, teamwork, and tasting moments. Jungkook and Jimin adjusted the flavor together until they found the taste they liked.</t>
-  </si>
-  <si>
-    <t>Exact measurements were not provided during the live. Quantities marked as estimates are recreated for fans who want to follow the recipe. Ingredients were based on the cooking process shown in the video.</t>
-  </si>
-  <si>
-    <t>Pasta&lt;br&gt;Carbonara Buldak Sauce (2 packets/sticks, confirmed)&lt;br&gt;Milk (~250ml estimated)&lt;br&gt;Butter (~2 tsp estimated)&lt;br&gt;Olive Oil&lt;br&gt;Garlic (2 cloves)&lt;br&gt;Onion&lt;br&gt;Mushrooms&lt;br&gt;Salt&lt;br&gt;Pepper&lt;br&gt;Pasta water</t>
-  </si>
-  <si>
-    <t>Prepare the sauce base with a small amount of olive oil, milk, butter, salt, and pepper.&lt;br&gt;Add Carbonara Buldak sauce sticks and mix until the sauce thickens.&lt;br&gt;Turn off the heat and set aside the sauce.&lt;br&gt;Boil water in a large pot, add salt, and cook the pasta.&lt;br&gt;In another pan, add oil and stir-fry garlic and onion.&lt;br&gt;Add mushrooms and cook together.&lt;br&gt;Add the prepared Carbonara sauce and mix well.&lt;br&gt;Add cooked pasta noodles and combine until evenly coated.&lt;br&gt;Adjust flavor by adding more Carbonara sauce if desired.</t>
-  </si>
-  <si>
-    <t>Jungkook explained that pasta cooked only in plain water does not absorb enough seasoning. He intentionally keeps the sauce less salty because the pasta water already contains salt.&lt;br&gt;He focused on getting the sauce consistency right before combining it with the pasta.</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=mHNCM-YALSA</t>
   </si>
   <si>
@@ -12882,9 +12855,6 @@
   </si>
   <si>
     <t>Doenjang Curry Pasta</t>
-  </si>
-  <si>
-    <t>35 min</t>
   </si>
   <si>
     <t>doenjang_curry_pasta.png</t>
@@ -12950,6 +12920,9 @@
     <t>Throughout the live, he playfully doubted the outcome, making viewers laugh with his reactions. Although he enjoyed the final dish, he ultimately decided the rich curry-doenjang sauce paired even better with rice than pasta.</t>
   </si>
   <si>
+    <t>cultural_notes</t>
+  </si>
+  <si>
     <t>Dice the potatoes very small so they soften quickly and naturally thicken the sauce.
 Finely sliced onions release moisture faster and develop more sweetness.
 The starch from the potatoes creates a naturally creamy texture.
@@ -12957,11 +12930,10 @@
 The recipe also works well with udon noodles.
 The sauce can easily be transformed into a risotto by stirring cooked rice into it.
 In Korea, it's common to mix rice into a flavorful soup or sauce (국물, gukmul) after finishing the noodles.
-After finishing the pasta, Jungkook jokingly mentioned that he was still hungry and suggested to his friend that they should eat kimchi-jjigae afterward.
-*Estimated measurements are based on observing the livestream.
----
-🌏 Cultural Notes
-Doenjang (된장)
+After finishing the pasta, Jungkook jokingly mentioned that he was still hungry and suggested to his friend that they should eat kimchi-jjigae afterward.</t>
+  </si>
+  <si>
+    <t>Doenjang (된장)
 Traditional Korean fermented soybean paste with a deep, salty, umami flavor.
 Miso Doenjang
 A soybean paste similar to Japanese miso. While related to doenjang, miso and doenjang are distinct fermented soybean products from different culinary traditions.
@@ -12975,6 +12947,212 @@
 The flavorful liquid portion of a dish, which can refer to broth, soup, or sauce depending on the context.
 Jjigae (찌개)
 A Korean stew, such as kimchi-jjigae.</t>
+  </si>
+  <si>
+    <t>Jungkook's Carbonara Buldak Pasta with BBQ &amp; War Potatoes</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Carbonara Pasta:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Pasta
+Milk (about 250 ml)*
+Butter (about 2 tsp)*
+Carbonara sauce sticks (2+ packets)*
+Olive oil
+Salt
+Black pepper
+Garlic (2 whole bulbs)*
+Onion (thinly sliced)
+Mushrooms
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BBQ Meat:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Meat
+Butcher paper
+Aluminum foil
+Olive oil
+Red wine (about 1 tsp)*
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>War Potatoes:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Rösti potatoes
+Olive oil</t>
+    </r>
+  </si>
+  <si>
+    <t>A memorable and funny cooking collaboration between Jungkook and Jimin filled with experimentation and laughter.
+Jimin helped prepare the Rösti potatoes, but his first attempt at making them into a pancake did not go as planned when the potatoes burst and splattered during cooking. After finally succeeding by covering them with a lid, he managed to cook them properly. Jungkook decided to serve them as a side dish instead, and they jokingly named them "War Potatoes."
+The two continued plating the dishes, shared the food with the staff and enjoyed the meal together.</t>
+  </si>
+  <si>
+    <t>Rösti (뢰스티)
+A traditional Swiss potato dish made from coarsely grated potatoes shaped into a flat cake and pan-fried until golden and crispy.
+War Potatoes
+Jungkook and Jimin's playful name for the Rösti potatoes after Jimin's chaotic but successful cooking attempt.
+Carbonara Buldak
+A creamy and spicy instant noodle sauce flavor from Samyang that Jungkook adapted into a pasta sauce.</t>
+  </si>
+  <si>
+    <t>carbonara_buldak_pasta.png&lt;br&gt;carbonara_buldak_meat_warpotatoes.png</t>
+  </si>
+  <si>
+    <t>A creamy and spicy pasta creation by Jungkook during Are You Sure?! Season 2 Ep.4, combining Carbonara Buldak sauce, pasta, vegetables, and a flavorful sauce.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Carbonara Pasta:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Add a small amount of olive oil to a pot.
+Add milk, butter, salt, and black pepper.
+Add Carbonara sauce sticks and cook until the sauce thickens.
+Turn off the heat and refrigerate the sauce.
+Boil water in a large pot, add salt, and cook the pasta.
+In another pan, add the meat oil and cook with garlic and red wine sauce.
+Add the prepared sauce and allow the flavors to combine.
+In a separate pan, add oil and stir-fry garlic and onion.
+Add mushrooms and cook together.
+Add the Carbonara sauce.
+Add cooked pasta noodles and mix until the sauce coats the pasta.
+Add additional Carbonara sauce if needed.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+BBQ Meat:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Spread butcher paper and wrap the meat.
+Wrap the butcher paper-covered meat again with aluminum foil.
+Cook the wrapped meat in the oven at around 70–75°C as Jungkook mentioned.
+Remove the meat from the foil and separate it before serving.
+Collect the flavorful meat oil for cooking.
+Quickly sear the meat in a pan with the prepared sauce.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>War Potatoes:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Add olive oil to a pan.
+Pan-fry Rösti potatoes until golden and crispy.
+Cover with a lid if needed to help cook evenly.</t>
+    </r>
+  </si>
+  <si>
+    <t>Jungkook prepared this meal during Are You Sure?! Season 2, with Jimin helping him with the preparation.
+Before cooking, Jungkook washed his hands and got ready to start preparing the meal.
+While looking up the cooking time for the meat, he found that it could take around 7 hours for the meat to cook and made a funny surprised expression. Jungkook being Jungkook, trusted his intuition and decided to cook it at around 70–75°C for 1.5 hours before quickly searing it.
+He also switched from cooking in a pot to a wider pan to combine the sauce and pasta more effectively.</t>
+  </si>
+  <si>
+    <t>Although the complete meal included BBQ Meat and War Potatoes, the main dish is the Carbonara Pasta. The additional sides required extra preparation time (about 1.5–2 hours), while the pasta itself was completed in approximately 40 minutes.
+Since the pasta water was already salted, Jungkook intentionally kept the sauce a little bland, knowing the pasta water would help season the final dish. He also mentioned that cooking pasta in plain water would not season the noodles properly.</t>
   </si>
 </sst>
 </file>
@@ -13503,31 +13681,31 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>2190</v>
+        <v>2181</v>
       </c>
       <c r="B1" t="s">
-        <v>2191</v>
+        <v>2182</v>
       </c>
       <c r="C1" t="s">
         <v>439</v>
       </c>
       <c r="D1" t="s">
-        <v>2192</v>
+        <v>2183</v>
       </c>
       <c r="E1" t="s">
         <v>198</v>
       </c>
       <c r="F1" t="s">
-        <v>2193</v>
+        <v>2184</v>
       </c>
       <c r="G1" t="s">
-        <v>2378</v>
+        <v>2369</v>
       </c>
       <c r="H1" t="s">
-        <v>2379</v>
+        <v>2370</v>
       </c>
       <c r="I1" t="s">
-        <v>2194</v>
+        <v>2185</v>
       </c>
       <c r="J1" t="s">
         <v>2123</v>
@@ -13544,10 +13722,10 @@
         <v>449</v>
       </c>
       <c r="C2" t="s">
-        <v>2176</v>
+        <v>2167</v>
       </c>
       <c r="D2" t="s">
-        <v>2177</v>
+        <v>2168</v>
       </c>
       <c r="E2" t="s">
         <v>423</v>
@@ -13556,10 +13734,10 @@
         <v>2063</v>
       </c>
       <c r="G2" t="s">
-        <v>2444</v>
+        <v>2435</v>
       </c>
       <c r="H2" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I2" t="s">
         <v>512</v>
@@ -13573,13 +13751,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2380</v>
+        <v>2371</v>
       </c>
       <c r="C3" t="s">
-        <v>2179</v>
+        <v>2170</v>
       </c>
       <c r="D3" t="s">
-        <v>2180</v>
+        <v>2171</v>
       </c>
       <c r="E3" t="s">
         <v>423</v>
@@ -13588,10 +13766,10 @@
         <v>2063</v>
       </c>
       <c r="G3" t="s">
-        <v>2469</v>
+        <v>2460</v>
       </c>
       <c r="H3" t="s">
-        <v>2381</v>
+        <v>2372</v>
       </c>
       <c r="I3" t="s">
         <v>512</v>
@@ -13605,13 +13783,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2382</v>
+        <v>2373</v>
       </c>
       <c r="C4" t="s">
-        <v>2181</v>
+        <v>2172</v>
       </c>
       <c r="D4" t="s">
-        <v>2182</v>
+        <v>2173</v>
       </c>
       <c r="E4" t="s">
         <v>423</v>
@@ -13620,10 +13798,10 @@
         <v>2063</v>
       </c>
       <c r="G4" t="s">
-        <v>2469</v>
+        <v>2460</v>
       </c>
       <c r="H4" t="s">
-        <v>2195</v>
+        <v>2186</v>
       </c>
       <c r="I4" t="s">
         <v>512</v>
@@ -13637,25 +13815,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2383</v>
+        <v>2374</v>
       </c>
       <c r="C5" t="s">
-        <v>2183</v>
+        <v>2174</v>
       </c>
       <c r="D5" t="s">
-        <v>2184</v>
+        <v>2175</v>
       </c>
       <c r="E5" t="s">
         <v>423</v>
       </c>
       <c r="F5" t="s">
-        <v>2185</v>
+        <v>2176</v>
       </c>
       <c r="G5" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H5" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I5" t="s">
         <v>443</v>
@@ -13664,7 +13842,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>2313</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -13675,22 +13853,22 @@
         <v>2006</v>
       </c>
       <c r="C6" t="s">
-        <v>2187</v>
+        <v>2178</v>
       </c>
       <c r="D6" t="s">
-        <v>2188</v>
+        <v>2179</v>
       </c>
       <c r="E6" t="s">
         <v>423</v>
       </c>
       <c r="F6" t="s">
-        <v>2185</v>
+        <v>2176</v>
       </c>
       <c r="G6" t="s">
-        <v>2446</v>
+        <v>2437</v>
       </c>
       <c r="H6" t="s">
-        <v>2189</v>
+        <v>2180</v>
       </c>
       <c r="I6" t="s">
         <v>443</v>
@@ -13704,25 +13882,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2384</v>
+        <v>2375</v>
       </c>
       <c r="C7" t="s">
-        <v>2196</v>
+        <v>2187</v>
       </c>
       <c r="D7" t="s">
-        <v>2197</v>
+        <v>2188</v>
       </c>
       <c r="E7" t="s">
         <v>423</v>
       </c>
       <c r="F7" t="s">
-        <v>2185</v>
+        <v>2176</v>
       </c>
       <c r="G7" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H7" t="s">
-        <v>2198</v>
+        <v>2189</v>
       </c>
       <c r="I7" t="s">
         <v>443</v>
@@ -13731,7 +13909,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>2385</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -13739,25 +13917,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2386</v>
+        <v>2377</v>
       </c>
       <c r="C8" t="s">
-        <v>2199</v>
+        <v>2190</v>
       </c>
       <c r="D8" t="s">
-        <v>2200</v>
+        <v>2191</v>
       </c>
       <c r="E8" t="s">
         <v>423</v>
       </c>
       <c r="F8" t="s">
-        <v>2185</v>
+        <v>2176</v>
       </c>
       <c r="G8" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H8" t="s">
-        <v>2198</v>
+        <v>2189</v>
       </c>
       <c r="I8" t="s">
         <v>443</v>
@@ -13766,7 +13944,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>2387</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -13777,22 +13955,22 @@
         <v>2008</v>
       </c>
       <c r="C9" t="s">
-        <v>2201</v>
+        <v>2192</v>
       </c>
       <c r="D9" t="s">
-        <v>2202</v>
+        <v>2193</v>
       </c>
       <c r="E9" t="s">
         <v>423</v>
       </c>
       <c r="F9" t="s">
-        <v>2185</v>
+        <v>2176</v>
       </c>
       <c r="G9" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H9" t="s">
-        <v>2203</v>
+        <v>2194</v>
       </c>
       <c r="I9" t="s">
         <v>443</v>
@@ -13809,22 +13987,22 @@
         <v>2007</v>
       </c>
       <c r="C10" t="s">
-        <v>2204</v>
+        <v>2195</v>
       </c>
       <c r="D10" t="s">
-        <v>2205</v>
+        <v>2196</v>
       </c>
       <c r="E10" t="s">
         <v>423</v>
       </c>
       <c r="F10" t="s">
-        <v>2185</v>
+        <v>2176</v>
       </c>
       <c r="G10" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H10" t="s">
-        <v>2206</v>
+        <v>2197</v>
       </c>
       <c r="I10" t="s">
         <v>443</v>
@@ -13841,22 +14019,22 @@
         <v>492</v>
       </c>
       <c r="C11" t="s">
-        <v>2207</v>
+        <v>2198</v>
       </c>
       <c r="D11" t="s">
-        <v>2208</v>
+        <v>2199</v>
       </c>
       <c r="E11" t="s">
         <v>423</v>
       </c>
       <c r="F11" t="s">
-        <v>2185</v>
+        <v>2176</v>
       </c>
       <c r="G11" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H11" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I11" t="s">
         <v>491</v>
@@ -13865,7 +14043,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>2388</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -13876,22 +14054,22 @@
         <v>983</v>
       </c>
       <c r="C12" t="s">
-        <v>2209</v>
+        <v>2200</v>
       </c>
       <c r="D12" t="s">
-        <v>2210</v>
+        <v>2201</v>
       </c>
       <c r="E12" t="s">
         <v>423</v>
       </c>
       <c r="F12" t="s">
-        <v>2185</v>
+        <v>2176</v>
       </c>
       <c r="G12" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H12" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I12" t="s">
         <v>486</v>
@@ -13900,7 +14078,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>2389</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -13911,10 +14089,10 @@
         <v>516</v>
       </c>
       <c r="C13" t="s">
-        <v>2211</v>
+        <v>2202</v>
       </c>
       <c r="D13" t="s">
-        <v>2212</v>
+        <v>2203</v>
       </c>
       <c r="E13" t="s">
         <v>423</v>
@@ -13923,10 +14101,10 @@
         <v>2063</v>
       </c>
       <c r="G13" t="s">
-        <v>2444</v>
+        <v>2435</v>
       </c>
       <c r="H13" t="s">
-        <v>2213</v>
+        <v>2204</v>
       </c>
       <c r="I13" t="s">
         <v>512</v>
@@ -13943,10 +14121,10 @@
         <v>626</v>
       </c>
       <c r="C14" t="s">
-        <v>2214</v>
+        <v>2205</v>
       </c>
       <c r="D14" t="s">
-        <v>2215</v>
+        <v>2206</v>
       </c>
       <c r="E14" t="s">
         <v>423</v>
@@ -13955,10 +14133,10 @@
         <v>2063</v>
       </c>
       <c r="G14" t="s">
-        <v>2444</v>
+        <v>2435</v>
       </c>
       <c r="H14" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I14" t="s">
         <v>512</v>
@@ -13975,10 +14153,10 @@
         <v>987</v>
       </c>
       <c r="C15" t="s">
-        <v>2216</v>
+        <v>2207</v>
       </c>
       <c r="D15" t="s">
-        <v>2217</v>
+        <v>2208</v>
       </c>
       <c r="E15" t="s">
         <v>423</v>
@@ -13987,10 +14165,10 @@
         <v>2063</v>
       </c>
       <c r="G15" t="s">
-        <v>2469</v>
+        <v>2460</v>
       </c>
       <c r="H15" t="s">
-        <v>2218</v>
+        <v>2209</v>
       </c>
       <c r="I15" t="s">
         <v>512</v>
@@ -14004,25 +14182,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>2390</v>
+        <v>2381</v>
       </c>
       <c r="C16" t="s">
-        <v>2219</v>
+        <v>2210</v>
       </c>
       <c r="D16" t="s">
-        <v>2220</v>
+        <v>2211</v>
       </c>
       <c r="E16" t="s">
         <v>423</v>
       </c>
       <c r="F16" t="s">
-        <v>2391</v>
+        <v>2382</v>
       </c>
       <c r="G16" t="s">
-        <v>2446</v>
+        <v>2437</v>
       </c>
       <c r="H16" t="s">
-        <v>2189</v>
+        <v>2180</v>
       </c>
       <c r="I16" t="s">
         <v>625</v>
@@ -14036,25 +14214,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>2392</v>
+        <v>2383</v>
       </c>
       <c r="C17" t="s">
-        <v>2221</v>
+        <v>2212</v>
       </c>
       <c r="D17" t="s">
-        <v>2222</v>
+        <v>2213</v>
       </c>
       <c r="E17" t="s">
         <v>423</v>
       </c>
       <c r="F17" t="s">
-        <v>2391</v>
+        <v>2382</v>
       </c>
       <c r="G17" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H17" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I17" t="s">
         <v>676</v>
@@ -14063,7 +14241,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>2393</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -14071,25 +14249,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>2394</v>
+        <v>2385</v>
       </c>
       <c r="C18" t="s">
-        <v>2223</v>
+        <v>2214</v>
       </c>
       <c r="D18" t="s">
-        <v>2224</v>
+        <v>2215</v>
       </c>
       <c r="E18" t="s">
         <v>423</v>
       </c>
       <c r="F18" t="s">
-        <v>2391</v>
+        <v>2382</v>
       </c>
       <c r="G18" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H18" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I18" t="s">
         <v>676</v>
@@ -14098,7 +14276,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>2395</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -14106,25 +14284,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>2396</v>
+        <v>2387</v>
       </c>
       <c r="C19" t="s">
-        <v>2223</v>
+        <v>2214</v>
       </c>
       <c r="D19" t="s">
-        <v>2224</v>
+        <v>2215</v>
       </c>
       <c r="E19" t="s">
         <v>423</v>
       </c>
       <c r="F19" t="s">
-        <v>2391</v>
+        <v>2382</v>
       </c>
       <c r="G19" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H19" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I19" t="s">
         <v>676</v>
@@ -14133,7 +14311,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>2397</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -14141,25 +14319,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>2398</v>
+        <v>2389</v>
       </c>
       <c r="C20" t="s">
-        <v>2225</v>
+        <v>2216</v>
       </c>
       <c r="D20" t="s">
-        <v>2226</v>
+        <v>2217</v>
       </c>
       <c r="E20" t="s">
         <v>423</v>
       </c>
       <c r="F20" t="s">
-        <v>2391</v>
+        <v>2382</v>
       </c>
       <c r="G20" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H20" t="s">
-        <v>2227</v>
+        <v>2218</v>
       </c>
       <c r="I20" t="s">
         <v>676</v>
@@ -14173,25 +14351,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>2399</v>
+        <v>2390</v>
       </c>
       <c r="C21" t="s">
-        <v>2228</v>
+        <v>2219</v>
       </c>
       <c r="D21" t="s">
-        <v>2229</v>
+        <v>2220</v>
       </c>
       <c r="E21" t="s">
         <v>423</v>
       </c>
       <c r="F21" t="s">
-        <v>2391</v>
+        <v>2382</v>
       </c>
       <c r="G21" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H21" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I21" t="s">
         <v>661</v>
@@ -14200,7 +14378,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>2400</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -14208,25 +14386,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>2401</v>
+        <v>2392</v>
       </c>
       <c r="C22" t="s">
-        <v>2228</v>
+        <v>2219</v>
       </c>
       <c r="D22" t="s">
-        <v>2229</v>
+        <v>2220</v>
       </c>
       <c r="E22" t="s">
         <v>423</v>
       </c>
       <c r="F22" t="s">
-        <v>2391</v>
+        <v>2382</v>
       </c>
       <c r="G22" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H22" t="s">
-        <v>2230</v>
+        <v>2221</v>
       </c>
       <c r="I22" t="s">
         <v>661</v>
@@ -14243,22 +14421,22 @@
         <v>656</v>
       </c>
       <c r="C23" t="s">
-        <v>2231</v>
+        <v>2222</v>
       </c>
       <c r="D23" t="s">
-        <v>2232</v>
+        <v>2223</v>
       </c>
       <c r="E23" t="s">
         <v>423</v>
       </c>
       <c r="F23" t="s">
-        <v>2391</v>
+        <v>2382</v>
       </c>
       <c r="G23" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H23" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I23" t="s">
         <v>650</v>
@@ -14267,7 +14445,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>2402</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -14275,25 +14453,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>2403</v>
+        <v>2394</v>
       </c>
       <c r="C24" t="s">
-        <v>2233</v>
+        <v>2224</v>
       </c>
       <c r="D24" t="s">
-        <v>2234</v>
+        <v>2225</v>
       </c>
       <c r="E24" t="s">
         <v>423</v>
       </c>
       <c r="F24" t="s">
-        <v>2391</v>
+        <v>2382</v>
       </c>
       <c r="G24" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H24" t="s">
-        <v>2235</v>
+        <v>2226</v>
       </c>
       <c r="I24" t="s">
         <v>650</v>
@@ -14302,7 +14480,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>2404</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -14313,10 +14491,10 @@
         <v>544</v>
       </c>
       <c r="C25" t="s">
-        <v>2236</v>
+        <v>2227</v>
       </c>
       <c r="D25" t="s">
-        <v>2237</v>
+        <v>2228</v>
       </c>
       <c r="E25" t="s">
         <v>423</v>
@@ -14325,10 +14503,10 @@
         <v>2063</v>
       </c>
       <c r="G25" t="s">
-        <v>2444</v>
+        <v>2435</v>
       </c>
       <c r="H25" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I25" t="s">
         <v>512</v>
@@ -14342,13 +14520,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>2405</v>
+        <v>2396</v>
       </c>
       <c r="C26" t="s">
-        <v>2238</v>
+        <v>2229</v>
       </c>
       <c r="D26" t="s">
-        <v>2239</v>
+        <v>2230</v>
       </c>
       <c r="E26" t="s">
         <v>423</v>
@@ -14357,10 +14535,10 @@
         <v>2063</v>
       </c>
       <c r="G26" t="s">
-        <v>2469</v>
+        <v>2460</v>
       </c>
       <c r="H26" t="s">
-        <v>2195</v>
+        <v>2186</v>
       </c>
       <c r="I26" t="s">
         <v>512</v>
@@ -14377,22 +14555,22 @@
         <v>717</v>
       </c>
       <c r="C27" t="s">
-        <v>2240</v>
+        <v>2231</v>
       </c>
       <c r="D27" t="s">
-        <v>2241</v>
+        <v>2232</v>
       </c>
       <c r="E27" t="s">
         <v>423</v>
       </c>
       <c r="F27" t="s">
-        <v>2406</v>
+        <v>2397</v>
       </c>
       <c r="G27" t="s">
-        <v>2446</v>
+        <v>2437</v>
       </c>
       <c r="H27" t="s">
-        <v>2189</v>
+        <v>2180</v>
       </c>
       <c r="I27" t="s">
         <v>704</v>
@@ -14409,22 +14587,22 @@
         <v>728</v>
       </c>
       <c r="C28" t="s">
-        <v>2242</v>
+        <v>2233</v>
       </c>
       <c r="D28" t="s">
-        <v>2243</v>
+        <v>2234</v>
       </c>
       <c r="E28" t="s">
         <v>423</v>
       </c>
       <c r="F28" t="s">
-        <v>2406</v>
+        <v>2397</v>
       </c>
       <c r="G28" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H28" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I28" t="s">
         <v>704</v>
@@ -14433,7 +14611,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>2407</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -14444,22 +14622,22 @@
         <v>725</v>
       </c>
       <c r="C29" t="s">
-        <v>2242</v>
+        <v>2233</v>
       </c>
       <c r="D29" t="s">
-        <v>2243</v>
+        <v>2234</v>
       </c>
       <c r="E29" t="s">
         <v>423</v>
       </c>
       <c r="F29" t="s">
-        <v>2406</v>
+        <v>2397</v>
       </c>
       <c r="G29" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H29" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I29" t="s">
         <v>704</v>
@@ -14468,7 +14646,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>2408</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -14479,22 +14657,22 @@
         <v>721</v>
       </c>
       <c r="C30" t="s">
-        <v>2244</v>
+        <v>2235</v>
       </c>
       <c r="D30" t="s">
-        <v>2245</v>
+        <v>2236</v>
       </c>
       <c r="E30" t="s">
         <v>423</v>
       </c>
       <c r="F30" t="s">
-        <v>2406</v>
+        <v>2397</v>
       </c>
       <c r="G30" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H30" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I30" t="s">
         <v>704</v>
@@ -14503,7 +14681,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>2409</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -14514,22 +14692,22 @@
         <v>713</v>
       </c>
       <c r="C31" t="s">
-        <v>2246</v>
+        <v>2237</v>
       </c>
       <c r="D31" t="s">
-        <v>2247</v>
+        <v>2238</v>
       </c>
       <c r="E31" t="s">
         <v>423</v>
       </c>
       <c r="F31" t="s">
-        <v>2406</v>
+        <v>2397</v>
       </c>
       <c r="G31" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H31" t="s">
-        <v>2248</v>
+        <v>2239</v>
       </c>
       <c r="I31" t="s">
         <v>704</v>
@@ -14538,7 +14716,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>2410</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -14549,22 +14727,22 @@
         <v>709</v>
       </c>
       <c r="C32" t="s">
-        <v>2249</v>
+        <v>2240</v>
       </c>
       <c r="D32" t="s">
-        <v>2250</v>
+        <v>2241</v>
       </c>
       <c r="E32" t="s">
         <v>423</v>
       </c>
       <c r="F32" t="s">
-        <v>2406</v>
+        <v>2397</v>
       </c>
       <c r="G32" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H32" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I32" t="s">
         <v>704</v>
@@ -14573,7 +14751,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>2411</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -14584,22 +14762,22 @@
         <v>733</v>
       </c>
       <c r="C33" t="s">
-        <v>2251</v>
+        <v>2242</v>
       </c>
       <c r="D33" t="s">
-        <v>2252</v>
+        <v>2243</v>
       </c>
       <c r="E33" t="s">
         <v>423</v>
       </c>
       <c r="F33" t="s">
-        <v>2406</v>
+        <v>2397</v>
       </c>
       <c r="G33" t="s">
-        <v>2445</v>
+        <v>2436</v>
       </c>
       <c r="H33" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I33" t="s">
         <v>732</v>
@@ -14608,7 +14786,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>2412</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -14619,10 +14797,10 @@
         <v>555</v>
       </c>
       <c r="C34" t="s">
-        <v>2253</v>
+        <v>2244</v>
       </c>
       <c r="D34" t="s">
-        <v>2254</v>
+        <v>2245</v>
       </c>
       <c r="E34" t="s">
         <v>423</v>
@@ -14631,10 +14809,10 @@
         <v>2063</v>
       </c>
       <c r="G34" t="s">
-        <v>2444</v>
+        <v>2435</v>
       </c>
       <c r="H34" t="s">
-        <v>2213</v>
+        <v>2204</v>
       </c>
       <c r="I34" t="s">
         <v>512</v>
@@ -14651,10 +14829,10 @@
         <v>524</v>
       </c>
       <c r="C35" t="s">
-        <v>2255</v>
+        <v>2246</v>
       </c>
       <c r="D35" t="s">
-        <v>2256</v>
+        <v>2247</v>
       </c>
       <c r="E35" t="s">
         <v>423</v>
@@ -14663,10 +14841,10 @@
         <v>2063</v>
       </c>
       <c r="G35" t="s">
-        <v>2444</v>
+        <v>2435</v>
       </c>
       <c r="H35" t="s">
-        <v>2213</v>
+        <v>2204</v>
       </c>
       <c r="I35" t="s">
         <v>512</v>
@@ -14683,10 +14861,10 @@
         <v>520</v>
       </c>
       <c r="C36" t="s">
-        <v>2257</v>
+        <v>2248</v>
       </c>
       <c r="D36" t="s">
-        <v>2258</v>
+        <v>2249</v>
       </c>
       <c r="E36" t="s">
         <v>423</v>
@@ -14695,10 +14873,10 @@
         <v>2063</v>
       </c>
       <c r="G36" t="s">
-        <v>2444</v>
+        <v>2435</v>
       </c>
       <c r="H36" t="s">
-        <v>2213</v>
+        <v>2204</v>
       </c>
       <c r="I36" t="s">
         <v>512</v>
@@ -14715,10 +14893,10 @@
         <v>540</v>
       </c>
       <c r="C37" t="s">
-        <v>2259</v>
+        <v>2250</v>
       </c>
       <c r="D37" t="s">
-        <v>2260</v>
+        <v>2251</v>
       </c>
       <c r="E37" t="s">
         <v>423</v>
@@ -14727,10 +14905,10 @@
         <v>2063</v>
       </c>
       <c r="G37" t="s">
-        <v>2444</v>
+        <v>2435</v>
       </c>
       <c r="H37" t="s">
-        <v>2213</v>
+        <v>2204</v>
       </c>
       <c r="I37" t="s">
         <v>512</v>
@@ -14747,10 +14925,10 @@
         <v>551</v>
       </c>
       <c r="C38" t="s">
-        <v>2261</v>
+        <v>2252</v>
       </c>
       <c r="D38" t="s">
-        <v>2262</v>
+        <v>2253</v>
       </c>
       <c r="E38" t="s">
         <v>423</v>
@@ -14759,10 +14937,10 @@
         <v>2063</v>
       </c>
       <c r="G38" t="s">
-        <v>2444</v>
+        <v>2435</v>
       </c>
       <c r="H38" t="s">
-        <v>2213</v>
+        <v>2204</v>
       </c>
       <c r="I38" t="s">
         <v>512</v>
@@ -14779,10 +14957,10 @@
         <v>536</v>
       </c>
       <c r="C39" t="s">
-        <v>2263</v>
+        <v>2254</v>
       </c>
       <c r="D39" t="s">
-        <v>2264</v>
+        <v>2255</v>
       </c>
       <c r="E39" t="s">
         <v>423</v>
@@ -14791,10 +14969,10 @@
         <v>2063</v>
       </c>
       <c r="G39" t="s">
-        <v>2444</v>
+        <v>2435</v>
       </c>
       <c r="H39" t="s">
-        <v>2213</v>
+        <v>2204</v>
       </c>
       <c r="I39" t="s">
         <v>512</v>
@@ -14814,7 +14992,7 @@
         <v>621</v>
       </c>
       <c r="D40" t="s">
-        <v>2265</v>
+        <v>2256</v>
       </c>
       <c r="E40" t="s">
         <v>423</v>
@@ -14823,10 +15001,10 @@
         <v>618</v>
       </c>
       <c r="G40" t="s">
-        <v>2447</v>
+        <v>2438</v>
       </c>
       <c r="H40" t="s">
-        <v>2289</v>
+        <v>2280</v>
       </c>
       <c r="I40" t="s">
         <v>617</v>
@@ -14843,10 +15021,10 @@
         <v>752</v>
       </c>
       <c r="C41" t="s">
-        <v>2266</v>
+        <v>2257</v>
       </c>
       <c r="D41" t="s">
-        <v>2267</v>
+        <v>2258</v>
       </c>
       <c r="E41" t="s">
         <v>423</v>
@@ -14855,10 +15033,10 @@
         <v>916</v>
       </c>
       <c r="G41" t="s">
-        <v>2447</v>
+        <v>2438</v>
       </c>
       <c r="H41" t="s">
-        <v>2268</v>
+        <v>2259</v>
       </c>
       <c r="I41" t="s">
         <v>2000</v>
@@ -14875,10 +15053,10 @@
         <v>602</v>
       </c>
       <c r="C42" t="s">
-        <v>2269</v>
+        <v>2260</v>
       </c>
       <c r="D42" t="s">
-        <v>2270</v>
+        <v>2261</v>
       </c>
       <c r="E42" t="s">
         <v>423</v>
@@ -14887,10 +15065,10 @@
         <v>601</v>
       </c>
       <c r="G42" t="s">
-        <v>2447</v>
+        <v>2438</v>
       </c>
       <c r="H42" t="s">
-        <v>2268</v>
+        <v>2259</v>
       </c>
       <c r="I42" t="s">
         <v>2059</v>
@@ -14907,10 +15085,10 @@
         <v>743</v>
       </c>
       <c r="C43" t="s">
-        <v>2271</v>
+        <v>2262</v>
       </c>
       <c r="D43" t="s">
-        <v>2272</v>
+        <v>2263</v>
       </c>
       <c r="E43" t="s">
         <v>423</v>
@@ -14919,10 +15097,10 @@
         <v>743</v>
       </c>
       <c r="G43" t="s">
-        <v>2447</v>
+        <v>2438</v>
       </c>
       <c r="H43" t="s">
-        <v>2273</v>
+        <v>2264</v>
       </c>
       <c r="I43" t="s">
         <v>742</v>
@@ -14939,10 +15117,10 @@
         <v>1028</v>
       </c>
       <c r="C44" t="s">
-        <v>2274</v>
+        <v>2265</v>
       </c>
       <c r="D44" t="s">
-        <v>2275</v>
+        <v>2266</v>
       </c>
       <c r="E44" t="s">
         <v>423</v>
@@ -14951,10 +15129,10 @@
         <v>1028</v>
       </c>
       <c r="G44" t="s">
-        <v>2447</v>
+        <v>2438</v>
       </c>
       <c r="H44" t="s">
-        <v>2276</v>
+        <v>2267</v>
       </c>
       <c r="I44" t="s">
         <v>737</v>
@@ -14971,22 +15149,22 @@
         <v>597</v>
       </c>
       <c r="C45" t="s">
-        <v>2277</v>
+        <v>2268</v>
       </c>
       <c r="D45" t="s">
-        <v>2278</v>
+        <v>2269</v>
       </c>
       <c r="E45" t="s">
         <v>423</v>
       </c>
       <c r="F45" t="s">
-        <v>2279</v>
+        <v>2270</v>
       </c>
       <c r="G45" t="s">
-        <v>2447</v>
+        <v>2438</v>
       </c>
       <c r="H45" t="s">
-        <v>2268</v>
+        <v>2259</v>
       </c>
       <c r="I45" t="s">
         <v>2001</v>
@@ -15003,10 +15181,10 @@
         <v>748</v>
       </c>
       <c r="C46" t="s">
-        <v>2280</v>
+        <v>2271</v>
       </c>
       <c r="D46" t="s">
-        <v>2281</v>
+        <v>2272</v>
       </c>
       <c r="E46" t="s">
         <v>423</v>
@@ -15015,10 +15193,10 @@
         <v>748</v>
       </c>
       <c r="G46" t="s">
-        <v>2448</v>
+        <v>2439</v>
       </c>
       <c r="H46" t="s">
-        <v>2282</v>
+        <v>2273</v>
       </c>
       <c r="I46" t="s">
         <v>747</v>
@@ -15027,7 +15205,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>2413</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -15038,10 +15216,10 @@
         <v>498</v>
       </c>
       <c r="C47" t="s">
-        <v>2283</v>
+        <v>2274</v>
       </c>
       <c r="D47" t="s">
-        <v>2284</v>
+        <v>2275</v>
       </c>
       <c r="E47" t="s">
         <v>423</v>
@@ -15050,10 +15228,10 @@
         <v>498</v>
       </c>
       <c r="G47" t="s">
-        <v>2448</v>
+        <v>2439</v>
       </c>
       <c r="H47" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I47" t="s">
         <v>496</v>
@@ -15062,7 +15240,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>2414</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -15070,13 +15248,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>2415</v>
+        <v>2406</v>
       </c>
       <c r="C48" t="s">
-        <v>2285</v>
+        <v>2276</v>
       </c>
       <c r="D48" t="s">
-        <v>2286</v>
+        <v>2277</v>
       </c>
       <c r="E48" t="s">
         <v>423</v>
@@ -15085,10 +15263,10 @@
         <v>2065</v>
       </c>
       <c r="G48" t="s">
-        <v>2448</v>
+        <v>2439</v>
       </c>
       <c r="H48" t="s">
-        <v>2282</v>
+        <v>2273</v>
       </c>
       <c r="I48" t="s">
         <v>565</v>
@@ -15097,7 +15275,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>2416</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -15108,10 +15286,10 @@
         <v>613</v>
       </c>
       <c r="C49" t="s">
-        <v>2287</v>
+        <v>2278</v>
       </c>
       <c r="D49" t="s">
-        <v>2288</v>
+        <v>2279</v>
       </c>
       <c r="E49" t="s">
         <v>423</v>
@@ -15120,10 +15298,10 @@
         <v>613</v>
       </c>
       <c r="G49" t="s">
-        <v>2447</v>
+        <v>2438</v>
       </c>
       <c r="H49" t="s">
-        <v>2289</v>
+        <v>2280</v>
       </c>
       <c r="I49" t="s">
         <v>612</v>
@@ -15140,10 +15318,10 @@
         <v>757</v>
       </c>
       <c r="C50" t="s">
-        <v>2290</v>
+        <v>2281</v>
       </c>
       <c r="D50" t="s">
-        <v>2291</v>
+        <v>2282</v>
       </c>
       <c r="E50" t="s">
         <v>421</v>
@@ -15152,10 +15330,10 @@
         <v>757</v>
       </c>
       <c r="G50" t="s">
-        <v>2449</v>
+        <v>2440</v>
       </c>
       <c r="H50" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I50" t="s">
         <v>756</v>
@@ -15169,13 +15347,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>2417</v>
+        <v>2408</v>
       </c>
       <c r="C51" t="s">
-        <v>2292</v>
+        <v>2283</v>
       </c>
       <c r="D51" t="s">
-        <v>2293</v>
+        <v>2284</v>
       </c>
       <c r="E51" t="s">
         <v>421</v>
@@ -15184,10 +15362,10 @@
         <v>2069</v>
       </c>
       <c r="G51" t="s">
-        <v>2450</v>
+        <v>2441</v>
       </c>
       <c r="H51" t="s">
-        <v>2282</v>
+        <v>2273</v>
       </c>
       <c r="I51" t="s">
         <v>894</v>
@@ -15196,7 +15374,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>2418</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -15204,25 +15382,25 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>2419</v>
+        <v>2410</v>
       </c>
       <c r="C52" t="s">
-        <v>2294</v>
+        <v>2285</v>
       </c>
       <c r="D52" t="s">
-        <v>2295</v>
+        <v>2286</v>
       </c>
       <c r="E52" t="s">
         <v>421</v>
       </c>
       <c r="F52" t="s">
-        <v>2420</v>
+        <v>2411</v>
       </c>
       <c r="G52" t="s">
-        <v>2451</v>
+        <v>2442</v>
       </c>
       <c r="H52" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I52" t="s">
         <v>894</v>
@@ -15231,7 +15409,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>2421</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -15239,25 +15417,25 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>2422</v>
+        <v>2413</v>
       </c>
       <c r="C53" t="s">
-        <v>2296</v>
+        <v>2287</v>
       </c>
       <c r="D53" t="s">
-        <v>2297</v>
+        <v>2288</v>
       </c>
       <c r="E53" t="s">
         <v>421</v>
       </c>
       <c r="F53" t="s">
-        <v>2420</v>
+        <v>2411</v>
       </c>
       <c r="G53" t="s">
-        <v>2452</v>
+        <v>2443</v>
       </c>
       <c r="H53" t="s">
-        <v>2189</v>
+        <v>2180</v>
       </c>
       <c r="I53" t="s">
         <v>894</v>
@@ -15271,25 +15449,25 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>2423</v>
+        <v>2414</v>
       </c>
       <c r="C54" t="s">
-        <v>2298</v>
+        <v>2289</v>
       </c>
       <c r="D54" t="s">
-        <v>2299</v>
+        <v>2290</v>
       </c>
       <c r="E54" t="s">
         <v>421</v>
       </c>
       <c r="F54" t="s">
-        <v>2420</v>
+        <v>2411</v>
       </c>
       <c r="G54" t="s">
-        <v>2451</v>
+        <v>2442</v>
       </c>
       <c r="H54" t="s">
-        <v>2300</v>
+        <v>2291</v>
       </c>
       <c r="I54" t="s">
         <v>894</v>
@@ -15306,10 +15484,10 @@
         <v>825</v>
       </c>
       <c r="C55" t="s">
-        <v>2301</v>
+        <v>2292</v>
       </c>
       <c r="D55" t="s">
-        <v>2302</v>
+        <v>2293</v>
       </c>
       <c r="E55" t="s">
         <v>421</v>
@@ -15318,10 +15496,10 @@
         <v>809</v>
       </c>
       <c r="G55" t="s">
-        <v>2453</v>
+        <v>2444</v>
       </c>
       <c r="H55" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I55" t="s">
         <v>808</v>
@@ -15338,10 +15516,10 @@
         <v>810</v>
       </c>
       <c r="C56" t="s">
-        <v>2303</v>
+        <v>2294</v>
       </c>
       <c r="D56" t="s">
-        <v>2304</v>
+        <v>2295</v>
       </c>
       <c r="E56" t="s">
         <v>421</v>
@@ -15350,10 +15528,10 @@
         <v>809</v>
       </c>
       <c r="G56" t="s">
-        <v>2453</v>
+        <v>2444</v>
       </c>
       <c r="H56" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I56" t="s">
         <v>808</v>
@@ -15370,10 +15548,10 @@
         <v>818</v>
       </c>
       <c r="C57" t="s">
-        <v>2305</v>
+        <v>2296</v>
       </c>
       <c r="D57" t="s">
-        <v>2306</v>
+        <v>2297</v>
       </c>
       <c r="E57" t="s">
         <v>421</v>
@@ -15382,10 +15560,10 @@
         <v>809</v>
       </c>
       <c r="G57" t="s">
-        <v>2453</v>
+        <v>2444</v>
       </c>
       <c r="H57" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I57" t="s">
         <v>808</v>
@@ -15402,10 +15580,10 @@
         <v>829</v>
       </c>
       <c r="C58" t="s">
-        <v>2307</v>
+        <v>2298</v>
       </c>
       <c r="D58" t="s">
-        <v>2308</v>
+        <v>2299</v>
       </c>
       <c r="E58" t="s">
         <v>421</v>
@@ -15414,10 +15592,10 @@
         <v>809</v>
       </c>
       <c r="G58" t="s">
-        <v>2453</v>
+        <v>2444</v>
       </c>
       <c r="H58" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I58" t="s">
         <v>808</v>
@@ -15434,10 +15612,10 @@
         <v>814</v>
       </c>
       <c r="C59" t="s">
-        <v>2309</v>
+        <v>2300</v>
       </c>
       <c r="D59" t="s">
-        <v>2310</v>
+        <v>2301</v>
       </c>
       <c r="E59" t="s">
         <v>421</v>
@@ -15446,10 +15624,10 @@
         <v>809</v>
       </c>
       <c r="G59" t="s">
-        <v>2453</v>
+        <v>2444</v>
       </c>
       <c r="H59" t="s">
-        <v>2213</v>
+        <v>2204</v>
       </c>
       <c r="I59" t="s">
         <v>808</v>
@@ -15463,13 +15641,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>2424</v>
+        <v>2415</v>
       </c>
       <c r="C60" t="s">
-        <v>2311</v>
+        <v>2302</v>
       </c>
       <c r="D60" t="s">
-        <v>2312</v>
+        <v>2303</v>
       </c>
       <c r="E60" t="s">
         <v>421</v>
@@ -15478,10 +15656,10 @@
         <v>809</v>
       </c>
       <c r="G60" t="s">
-        <v>2453</v>
+        <v>2444</v>
       </c>
       <c r="H60" t="s">
-        <v>2313</v>
+        <v>2304</v>
       </c>
       <c r="I60" t="s">
         <v>808</v>
@@ -15498,10 +15676,10 @@
         <v>917</v>
       </c>
       <c r="C61" t="s">
-        <v>2314</v>
+        <v>2305</v>
       </c>
       <c r="D61" t="s">
-        <v>2315</v>
+        <v>2306</v>
       </c>
       <c r="E61" t="s">
         <v>421</v>
@@ -15510,10 +15688,10 @@
         <v>916</v>
       </c>
       <c r="G61" t="s">
-        <v>2449</v>
+        <v>2440</v>
       </c>
       <c r="H61" t="s">
-        <v>2268</v>
+        <v>2259</v>
       </c>
       <c r="I61" t="s">
         <v>2000</v>
@@ -15530,22 +15708,22 @@
         <v>846</v>
       </c>
       <c r="C62" t="s">
-        <v>2316</v>
+        <v>2307</v>
       </c>
       <c r="D62" t="s">
-        <v>2317</v>
+        <v>2308</v>
       </c>
       <c r="E62" t="s">
         <v>421</v>
       </c>
       <c r="F62" t="s">
-        <v>2279</v>
+        <v>2270</v>
       </c>
       <c r="G62" t="s">
-        <v>2449</v>
+        <v>2440</v>
       </c>
       <c r="H62" t="s">
-        <v>2268</v>
+        <v>2259</v>
       </c>
       <c r="I62" t="s">
         <v>2001</v>
@@ -15562,10 +15740,10 @@
         <v>850</v>
       </c>
       <c r="C63" t="s">
-        <v>2318</v>
+        <v>2309</v>
       </c>
       <c r="D63" t="s">
-        <v>2319</v>
+        <v>2310</v>
       </c>
       <c r="E63" t="s">
         <v>421</v>
@@ -15574,10 +15752,10 @@
         <v>601</v>
       </c>
       <c r="G63" t="s">
-        <v>2449</v>
+        <v>2440</v>
       </c>
       <c r="H63" t="s">
-        <v>2268</v>
+        <v>2259</v>
       </c>
       <c r="I63" t="s">
         <v>2059</v>
@@ -15594,10 +15772,10 @@
         <v>856</v>
       </c>
       <c r="C64" t="s">
-        <v>2320</v>
+        <v>2311</v>
       </c>
       <c r="D64" t="s">
-        <v>2321</v>
+        <v>2312</v>
       </c>
       <c r="E64" t="s">
         <v>421</v>
@@ -15606,10 +15784,10 @@
         <v>2061</v>
       </c>
       <c r="G64" t="s">
-        <v>2454</v>
+        <v>2445</v>
       </c>
       <c r="H64" t="s">
-        <v>2276</v>
+        <v>2267</v>
       </c>
       <c r="I64" t="s">
         <v>860</v>
@@ -15623,13 +15801,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>2322</v>
+        <v>2313</v>
       </c>
       <c r="C65" t="s">
-        <v>2323</v>
+        <v>2314</v>
       </c>
       <c r="D65" t="s">
-        <v>2324</v>
+        <v>2315</v>
       </c>
       <c r="E65" t="s">
         <v>421</v>
@@ -15638,10 +15816,10 @@
         <v>2061</v>
       </c>
       <c r="G65" t="s">
-        <v>2455</v>
+        <v>2446</v>
       </c>
       <c r="H65" t="s">
-        <v>2189</v>
+        <v>2180</v>
       </c>
       <c r="I65" t="s">
         <v>860</v>
@@ -15658,10 +15836,10 @@
         <v>885</v>
       </c>
       <c r="C66" t="s">
-        <v>2325</v>
+        <v>2316</v>
       </c>
       <c r="D66" t="s">
-        <v>2326</v>
+        <v>2317</v>
       </c>
       <c r="E66" t="s">
         <v>421</v>
@@ -15670,10 +15848,10 @@
         <v>2064</v>
       </c>
       <c r="G66" t="s">
-        <v>2454</v>
+        <v>2445</v>
       </c>
       <c r="H66" t="s">
-        <v>2327</v>
+        <v>2318</v>
       </c>
       <c r="I66" t="s">
         <v>884</v>
@@ -15690,22 +15868,22 @@
         <v>793</v>
       </c>
       <c r="C67" t="s">
-        <v>2328</v>
+        <v>2319</v>
       </c>
       <c r="D67" t="s">
-        <v>2329</v>
+        <v>2320</v>
       </c>
       <c r="E67" t="s">
         <v>421</v>
       </c>
       <c r="F67" t="s">
-        <v>2330</v>
+        <v>2321</v>
       </c>
       <c r="G67" t="s">
-        <v>2449</v>
+        <v>2440</v>
       </c>
       <c r="H67" t="s">
-        <v>2276</v>
+        <v>2267</v>
       </c>
       <c r="I67" t="s">
         <v>791</v>
@@ -15719,25 +15897,25 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>2331</v>
+        <v>2322</v>
       </c>
       <c r="C68" t="s">
-        <v>2332</v>
+        <v>2323</v>
       </c>
       <c r="D68" t="s">
-        <v>2333</v>
+        <v>2324</v>
       </c>
       <c r="E68" t="s">
         <v>421</v>
       </c>
       <c r="F68" t="s">
-        <v>2330</v>
+        <v>2321</v>
       </c>
       <c r="G68" t="s">
-        <v>2456</v>
+        <v>2447</v>
       </c>
       <c r="H68" t="s">
-        <v>2189</v>
+        <v>2180</v>
       </c>
       <c r="I68" t="s">
         <v>791</v>
@@ -15754,10 +15932,10 @@
         <v>922</v>
       </c>
       <c r="C69" t="s">
-        <v>2334</v>
+        <v>2325</v>
       </c>
       <c r="D69" t="s">
-        <v>2335</v>
+        <v>2326</v>
       </c>
       <c r="E69" t="s">
         <v>421</v>
@@ -15766,10 +15944,10 @@
         <v>922</v>
       </c>
       <c r="G69" t="s">
-        <v>2449</v>
+        <v>2440</v>
       </c>
       <c r="H69" t="s">
-        <v>2273</v>
+        <v>2264</v>
       </c>
       <c r="I69" t="s">
         <v>921</v>
@@ -15786,10 +15964,10 @@
         <v>870</v>
       </c>
       <c r="C70" t="s">
-        <v>2336</v>
+        <v>2327</v>
       </c>
       <c r="D70" t="s">
-        <v>2337</v>
+        <v>2328</v>
       </c>
       <c r="E70" t="s">
         <v>421</v>
@@ -15798,10 +15976,10 @@
         <v>870</v>
       </c>
       <c r="G70" t="s">
-        <v>2449</v>
+        <v>2440</v>
       </c>
       <c r="H70" t="s">
-        <v>2273</v>
+        <v>2264</v>
       </c>
       <c r="I70" t="s">
         <v>869</v>
@@ -15818,22 +15996,22 @@
         <v>778</v>
       </c>
       <c r="C71" t="s">
-        <v>2338</v>
+        <v>2329</v>
       </c>
       <c r="D71" t="s">
-        <v>2339</v>
+        <v>2330</v>
       </c>
       <c r="E71" t="s">
         <v>421</v>
       </c>
       <c r="F71" t="s">
-        <v>2340</v>
+        <v>2331</v>
       </c>
       <c r="G71" t="s">
-        <v>2450</v>
+        <v>2441</v>
       </c>
       <c r="H71" t="s">
-        <v>2276</v>
+        <v>2267</v>
       </c>
       <c r="I71" t="s">
         <v>782</v>
@@ -15842,7 +16020,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>2425</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
@@ -15850,25 +16028,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>2426</v>
+        <v>2417</v>
       </c>
       <c r="C72" t="s">
-        <v>2341</v>
+        <v>2332</v>
       </c>
       <c r="D72" t="s">
-        <v>2342</v>
+        <v>2333</v>
       </c>
       <c r="E72" t="s">
         <v>421</v>
       </c>
       <c r="F72" t="s">
-        <v>2340</v>
+        <v>2331</v>
       </c>
       <c r="G72" t="s">
-        <v>2452</v>
+        <v>2443</v>
       </c>
       <c r="H72" t="s">
-        <v>2189</v>
+        <v>2180</v>
       </c>
       <c r="I72" t="s">
         <v>782</v>
@@ -15885,22 +16063,22 @@
         <v>880</v>
       </c>
       <c r="C73" t="s">
-        <v>2343</v>
+        <v>2334</v>
       </c>
       <c r="D73" t="s">
-        <v>2344</v>
+        <v>2335</v>
       </c>
       <c r="E73" t="s">
         <v>421</v>
       </c>
       <c r="F73" t="s">
-        <v>2427</v>
+        <v>2418</v>
       </c>
       <c r="G73" t="s">
-        <v>2457</v>
+        <v>2448</v>
       </c>
       <c r="H73" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I73" t="s">
         <v>874</v>
@@ -15909,7 +16087,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>2428</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
@@ -15920,22 +16098,22 @@
         <v>876</v>
       </c>
       <c r="C74" t="s">
-        <v>2345</v>
+        <v>2336</v>
       </c>
       <c r="D74" t="s">
-        <v>2346</v>
+        <v>2337</v>
       </c>
       <c r="E74" t="s">
         <v>421</v>
       </c>
       <c r="F74" t="s">
-        <v>2427</v>
+        <v>2418</v>
       </c>
       <c r="G74" t="s">
-        <v>2457</v>
+        <v>2448</v>
       </c>
       <c r="H74" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I74" t="s">
         <v>874</v>
@@ -15944,7 +16122,7 @@
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>2429</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
@@ -15952,13 +16130,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>2430</v>
+        <v>2421</v>
       </c>
       <c r="C75" t="s">
-        <v>2347</v>
+        <v>2338</v>
       </c>
       <c r="D75" t="s">
-        <v>2348</v>
+        <v>2339</v>
       </c>
       <c r="E75" t="s">
         <v>421</v>
@@ -15967,10 +16145,10 @@
         <v>949</v>
       </c>
       <c r="G75" t="s">
-        <v>2454</v>
+        <v>2445</v>
       </c>
       <c r="H75" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I75" t="s">
         <v>947</v>
@@ -15979,7 +16157,7 @@
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>2431</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
@@ -15987,13 +16165,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>2432</v>
+        <v>2423</v>
       </c>
       <c r="C76" t="s">
-        <v>2349</v>
+        <v>2340</v>
       </c>
       <c r="D76" t="s">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="E76" t="s">
         <v>421</v>
@@ -16002,10 +16180,10 @@
         <v>949</v>
       </c>
       <c r="G76" t="s">
-        <v>2454</v>
+        <v>2445</v>
       </c>
       <c r="H76" t="s">
-        <v>2351</v>
+        <v>2342</v>
       </c>
       <c r="I76" t="s">
         <v>947</v>
@@ -16022,10 +16200,10 @@
         <v>1061</v>
       </c>
       <c r="C77" t="s">
-        <v>2352</v>
+        <v>2343</v>
       </c>
       <c r="D77" t="s">
-        <v>2353</v>
+        <v>2344</v>
       </c>
       <c r="E77" t="s">
         <v>421</v>
@@ -16034,10 +16212,10 @@
         <v>949</v>
       </c>
       <c r="G77" t="s">
-        <v>2455</v>
+        <v>2446</v>
       </c>
       <c r="H77" t="s">
-        <v>2189</v>
+        <v>2180</v>
       </c>
       <c r="I77" t="s">
         <v>947</v>
@@ -16051,13 +16229,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>2433</v>
+        <v>2424</v>
       </c>
       <c r="C78" t="s">
-        <v>2354</v>
+        <v>2345</v>
       </c>
       <c r="D78" t="s">
-        <v>2355</v>
+        <v>2346</v>
       </c>
       <c r="E78" t="s">
         <v>421</v>
@@ -16066,10 +16244,10 @@
         <v>949</v>
       </c>
       <c r="G78" t="s">
-        <v>2454</v>
+        <v>2445</v>
       </c>
       <c r="H78" t="s">
-        <v>2356</v>
+        <v>2347</v>
       </c>
       <c r="I78" t="s">
         <v>947</v>
@@ -16083,13 +16261,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>2434</v>
+        <v>2425</v>
       </c>
       <c r="C79" t="s">
-        <v>2357</v>
+        <v>2348</v>
       </c>
       <c r="D79" t="s">
-        <v>2358</v>
+        <v>2349</v>
       </c>
       <c r="E79" t="s">
         <v>421</v>
@@ -16098,10 +16276,10 @@
         <v>927</v>
       </c>
       <c r="G79" t="s">
-        <v>2454</v>
+        <v>2445</v>
       </c>
       <c r="H79" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I79" t="s">
         <v>926</v>
@@ -16110,7 +16288,7 @@
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>2435</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
@@ -16118,13 +16296,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>2436</v>
+        <v>2427</v>
       </c>
       <c r="C80" t="s">
-        <v>2359</v>
+        <v>2350</v>
       </c>
       <c r="D80" t="s">
-        <v>2360</v>
+        <v>2351</v>
       </c>
       <c r="E80" t="s">
         <v>421</v>
@@ -16133,19 +16311,19 @@
         <v>927</v>
       </c>
       <c r="G80" t="s">
-        <v>2454</v>
+        <v>2445</v>
       </c>
       <c r="H80" t="s">
-        <v>2313</v>
+        <v>2304</v>
       </c>
       <c r="I80" t="s">
-        <v>2471</v>
+        <v>2462</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>2443</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
@@ -16153,13 +16331,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>2437</v>
+        <v>2428</v>
       </c>
       <c r="C81" t="s">
-        <v>2361</v>
+        <v>2352</v>
       </c>
       <c r="D81" t="s">
-        <v>2362</v>
+        <v>2353</v>
       </c>
       <c r="E81" t="s">
         <v>421</v>
@@ -16168,10 +16346,10 @@
         <v>927</v>
       </c>
       <c r="G81" t="s">
-        <v>2454</v>
+        <v>2445</v>
       </c>
       <c r="H81" t="s">
-        <v>2363</v>
+        <v>2354</v>
       </c>
       <c r="I81" t="s">
         <v>926</v>
@@ -16185,13 +16363,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>2438</v>
+        <v>2429</v>
       </c>
       <c r="C82" t="s">
-        <v>2364</v>
+        <v>2355</v>
       </c>
       <c r="D82" t="s">
-        <v>2365</v>
+        <v>2356</v>
       </c>
       <c r="E82" t="s">
         <v>421</v>
@@ -16200,13 +16378,13 @@
         <v>927</v>
       </c>
       <c r="G82" t="s">
-        <v>2454</v>
+        <v>2445</v>
       </c>
       <c r="H82" t="s">
-        <v>2198</v>
+        <v>2189</v>
       </c>
       <c r="I82" t="s">
-        <v>2471</v>
+        <v>2462</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
@@ -16217,28 +16395,28 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>2439</v>
+        <v>2430</v>
       </c>
       <c r="C83" t="s">
-        <v>2366</v>
+        <v>2357</v>
       </c>
       <c r="D83" t="s">
-        <v>2367</v>
+        <v>2358</v>
       </c>
       <c r="E83" t="s">
         <v>200</v>
       </c>
       <c r="F83" t="s">
-        <v>2368</v>
+        <v>2359</v>
       </c>
       <c r="G83" t="s">
-        <v>2448</v>
+        <v>2439</v>
       </c>
       <c r="H83" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I83" t="s">
-        <v>2468</v>
+        <v>2459</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
@@ -16249,28 +16427,28 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>2369</v>
+        <v>2360</v>
       </c>
       <c r="C84" t="s">
-        <v>2370</v>
+        <v>2361</v>
       </c>
       <c r="D84" t="s">
-        <v>2371</v>
+        <v>2362</v>
       </c>
       <c r="E84" t="s">
         <v>200</v>
       </c>
       <c r="F84" t="s">
-        <v>2368</v>
+        <v>2359</v>
       </c>
       <c r="G84" t="s">
-        <v>2470</v>
+        <v>2461</v>
       </c>
       <c r="H84" t="s">
-        <v>2218</v>
+        <v>2209</v>
       </c>
       <c r="I84" t="s">
-        <v>2468</v>
+        <v>2459</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
@@ -16281,34 +16459,34 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>2440</v>
+        <v>2431</v>
       </c>
       <c r="C85" t="s">
-        <v>2372</v>
+        <v>2363</v>
       </c>
       <c r="D85" t="s">
-        <v>2373</v>
+        <v>2364</v>
       </c>
       <c r="E85" t="s">
         <v>423</v>
       </c>
       <c r="F85" t="s">
-        <v>2441</v>
+        <v>2432</v>
       </c>
       <c r="G85" t="s">
-        <v>2458</v>
+        <v>2449</v>
       </c>
       <c r="H85" t="s">
-        <v>2227</v>
+        <v>2218</v>
       </c>
       <c r="I85" t="s">
-        <v>2468</v>
+        <v>2459</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>2442</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -16316,34 +16494,34 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>2374</v>
+        <v>2365</v>
       </c>
       <c r="C86" t="s">
-        <v>2375</v>
+        <v>2366</v>
       </c>
       <c r="D86" t="s">
-        <v>2376</v>
+        <v>2367</v>
       </c>
       <c r="E86" t="s">
         <v>421</v>
       </c>
       <c r="F86" t="s">
-        <v>2441</v>
+        <v>2432</v>
       </c>
       <c r="G86" t="s">
-        <v>2451</v>
+        <v>2442</v>
       </c>
       <c r="H86" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="I86" t="s">
-        <v>2468</v>
+        <v>2459</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>2442</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
@@ -16351,28 +16529,28 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>2459</v>
+        <v>2450</v>
       </c>
       <c r="C87" t="s">
-        <v>2464</v>
+        <v>2455</v>
       </c>
       <c r="D87" t="s">
-        <v>2465</v>
+        <v>2456</v>
       </c>
       <c r="E87" t="s">
         <v>200</v>
       </c>
       <c r="F87" t="s">
-        <v>2368</v>
+        <v>2359</v>
       </c>
       <c r="G87" t="s">
-        <v>2448</v>
+        <v>2439</v>
       </c>
       <c r="H87" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I87" t="s">
-        <v>2468</v>
+        <v>2459</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
@@ -16383,28 +16561,28 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>2460</v>
+        <v>2451</v>
       </c>
       <c r="C88" t="s">
-        <v>2463</v>
+        <v>2454</v>
       </c>
       <c r="D88" t="s">
-        <v>2462</v>
+        <v>2453</v>
       </c>
       <c r="E88" t="s">
         <v>200</v>
       </c>
       <c r="F88" t="s">
-        <v>2368</v>
+        <v>2359</v>
       </c>
       <c r="G88" t="s">
-        <v>2448</v>
+        <v>2439</v>
       </c>
       <c r="H88" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I88" t="s">
-        <v>2468</v>
+        <v>2459</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
@@ -16416,28 +16594,28 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>2461</v>
+        <v>2452</v>
       </c>
       <c r="C89" t="s">
-        <v>2466</v>
+        <v>2457</v>
       </c>
       <c r="D89" t="s">
-        <v>2467</v>
+        <v>2458</v>
       </c>
       <c r="E89" t="s">
         <v>200</v>
       </c>
       <c r="F89" t="s">
-        <v>2368</v>
+        <v>2359</v>
       </c>
       <c r="G89" t="s">
-        <v>2448</v>
+        <v>2439</v>
       </c>
       <c r="H89" t="s">
-        <v>2178</v>
+        <v>2169</v>
       </c>
       <c r="I89" t="s">
-        <v>2468</v>
+        <v>2459</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
@@ -38309,15 +38487,15 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55941987-30AF-6648-9A85-31A79E0640F5}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" customWidth="1"/>
-    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.83203125" customWidth="1"/>
     <col min="7" max="7" width="31.5" customWidth="1"/>
     <col min="8" max="8" width="62.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="66.83203125" bestFit="1" customWidth="1"/>
@@ -38325,10 +38503,11 @@
     <col min="11" max="11" width="90.83203125" customWidth="1"/>
     <col min="12" max="12" width="62.5" customWidth="1"/>
     <col min="13" max="13" width="74.1640625" customWidth="1"/>
-    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="68.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2115</v>
       </c>
@@ -38348,7 +38527,7 @@
         <v>147</v>
       </c>
       <c r="G1" t="s">
-        <v>2478</v>
+        <v>2468</v>
       </c>
       <c r="H1" t="s">
         <v>146</v>
@@ -38369,10 +38548,13 @@
         <v>2122</v>
       </c>
       <c r="N1" t="s">
+        <v>2474</v>
+      </c>
+      <c r="O1" t="s">
         <v>2123</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2151</v>
       </c>
@@ -38387,7 +38569,7 @@
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>2377</v>
+        <v>2368</v>
       </c>
       <c r="H2" t="s">
         <v>2124</v>
@@ -38404,11 +38586,11 @@
       <c r="M2" t="s">
         <v>2128</v>
       </c>
-      <c r="N2" t="b">
+      <c r="O2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2152</v>
       </c>
@@ -38439,11 +38621,11 @@
       <c r="M3" t="s">
         <v>2133</v>
       </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2153</v>
       </c>
@@ -38474,11 +38656,11 @@
       <c r="M4" t="s">
         <v>2138</v>
       </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2154</v>
       </c>
@@ -38509,11 +38691,11 @@
       <c r="M5" t="s">
         <v>2143</v>
       </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2155</v>
       </c>
@@ -38545,13 +38727,13 @@
       <c r="M6" t="s">
         <v>2148</v>
       </c>
-      <c r="N6" t="b">
+      <c r="O6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>2167</v>
+        <v>2477</v>
       </c>
       <c r="B7" t="s">
         <v>2165</v>
@@ -38560,36 +38742,42 @@
         <v>2150</v>
       </c>
       <c r="D7" t="s">
-        <v>2168</v>
-      </c>
-      <c r="F7" t="s">
-        <v>2169</v>
-      </c>
-      <c r="H7" t="s">
-        <v>2170</v>
-      </c>
-      <c r="I7" t="s">
-        <v>2173</v>
-      </c>
-      <c r="J7" t="s">
-        <v>2174</v>
-      </c>
-      <c r="K7" t="s">
-        <v>2175</v>
-      </c>
-      <c r="L7" t="s">
-        <v>2171</v>
+        <v>2157</v>
+      </c>
+      <c r="E7" s="9">
+        <v>46001</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>2481</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>2482</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>2483</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>2484</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>2479</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>2172</v>
-      </c>
-      <c r="N7" t="b">
+        <v>2485</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>2480</v>
+      </c>
+      <c r="O7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>2475</v>
+        <v>2466</v>
       </c>
       <c r="B8" t="s">
         <v>2165</v>
@@ -38597,37 +38785,37 @@
       <c r="C8" t="s">
         <v>2150</v>
       </c>
-      <c r="D8" t="s">
-        <v>2476</v>
-      </c>
       <c r="E8" s="9">
         <v>45994</v>
       </c>
       <c r="F8" t="s">
-        <v>2477</v>
+        <v>2467</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>2377</v>
+        <v>2368</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>2482</v>
+        <v>2472</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>2481</v>
+        <v>2471</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>2479</v>
+        <v>2469</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>2483</v>
+        <v>2473</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>2484</v>
-      </c>
-      <c r="N8" t="b">
+        <v>2475</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>2476</v>
+      </c>
+      <c r="O8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -71958,13 +72146,13 @@
         <v>46235</v>
       </c>
       <c r="B2" t="s">
-        <v>2473</v>
+        <v>2464</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>2474</v>
+        <v>2465</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2472</v>
+        <v>2463</v>
       </c>
       <c r="G2" s="5"/>
     </row>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F785142-A355-B543-B7EE-DD6313B9C333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FE3688-C97C-2F4B-A5BC-DCCE885E9C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-33320" yWindow="2920" windowWidth="29560" windowHeight="19060" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3942" uniqueCount="2486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3956" uniqueCount="2497">
   <si>
     <t>date</t>
   </si>
@@ -12857,6 +12857,9 @@
     <t>Doenjang Curry Pasta</t>
   </si>
   <si>
+    <t>35 min</t>
+  </si>
+  <si>
     <t>doenjang_curry_pasta.png</t>
   </si>
   <si>
@@ -12947,9 +12950,6 @@
 The flavorful liquid portion of a dish, which can refer to broth, soup, or sauce depending on the context.
 Jjigae (찌개)
 A Korean stew, such as kimchi-jjigae.</t>
-  </si>
-  <si>
-    <t>Jungkook's Carbonara Buldak Pasta with BBQ &amp; War Potatoes</t>
   </si>
   <si>
     <r>
@@ -13153,6 +13153,92 @@
   <si>
     <t>Although the complete meal included BBQ Meat and War Potatoes, the main dish is the Carbonara Pasta. The additional sides required extra preparation time (about 1.5–2 hours), while the pasta itself was completed in approximately 40 minutes.
 Since the pasta water was already salted, Jungkook intentionally kept the sauce a little bland, knowing the pasta water would help season the final dish. He also mentioned that cooking pasta in plain water would not season the noodles properly.</t>
+  </si>
+  <si>
+    <t>Truffle Pasta (Without Truffle)</t>
+  </si>
+  <si>
+    <t>truffle_pasta.png</t>
+  </si>
+  <si>
+    <t>https://weverse.io/bts/live/4-210577196</t>
+  </si>
+  <si>
+    <t>속여 버리게 (Sogyeo beorige)
+A playful expression meaning "to make it seem like something it is not" or "to fake it." Jungkook used this jokingly while creating a truffle pasta without actual truffle, using truffle oil and truffle butter to recreate the flavor.
+Parmigiano Reggiano
+A famous Italian hard-aged cheese known for its rich umami flavor, granular texture, and strict production standards. Often called the "King of Cheeses."
+Mantecare
+An Italian cooking technique where pasta is vigorously mixed with sauce and pasta water to create a smooth, emulsified texture.
+느타리버섯 (Neutari-beoseot)
+Korean oyster mushroom, commonly used in Korean cooking.
+빨리 이겨라 (Palli igyeora)
+A playful phrase meaning "Hurry up and win!"
+진실의 미간 (Jinsil-ui-migan)
+A Korean internet slang expression describing the intense facial expression people make when experiencing something extremely delicious.</t>
+  </si>
+  <si>
+    <t>Carbonara Buldak Pasta with BBQ &amp; War Potatoes</t>
+  </si>
+  <si>
+    <t>Onion (1, thinly sliced)
+Button mushrooms, roughly sliced
+Oyster mushrooms (느타리버섯)
+Pasta
+Oil
+Salt
+Black pepper
+Butter
+Truffle oil (Levante White Truffle Oil)
+Truffle butter (about 2 tsp)*
+Milk (about ½–1 cup)*
+Sugar (a pinch)
+Pasta water
+Parmigiano Reggiano</t>
+  </si>
+  <si>
+    <t>Jungkook started cutting onions, but after finishing he suddenly realized that he did not remember using onions in his previous pasta recipes, making everyone laugh.
+While preparing the dish, he playfully thought about what to name it, considering names like Truffle Oil Pasta and Truffle Cream Pasta before creating a truffle pasta without actual truffle.
+He jokingly described the idea as "속여 버리게" (Sogyeo beorige), using truffle oil and truffle butter to recreate the truffle flavor.
+While waiting for the pasta to cook, he started singing "빨리 이겨라" (Palli igyeora — Hurry up and win!) to the pasta in his own playful way.</t>
+  </si>
+  <si>
+    <t>Jungkook shared small everyday moments with ARMY while cooking, including asking if anyone had gone running at the Han River and jokingly inviting them to run together.
+There was also a quiet moment while he was sautéing mushrooms, until he suddenly looked at the camera and gave a playful "he he" laugh.
+While eating, Jungkook showed what fans refer to as the "진실의 미간" (Jinsil-ui-migan), the involuntary facial expression people make when food is extremely delicious.</t>
+  </si>
+  <si>
+    <t>Although the dish was inspired by truffle flavors, no fresh truffle was used. Jungkook used truffle oil and truffle butter instead.
+Jungkook mentioned that adding sugar noticeably enhances the overall flavor of the pasta.
+The pasta package suggested 13 minutes of cooking time, but Jungkook cooked it for around 17 minutes because he prefers a softer texture instead of al dente.
+Jungkook received the pasta noodles through Baemin (배달의민족) and Parmigiano Reggiano through B Mart, both Korean delivery services.</t>
+  </si>
+  <si>
+    <t>A creamy mushroom pasta created by Jungkook using truffle oil and truffle butter to recreate the rich aroma of truffle flavors without using actual truffle.</t>
+  </si>
+  <si>
+    <t>Preparing the Pasta
+Boil water in a large pot, add salt, and cook the pasta.
+Jungkook cooked his pasta for around 17 minutes instead of the suggested 13 minutes on the packet, as he prefers well-cooked pasta rather than al dente.
+Preparing the Mushroom Sauce
+Add oil to a pan.
+Add sliced onion and sauté.
+Season with salt and pepper.
+Add button mushrooms and oyster mushrooms.
+Add truffle oil and continue sautéing.
+Building the Creamy Sauce
+Once the mushrooms are cooked, turn off the heat.
+Add truffle butter and allow it to melt using the remaining heat.
+Turn the heat back on.
+Add pasta water as needed.
+Add milk and a pinch of sugar.
+Mix well until the sauce reduces.
+Combining Everything
+Add cooked pasta and combine.
+Perform mantecare by mixing the pasta until the sauce becomes smooth and creamy.
+Grate Parmigiano Reggiano into the pasta and continue cooking briefly.
+Turn off the heat and serve.
+Top with additional grated Parmigiano Reggiano and freshly ground pepper.</t>
   </si>
 </sst>
 </file>
@@ -38487,7 +38573,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55941987-30AF-6648-9A85-31A79E0640F5}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
@@ -38527,7 +38613,7 @@
         <v>147</v>
       </c>
       <c r="G1" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="H1" t="s">
         <v>146</v>
@@ -38548,7 +38634,7 @@
         <v>2122</v>
       </c>
       <c r="N1" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="O1" t="s">
         <v>2123</v>
@@ -38731,9 +38817,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>2477</v>
+        <v>2490</v>
       </c>
       <c r="B7" t="s">
         <v>2165</v>
@@ -38775,7 +38861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>2466</v>
       </c>
@@ -38785,37 +38871,87 @@
       <c r="C8" t="s">
         <v>2150</v>
       </c>
+      <c r="D8" t="s">
+        <v>2467</v>
+      </c>
       <c r="E8" s="9">
         <v>45994</v>
       </c>
       <c r="F8" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>2368</v>
       </c>
       <c r="H8" s="8" t="s">
+        <v>2473</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>2472</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
+        <v>2470</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>2471</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>2469</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>2470</v>
-      </c>
       <c r="L8" s="8" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="O8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2150</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2467</v>
+      </c>
+      <c r="E9" s="9">
+        <v>45928</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2487</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>2488</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>2495</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>2491</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>2496</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>2492</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>2493</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>2494</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>2489</v>
+      </c>
+      <c r="O9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -38823,6 +38959,7 @@
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{0D225B07-4494-C44D-997D-1695264A8219}"/>
     <hyperlink ref="G8" r:id="rId2" xr:uid="{F237ABC7-87F1-A443-83D7-225DCF79C51C}"/>
+    <hyperlink ref="G9" r:id="rId3" xr:uid="{3306A533-3C8E-6844-BA56-EF62907FDE00}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FE3688-C97C-2F4B-A5BC-DCCE885E9C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B21960F-97BE-B24E-A495-749B2C98A570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-33320" yWindow="2920" windowWidth="29560" windowHeight="19060" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3956" uniqueCount="2497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3959" uniqueCount="2498">
   <si>
     <t>date</t>
   </si>
@@ -13239,6 +13239,9 @@
 Grate Parmigiano Reggiano into the pasta and continue cooking briefly.
 Turn off the heat and serve.
 Top with additional grated Parmigiano Reggiano and freshly ground pepper.</t>
+  </si>
+  <si>
+    <t>Shrimp Pasta</t>
   </si>
 </sst>
 </file>
@@ -38573,7 +38576,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55941987-30AF-6648-9A85-31A79E0640F5}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
@@ -38817,7 +38820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>2490</v>
       </c>
@@ -38861,7 +38864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>2466</v>
       </c>
@@ -38908,7 +38911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>2486</v>
       </c>
@@ -38953,6 +38956,20 @@
       </c>
       <c r="O9" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>2497</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E10" s="9">
+        <v>45985</v>
       </c>
     </row>
   </sheetData>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B21960F-97BE-B24E-A495-749B2C98A570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D36BB71-EB88-0542-B649-3BC56707B32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-33320" yWindow="2920" windowWidth="29560" windowHeight="19060" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3959" uniqueCount="2498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3959" uniqueCount="2497">
   <si>
     <t>date</t>
   </si>
@@ -13239,9 +13239,6 @@
 Grate Parmigiano Reggiano into the pasta and continue cooking briefly.
 Turn off the heat and serve.
 Top with additional grated Parmigiano Reggiano and freshly ground pepper.</t>
-  </si>
-  <si>
-    <t>Shrimp Pasta</t>
   </si>
 </sst>
 </file>
@@ -38960,7 +38957,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>2497</v>
+        <v>2153</v>
       </c>
       <c r="B10" t="s">
         <v>2165</v>
@@ -38970,6 +38967,9 @@
       </c>
       <c r="E10" s="9">
         <v>45985</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9557E68-6A99-FE41-AB01-F388F91F3B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFC0279-2CB5-074E-9018-4FD9DD9FA8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33500" yWindow="2720" windowWidth="29560" windowHeight="19060" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-33500" yWindow="2720" windowWidth="29560" windowHeight="19060" firstSheet="5" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4020" uniqueCount="2545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="2548">
   <si>
     <t>date</t>
   </si>
@@ -13391,6 +13391,15 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=eCqHMOX_rQ8</t>
+  </si>
+  <si>
+    <t>GRAFF</t>
+  </si>
+  <si>
+    <t>koo_graff.webp</t>
+  </si>
+  <si>
+    <t>https://www.graff.com</t>
   </si>
 </sst>
 </file>
@@ -69829,7 +69838,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64C35039-B9B3-DA4C-95BA-F339368624DF}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -70180,21 +70189,41 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s">
-        <v>2535</v>
+        <v>2545</v>
       </c>
       <c r="C18" t="s">
         <v>1834</v>
       </c>
       <c r="D18" t="s">
+        <v>2546</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>2547</v>
+      </c>
+      <c r="F18">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D19" t="s">
         <v>2536</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E19" s="6" t="s">
         <v>2537</v>
       </c>
-      <c r="F18">
+      <c r="F19">
         <v>2026</v>
       </c>
     </row>
@@ -70205,7 +70234,8 @@
     <hyperlink ref="E14" r:id="rId3" xr:uid="{374FF3EB-AAC2-E44C-85A5-12CD5800A2FB}"/>
     <hyperlink ref="E16" r:id="rId4" xr:uid="{5AAE3747-957D-3845-989F-707851F55413}"/>
     <hyperlink ref="E17" r:id="rId5" xr:uid="{EBA670F1-9C27-C94F-8055-EECE2FA9BAA1}"/>
-    <hyperlink ref="E18" r:id="rId6" xr:uid="{72B5C3E8-0667-F34E-87CF-50F50BFE1809}"/>
+    <hyperlink ref="E19" r:id="rId6" xr:uid="{72B5C3E8-0667-F34E-87CF-50F50BFE1809}"/>
+    <hyperlink ref="E18" r:id="rId7" xr:uid="{80E4CD18-E157-8F45-B5FD-0124FCF4AD1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7C6ED5-6A64-1F4E-B0A3-A2F76E46FE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813511D3-BEBD-6648-99D9-7F25738B1000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" firstSheet="5" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -6321,23 +6321,6 @@
 https://x.com/tetekoofm/status/1857146037657616830</t>
   </si>
   <si>
-    <t xml:space="preserve">
-To_Find_You_-_A_Taekook_Scavenger_Hunt_MainPoster.webp,
-To_Find_You_-_A_Taekook_Scavenger_Hunt_Details.webp,
-To_Find_You_-_A_Taekook_Scavenger_Hunt_BlazeRiders.mp4,
-To_Find_You_-_A_Taekook_Scavenger_Hunt_MapleMarauders.mp4,
-To_Find_You_-_A_Taekook_Scavenger_Hunt_SnowDrifters.mp4,
-https://x.com/tetekoofm/status/1842580599825158489,
-https://x.com/tetekoofm/status/1842943209036456132,
-https://x.com/stream4taekook/status/1843940502233895070,
-https://x.com/uktaekook/status/1843939493826752666,
-https://x.com/tetekoofm/status/1843939603478364398,
-https://x.com/_TKASIA/status/1845113105879060707,
-https://x.com/TKTiktok_/status/1845108275060277279,
-https://x.com/tetekoofm/status/1845080927744962675,
-https://x.com/tetekoofm/status/1845099755396878437</t>
-  </si>
-  <si>
     <t>Golden_Layover_TaeKook_Streaming_Party_MainPoster.webp,
 Golden_Layover_TaeKook_Streaming_Party_Winner1.webp,
 Golden_Layover_TaeKook_Streaming_Party_Winner2.webp,
@@ -6348,15 +6331,6 @@
     <t>Layover_Vinyl_GA.webp,
 https://x.com/tetekoofm/status/1832810316817948966,
 https://x.com/tetekoofm/status/1841149515283239307</t>
-  </si>
-  <si>
-    <t>Layover_LTAF_Main_Poster.mp4, 
-Layover_LTAF_Details.webp, 
-Layover_LTAF_GA.webp,
-https://x.com/tetekoofm/status/1830672321646076049,
-https://x.com/tetekoofm/status/1830991858291335218,
-https://x.com/tetekoofm/status/1831361195380720081,
-https://x.com/tetekoofm/status/1834998613828644916</t>
   </si>
   <si>
     <t>JKDay_Main_Poster.webp, 
@@ -13400,6 +13374,28 @@
   </si>
   <si>
     <t>discography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+To_Find_You_-_A_Taekook_Scavenger_Hunt_MainPoster.webp,
+To_Find_You_-_A_Taekook_Scavenger_Hunt_Details.webp,
+https://x.com/tetekoofm/status/1842580599825158489,
+https://x.com/tetekoofm/status/1842943209036456132,
+https://x.com/stream4taekook/status/1843940502233895070,
+https://x.com/uktaekook/status/1843939493826752666,
+https://x.com/tetekoofm/status/1843939603478364398,
+https://x.com/_TKASIA/status/1845113105879060707,
+https://x.com/TKTiktok_/status/1845108275060277279,
+https://x.com/tetekoofm/status/1845080927744962675,
+https://x.com/tetekoofm/status/1845099755396878437</t>
+  </si>
+  <si>
+    <t>https://x.com/tetekoofm/status/1830672321646076049,
+Layover_LTAF_Details.webp, 
+Layover_LTAF_GA.webp,
+https://x.com/tetekoofm/status/1830991858291335218,
+https://x.com/tetekoofm/status/1831361195380720081,
+https://x.com/tetekoofm/status/1834998613828644916</t>
   </si>
 </sst>
 </file>
@@ -13946,37 +13942,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="B1" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="C1" t="s">
         <v>438</v>
       </c>
       <c r="D1" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="E1" t="s">
         <v>197</v>
       </c>
       <c r="F1" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="G1" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="H1" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="I1" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="J1" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="K1" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -13987,22 +13983,22 @@
         <v>448</v>
       </c>
       <c r="C2" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="D2" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="E2" t="s">
         <v>422</v>
       </c>
       <c r="F2" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G2" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H2" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I2" t="s">
         <v>511</v>
@@ -14016,25 +14012,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="C3" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="D3" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="E3" t="s">
         <v>422</v>
       </c>
       <c r="F3" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G3" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="H3" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="I3" t="s">
         <v>511</v>
@@ -14048,25 +14044,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="C4" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="D4" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="E4" t="s">
         <v>422</v>
       </c>
       <c r="F4" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G4" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="H4" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="I4" t="s">
         <v>511</v>
@@ -14080,25 +14076,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="C5" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="D5" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="E5" t="s">
         <v>422</v>
       </c>
       <c r="F5" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="G5" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H5" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I5" t="s">
         <v>442</v>
@@ -14107,7 +14103,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -14115,25 +14111,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C6" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="D6" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="E6" t="s">
         <v>422</v>
       </c>
       <c r="F6" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="G6" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="H6" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="I6" t="s">
         <v>442</v>
@@ -14147,25 +14143,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="C7" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="D7" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="E7" t="s">
         <v>422</v>
       </c>
       <c r="F7" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="G7" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H7" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="I7" t="s">
         <v>442</v>
@@ -14174,7 +14170,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -14182,25 +14178,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="C8" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="D8" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="E8" t="s">
         <v>422</v>
       </c>
       <c r="F8" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="G8" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H8" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="I8" t="s">
         <v>442</v>
@@ -14209,7 +14205,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -14217,25 +14213,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="C9" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="D9" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="E9" t="s">
         <v>422</v>
       </c>
       <c r="F9" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="G9" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H9" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="I9" t="s">
         <v>442</v>
@@ -14249,25 +14245,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C10" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="D10" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="E10" t="s">
         <v>422</v>
       </c>
       <c r="F10" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="G10" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H10" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="I10" t="s">
         <v>442</v>
@@ -14284,22 +14280,22 @@
         <v>491</v>
       </c>
       <c r="C11" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="D11" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="E11" t="s">
         <v>422</v>
       </c>
       <c r="F11" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="G11" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H11" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I11" t="s">
         <v>490</v>
@@ -14308,7 +14304,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -14319,22 +14315,22 @@
         <v>982</v>
       </c>
       <c r="C12" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="D12" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="E12" t="s">
         <v>422</v>
       </c>
       <c r="F12" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="G12" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H12" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I12" t="s">
         <v>485</v>
@@ -14343,7 +14339,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -14354,22 +14350,22 @@
         <v>515</v>
       </c>
       <c r="C13" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="D13" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="E13" t="s">
         <v>422</v>
       </c>
       <c r="F13" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G13" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H13" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="I13" t="s">
         <v>511</v>
@@ -14386,22 +14382,22 @@
         <v>625</v>
       </c>
       <c r="C14" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="D14" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="E14" t="s">
         <v>422</v>
       </c>
       <c r="F14" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G14" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H14" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I14" t="s">
         <v>511</v>
@@ -14418,22 +14414,22 @@
         <v>985</v>
       </c>
       <c r="C15" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="D15" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="E15" t="s">
         <v>422</v>
       </c>
       <c r="F15" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G15" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="H15" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="I15" t="s">
         <v>511</v>
@@ -14447,25 +14443,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="C16" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="D16" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="E16" t="s">
         <v>422</v>
       </c>
       <c r="F16" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="G16" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="H16" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="I16" t="s">
         <v>624</v>
@@ -14479,25 +14475,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="C17" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="D17" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="E17" t="s">
         <v>422</v>
       </c>
       <c r="F17" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="G17" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H17" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I17" t="s">
         <v>675</v>
@@ -14506,7 +14502,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -14514,25 +14510,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="C18" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="D18" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="E18" t="s">
         <v>422</v>
       </c>
       <c r="F18" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="G18" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H18" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I18" t="s">
         <v>675</v>
@@ -14541,7 +14537,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -14549,25 +14545,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="C19" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="D19" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="E19" t="s">
         <v>422</v>
       </c>
       <c r="F19" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="G19" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H19" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I19" t="s">
         <v>675</v>
@@ -14576,7 +14572,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -14584,25 +14580,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="C20" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="D20" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="E20" t="s">
         <v>422</v>
       </c>
       <c r="F20" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="G20" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H20" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="I20" t="s">
         <v>675</v>
@@ -14616,25 +14612,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="C21" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="D21" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E21" t="s">
         <v>422</v>
       </c>
       <c r="F21" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="G21" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H21" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I21" t="s">
         <v>660</v>
@@ -14643,7 +14639,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -14651,25 +14647,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="C22" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="D22" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="E22" t="s">
         <v>422</v>
       </c>
       <c r="F22" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="G22" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H22" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="I22" t="s">
         <v>660</v>
@@ -14686,22 +14682,22 @@
         <v>655</v>
       </c>
       <c r="C23" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="D23" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="E23" t="s">
         <v>422</v>
       </c>
       <c r="F23" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="G23" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H23" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I23" t="s">
         <v>649</v>
@@ -14710,7 +14706,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -14718,25 +14714,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="C24" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="D24" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="E24" t="s">
         <v>422</v>
       </c>
       <c r="F24" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="G24" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H24" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="I24" t="s">
         <v>649</v>
@@ -14745,7 +14741,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -14756,22 +14752,22 @@
         <v>543</v>
       </c>
       <c r="C25" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="D25" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="E25" t="s">
         <v>422</v>
       </c>
       <c r="F25" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G25" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H25" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I25" t="s">
         <v>511</v>
@@ -14785,25 +14781,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="C26" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="D26" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="E26" t="s">
         <v>422</v>
       </c>
       <c r="F26" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G26" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="H26" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="I26" t="s">
         <v>511</v>
@@ -14820,22 +14816,22 @@
         <v>716</v>
       </c>
       <c r="C27" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="D27" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="E27" t="s">
         <v>422</v>
       </c>
       <c r="F27" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="G27" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="H27" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="I27" t="s">
         <v>703</v>
@@ -14852,22 +14848,22 @@
         <v>727</v>
       </c>
       <c r="C28" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="D28" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="E28" t="s">
         <v>422</v>
       </c>
       <c r="F28" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="G28" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H28" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I28" t="s">
         <v>703</v>
@@ -14876,7 +14872,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -14887,22 +14883,22 @@
         <v>724</v>
       </c>
       <c r="C29" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="D29" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="E29" t="s">
         <v>422</v>
       </c>
       <c r="F29" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="G29" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H29" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I29" t="s">
         <v>703</v>
@@ -14911,7 +14907,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -14922,22 +14918,22 @@
         <v>720</v>
       </c>
       <c r="C30" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="D30" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="E30" t="s">
         <v>422</v>
       </c>
       <c r="F30" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="G30" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H30" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I30" t="s">
         <v>703</v>
@@ -14946,7 +14942,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -14957,22 +14953,22 @@
         <v>712</v>
       </c>
       <c r="C31" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="D31" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="E31" t="s">
         <v>422</v>
       </c>
       <c r="F31" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="G31" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H31" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="I31" t="s">
         <v>703</v>
@@ -14981,7 +14977,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -14992,22 +14988,22 @@
         <v>708</v>
       </c>
       <c r="C32" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="D32" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E32" t="s">
         <v>422</v>
       </c>
       <c r="F32" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="G32" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H32" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I32" t="s">
         <v>703</v>
@@ -15016,7 +15012,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -15027,22 +15023,22 @@
         <v>732</v>
       </c>
       <c r="C33" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="D33" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="E33" t="s">
         <v>422</v>
       </c>
       <c r="F33" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="G33" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H33" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I33" t="s">
         <v>731</v>
@@ -15051,7 +15047,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -15062,22 +15058,22 @@
         <v>554</v>
       </c>
       <c r="C34" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
       <c r="D34" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="E34" t="s">
         <v>422</v>
       </c>
       <c r="F34" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G34" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H34" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="I34" t="s">
         <v>511</v>
@@ -15094,22 +15090,22 @@
         <v>523</v>
       </c>
       <c r="C35" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
       <c r="D35" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="E35" t="s">
         <v>422</v>
       </c>
       <c r="F35" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G35" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H35" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="I35" t="s">
         <v>511</v>
@@ -15126,22 +15122,22 @@
         <v>519</v>
       </c>
       <c r="C36" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="D36" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
       <c r="E36" t="s">
         <v>422</v>
       </c>
       <c r="F36" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G36" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H36" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="I36" t="s">
         <v>511</v>
@@ -15158,22 +15154,22 @@
         <v>539</v>
       </c>
       <c r="C37" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="D37" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="E37" t="s">
         <v>422</v>
       </c>
       <c r="F37" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G37" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H37" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="I37" t="s">
         <v>511</v>
@@ -15190,22 +15186,22 @@
         <v>550</v>
       </c>
       <c r="C38" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="D38" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="E38" t="s">
         <v>422</v>
       </c>
       <c r="F38" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G38" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H38" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="I38" t="s">
         <v>511</v>
@@ -15222,22 +15218,22 @@
         <v>535</v>
       </c>
       <c r="C39" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="D39" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="E39" t="s">
         <v>422</v>
       </c>
       <c r="F39" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G39" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H39" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="I39" t="s">
         <v>511</v>
@@ -15257,7 +15253,7 @@
         <v>620</v>
       </c>
       <c r="D40" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="E40" t="s">
         <v>422</v>
@@ -15266,10 +15262,10 @@
         <v>617</v>
       </c>
       <c r="G40" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H40" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="I40" t="s">
         <v>616</v>
@@ -15286,10 +15282,10 @@
         <v>751</v>
       </c>
       <c r="C41" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="D41" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="E41" t="s">
         <v>422</v>
@@ -15298,13 +15294,13 @@
         <v>915</v>
       </c>
       <c r="G41" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H41" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="I41" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
@@ -15318,10 +15314,10 @@
         <v>601</v>
       </c>
       <c r="C42" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="D42" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="E42" t="s">
         <v>422</v>
@@ -15330,13 +15326,13 @@
         <v>600</v>
       </c>
       <c r="G42" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H42" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="I42" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
@@ -15350,10 +15346,10 @@
         <v>742</v>
       </c>
       <c r="C43" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="D43" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="E43" t="s">
         <v>422</v>
@@ -15362,10 +15358,10 @@
         <v>742</v>
       </c>
       <c r="G43" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H43" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
       <c r="I43" t="s">
         <v>741</v>
@@ -15382,10 +15378,10 @@
         <v>1026</v>
       </c>
       <c r="C44" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="D44" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="E44" t="s">
         <v>422</v>
@@ -15394,10 +15390,10 @@
         <v>1026</v>
       </c>
       <c r="G44" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H44" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="I44" t="s">
         <v>736</v>
@@ -15414,25 +15410,25 @@
         <v>596</v>
       </c>
       <c r="C45" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
       <c r="D45" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="E45" t="s">
         <v>422</v>
       </c>
       <c r="F45" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="G45" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H45" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="I45" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
@@ -15446,10 +15442,10 @@
         <v>747</v>
       </c>
       <c r="C46" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="D46" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="E46" t="s">
         <v>422</v>
@@ -15458,10 +15454,10 @@
         <v>747</v>
       </c>
       <c r="G46" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="H46" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="I46" t="s">
         <v>746</v>
@@ -15470,7 +15466,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -15481,10 +15477,10 @@
         <v>497</v>
       </c>
       <c r="C47" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="D47" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
       <c r="E47" t="s">
         <v>422</v>
@@ -15493,10 +15489,10 @@
         <v>497</v>
       </c>
       <c r="G47" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="H47" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I47" t="s">
         <v>495</v>
@@ -15505,7 +15501,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -15513,25 +15509,25 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="C48" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
       <c r="D48" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="E48" t="s">
         <v>422</v>
       </c>
       <c r="F48" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="G48" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="H48" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="I48" t="s">
         <v>564</v>
@@ -15540,7 +15536,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -15551,10 +15547,10 @@
         <v>612</v>
       </c>
       <c r="C49" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="D49" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
       <c r="E49" t="s">
         <v>422</v>
@@ -15563,10 +15559,10 @@
         <v>612</v>
       </c>
       <c r="G49" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H49" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="I49" t="s">
         <v>611</v>
@@ -15583,10 +15579,10 @@
         <v>756</v>
       </c>
       <c r="C50" t="s">
-        <v>2277</v>
+        <v>2275</v>
       </c>
       <c r="D50" t="s">
-        <v>2278</v>
+        <v>2276</v>
       </c>
       <c r="E50" t="s">
         <v>420</v>
@@ -15595,10 +15591,10 @@
         <v>756</v>
       </c>
       <c r="G50" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="H50" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I50" t="s">
         <v>755</v>
@@ -15612,25 +15608,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="C51" t="s">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="D51" t="s">
-        <v>2280</v>
+        <v>2278</v>
       </c>
       <c r="E51" t="s">
         <v>420</v>
       </c>
       <c r="F51" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="G51" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="H51" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="I51" t="s">
         <v>893</v>
@@ -15639,7 +15635,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -15647,25 +15643,25 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="C52" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="D52" t="s">
-        <v>2282</v>
+        <v>2280</v>
       </c>
       <c r="E52" t="s">
         <v>420</v>
       </c>
       <c r="F52" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="G52" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="H52" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I52" t="s">
         <v>893</v>
@@ -15674,7 +15670,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -15682,25 +15678,25 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="C53" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="D53" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="E53" t="s">
         <v>420</v>
       </c>
       <c r="F53" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="G53" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H53" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="I53" t="s">
         <v>893</v>
@@ -15714,25 +15710,25 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="C54" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="D54" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="E54" t="s">
         <v>420</v>
       </c>
       <c r="F54" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="G54" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="H54" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="I54" t="s">
         <v>893</v>
@@ -15749,10 +15745,10 @@
         <v>824</v>
       </c>
       <c r="C55" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="D55" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="E55" t="s">
         <v>420</v>
@@ -15761,10 +15757,10 @@
         <v>808</v>
       </c>
       <c r="G55" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="H55" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I55" t="s">
         <v>807</v>
@@ -15781,10 +15777,10 @@
         <v>809</v>
       </c>
       <c r="C56" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
       <c r="D56" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="E56" t="s">
         <v>420</v>
@@ -15793,10 +15789,10 @@
         <v>808</v>
       </c>
       <c r="G56" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="H56" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I56" t="s">
         <v>807</v>
@@ -15813,10 +15809,10 @@
         <v>817</v>
       </c>
       <c r="C57" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="D57" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="E57" t="s">
         <v>420</v>
@@ -15825,10 +15821,10 @@
         <v>808</v>
       </c>
       <c r="G57" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="H57" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I57" t="s">
         <v>807</v>
@@ -15845,10 +15841,10 @@
         <v>828</v>
       </c>
       <c r="C58" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="D58" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="E58" t="s">
         <v>420</v>
@@ -15857,10 +15853,10 @@
         <v>808</v>
       </c>
       <c r="G58" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="H58" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I58" t="s">
         <v>807</v>
@@ -15877,10 +15873,10 @@
         <v>813</v>
       </c>
       <c r="C59" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="D59" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="E59" t="s">
         <v>420</v>
@@ -15889,10 +15885,10 @@
         <v>808</v>
       </c>
       <c r="G59" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="H59" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="I59" t="s">
         <v>807</v>
@@ -15906,13 +15902,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="C60" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
       <c r="D60" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="E60" t="s">
         <v>420</v>
@@ -15921,10 +15917,10 @@
         <v>808</v>
       </c>
       <c r="G60" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="H60" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="I60" t="s">
         <v>807</v>
@@ -15941,10 +15937,10 @@
         <v>916</v>
       </c>
       <c r="C61" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="D61" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="E61" t="s">
         <v>420</v>
@@ -15953,13 +15949,13 @@
         <v>915</v>
       </c>
       <c r="G61" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="H61" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="I61" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
@@ -15973,25 +15969,25 @@
         <v>845</v>
       </c>
       <c r="C62" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="D62" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="E62" t="s">
         <v>420</v>
       </c>
       <c r="F62" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="G62" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="H62" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="I62" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
@@ -16005,10 +16001,10 @@
         <v>849</v>
       </c>
       <c r="C63" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="D63" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="E63" t="s">
         <v>420</v>
@@ -16017,13 +16013,13 @@
         <v>600</v>
       </c>
       <c r="G63" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="H63" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="I63" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
@@ -16037,22 +16033,22 @@
         <v>855</v>
       </c>
       <c r="C64" t="s">
-        <v>2307</v>
+        <v>2305</v>
       </c>
       <c r="D64" t="s">
-        <v>2308</v>
+        <v>2306</v>
       </c>
       <c r="E64" t="s">
         <v>420</v>
       </c>
       <c r="F64" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G64" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="H64" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="I64" t="s">
         <v>859</v>
@@ -16066,25 +16062,25 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D65" t="s">
         <v>2309</v>
-      </c>
-      <c r="C65" t="s">
-        <v>2310</v>
-      </c>
-      <c r="D65" t="s">
-        <v>2311</v>
       </c>
       <c r="E65" t="s">
         <v>420</v>
       </c>
       <c r="F65" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G65" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="H65" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="I65" t="s">
         <v>859</v>
@@ -16101,22 +16097,22 @@
         <v>884</v>
       </c>
       <c r="C66" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="D66" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="E66" t="s">
         <v>420</v>
       </c>
       <c r="F66" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="G66" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="H66" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="I66" t="s">
         <v>883</v>
@@ -16133,22 +16129,22 @@
         <v>792</v>
       </c>
       <c r="C67" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
       <c r="D67" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="E67" t="s">
         <v>420</v>
       </c>
       <c r="F67" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
       <c r="G67" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="H67" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="I67" t="s">
         <v>790</v>
@@ -16162,25 +16158,25 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D68" t="s">
         <v>2318</v>
-      </c>
-      <c r="C68" t="s">
-        <v>2319</v>
-      </c>
-      <c r="D68" t="s">
-        <v>2320</v>
       </c>
       <c r="E68" t="s">
         <v>420</v>
       </c>
       <c r="F68" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
       <c r="G68" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="H68" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="I68" t="s">
         <v>790</v>
@@ -16197,10 +16193,10 @@
         <v>921</v>
       </c>
       <c r="C69" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="D69" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="E69" t="s">
         <v>420</v>
@@ -16209,10 +16205,10 @@
         <v>921</v>
       </c>
       <c r="G69" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="H69" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
       <c r="I69" t="s">
         <v>920</v>
@@ -16229,10 +16225,10 @@
         <v>869</v>
       </c>
       <c r="C70" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="D70" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="E70" t="s">
         <v>420</v>
@@ -16241,10 +16237,10 @@
         <v>869</v>
       </c>
       <c r="G70" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="H70" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
       <c r="I70" t="s">
         <v>868</v>
@@ -16261,22 +16257,22 @@
         <v>777</v>
       </c>
       <c r="C71" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="D71" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="E71" t="s">
         <v>420</v>
       </c>
       <c r="F71" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="G71" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="H71" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="I71" t="s">
         <v>781</v>
@@ -16285,7 +16281,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
@@ -16293,25 +16289,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="C72" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
       <c r="D72" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="E72" t="s">
         <v>420</v>
       </c>
       <c r="F72" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="G72" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H72" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="I72" t="s">
         <v>781</v>
@@ -16328,22 +16324,22 @@
         <v>879</v>
       </c>
       <c r="C73" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="D73" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
       <c r="E73" t="s">
         <v>420</v>
       </c>
       <c r="F73" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="G73" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="H73" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I73" t="s">
         <v>873</v>
@@ -16352,7 +16348,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
@@ -16363,22 +16359,22 @@
         <v>875</v>
       </c>
       <c r="C74" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
       <c r="D74" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="E74" t="s">
         <v>420</v>
       </c>
       <c r="F74" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="G74" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="H74" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I74" t="s">
         <v>873</v>
@@ -16387,7 +16383,7 @@
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
@@ -16395,13 +16391,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="C75" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="D75" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="E75" t="s">
         <v>420</v>
@@ -16410,10 +16406,10 @@
         <v>948</v>
       </c>
       <c r="G75" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="H75" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I75" t="s">
         <v>946</v>
@@ -16422,7 +16418,7 @@
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
@@ -16430,13 +16426,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="C76" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="D76" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="E76" t="s">
         <v>420</v>
@@ -16445,10 +16441,10 @@
         <v>948</v>
       </c>
       <c r="G76" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="H76" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="I76" t="s">
         <v>946</v>
@@ -16465,10 +16461,10 @@
         <v>1059</v>
       </c>
       <c r="C77" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="D77" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="E77" t="s">
         <v>420</v>
@@ -16477,10 +16473,10 @@
         <v>948</v>
       </c>
       <c r="G77" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="H77" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="I77" t="s">
         <v>946</v>
@@ -16494,13 +16490,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="C78" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="D78" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="E78" t="s">
         <v>420</v>
@@ -16509,10 +16505,10 @@
         <v>948</v>
       </c>
       <c r="G78" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="H78" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="I78" t="s">
         <v>946</v>
@@ -16526,13 +16522,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="C79" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="D79" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="E79" t="s">
         <v>420</v>
@@ -16541,10 +16537,10 @@
         <v>926</v>
       </c>
       <c r="G79" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="H79" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I79" t="s">
         <v>925</v>
@@ -16553,7 +16549,7 @@
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
@@ -16561,13 +16557,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="C80" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="D80" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="E80" t="s">
         <v>420</v>
@@ -16576,19 +16572,19 @@
         <v>926</v>
       </c>
       <c r="G80" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="H80" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="I80" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
@@ -16596,13 +16592,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="C81" t="s">
-        <v>2348</v>
+        <v>2346</v>
       </c>
       <c r="D81" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
       <c r="E81" t="s">
         <v>420</v>
@@ -16611,10 +16607,10 @@
         <v>926</v>
       </c>
       <c r="G81" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="H81" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
       <c r="I81" t="s">
         <v>925</v>
@@ -16628,13 +16624,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="C82" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="D82" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="E82" t="s">
         <v>420</v>
@@ -16643,13 +16639,13 @@
         <v>926</v>
       </c>
       <c r="G82" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="H82" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="I82" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
@@ -16660,28 +16656,28 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="C83" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="D83" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="E83" t="s">
         <v>199</v>
       </c>
       <c r="F83" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="G83" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="H83" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I83" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
@@ -16692,28 +16688,28 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2355</v>
+      </c>
+      <c r="D84" t="s">
         <v>2356</v>
-      </c>
-      <c r="C84" t="s">
-        <v>2357</v>
-      </c>
-      <c r="D84" t="s">
-        <v>2358</v>
       </c>
       <c r="E84" t="s">
         <v>199</v>
       </c>
       <c r="F84" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="G84" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="H84" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="I84" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
@@ -16724,34 +16720,34 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="C85" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="D85" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="E85" t="s">
         <v>422</v>
       </c>
       <c r="F85" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="G85" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="H85" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="I85" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -16759,34 +16755,34 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D86" t="s">
         <v>2361</v>
-      </c>
-      <c r="C86" t="s">
-        <v>2362</v>
-      </c>
-      <c r="D86" t="s">
-        <v>2363</v>
       </c>
       <c r="E86" t="s">
         <v>420</v>
       </c>
       <c r="F86" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="G86" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="H86" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="I86" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
@@ -16794,28 +16790,28 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="C87" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="D87" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
       <c r="E87" t="s">
         <v>199</v>
       </c>
       <c r="F87" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="G87" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="H87" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I87" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
@@ -16826,28 +16822,28 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>2445</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2448</v>
+      </c>
+      <c r="D88" t="s">
         <v>2447</v>
-      </c>
-      <c r="C88" t="s">
-        <v>2450</v>
-      </c>
-      <c r="D88" t="s">
-        <v>2449</v>
       </c>
       <c r="E88" t="s">
         <v>199</v>
       </c>
       <c r="F88" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="G88" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="H88" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I88" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
@@ -16859,28 +16855,28 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="C89" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="D89" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="E89" t="s">
         <v>199</v>
       </c>
       <c r="F89" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="G89" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="H89" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="I89" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
@@ -16908,28 +16904,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>1985</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="E1" s="5" t="s">
+        <v>1987</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>1988</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>1986</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>1987</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>1989</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>1990</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>1991</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>1992</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -16937,7 +16933,7 @@
         <v>216</v>
       </c>
       <c r="B2" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="C2" t="s">
         <v>916</v>
@@ -16946,16 +16942,16 @@
         <v>915</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>1991</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>1993</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>1995</v>
-      </c>
       <c r="H2" s="8" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -16963,7 +16959,7 @@
         <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="C3" t="s">
         <v>751</v>
@@ -16972,16 +16968,16 @@
         <v>915</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>1996</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>1997</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>1998</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>1999</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>2000</v>
-      </c>
       <c r="H3" s="8" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -16995,19 +16991,19 @@
         <v>777</v>
       </c>
       <c r="D4" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>2033</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>2034</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>2035</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>2036</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>2037</v>
-      </c>
       <c r="H4" s="8" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17015,7 +17011,7 @@
         <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="C5" t="s">
         <v>596</v>
@@ -17024,16 +17020,16 @@
         <v>595</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>2008</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>2009</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>2010</v>
-      </c>
       <c r="H5" s="8" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17041,7 +17037,7 @@
         <v>216</v>
       </c>
       <c r="B6" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="C6" t="s">
         <v>845</v>
@@ -17050,16 +17046,16 @@
         <v>595</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>2010</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>2011</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>2012</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>2013</v>
-      </c>
       <c r="H6" s="8" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17073,19 +17069,19 @@
         <v>869</v>
       </c>
       <c r="D7" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>2036</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>2040</v>
-      </c>
       <c r="H7" s="8" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17099,19 +17095,19 @@
         <v>921</v>
       </c>
       <c r="D8" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="F8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17119,7 +17115,7 @@
         <v>206</v>
       </c>
       <c r="B9" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="C9" t="s">
         <v>601</v>
@@ -17128,16 +17124,16 @@
         <v>600</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>2030</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>2031</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>2032</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>2033</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>2034</v>
-      </c>
       <c r="H9" s="8" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17145,7 +17141,7 @@
         <v>216</v>
       </c>
       <c r="B10" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="C10" t="s">
         <v>849</v>
@@ -17154,16 +17150,16 @@
         <v>600</v>
       </c>
       <c r="E10" s="8" t="s">
+        <v>2013</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>2015</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>2016</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>2017</v>
-      </c>
       <c r="H10" s="8" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17177,19 +17173,19 @@
         <v>792</v>
       </c>
       <c r="D11" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="F11" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G11" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17203,19 +17199,19 @@
         <v>742</v>
       </c>
       <c r="D12" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>2041</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>2042</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>2043</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>2044</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>2045</v>
-      </c>
       <c r="H12" s="8" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -17226,22 +17222,22 @@
         <v>883</v>
       </c>
       <c r="C13" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="D13" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E13" s="8" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>2046</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>2047</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>2048</v>
-      </c>
       <c r="H13" s="8" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -17255,19 +17251,19 @@
         <v>855</v>
       </c>
       <c r="D14" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>2017</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>2018</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>2019</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>2020</v>
-      </c>
       <c r="H14" s="8" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17281,19 +17277,19 @@
         <v>1026</v>
       </c>
       <c r="D15" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17307,19 +17303,19 @@
         <v>612</v>
       </c>
       <c r="D16" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>2050</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>2051</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>2052</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>2053</v>
-      </c>
       <c r="H16" s="8" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -17330,22 +17326,22 @@
         <v>564</v>
       </c>
       <c r="C17" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="D17" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="F17" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G17" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -17362,16 +17358,16 @@
         <v>497</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="F18" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G18" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17382,22 +17378,22 @@
         <v>511</v>
       </c>
       <c r="C19" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="D19" t="s">
         <v>512</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="F19" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G19" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -17414,16 +17410,16 @@
         <v>808</v>
       </c>
       <c r="E20" s="8" t="s">
+        <v>2020</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>2021</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>2022</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>2023</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>2024</v>
-      </c>
       <c r="H20" s="8" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17440,16 +17436,16 @@
         <v>808</v>
       </c>
       <c r="E21" s="8" t="s">
+        <v>2023</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>2024</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>2025</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>2026</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>2027</v>
-      </c>
       <c r="H21" s="8" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -17466,16 +17462,16 @@
         <v>808</v>
       </c>
       <c r="E22" s="8" t="s">
+        <v>2066</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>2067</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>2068</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>2069</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>2070</v>
-      </c>
       <c r="H22" s="8" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17492,16 +17488,16 @@
         <v>808</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="F23" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G23" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -17518,16 +17514,16 @@
         <v>808</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="F24" s="8" t="s">
+        <v>2070</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>2072</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>2074</v>
-      </c>
       <c r="H24" s="8" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -17538,22 +17534,22 @@
         <v>511</v>
       </c>
       <c r="C25" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="D25" t="s">
         <v>512</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="F25" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G25" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17567,19 +17563,19 @@
         <v>747</v>
       </c>
       <c r="D26" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="F26" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G26" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17590,22 +17586,22 @@
         <v>511</v>
       </c>
       <c r="C27" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="D27" t="s">
         <v>512</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="F27" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G27" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -17622,16 +17618,16 @@
         <v>512</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="F28" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G28" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -17642,22 +17638,22 @@
         <v>511</v>
       </c>
       <c r="C29" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="D29" t="s">
         <v>512</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="F29" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G29" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17674,16 +17670,16 @@
         <v>512</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="F30" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G30" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17700,16 +17696,16 @@
         <v>512</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="F31" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G31" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -17726,16 +17722,16 @@
         <v>512</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="F32" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G32" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -17752,16 +17748,16 @@
         <v>512</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="F33" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G33" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -17778,13 +17774,13 @@
         <v>512</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F34" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G34" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -17801,16 +17797,16 @@
         <v>512</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="F35" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G35" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17821,22 +17817,22 @@
         <v>893</v>
       </c>
       <c r="C36" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="D36" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G36" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -17850,19 +17846,19 @@
         <v>756</v>
       </c>
       <c r="D37" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="F37" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G37" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17873,22 +17869,22 @@
         <v>558</v>
       </c>
       <c r="C38" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="D38" t="s">
         <v>559</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17902,19 +17898,19 @@
         <v>617</v>
       </c>
       <c r="D39" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="F39" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G39" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.2">
@@ -17928,19 +17924,19 @@
         <v>926</v>
       </c>
       <c r="D40" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E40" s="8" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F40" t="s">
         <v>2089</v>
       </c>
-      <c r="F40" t="s">
-        <v>2091</v>
-      </c>
       <c r="G40" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.2">
@@ -17954,19 +17950,19 @@
         <v>948</v>
       </c>
       <c r="D41" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="F41" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="G41" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
   </sheetData>
@@ -19345,7 +19341,7 @@
         <v>206</v>
       </c>
       <c r="B36" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>595</v>
@@ -19383,7 +19379,7 @@
         <v>206</v>
       </c>
       <c r="B37" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>600</v>
@@ -20666,7 +20662,7 @@
         <v>736</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>737</v>
@@ -20777,7 +20773,7 @@
         <v>206</v>
       </c>
       <c r="B74" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>751</v>
@@ -21553,7 +21549,7 @@
         <v>216</v>
       </c>
       <c r="B94" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>595</v>
@@ -21591,7 +21587,7 @@
         <v>216</v>
       </c>
       <c r="B95" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>600</v>
@@ -22127,7 +22123,7 @@
         <v>216</v>
       </c>
       <c r="B109" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>915</v>
@@ -37972,7 +37968,7 @@
         <v>515</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -38774,16 +38770,16 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C1" t="s">
         <v>2111</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>2112</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2113</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2114</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -38792,64 +38788,64 @@
         <v>147</v>
       </c>
       <c r="G1" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="H1" t="s">
         <v>146</v>
       </c>
       <c r="I1" t="s">
+        <v>2113</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="K1" t="s">
+        <v>2160</v>
+      </c>
+      <c r="L1" t="s">
         <v>2115</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>2116</v>
       </c>
-      <c r="K1" t="s">
-        <v>2162</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
+        <v>2468</v>
+      </c>
+      <c r="O1" t="s">
         <v>2117</v>
-      </c>
-      <c r="M1" t="s">
-        <v>2118</v>
-      </c>
-      <c r="N1" t="s">
-        <v>2470</v>
-      </c>
-      <c r="O1" t="s">
-        <v>2119</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="B2" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="C2" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="D2" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="H2" t="s">
+        <v>2118</v>
+      </c>
+      <c r="I2" t="s">
+        <v>2119</v>
+      </c>
+      <c r="J2" t="s">
         <v>2120</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>2121</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>2122</v>
-      </c>
-      <c r="L2" t="s">
-        <v>2123</v>
-      </c>
-      <c r="M2" t="s">
-        <v>2124</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -38857,34 +38853,34 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="B3" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C3" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="D3" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="F3" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="H3" t="s">
+        <v>2123</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2124</v>
+      </c>
+      <c r="J3" t="s">
         <v>2125</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
         <v>2126</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>2127</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2128</v>
-      </c>
-      <c r="M3" t="s">
-        <v>2129</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -38892,34 +38888,34 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="B4" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C4" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="D4" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="F4" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="H4" t="s">
+        <v>2128</v>
+      </c>
+      <c r="I4" t="s">
+        <v>2129</v>
+      </c>
+      <c r="J4" t="s">
         <v>2130</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>2131</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>2132</v>
-      </c>
-      <c r="L4" t="s">
-        <v>2133</v>
-      </c>
-      <c r="M4" t="s">
-        <v>2134</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -38927,34 +38923,34 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="B5" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C5" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="D5" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="F5" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="H5" t="s">
+        <v>2133</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2134</v>
+      </c>
+      <c r="J5" t="s">
         <v>2135</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>2136</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>2137</v>
-      </c>
-      <c r="L5" t="s">
-        <v>2138</v>
-      </c>
-      <c r="M5" t="s">
-        <v>2139</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
@@ -38962,35 +38958,35 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="B6" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="C6" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="D6" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="H6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="I6" t="s">
+        <v>2139</v>
+      </c>
+      <c r="J6" t="s">
         <v>2140</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>2141</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>2142</v>
-      </c>
-      <c r="L6" t="s">
-        <v>2143</v>
-      </c>
-      <c r="M6" t="s">
-        <v>2144</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -38998,43 +38994,43 @@
     </row>
     <row r="7" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="B7" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C7" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="D7" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="E7" s="9">
         <v>46001</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>2474</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>2475</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>2471</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>2476</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>2477</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="L7" s="8" t="s">
+        <v>2472</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>2478</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>2473</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>2478</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>2479</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>2474</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>2480</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>2475</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -39042,46 +39038,46 @@
     </row>
     <row r="8" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="B8" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C8" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="D8" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="E8" s="9">
         <v>45994</v>
       </c>
       <c r="F8" t="s">
+        <v>2461</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>2362</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>2466</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>2465</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>2463</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>2364</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>2468</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="K8" s="8" t="s">
+        <v>2464</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>2467</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>2465</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>2466</v>
-      </c>
-      <c r="L8" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>2469</v>
       </c>
-      <c r="M8" s="8" t="s">
-        <v>2471</v>
-      </c>
       <c r="N8" s="8" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
@@ -39089,46 +39085,46 @@
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="B9" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C9" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="D9" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="E9" s="9">
         <v>45928</v>
       </c>
       <c r="F9" t="s">
+        <v>2480</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>2481</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>2488</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>2484</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>2489</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>2485</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>2486</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>2487</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>2482</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>2483</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>2490</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>2486</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>2491</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>2487</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>2488</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>2489</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>2484</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -39136,13 +39132,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="B10" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C10" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="E10" s="9">
         <v>45985</v>
@@ -39215,7 +39211,7 @@
         <v>1077</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1079</v>
@@ -39396,12 +39392,12 @@
         <v>1109</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="6" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -39443,14 +39439,14 @@
         <v>1116</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>1117</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="6" t="s">
@@ -39650,7 +39646,7 @@
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="6" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="6" t="s">
@@ -39695,7 +39691,7 @@
         <v>1146</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -39777,7 +39773,7 @@
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -39820,7 +39816,7 @@
         <v>1160</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -69001,7 +68997,7 @@
     </row>
     <row r="2" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="34" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="B2" s="37">
         <v>45875</v>
@@ -69010,18 +69006,18 @@
         <v>1113</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="B3" s="37">
         <v>46231</v>
@@ -69030,10 +69026,10 @@
         <v>1106</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>1276</v>
@@ -69053,7 +69049,7 @@
         <v>1275</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>1276</v>
@@ -69096,7 +69092,7 @@
         <v>1283</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -69161,7 +69157,7 @@
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="76.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="51.6640625" bestFit="1" customWidth="1"/>
@@ -69329,7 +69325,7 @@
         <v>1318</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>1319</v>
@@ -69377,7 +69373,7 @@
         <v>1326</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>1327</v>
@@ -69556,7 +69552,7 @@
       </c>
       <c r="E23" s="8"/>
     </row>
-    <row r="24" spans="1:6" ht="289" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="238" x14ac:dyDescent="0.2">
       <c r="A24" s="17">
         <v>45574</v>
       </c>
@@ -69564,7 +69560,7 @@
         <v>1358</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1890</v>
+        <v>2546</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>1359</v>
@@ -69584,7 +69580,7 @@
         <v>1362</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>1363</v>
@@ -69599,7 +69595,7 @@
         <v>1364</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>1365</v>
@@ -69616,7 +69612,7 @@
         <v>1367</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>1368</v>
@@ -69631,7 +69627,7 @@
         <v>1369</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1893</v>
+        <v>2547</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>1370</v>
@@ -69648,7 +69644,7 @@
         <v>1372</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>1373</v>
@@ -69662,7 +69658,7 @@
         <v>1374</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>1375</v>
@@ -69679,7 +69675,7 @@
         <v>1377</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>1378</v>
@@ -69696,7 +69692,7 @@
         <v>1380</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1381</v>
@@ -69713,7 +69709,7 @@
         <v>1383</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>1384</v>
@@ -69730,7 +69726,7 @@
         <v>1386</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>1387</v>
@@ -69747,7 +69743,7 @@
         <v>1389</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>1390</v>
@@ -69762,7 +69758,7 @@
         <v>1391</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1392</v>
@@ -69777,7 +69773,7 @@
         <v>1391</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>1393</v>
@@ -69792,7 +69788,7 @@
         <v>1394</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>1395</v>
@@ -69807,7 +69803,7 @@
         <v>1396</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>1397</v>
@@ -69824,7 +69820,7 @@
         <v>1399</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>1400</v>
@@ -70192,16 +70188,16 @@
         <v>206</v>
       </c>
       <c r="B18" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="C18" t="s">
         <v>1833</v>
       </c>
       <c r="D18" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="F18">
         <v>2026</v>
@@ -70212,16 +70208,16 @@
         <v>216</v>
       </c>
       <c r="B19" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="C19" t="s">
         <v>1833</v>
       </c>
       <c r="D19" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="F19">
         <v>2026</v>
@@ -70365,7 +70361,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="B6" t="s">
         <v>167</v>
@@ -70411,7 +70407,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="E8" t="s">
         <v>154</v>
@@ -72146,7 +72142,7 @@
         <v>1745</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="D3" s="9">
         <v>45820</v>
@@ -72160,7 +72156,7 @@
         <v>1746</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="D4" s="9">
         <v>45820</v>
@@ -72567,13 +72563,13 @@
         <v>46248</v>
       </c>
       <c r="B2" s="34" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>2540</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>2541</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>2542</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>2543</v>
       </c>
       <c r="G2" s="33"/>
     </row>
@@ -72582,13 +72578,13 @@
         <v>46241</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="G3" s="33"/>
     </row>
@@ -72597,13 +72593,13 @@
         <v>46234</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="G4" s="33"/>
     </row>
@@ -72612,13 +72608,13 @@
         <v>46227</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="G5" s="33"/>
     </row>
@@ -72627,13 +72623,13 @@
         <v>46220</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="C6" s="36" t="s">
+        <v>1922</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>1924</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>1926</v>
       </c>
       <c r="G6" s="33"/>
     </row>
@@ -72642,13 +72638,13 @@
         <v>46213</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="G7" s="33"/>
     </row>
@@ -74911,16 +74907,16 @@
         <v>167</v>
       </c>
       <c r="C2" s="22" t="s">
+        <v>2535</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>2537</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>2539</v>
-      </c>
       <c r="E2" s="22" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>2538</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>2540</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -74931,16 +74927,16 @@
         <v>216</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>2519</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>2520</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>2519</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>2521</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>2522</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -74951,16 +74947,16 @@
         <v>206</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>2514</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>2515</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>2516</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>2517</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>2518</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -74971,16 +74967,16 @@
         <v>216</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>2510</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>2509</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>2511</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>2512</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>2511</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>2513</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>2514</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -74991,16 +74987,16 @@
         <v>206</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>2505</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>2506</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>2507</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>2508</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>2509</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>2510</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75011,16 +75007,16 @@
         <v>216</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>2502</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>2501</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>2504</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>2503</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>2505</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>2506</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75031,16 +75027,16 @@
         <v>206</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>2497</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>2500</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>2498</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>2499</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>2502</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>2501</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -75051,16 +75047,16 @@
         <v>206</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>2495</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>2496</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>2498</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75071,16 +75067,16 @@
         <v>216</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>1971</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>1970</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1972</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>1973</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75091,16 +75087,16 @@
         <v>206</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75111,16 +75107,16 @@
         <v>216</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="D12" s="23" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E12" s="22" t="s">
         <v>1964</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>1966</v>
-      </c>
       <c r="F12" s="6" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75131,16 +75127,16 @@
         <v>206</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D13" s="23" t="s">
         <v>1961</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>1963</v>
-      </c>
       <c r="E13" s="22" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="289" x14ac:dyDescent="0.2">
@@ -75151,16 +75147,16 @@
         <v>167</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E14" s="22" t="s">
         <v>1958</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>1959</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>1960</v>
-      </c>
       <c r="F14" s="11" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="238" x14ac:dyDescent="0.2">
@@ -75171,16 +75167,16 @@
         <v>167</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>1955</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>1954</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1957</v>
-      </c>
       <c r="F15" s="11" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="204" x14ac:dyDescent="0.2">
@@ -75191,16 +75187,16 @@
         <v>167</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -75211,16 +75207,16 @@
         <v>206</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="D17" s="30" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E17" s="22" t="s">
         <v>1949</v>
       </c>
-      <c r="E17" s="22" t="s">
-        <v>1951</v>
-      </c>
       <c r="F17" s="6" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75231,16 +75227,16 @@
         <v>216</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="D18" s="30" t="s">
+        <v>1944</v>
+      </c>
+      <c r="E18" s="22" t="s">
         <v>1946</v>
       </c>
-      <c r="E18" s="22" t="s">
-        <v>1948</v>
-      </c>
       <c r="F18" s="6" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75251,16 +75247,16 @@
         <v>216</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>1941</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>1940</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F19" s="29" t="s">
         <v>1943</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>1942</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>1944</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>1945</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75271,16 +75267,16 @@
         <v>206</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="D20" s="30" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E20" s="22" t="s">
         <v>1939</v>
       </c>
-      <c r="E20" s="22" t="s">
-        <v>1941</v>
-      </c>
       <c r="F20" s="6" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="238" x14ac:dyDescent="0.2">
@@ -75291,16 +75287,16 @@
         <v>167</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="D21" s="30" t="s">
+        <v>1934</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>1936</v>
       </c>
-      <c r="E21" s="22" t="s">
-        <v>1938</v>
-      </c>
       <c r="F21" s="11" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75311,16 +75307,16 @@
         <v>216</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="D22" s="30" t="s">
+        <v>1931</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>1933</v>
       </c>
-      <c r="E22" s="22" t="s">
-        <v>1935</v>
-      </c>
       <c r="F22" s="6" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -75331,16 +75327,16 @@
         <v>206</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="D23" s="30" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E23" s="22" t="s">
         <v>1930</v>
       </c>
-      <c r="E23" s="22" t="s">
-        <v>1932</v>
-      </c>
       <c r="F23" s="6" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75351,16 +75347,16 @@
         <v>216</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E24" s="22" t="s">
         <v>1927</v>
       </c>
-      <c r="D24" s="30" t="s">
-        <v>1928</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1929</v>
-      </c>
       <c r="F24" s="6" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="85" x14ac:dyDescent="0.2">

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813511D3-BEBD-6648-99D9-7F25738B1000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6DF35C-62FF-6C45-B6EE-5375E8FDACE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" firstSheet="5" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -38848,7 +38848,7 @@
         <v>2122</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -38989,7 +38989,7 @@
         <v>2142</v>
       </c>
       <c r="O6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6DF35C-62FF-6C45-B6EE-5375E8FDACE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F16EEBD-888E-A14E-BB09-4A6459818B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" firstSheet="8" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="2548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="2550">
   <si>
     <t>date</t>
   </si>
@@ -5756,13 +5756,7 @@
     <t>date_added</t>
   </si>
   <si>
-    <t>07.07.shazam</t>
-  </si>
-  <si>
     <t>Join our everyday Shazam Challenge hosted by Taekook USA</t>
-  </si>
-  <si>
-    <t>07.06.radio</t>
   </si>
   <si>
     <t>Request for Winter Ahead in Usen</t>
@@ -13396,6 +13390,18 @@
 https://x.com/tetekoofm/status/1830991858291335218,
 https://x.com/tetekoofm/status/1831361195380720081,
 https://x.com/tetekoofm/status/1834998613828644916</t>
+  </si>
+  <si>
+    <t>Vote for BTS Swim at MTV Song of the Year</t>
+  </si>
+  <si>
+    <t>https://vote.mtv.com/song-of-the-year</t>
+  </si>
+  <si>
+    <t>https://vote.mtv.com/best-k-pop</t>
+  </si>
+  <si>
+    <t>Vote for BTS Swim at MTV Best Kpop</t>
   </si>
 </sst>
 </file>
@@ -13942,37 +13948,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="B1" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="C1" t="s">
         <v>438</v>
       </c>
       <c r="D1" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="E1" t="s">
         <v>197</v>
       </c>
       <c r="F1" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="G1" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="H1" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="I1" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="J1" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="K1" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -13983,22 +13989,22 @@
         <v>448</v>
       </c>
       <c r="C2" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="D2" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="E2" t="s">
         <v>422</v>
       </c>
       <c r="F2" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G2" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="H2" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I2" t="s">
         <v>511</v>
@@ -14012,25 +14018,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="C3" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="D3" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="E3" t="s">
         <v>422</v>
       </c>
       <c r="F3" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G3" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="H3" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="I3" t="s">
         <v>511</v>
@@ -14044,25 +14050,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="C4" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="D4" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="E4" t="s">
         <v>422</v>
       </c>
       <c r="F4" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G4" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="H4" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="I4" t="s">
         <v>511</v>
@@ -14076,25 +14082,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="C5" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="D5" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="E5" t="s">
         <v>422</v>
       </c>
       <c r="F5" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="G5" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H5" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I5" t="s">
         <v>442</v>
@@ -14103,7 +14109,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -14111,25 +14117,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="C6" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="D6" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="E6" t="s">
         <v>422</v>
       </c>
       <c r="F6" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="G6" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H6" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="I6" t="s">
         <v>442</v>
@@ -14143,25 +14149,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="C7" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="D7" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="E7" t="s">
         <v>422</v>
       </c>
       <c r="F7" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="G7" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H7" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="I7" t="s">
         <v>442</v>
@@ -14170,7 +14176,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -14178,25 +14184,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="C8" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="D8" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="E8" t="s">
         <v>422</v>
       </c>
       <c r="F8" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="G8" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H8" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="I8" t="s">
         <v>442</v>
@@ -14205,7 +14211,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -14213,25 +14219,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C9" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="D9" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="E9" t="s">
         <v>422</v>
       </c>
       <c r="F9" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="G9" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H9" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="I9" t="s">
         <v>442</v>
@@ -14245,25 +14251,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C10" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="D10" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="E10" t="s">
         <v>422</v>
       </c>
       <c r="F10" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="G10" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H10" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="I10" t="s">
         <v>442</v>
@@ -14280,22 +14286,22 @@
         <v>491</v>
       </c>
       <c r="C11" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="D11" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="E11" t="s">
         <v>422</v>
       </c>
       <c r="F11" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="G11" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H11" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I11" t="s">
         <v>490</v>
@@ -14304,7 +14310,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -14315,22 +14321,22 @@
         <v>982</v>
       </c>
       <c r="C12" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="D12" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="E12" t="s">
         <v>422</v>
       </c>
       <c r="F12" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="G12" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H12" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I12" t="s">
         <v>485</v>
@@ -14339,7 +14345,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -14350,22 +14356,22 @@
         <v>515</v>
       </c>
       <c r="C13" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="D13" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="E13" t="s">
         <v>422</v>
       </c>
       <c r="F13" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G13" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="H13" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="I13" t="s">
         <v>511</v>
@@ -14382,22 +14388,22 @@
         <v>625</v>
       </c>
       <c r="C14" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="D14" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="E14" t="s">
         <v>422</v>
       </c>
       <c r="F14" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G14" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="H14" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I14" t="s">
         <v>511</v>
@@ -14414,22 +14420,22 @@
         <v>985</v>
       </c>
       <c r="C15" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="D15" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="E15" t="s">
         <v>422</v>
       </c>
       <c r="F15" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G15" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="H15" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="I15" t="s">
         <v>511</v>
@@ -14443,25 +14449,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="C16" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="D16" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="E16" t="s">
         <v>422</v>
       </c>
       <c r="F16" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="G16" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H16" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="I16" t="s">
         <v>624</v>
@@ -14475,25 +14481,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="C17" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="D17" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="E17" t="s">
         <v>422</v>
       </c>
       <c r="F17" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="G17" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H17" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I17" t="s">
         <v>675</v>
@@ -14502,7 +14508,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -14510,25 +14516,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="C18" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="D18" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="E18" t="s">
         <v>422</v>
       </c>
       <c r="F18" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="G18" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H18" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I18" t="s">
         <v>675</v>
@@ -14537,7 +14543,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -14545,25 +14551,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="C19" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="D19" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="E19" t="s">
         <v>422</v>
       </c>
       <c r="F19" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="G19" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H19" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I19" t="s">
         <v>675</v>
@@ -14572,7 +14578,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -14580,25 +14586,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="C20" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="D20" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="E20" t="s">
         <v>422</v>
       </c>
       <c r="F20" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="G20" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H20" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="I20" t="s">
         <v>675</v>
@@ -14612,25 +14618,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="C21" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="D21" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="E21" t="s">
         <v>422</v>
       </c>
       <c r="F21" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="G21" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H21" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I21" t="s">
         <v>660</v>
@@ -14639,7 +14645,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -14647,25 +14653,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="C22" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="D22" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="E22" t="s">
         <v>422</v>
       </c>
       <c r="F22" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="G22" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H22" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="I22" t="s">
         <v>660</v>
@@ -14682,22 +14688,22 @@
         <v>655</v>
       </c>
       <c r="C23" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="D23" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="E23" t="s">
         <v>422</v>
       </c>
       <c r="F23" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="G23" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H23" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I23" t="s">
         <v>649</v>
@@ -14706,7 +14712,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -14714,25 +14720,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="C24" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="D24" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="E24" t="s">
         <v>422</v>
       </c>
       <c r="F24" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="G24" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H24" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="I24" t="s">
         <v>649</v>
@@ -14741,7 +14747,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -14752,22 +14758,22 @@
         <v>543</v>
       </c>
       <c r="C25" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="D25" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="E25" t="s">
         <v>422</v>
       </c>
       <c r="F25" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G25" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="H25" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I25" t="s">
         <v>511</v>
@@ -14781,25 +14787,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="C26" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="D26" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="E26" t="s">
         <v>422</v>
       </c>
       <c r="F26" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G26" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="H26" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="I26" t="s">
         <v>511</v>
@@ -14816,22 +14822,22 @@
         <v>716</v>
       </c>
       <c r="C27" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="D27" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="E27" t="s">
         <v>422</v>
       </c>
       <c r="F27" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="G27" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="H27" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="I27" t="s">
         <v>703</v>
@@ -14848,22 +14854,22 @@
         <v>727</v>
       </c>
       <c r="C28" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="D28" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="E28" t="s">
         <v>422</v>
       </c>
       <c r="F28" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="G28" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H28" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I28" t="s">
         <v>703</v>
@@ -14872,7 +14878,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -14883,22 +14889,22 @@
         <v>724</v>
       </c>
       <c r="C29" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="D29" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="E29" t="s">
         <v>422</v>
       </c>
       <c r="F29" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="G29" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H29" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I29" t="s">
         <v>703</v>
@@ -14907,7 +14913,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -14918,22 +14924,22 @@
         <v>720</v>
       </c>
       <c r="C30" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="D30" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="E30" t="s">
         <v>422</v>
       </c>
       <c r="F30" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="G30" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H30" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I30" t="s">
         <v>703</v>
@@ -14942,7 +14948,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -14953,22 +14959,22 @@
         <v>712</v>
       </c>
       <c r="C31" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="D31" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="E31" t="s">
         <v>422</v>
       </c>
       <c r="F31" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="G31" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H31" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="I31" t="s">
         <v>703</v>
@@ -14977,7 +14983,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -14988,22 +14994,22 @@
         <v>708</v>
       </c>
       <c r="C32" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D32" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="E32" t="s">
         <v>422</v>
       </c>
       <c r="F32" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="G32" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H32" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I32" t="s">
         <v>703</v>
@@ -15012,7 +15018,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -15023,22 +15029,22 @@
         <v>732</v>
       </c>
       <c r="C33" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="D33" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="E33" t="s">
         <v>422</v>
       </c>
       <c r="F33" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="G33" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="H33" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I33" t="s">
         <v>731</v>
@@ -15047,7 +15053,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -15058,22 +15064,22 @@
         <v>554</v>
       </c>
       <c r="C34" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="D34" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="E34" t="s">
         <v>422</v>
       </c>
       <c r="F34" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G34" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="H34" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="I34" t="s">
         <v>511</v>
@@ -15090,22 +15096,22 @@
         <v>523</v>
       </c>
       <c r="C35" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
       <c r="D35" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="E35" t="s">
         <v>422</v>
       </c>
       <c r="F35" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G35" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="H35" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="I35" t="s">
         <v>511</v>
@@ -15122,22 +15128,22 @@
         <v>519</v>
       </c>
       <c r="C36" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
       <c r="D36" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="E36" t="s">
         <v>422</v>
       </c>
       <c r="F36" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G36" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="H36" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="I36" t="s">
         <v>511</v>
@@ -15154,22 +15160,22 @@
         <v>539</v>
       </c>
       <c r="C37" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="D37" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
       <c r="E37" t="s">
         <v>422</v>
       </c>
       <c r="F37" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G37" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="H37" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="I37" t="s">
         <v>511</v>
@@ -15186,22 +15192,22 @@
         <v>550</v>
       </c>
       <c r="C38" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="D38" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="E38" t="s">
         <v>422</v>
       </c>
       <c r="F38" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G38" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="H38" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="I38" t="s">
         <v>511</v>
@@ -15218,22 +15224,22 @@
         <v>535</v>
       </c>
       <c r="C39" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="D39" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="E39" t="s">
         <v>422</v>
       </c>
       <c r="F39" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="G39" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="H39" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="I39" t="s">
         <v>511</v>
@@ -15253,7 +15259,7 @@
         <v>620</v>
       </c>
       <c r="D40" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="E40" t="s">
         <v>422</v>
@@ -15262,10 +15268,10 @@
         <v>617</v>
       </c>
       <c r="G40" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H40" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="I40" t="s">
         <v>616</v>
@@ -15282,10 +15288,10 @@
         <v>751</v>
       </c>
       <c r="C41" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="D41" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="E41" t="s">
         <v>422</v>
@@ -15294,13 +15300,13 @@
         <v>915</v>
       </c>
       <c r="G41" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H41" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="I41" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
@@ -15314,10 +15320,10 @@
         <v>601</v>
       </c>
       <c r="C42" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="D42" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="E42" t="s">
         <v>422</v>
@@ -15326,13 +15332,13 @@
         <v>600</v>
       </c>
       <c r="G42" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H42" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="I42" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
@@ -15346,10 +15352,10 @@
         <v>742</v>
       </c>
       <c r="C43" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="D43" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="E43" t="s">
         <v>422</v>
@@ -15358,10 +15364,10 @@
         <v>742</v>
       </c>
       <c r="G43" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H43" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="I43" t="s">
         <v>741</v>
@@ -15378,10 +15384,10 @@
         <v>1026</v>
       </c>
       <c r="C44" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="D44" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
       <c r="E44" t="s">
         <v>422</v>
@@ -15390,10 +15396,10 @@
         <v>1026</v>
       </c>
       <c r="G44" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H44" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="I44" t="s">
         <v>736</v>
@@ -15410,25 +15416,25 @@
         <v>596</v>
       </c>
       <c r="C45" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="D45" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="E45" t="s">
         <v>422</v>
       </c>
       <c r="F45" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
       <c r="G45" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H45" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="I45" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
@@ -15442,10 +15448,10 @@
         <v>747</v>
       </c>
       <c r="C46" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="D46" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="E46" t="s">
         <v>422</v>
@@ -15454,10 +15460,10 @@
         <v>747</v>
       </c>
       <c r="G46" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="H46" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="I46" t="s">
         <v>746</v>
@@ -15466,7 +15472,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -15477,10 +15483,10 @@
         <v>497</v>
       </c>
       <c r="C47" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="D47" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="E47" t="s">
         <v>422</v>
@@ -15489,10 +15495,10 @@
         <v>497</v>
       </c>
       <c r="G47" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="H47" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I47" t="s">
         <v>495</v>
@@ -15501,7 +15507,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -15509,25 +15515,25 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="C48" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="D48" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
       <c r="E48" t="s">
         <v>422</v>
       </c>
       <c r="F48" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="G48" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="H48" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="I48" t="s">
         <v>564</v>
@@ -15536,7 +15542,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -15547,10 +15553,10 @@
         <v>612</v>
       </c>
       <c r="C49" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
       <c r="D49" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="E49" t="s">
         <v>422</v>
@@ -15559,10 +15565,10 @@
         <v>612</v>
       </c>
       <c r="G49" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="H49" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="I49" t="s">
         <v>611</v>
@@ -15579,10 +15585,10 @@
         <v>756</v>
       </c>
       <c r="C50" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
       <c r="D50" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="E50" t="s">
         <v>420</v>
@@ -15591,10 +15597,10 @@
         <v>756</v>
       </c>
       <c r="G50" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H50" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I50" t="s">
         <v>755</v>
@@ -15608,25 +15614,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="C51" t="s">
-        <v>2277</v>
+        <v>2275</v>
       </c>
       <c r="D51" t="s">
-        <v>2278</v>
+        <v>2276</v>
       </c>
       <c r="E51" t="s">
         <v>420</v>
       </c>
       <c r="F51" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="G51" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="H51" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="I51" t="s">
         <v>893</v>
@@ -15635,7 +15641,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -15643,25 +15649,25 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="C52" t="s">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="D52" t="s">
-        <v>2280</v>
+        <v>2278</v>
       </c>
       <c r="E52" t="s">
         <v>420</v>
       </c>
       <c r="F52" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="G52" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="H52" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I52" t="s">
         <v>893</v>
@@ -15670,7 +15676,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -15678,25 +15684,25 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="C53" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="D53" t="s">
-        <v>2282</v>
+        <v>2280</v>
       </c>
       <c r="E53" t="s">
         <v>420</v>
       </c>
       <c r="F53" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="G53" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="H53" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="I53" t="s">
         <v>893</v>
@@ -15710,25 +15716,25 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="C54" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="D54" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="E54" t="s">
         <v>420</v>
       </c>
       <c r="F54" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="G54" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="H54" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="I54" t="s">
         <v>893</v>
@@ -15745,10 +15751,10 @@
         <v>824</v>
       </c>
       <c r="C55" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="D55" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="E55" t="s">
         <v>420</v>
@@ -15757,10 +15763,10 @@
         <v>808</v>
       </c>
       <c r="G55" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="H55" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I55" t="s">
         <v>807</v>
@@ -15777,10 +15783,10 @@
         <v>809</v>
       </c>
       <c r="C56" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="D56" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="E56" t="s">
         <v>420</v>
@@ -15789,10 +15795,10 @@
         <v>808</v>
       </c>
       <c r="G56" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="H56" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I56" t="s">
         <v>807</v>
@@ -15809,10 +15815,10 @@
         <v>817</v>
       </c>
       <c r="C57" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
       <c r="D57" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="E57" t="s">
         <v>420</v>
@@ -15821,10 +15827,10 @@
         <v>808</v>
       </c>
       <c r="G57" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="H57" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I57" t="s">
         <v>807</v>
@@ -15841,10 +15847,10 @@
         <v>828</v>
       </c>
       <c r="C58" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="D58" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="E58" t="s">
         <v>420</v>
@@ -15853,10 +15859,10 @@
         <v>808</v>
       </c>
       <c r="G58" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="H58" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I58" t="s">
         <v>807</v>
@@ -15873,10 +15879,10 @@
         <v>813</v>
       </c>
       <c r="C59" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="D59" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="E59" t="s">
         <v>420</v>
@@ -15885,10 +15891,10 @@
         <v>808</v>
       </c>
       <c r="G59" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="H59" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="I59" t="s">
         <v>807</v>
@@ -15902,13 +15908,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="C60" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="D60" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="E60" t="s">
         <v>420</v>
@@ -15917,10 +15923,10 @@
         <v>808</v>
       </c>
       <c r="G60" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="H60" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
       <c r="I60" t="s">
         <v>807</v>
@@ -15937,10 +15943,10 @@
         <v>916</v>
       </c>
       <c r="C61" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="D61" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="E61" t="s">
         <v>420</v>
@@ -15949,13 +15955,13 @@
         <v>915</v>
       </c>
       <c r="G61" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H61" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="I61" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
@@ -15969,25 +15975,25 @@
         <v>845</v>
       </c>
       <c r="C62" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="D62" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="E62" t="s">
         <v>420</v>
       </c>
       <c r="F62" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
       <c r="G62" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H62" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="I62" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
@@ -16001,10 +16007,10 @@
         <v>849</v>
       </c>
       <c r="C63" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="D63" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="E63" t="s">
         <v>420</v>
@@ -16013,13 +16019,13 @@
         <v>600</v>
       </c>
       <c r="G63" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H63" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="I63" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
@@ -16033,22 +16039,22 @@
         <v>855</v>
       </c>
       <c r="C64" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="D64" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="E64" t="s">
         <v>420</v>
       </c>
       <c r="F64" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="G64" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H64" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="I64" t="s">
         <v>859</v>
@@ -16062,25 +16068,25 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D65" t="s">
         <v>2307</v>
-      </c>
-      <c r="C65" t="s">
-        <v>2308</v>
-      </c>
-      <c r="D65" t="s">
-        <v>2309</v>
       </c>
       <c r="E65" t="s">
         <v>420</v>
       </c>
       <c r="F65" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="G65" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="H65" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="I65" t="s">
         <v>859</v>
@@ -16097,22 +16103,22 @@
         <v>884</v>
       </c>
       <c r="C66" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
       <c r="D66" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
       <c r="E66" t="s">
         <v>420</v>
       </c>
       <c r="F66" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="G66" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H66" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="I66" t="s">
         <v>883</v>
@@ -16129,22 +16135,22 @@
         <v>792</v>
       </c>
       <c r="C67" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="D67" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="E67" t="s">
         <v>420</v>
       </c>
       <c r="F67" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
       <c r="G67" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H67" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="I67" t="s">
         <v>790</v>
@@ -16158,25 +16164,25 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D68" t="s">
         <v>2316</v>
-      </c>
-      <c r="C68" t="s">
-        <v>2317</v>
-      </c>
-      <c r="D68" t="s">
-        <v>2318</v>
       </c>
       <c r="E68" t="s">
         <v>420</v>
       </c>
       <c r="F68" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
       <c r="G68" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="H68" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="I68" t="s">
         <v>790</v>
@@ -16193,10 +16199,10 @@
         <v>921</v>
       </c>
       <c r="C69" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
       <c r="D69" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="E69" t="s">
         <v>420</v>
@@ -16205,10 +16211,10 @@
         <v>921</v>
       </c>
       <c r="G69" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H69" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="I69" t="s">
         <v>920</v>
@@ -16225,10 +16231,10 @@
         <v>869</v>
       </c>
       <c r="C70" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="D70" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="E70" t="s">
         <v>420</v>
@@ -16237,10 +16243,10 @@
         <v>869</v>
       </c>
       <c r="G70" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="H70" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="I70" t="s">
         <v>868</v>
@@ -16257,22 +16263,22 @@
         <v>777</v>
       </c>
       <c r="C71" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="D71" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="E71" t="s">
         <v>420</v>
       </c>
       <c r="F71" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="G71" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="H71" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="I71" t="s">
         <v>781</v>
@@ -16281,7 +16287,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
@@ -16289,25 +16295,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="C72" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="D72" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="E72" t="s">
         <v>420</v>
       </c>
       <c r="F72" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="G72" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="H72" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="I72" t="s">
         <v>781</v>
@@ -16324,22 +16330,22 @@
         <v>879</v>
       </c>
       <c r="C73" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
       <c r="D73" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="E73" t="s">
         <v>420</v>
       </c>
       <c r="F73" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="G73" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="H73" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I73" t="s">
         <v>873</v>
@@ -16348,7 +16354,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
@@ -16359,22 +16365,22 @@
         <v>875</v>
       </c>
       <c r="C74" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="D74" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
       <c r="E74" t="s">
         <v>420</v>
       </c>
       <c r="F74" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="G74" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="H74" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I74" t="s">
         <v>873</v>
@@ -16383,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
@@ -16391,13 +16397,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="C75" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
       <c r="D75" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="E75" t="s">
         <v>420</v>
@@ -16406,10 +16412,10 @@
         <v>948</v>
       </c>
       <c r="G75" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H75" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I75" t="s">
         <v>946</v>
@@ -16418,7 +16424,7 @@
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
@@ -16426,13 +16432,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="C76" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="D76" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="E76" t="s">
         <v>420</v>
@@ -16441,10 +16447,10 @@
         <v>948</v>
       </c>
       <c r="G76" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H76" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="I76" t="s">
         <v>946</v>
@@ -16461,10 +16467,10 @@
         <v>1059</v>
       </c>
       <c r="C77" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="D77" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="E77" t="s">
         <v>420</v>
@@ -16473,10 +16479,10 @@
         <v>948</v>
       </c>
       <c r="G77" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="H77" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="I77" t="s">
         <v>946</v>
@@ -16490,13 +16496,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="C78" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="D78" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="E78" t="s">
         <v>420</v>
@@ -16505,10 +16511,10 @@
         <v>948</v>
       </c>
       <c r="G78" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H78" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="I78" t="s">
         <v>946</v>
@@ -16522,13 +16528,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="C79" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="D79" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="E79" t="s">
         <v>420</v>
@@ -16537,10 +16543,10 @@
         <v>926</v>
       </c>
       <c r="G79" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H79" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I79" t="s">
         <v>925</v>
@@ -16549,7 +16555,7 @@
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
@@ -16557,13 +16563,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="C80" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="D80" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="E80" t="s">
         <v>420</v>
@@ -16572,19 +16578,19 @@
         <v>926</v>
       </c>
       <c r="G80" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H80" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
       <c r="I80" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
@@ -16592,13 +16598,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="C81" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="D81" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="E81" t="s">
         <v>420</v>
@@ -16607,10 +16613,10 @@
         <v>926</v>
       </c>
       <c r="G81" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H81" t="s">
-        <v>2348</v>
+        <v>2346</v>
       </c>
       <c r="I81" t="s">
         <v>925</v>
@@ -16624,13 +16630,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="C82" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
       <c r="D82" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
       <c r="E82" t="s">
         <v>420</v>
@@ -16639,13 +16645,13 @@
         <v>926</v>
       </c>
       <c r="G82" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="H82" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="I82" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
@@ -16656,28 +16662,28 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="C83" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="D83" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="E83" t="s">
         <v>199</v>
       </c>
       <c r="F83" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="G83" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="H83" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I83" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
@@ -16688,28 +16694,28 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>2352</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2353</v>
+      </c>
+      <c r="D84" t="s">
         <v>2354</v>
-      </c>
-      <c r="C84" t="s">
-        <v>2355</v>
-      </c>
-      <c r="D84" t="s">
-        <v>2356</v>
       </c>
       <c r="E84" t="s">
         <v>199</v>
       </c>
       <c r="F84" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="G84" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="H84" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="I84" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
@@ -16720,34 +16726,34 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="C85" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="D85" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="E85" t="s">
         <v>422</v>
       </c>
       <c r="F85" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="G85" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="H85" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="I85" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -16755,34 +16761,34 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D86" t="s">
         <v>2359</v>
-      </c>
-      <c r="C86" t="s">
-        <v>2360</v>
-      </c>
-      <c r="D86" t="s">
-        <v>2361</v>
       </c>
       <c r="E86" t="s">
         <v>420</v>
       </c>
       <c r="F86" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="G86" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="H86" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="I86" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
@@ -16790,28 +16796,28 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="C87" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
       <c r="D87" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="E87" t="s">
         <v>199</v>
       </c>
       <c r="F87" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="G87" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="H87" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I87" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
@@ -16822,28 +16828,28 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2446</v>
+      </c>
+      <c r="D88" t="s">
         <v>2445</v>
-      </c>
-      <c r="C88" t="s">
-        <v>2448</v>
-      </c>
-      <c r="D88" t="s">
-        <v>2447</v>
       </c>
       <c r="E88" t="s">
         <v>199</v>
       </c>
       <c r="F88" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="G88" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="H88" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I88" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
@@ -16855,28 +16861,28 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="C89" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="D89" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
       <c r="E89" t="s">
         <v>199</v>
       </c>
       <c r="F89" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="G89" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="H89" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="I89" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
@@ -16904,28 +16910,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>1983</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="E1" s="5" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>1986</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>1984</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>1985</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>1987</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>1988</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>1989</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>1990</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -16933,7 +16939,7 @@
         <v>216</v>
       </c>
       <c r="B2" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="C2" t="s">
         <v>916</v>
@@ -16942,16 +16948,16 @@
         <v>915</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>1989</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>1991</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>1993</v>
-      </c>
       <c r="H2" s="8" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -16959,7 +16965,7 @@
         <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="C3" t="s">
         <v>751</v>
@@ -16968,16 +16974,16 @@
         <v>915</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>1994</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>1995</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>1996</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>1997</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>1998</v>
-      </c>
       <c r="H3" s="8" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -16991,19 +16997,19 @@
         <v>777</v>
       </c>
       <c r="D4" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>2031</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>2032</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>2033</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>2034</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>2035</v>
-      </c>
       <c r="H4" s="8" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17011,7 +17017,7 @@
         <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="C5" t="s">
         <v>596</v>
@@ -17020,16 +17026,16 @@
         <v>595</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>2004</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>2005</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>2006</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>2007</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>2008</v>
-      </c>
       <c r="H5" s="8" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17037,7 +17043,7 @@
         <v>216</v>
       </c>
       <c r="B6" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="C6" t="s">
         <v>845</v>
@@ -17046,16 +17052,16 @@
         <v>595</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>2007</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>2008</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>2009</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>2010</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>2011</v>
-      </c>
       <c r="H6" s="8" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17069,19 +17075,19 @@
         <v>869</v>
       </c>
       <c r="D7" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>2034</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>2036</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>2038</v>
-      </c>
       <c r="H7" s="8" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17095,19 +17101,19 @@
         <v>921</v>
       </c>
       <c r="D8" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="F8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17115,7 +17121,7 @@
         <v>206</v>
       </c>
       <c r="B9" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="C9" t="s">
         <v>601</v>
@@ -17124,16 +17130,16 @@
         <v>600</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>2028</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>2029</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>2030</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>2031</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>2032</v>
-      </c>
       <c r="H9" s="8" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17141,7 +17147,7 @@
         <v>216</v>
       </c>
       <c r="B10" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="C10" t="s">
         <v>849</v>
@@ -17150,16 +17156,16 @@
         <v>600</v>
       </c>
       <c r="E10" s="8" t="s">
+        <v>2011</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>2012</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>2013</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>2014</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>2015</v>
-      </c>
       <c r="H10" s="8" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17173,19 +17179,19 @@
         <v>792</v>
       </c>
       <c r="D11" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="F11" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G11" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17199,19 +17205,19 @@
         <v>742</v>
       </c>
       <c r="D12" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>2039</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>2040</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>2041</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>2042</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>2043</v>
-      </c>
       <c r="H12" s="8" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -17222,22 +17228,22 @@
         <v>883</v>
       </c>
       <c r="C13" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="D13" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E13" s="8" t="s">
+        <v>2042</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>2043</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>2044</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>2045</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>2046</v>
-      </c>
       <c r="H13" s="8" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -17251,19 +17257,19 @@
         <v>855</v>
       </c>
       <c r="D14" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>2015</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>2016</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>2017</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>2018</v>
-      </c>
       <c r="H14" s="8" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17277,19 +17283,19 @@
         <v>1026</v>
       </c>
       <c r="D15" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17303,19 +17309,19 @@
         <v>612</v>
       </c>
       <c r="D16" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>2047</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>2048</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>2049</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>2050</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>2051</v>
-      </c>
       <c r="H16" s="8" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -17326,22 +17332,22 @@
         <v>564</v>
       </c>
       <c r="C17" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="D17" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="F17" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G17" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -17358,16 +17364,16 @@
         <v>497</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="F18" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G18" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17378,22 +17384,22 @@
         <v>511</v>
       </c>
       <c r="C19" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="D19" t="s">
         <v>512</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="F19" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G19" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -17410,16 +17416,16 @@
         <v>808</v>
       </c>
       <c r="E20" s="8" t="s">
+        <v>2018</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>2019</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>2020</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>2021</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>2022</v>
-      </c>
       <c r="H20" s="8" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17436,16 +17442,16 @@
         <v>808</v>
       </c>
       <c r="E21" s="8" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>2022</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>2023</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>2024</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>2025</v>
-      </c>
       <c r="H21" s="8" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -17462,16 +17468,16 @@
         <v>808</v>
       </c>
       <c r="E22" s="8" t="s">
+        <v>2064</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>2065</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>2066</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>2067</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>2068</v>
-      </c>
       <c r="H22" s="8" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17488,16 +17494,16 @@
         <v>808</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="F23" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G23" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -17514,16 +17520,16 @@
         <v>808</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="F24" s="8" t="s">
+        <v>2068</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>2070</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>2072</v>
-      </c>
       <c r="H24" s="8" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -17534,22 +17540,22 @@
         <v>511</v>
       </c>
       <c r="C25" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="D25" t="s">
         <v>512</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="F25" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G25" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
@@ -17563,19 +17569,19 @@
         <v>747</v>
       </c>
       <c r="D26" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="F26" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G26" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17586,22 +17592,22 @@
         <v>511</v>
       </c>
       <c r="C27" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="D27" t="s">
         <v>512</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F27" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G27" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -17618,16 +17624,16 @@
         <v>512</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="F28" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G28" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -17638,22 +17644,22 @@
         <v>511</v>
       </c>
       <c r="C29" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="D29" t="s">
         <v>512</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="F29" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G29" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17670,16 +17676,16 @@
         <v>512</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="F30" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G30" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -17696,16 +17702,16 @@
         <v>512</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="F31" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G31" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -17722,16 +17728,16 @@
         <v>512</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="F32" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G32" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -17748,16 +17754,16 @@
         <v>512</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="F33" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G33" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -17774,13 +17780,13 @@
         <v>512</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="F34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -17797,16 +17803,16 @@
         <v>512</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="F35" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G35" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17817,22 +17823,22 @@
         <v>893</v>
       </c>
       <c r="C36" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="D36" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G36" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -17846,19 +17852,19 @@
         <v>756</v>
       </c>
       <c r="D37" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="F37" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G37" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17869,22 +17875,22 @@
         <v>558</v>
       </c>
       <c r="C38" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="D38" t="s">
         <v>559</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -17898,19 +17904,19 @@
         <v>617</v>
       </c>
       <c r="D39" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="F39" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G39" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.2">
@@ -17924,19 +17930,19 @@
         <v>926</v>
       </c>
       <c r="D40" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E40" s="8" t="s">
+        <v>2085</v>
+      </c>
+      <c r="F40" t="s">
         <v>2087</v>
       </c>
-      <c r="F40" t="s">
-        <v>2089</v>
-      </c>
       <c r="G40" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.2">
@@ -17950,19 +17956,19 @@
         <v>948</v>
       </c>
       <c r="D41" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="F41" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="G41" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
   </sheetData>
@@ -19341,7 +19347,7 @@
         <v>206</v>
       </c>
       <c r="B36" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>595</v>
@@ -19379,7 +19385,7 @@
         <v>206</v>
       </c>
       <c r="B37" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>600</v>
@@ -20662,7 +20668,7 @@
         <v>736</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>737</v>
@@ -20773,7 +20779,7 @@
         <v>206</v>
       </c>
       <c r="B74" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>751</v>
@@ -21549,7 +21555,7 @@
         <v>216</v>
       </c>
       <c r="B94" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>595</v>
@@ -21587,7 +21593,7 @@
         <v>216</v>
       </c>
       <c r="B95" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>600</v>
@@ -22123,7 +22129,7 @@
         <v>216</v>
       </c>
       <c r="B109" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>915</v>
@@ -37968,7 +37974,7 @@
         <v>515</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -38770,16 +38776,16 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C1" t="s">
         <v>2109</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>2110</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2111</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2112</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -38788,64 +38794,64 @@
         <v>147</v>
       </c>
       <c r="G1" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="H1" t="s">
         <v>146</v>
       </c>
       <c r="I1" t="s">
+        <v>2111</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2112</v>
+      </c>
+      <c r="K1" t="s">
+        <v>2158</v>
+      </c>
+      <c r="L1" t="s">
         <v>2113</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>2114</v>
       </c>
-      <c r="K1" t="s">
-        <v>2160</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
+        <v>2466</v>
+      </c>
+      <c r="O1" t="s">
         <v>2115</v>
-      </c>
-      <c r="M1" t="s">
-        <v>2116</v>
-      </c>
-      <c r="N1" t="s">
-        <v>2468</v>
-      </c>
-      <c r="O1" t="s">
-        <v>2117</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="B2" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="C2" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="D2" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="H2" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I2" t="s">
+        <v>2117</v>
+      </c>
+      <c r="J2" t="s">
         <v>2118</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>2119</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>2120</v>
-      </c>
-      <c r="L2" t="s">
-        <v>2121</v>
-      </c>
-      <c r="M2" t="s">
-        <v>2122</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
@@ -38853,34 +38859,34 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="B3" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C3" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="D3" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="F3" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="H3" t="s">
+        <v>2121</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2122</v>
+      </c>
+      <c r="J3" t="s">
         <v>2123</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
         <v>2124</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>2125</v>
-      </c>
-      <c r="L3" t="s">
-        <v>2126</v>
-      </c>
-      <c r="M3" t="s">
-        <v>2127</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -38888,34 +38894,34 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="B4" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C4" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="D4" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="F4" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="H4" t="s">
+        <v>2126</v>
+      </c>
+      <c r="I4" t="s">
+        <v>2127</v>
+      </c>
+      <c r="J4" t="s">
         <v>2128</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>2129</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>2130</v>
-      </c>
-      <c r="L4" t="s">
-        <v>2131</v>
-      </c>
-      <c r="M4" t="s">
-        <v>2132</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
@@ -38923,34 +38929,34 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="B5" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C5" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="D5" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="F5" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="H5" t="s">
+        <v>2131</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2132</v>
+      </c>
+      <c r="J5" t="s">
         <v>2133</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>2134</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>2135</v>
-      </c>
-      <c r="L5" t="s">
-        <v>2136</v>
-      </c>
-      <c r="M5" t="s">
-        <v>2137</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
@@ -38958,35 +38964,35 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="B6" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="C6" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="D6" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="H6" t="s">
+        <v>2136</v>
+      </c>
+      <c r="I6" t="s">
+        <v>2137</v>
+      </c>
+      <c r="J6" t="s">
         <v>2138</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>2139</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>2140</v>
-      </c>
-      <c r="L6" t="s">
-        <v>2141</v>
-      </c>
-      <c r="M6" t="s">
-        <v>2142</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -38994,43 +39000,43 @@
     </row>
     <row r="7" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="B7" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C7" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="D7" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="E7" s="9">
         <v>46001</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>2472</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>2473</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>2474</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>2475</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="L7" s="8" t="s">
+        <v>2470</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>2476</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>2471</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>2476</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>2477</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>2472</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>2478</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>2473</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -39038,46 +39044,46 @@
     </row>
     <row r="8" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="B8" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C8" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="D8" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="E8" s="9">
         <v>45994</v>
       </c>
       <c r="F8" t="s">
+        <v>2459</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>2360</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>2464</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>2463</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>2461</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>2362</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>2466</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="K8" s="8" t="s">
+        <v>2462</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>2465</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>2463</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>2464</v>
-      </c>
-      <c r="L8" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>2467</v>
       </c>
-      <c r="M8" s="8" t="s">
-        <v>2469</v>
-      </c>
       <c r="N8" s="8" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
@@ -39085,46 +39091,46 @@
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="B9" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C9" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="D9" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="E9" s="9">
         <v>45928</v>
       </c>
       <c r="F9" t="s">
+        <v>2478</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>2479</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>2486</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>2482</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>2487</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>2483</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>2484</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>2485</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>2480</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>2481</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>2488</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>2484</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>2489</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>2485</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>2486</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>2487</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>2482</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -39132,13 +39138,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="B10" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C10" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="E10" s="9">
         <v>45985</v>
@@ -39211,7 +39217,7 @@
         <v>1077</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>1079</v>
@@ -39392,12 +39398,12 @@
         <v>1109</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="6" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -39439,14 +39445,14 @@
         <v>1116</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>1117</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="6" t="s">
@@ -39646,7 +39652,7 @@
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="6" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="6" t="s">
@@ -39691,7 +39697,7 @@
         <v>1146</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -39773,7 +39779,7 @@
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -39816,7 +39822,7 @@
         <v>1160</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -68997,7 +69003,7 @@
     </row>
     <row r="2" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="34" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="B2" s="37">
         <v>45875</v>
@@ -69006,18 +69012,18 @@
         <v>1113</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="B3" s="37">
         <v>46231</v>
@@ -69026,10 +69032,10 @@
         <v>1106</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>1276</v>
@@ -69049,7 +69055,7 @@
         <v>1275</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>1276</v>
@@ -69092,7 +69098,7 @@
         <v>1283</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
@@ -69191,7 +69197,7 @@
         <v>1294</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>1295</v>
@@ -69208,7 +69214,7 @@
         <v>1297</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>1298</v>
@@ -69225,7 +69231,7 @@
         <v>1300</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>1301</v>
@@ -69257,7 +69263,7 @@
         <v>1306</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>1307</v>
@@ -69274,7 +69280,7 @@
         <v>1309</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>1310</v>
@@ -69291,7 +69297,7 @@
         <v>1312</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>1313</v>
@@ -69308,7 +69314,7 @@
         <v>1315</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>1316</v>
@@ -69325,7 +69331,7 @@
         <v>1318</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>1319</v>
@@ -69342,7 +69348,7 @@
         <v>1321</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>1322</v>
@@ -69359,7 +69365,7 @@
         <v>1324</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>1325</v>
@@ -69373,7 +69379,7 @@
         <v>1326</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>1327</v>
@@ -69393,7 +69399,7 @@
         <v>1330</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>1331</v>
@@ -69411,7 +69417,7 @@
         <v>1333</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>1334</v>
@@ -69428,7 +69434,7 @@
         <v>1336</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>1337</v>
@@ -69443,7 +69449,7 @@
         <v>1338</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>1339</v>
@@ -69460,7 +69466,7 @@
         <v>1341</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>1342</v>
@@ -69477,7 +69483,7 @@
         <v>1344</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>1345</v>
@@ -69494,7 +69500,7 @@
         <v>1347</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>1348</v>
@@ -69511,7 +69517,7 @@
         <v>1350</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>1351</v>
@@ -69528,7 +69534,7 @@
         <v>1353</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>1354</v>
@@ -69545,7 +69551,7 @@
         <v>1356</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>1357</v>
@@ -69560,7 +69566,7 @@
         <v>1358</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>1359</v>
@@ -69580,7 +69586,7 @@
         <v>1362</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>1363</v>
@@ -69595,7 +69601,7 @@
         <v>1364</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>1365</v>
@@ -69612,7 +69618,7 @@
         <v>1367</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>1368</v>
@@ -69627,7 +69633,7 @@
         <v>1369</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>1370</v>
@@ -69644,7 +69650,7 @@
         <v>1372</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>1373</v>
@@ -69658,7 +69664,7 @@
         <v>1374</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>1375</v>
@@ -69675,7 +69681,7 @@
         <v>1377</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>1378</v>
@@ -69692,7 +69698,7 @@
         <v>1380</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1381</v>
@@ -69709,7 +69715,7 @@
         <v>1383</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>1384</v>
@@ -69726,7 +69732,7 @@
         <v>1386</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>1387</v>
@@ -69743,7 +69749,7 @@
         <v>1389</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>1390</v>
@@ -69758,7 +69764,7 @@
         <v>1391</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1392</v>
@@ -69773,7 +69779,7 @@
         <v>1391</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>1393</v>
@@ -69788,7 +69794,7 @@
         <v>1394</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>1395</v>
@@ -69803,7 +69809,7 @@
         <v>1396</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>1397</v>
@@ -69820,7 +69826,7 @@
         <v>1399</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>1400</v>
@@ -69868,16 +69874,16 @@
         <v>216</v>
       </c>
       <c r="B2" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="C2" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D2" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="E2" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="F2">
         <v>2023</v>
@@ -69888,16 +69894,16 @@
         <v>216</v>
       </c>
       <c r="B3" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="C3" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D3" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="E3" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="F3">
         <v>2023</v>
@@ -69908,16 +69914,16 @@
         <v>216</v>
       </c>
       <c r="B4" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="C4" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D4" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="F4">
         <v>2023</v>
@@ -69928,16 +69934,16 @@
         <v>216</v>
       </c>
       <c r="B5" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="C5" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D5" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="E5" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="F5">
         <v>2023</v>
@@ -69948,16 +69954,16 @@
         <v>216</v>
       </c>
       <c r="B6" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="C6" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D6" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="E6" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="F6">
         <v>2025</v>
@@ -69968,16 +69974,16 @@
         <v>216</v>
       </c>
       <c r="B7" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="C7" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D7" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="E7" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="F7">
         <v>2025</v>
@@ -69988,16 +69994,16 @@
         <v>216</v>
       </c>
       <c r="B8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="C8" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D8" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="E8" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="F8">
         <v>2025</v>
@@ -70008,16 +70014,16 @@
         <v>216</v>
       </c>
       <c r="B9" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C9" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D9" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="E9" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="F9">
         <v>2025</v>
@@ -70028,16 +70034,16 @@
         <v>216</v>
       </c>
       <c r="B10" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="C10" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D10" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="E10" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="F10">
         <v>2025</v>
@@ -70048,16 +70054,16 @@
         <v>216</v>
       </c>
       <c r="B11" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="C11" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D11" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="E11" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="F11">
         <v>2026</v>
@@ -70068,16 +70074,16 @@
         <v>216</v>
       </c>
       <c r="B12" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="C12" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D12" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="E12" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="F12">
         <v>2023</v>
@@ -70088,16 +70094,16 @@
         <v>206</v>
       </c>
       <c r="B13" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C13" t="s">
         <v>1831</v>
       </c>
-      <c r="C13" t="s">
-        <v>1833</v>
-      </c>
       <c r="D13" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="F13">
         <v>2023</v>
@@ -70108,16 +70114,16 @@
         <v>206</v>
       </c>
       <c r="B14" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="C14" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D14" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="F14">
         <v>2023</v>
@@ -70128,16 +70134,16 @@
         <v>206</v>
       </c>
       <c r="B15" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="C15" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D15" t="s">
         <v>1833</v>
       </c>
-      <c r="D15" t="s">
-        <v>1835</v>
-      </c>
       <c r="E15" s="8" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="F15">
         <v>2026</v>
@@ -70148,16 +70154,16 @@
         <v>206</v>
       </c>
       <c r="B16" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="C16" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D16" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="F16">
         <v>2025</v>
@@ -70168,16 +70174,16 @@
         <v>206</v>
       </c>
       <c r="B17" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="C17" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="D17" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="F17">
         <v>2026</v>
@@ -70188,16 +70194,16 @@
         <v>206</v>
       </c>
       <c r="B18" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>2542</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1833</v>
-      </c>
-      <c r="D18" t="s">
-        <v>2543</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>2544</v>
       </c>
       <c r="F18">
         <v>2026</v>
@@ -70208,16 +70214,16 @@
         <v>216</v>
       </c>
       <c r="B19" t="s">
+        <v>2530</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2531</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>2532</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1833</v>
-      </c>
-      <c r="D19" t="s">
-        <v>2533</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>2534</v>
       </c>
       <c r="F19">
         <v>2026</v>
@@ -70361,7 +70367,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
       <c r="B6" t="s">
         <v>167</v>
@@ -70407,7 +70413,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="E8" t="s">
         <v>154</v>
@@ -72098,12 +72104,12 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="84.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -72122,10 +72128,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" t="s">
         <v>1742</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1743</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>1108</v>
@@ -72136,13 +72142,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1744</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="D3" s="9">
         <v>45820</v>
@@ -72150,21 +72156,45 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" t="s">
         <v>1744</v>
       </c>
-      <c r="B4" t="s">
-        <v>1746</v>
-      </c>
       <c r="C4" s="6" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="D4" s="9">
         <v>45820</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C5" s="6"/>
-      <c r="D5" s="9"/>
+      <c r="A5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>2547</v>
+      </c>
+      <c r="D5" s="9">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2549</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>2548</v>
+      </c>
+      <c r="D6" s="9">
+        <v>46257</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -72249,16 +72279,16 @@
         <v>216</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>1796</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F2" s="19" t="s">
         <v>1797</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>1798</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>1870</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>1799</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="85" x14ac:dyDescent="0.2">
@@ -72269,16 +72299,16 @@
         <v>206</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="102" x14ac:dyDescent="0.2">
@@ -72289,16 +72319,16 @@
         <v>216</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>1750</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>1752</v>
-      </c>
       <c r="E4" s="19" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="119" x14ac:dyDescent="0.2">
@@ -72309,16 +72339,16 @@
         <v>206</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="221" customHeight="1" x14ac:dyDescent="0.2">
@@ -72335,7 +72365,7 @@
         <v>201</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>202</v>
@@ -72355,7 +72385,7 @@
         <v>204</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="F7" s="19" t="s">
         <v>205</v>
@@ -72375,10 +72405,10 @@
         <v>208</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="187" customHeight="1" x14ac:dyDescent="0.2">
@@ -72415,7 +72445,7 @@
         <v>214</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>215</v>
@@ -72563,13 +72593,13 @@
         <v>46248</v>
       </c>
       <c r="B2" s="34" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>2539</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>2540</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>2541</v>
       </c>
       <c r="G2" s="33"/>
     </row>
@@ -72578,13 +72608,13 @@
         <v>46241</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="G3" s="33"/>
     </row>
@@ -72593,13 +72623,13 @@
         <v>46234</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="G4" s="33"/>
     </row>
@@ -72608,13 +72638,13 @@
         <v>46227</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="G5" s="33"/>
     </row>
@@ -72623,13 +72653,13 @@
         <v>46220</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="C6" s="36" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>1922</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>1924</v>
       </c>
       <c r="G6" s="33"/>
     </row>
@@ -72638,13 +72668,13 @@
         <v>46213</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="G7" s="33"/>
     </row>
@@ -72653,13 +72683,13 @@
         <v>46206</v>
       </c>
       <c r="B8" s="34" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>1867</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>1869</v>
-      </c>
       <c r="D8" s="23" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="G8" s="33"/>
     </row>
@@ -72668,13 +72698,13 @@
         <v>46199</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="C9" s="36" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>1747</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>1749</v>
       </c>
       <c r="G9" s="33"/>
     </row>
@@ -74907,16 +74937,16 @@
         <v>167</v>
       </c>
       <c r="C2" s="22" t="s">
+        <v>2533</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>2535</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>2537</v>
-      </c>
       <c r="E2" s="22" t="s">
+        <v>2534</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>2536</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>2538</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -74927,16 +74957,16 @@
         <v>216</v>
       </c>
       <c r="C3" s="22" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>2517</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>2518</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>2517</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>2519</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>2520</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -74947,16 +74977,16 @@
         <v>206</v>
       </c>
       <c r="C4" s="22" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>2512</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>2513</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>2514</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>2515</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>2516</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -74967,16 +74997,16 @@
         <v>216</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>2508</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>2507</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>2509</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>2510</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>2509</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>2511</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>2512</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -74987,16 +75017,16 @@
         <v>206</v>
       </c>
       <c r="C6" s="22" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>2504</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>2505</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>2506</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>2507</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>2508</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75007,16 +75037,16 @@
         <v>216</v>
       </c>
       <c r="C7" s="22" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>2499</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>2502</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>2501</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>2504</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75027,16 +75057,16 @@
         <v>206</v>
       </c>
       <c r="C8" s="22" t="s">
+        <v>2495</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>2498</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>2496</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>2497</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>2500</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>2499</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -75047,16 +75077,16 @@
         <v>206</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>2491</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>2492</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>2493</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>2494</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>2496</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75067,16 +75097,16 @@
         <v>216</v>
       </c>
       <c r="C10" s="22" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>1968</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>1969</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>1968</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>1970</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>1971</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75087,16 +75117,16 @@
         <v>206</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75107,16 +75137,16 @@
         <v>216</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="D12" s="23" t="s">
+        <v>1960</v>
+      </c>
+      <c r="E12" s="22" t="s">
         <v>1962</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>1964</v>
-      </c>
       <c r="F12" s="6" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75127,16 +75157,16 @@
         <v>206</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D13" s="23" t="s">
         <v>1959</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>1961</v>
-      </c>
       <c r="E13" s="22" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="289" x14ac:dyDescent="0.2">
@@ -75147,16 +75177,16 @@
         <v>167</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E14" s="22" t="s">
         <v>1956</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>1957</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>1958</v>
-      </c>
       <c r="F14" s="11" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="238" x14ac:dyDescent="0.2">
@@ -75167,16 +75197,16 @@
         <v>167</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>1953</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>1952</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>1955</v>
-      </c>
       <c r="F15" s="11" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="204" x14ac:dyDescent="0.2">
@@ -75187,16 +75217,16 @@
         <v>167</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -75207,16 +75237,16 @@
         <v>206</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="D17" s="30" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E17" s="22" t="s">
         <v>1947</v>
       </c>
-      <c r="E17" s="22" t="s">
-        <v>1949</v>
-      </c>
       <c r="F17" s="6" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75227,16 +75257,16 @@
         <v>216</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="D18" s="30" t="s">
+        <v>1942</v>
+      </c>
+      <c r="E18" s="22" t="s">
         <v>1944</v>
       </c>
-      <c r="E18" s="22" t="s">
-        <v>1946</v>
-      </c>
       <c r="F18" s="6" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75247,16 +75277,16 @@
         <v>216</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>1938</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>1940</v>
+      </c>
+      <c r="F19" s="29" t="s">
         <v>1941</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>1940</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>1942</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>1943</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75267,16 +75297,16 @@
         <v>206</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="D20" s="30" t="s">
+        <v>1935</v>
+      </c>
+      <c r="E20" s="22" t="s">
         <v>1937</v>
       </c>
-      <c r="E20" s="22" t="s">
-        <v>1939</v>
-      </c>
       <c r="F20" s="6" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="238" x14ac:dyDescent="0.2">
@@ -75287,16 +75317,16 @@
         <v>167</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="D21" s="30" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>1934</v>
       </c>
-      <c r="E21" s="22" t="s">
-        <v>1936</v>
-      </c>
       <c r="F21" s="11" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75307,16 +75337,16 @@
         <v>216</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="D22" s="30" t="s">
+        <v>1929</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>1931</v>
       </c>
-      <c r="E22" s="22" t="s">
-        <v>1933</v>
-      </c>
       <c r="F22" s="6" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -75327,16 +75357,16 @@
         <v>206</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="D23" s="30" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E23" s="22" t="s">
         <v>1928</v>
       </c>
-      <c r="E23" s="22" t="s">
-        <v>1930</v>
-      </c>
       <c r="F23" s="6" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75347,16 +75377,16 @@
         <v>216</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E24" s="22" t="s">
         <v>1925</v>
       </c>
-      <c r="D24" s="30" t="s">
-        <v>1926</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1927</v>
-      </c>
       <c r="F24" s="6" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="85" x14ac:dyDescent="0.2">
@@ -75367,16 +75397,16 @@
         <v>216</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>1814</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>1817</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1815</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75387,16 +75417,16 @@
         <v>206</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F26" s="29" t="s">
         <v>1810</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>1813</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1811</v>
-      </c>
-      <c r="F26" s="29" t="s">
-        <v>1812</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75407,16 +75437,16 @@
         <v>216</v>
       </c>
       <c r="C27" s="22" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F27" s="30" t="s">
         <v>1807</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>1802</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>1808</v>
-      </c>
-      <c r="F27" s="30" t="s">
-        <v>1809</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -75427,16 +75457,16 @@
         <v>206</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>1803</v>
+      </c>
+      <c r="F28" s="29" t="s">
         <v>1804</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>1803</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1805</v>
-      </c>
-      <c r="F28" s="29" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -75447,16 +75477,16 @@
         <v>216</v>
       </c>
       <c r="C29" s="25" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E29" s="25" t="s">
         <v>1763</v>
       </c>
-      <c r="D29" s="29" t="s">
-        <v>1764</v>
-      </c>
-      <c r="E29" s="25" t="s">
-        <v>1765</v>
-      </c>
       <c r="F29" s="29" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75467,16 +75497,16 @@
         <v>206</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="D30" s="25" t="s">
+        <v>1764</v>
+      </c>
+      <c r="E30" s="25" t="s">
         <v>1766</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="F30" s="29" t="s">
         <v>1768</v>
-      </c>
-      <c r="F30" s="29" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75487,16 +75517,16 @@
         <v>216</v>
       </c>
       <c r="C31" s="25" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E31" s="25" t="s">
         <v>1772</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="F31" s="29" t="s">
         <v>1771</v>
-      </c>
-      <c r="E31" s="25" t="s">
-        <v>1774</v>
-      </c>
-      <c r="F31" s="29" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -75507,16 +75537,16 @@
         <v>206</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="E32" s="25" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F32" s="29" t="s">
         <v>1776</v>
-      </c>
-      <c r="F32" s="29" t="s">
-        <v>1778</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="85" x14ac:dyDescent="0.2">
@@ -75527,16 +75557,16 @@
         <v>216</v>
       </c>
       <c r="C33" s="25" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D33" s="29" t="s">
         <v>1779</v>
       </c>
-      <c r="D33" s="29" t="s">
-        <v>1781</v>
-      </c>
       <c r="E33" s="25" t="s">
+        <v>1778</v>
+      </c>
+      <c r="F33" s="29" t="s">
         <v>1780</v>
-      </c>
-      <c r="F33" s="29" t="s">
-        <v>1782</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="102" x14ac:dyDescent="0.2">
@@ -75547,16 +75577,16 @@
         <v>206</v>
       </c>
       <c r="C34" s="25" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>1781</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F34" s="29" t="s">
         <v>1784</v>
-      </c>
-      <c r="D34" s="29" t="s">
-        <v>1783</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>1785</v>
-      </c>
-      <c r="F34" s="29" t="s">
-        <v>1786</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="85" x14ac:dyDescent="0.2">
@@ -75567,16 +75597,16 @@
         <v>216</v>
       </c>
       <c r="C35" s="25" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F35" s="29" t="s">
         <v>1788</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>1787</v>
-      </c>
-      <c r="E35" s="25" t="s">
-        <v>1789</v>
-      </c>
-      <c r="F35" s="29" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -75587,16 +75617,16 @@
         <v>206</v>
       </c>
       <c r="C36" s="25" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>1789</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>1791</v>
+      </c>
+      <c r="F36" s="29" t="s">
         <v>1792</v>
-      </c>
-      <c r="D36" s="29" t="s">
-        <v>1791</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>1793</v>
-      </c>
-      <c r="F36" s="29" t="s">
-        <v>1794</v>
       </c>
     </row>
   </sheetData>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F16EEBD-888E-A14E-BB09-4A6459818B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28C6BCF-F4BB-944C-9E05-2A8D9E64FBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" firstSheet="8" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="2550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4034" uniqueCount="2553">
   <si>
     <t>date</t>
   </si>
@@ -13402,6 +13402,18 @@
   </si>
   <si>
     <t>Vote for BTS Swim at MTV Best Kpop</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=DghRuL_ADgU</t>
+  </si>
+  <si>
+    <t>Another week filled with incredible moments! 🥹💚💜
+We enjoyed two unforgettable BTS concerts in Texas, followed by even more memories from their time there! Jungkook treated us to another amazing vlog with Taehyung and Hobi, while Tae shared more special Texas moments of his own. ✨
+Add in new brand content, music milestones, achievements and more, and there was plenty to celebrate!
+Catch up on anything you may have missed in this week’s TaeKook Weekly Recap! 💚💜</t>
+  </si>
+  <si>
+    <t>Week of August 21, 2026</t>
   </si>
 </sst>
 </file>
@@ -72560,7 +72572,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="34" bestFit="1" customWidth="1"/>
@@ -72588,921 +72600,936 @@
       </c>
       <c r="G1" s="33"/>
     </row>
-    <row r="2" spans="1:7" ht="136" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A2" s="35">
+        <v>46255</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>2550</v>
+      </c>
+      <c r="G2" s="33"/>
+    </row>
+    <row r="3" spans="1:7" ht="136" x14ac:dyDescent="0.2">
+      <c r="A3" s="35">
         <v>46248</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B3" s="34" t="s">
         <v>2537</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C3" s="36" t="s">
         <v>2538</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D3" s="23" t="s">
         <v>2539</v>
       </c>
-      <c r="G2" s="33"/>
-    </row>
-    <row r="3" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A3" s="35">
+      <c r="G3" s="33"/>
+    </row>
+    <row r="4" spans="1:7" ht="102" x14ac:dyDescent="0.2">
+      <c r="A4" s="35">
         <v>46241</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B4" s="34" t="s">
         <v>2490</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C4" s="36" t="s">
         <v>2489</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D4" s="23" t="s">
         <v>2488</v>
       </c>
-      <c r="G3" s="33"/>
-    </row>
-    <row r="4" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="35">
+      <c r="G4" s="33"/>
+    </row>
+    <row r="5" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="35">
         <v>46234</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B5" s="34" t="s">
         <v>2528</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C5" s="36" t="s">
         <v>2456</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D5" s="23" t="s">
         <v>2455</v>
-      </c>
-      <c r="G4" s="33"/>
-    </row>
-    <row r="5" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="35">
-        <v>46227</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>2002</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>2003</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>2001</v>
       </c>
       <c r="G5" s="33"/>
     </row>
     <row r="6" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="35">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>1921</v>
+        <v>2002</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1920</v>
+        <v>2003</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>1922</v>
+        <v>2001</v>
       </c>
       <c r="G6" s="33"/>
     </row>
     <row r="7" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="35">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>1915</v>
+        <v>1921</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1916</v>
+        <v>1920</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>1914</v>
+        <v>1922</v>
       </c>
       <c r="G7" s="33"/>
     </row>
     <row r="8" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="35">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>1865</v>
+        <v>1915</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1867</v>
+        <v>1916</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>1866</v>
+        <v>1914</v>
       </c>
       <c r="G8" s="33"/>
     </row>
     <row r="9" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="35">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>1746</v>
+        <v>1865</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1745</v>
+        <v>1867</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>1747</v>
+        <v>1866</v>
       </c>
       <c r="G9" s="33"/>
     </row>
     <row r="10" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="35">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>4</v>
+        <v>1746</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>5</v>
+        <v>1745</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>6</v>
+        <v>1747</v>
       </c>
       <c r="G10" s="33"/>
     </row>
     <row r="11" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="35">
-        <v>46185</v>
+        <v>46192</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G11" s="33"/>
     </row>
     <row r="12" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="35">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G12" s="33"/>
     </row>
     <row r="13" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="35">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G13" s="33"/>
     </row>
     <row r="14" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="35">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G14" s="33"/>
     </row>
     <row r="15" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="35">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G15" s="33"/>
     </row>
     <row r="16" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="35">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G16" s="33"/>
     </row>
     <row r="17" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="35">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G17" s="33"/>
     </row>
     <row r="18" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="35">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G18" s="33"/>
     </row>
     <row r="19" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="35">
-        <v>46129</v>
+        <v>46136</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G19" s="33"/>
     </row>
     <row r="20" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="35">
-        <v>46115</v>
+        <v>46129</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G20" s="33"/>
     </row>
     <row r="21" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="35">
-        <v>46094</v>
+        <v>46115</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G21" s="33"/>
     </row>
     <row r="22" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="35">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G22" s="33"/>
     </row>
     <row r="23" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="35">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G23" s="33"/>
     </row>
     <row r="24" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="35">
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G24" s="33"/>
     </row>
     <row r="25" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="35">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G25" s="33"/>
     </row>
     <row r="26" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="35">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C26" s="36" t="s">
         <v>50</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G26" s="33"/>
     </row>
     <row r="27" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="35">
-        <v>46052</v>
+        <v>46059</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G27" s="33"/>
     </row>
     <row r="28" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="35">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G28" s="33"/>
     </row>
     <row r="29" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="35">
+        <v>46045</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29" s="33"/>
+    </row>
+    <row r="30" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="35">
         <v>46038</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C30" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D30" s="23" t="s">
         <v>61</v>
-      </c>
-      <c r="G29" s="33"/>
-    </row>
-    <row r="30" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="35">
-        <v>46031</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>64</v>
       </c>
       <c r="G30" s="33"/>
     </row>
     <row r="31" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="35">
+        <v>46031</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G31" s="33"/>
+    </row>
+    <row r="32" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="35">
         <v>46024</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B32" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C32" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D32" s="23" t="s">
         <v>67</v>
-      </c>
-      <c r="G31" s="33"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="35">
-        <v>46017</v>
-      </c>
-      <c r="B32" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>70</v>
       </c>
       <c r="G32" s="33"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="35">
+        <v>46017</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" s="33"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="35">
         <v>46010</v>
       </c>
-      <c r="B33" s="34" t="s">
+      <c r="B34" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C34" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D34" s="23" t="s">
         <v>73</v>
-      </c>
-      <c r="G33" s="33"/>
-    </row>
-    <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="35">
-        <v>46003</v>
-      </c>
-      <c r="B34" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>76</v>
       </c>
       <c r="G34" s="33"/>
     </row>
     <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="35">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="G35" s="23"/>
+        <v>76</v>
+      </c>
+      <c r="G35" s="33"/>
     </row>
     <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="35">
-        <v>45989</v>
+        <v>45996</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G36" s="23"/>
     </row>
     <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="35">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G37" s="23"/>
     </row>
     <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="35">
-        <v>45975</v>
+        <v>45982</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G38" s="23"/>
     </row>
     <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="35">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G39" s="23"/>
     </row>
     <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="35">
+        <v>45968</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G40" s="23"/>
+    </row>
+    <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="35">
         <v>45961</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B41" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="C40" s="36" t="s">
+      <c r="C41" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="D40" s="23" t="s">
+      <c r="D41" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="G40" s="23"/>
-    </row>
-    <row r="41" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="35">
+      <c r="G41" s="23"/>
+    </row>
+    <row r="42" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="35">
         <v>45954</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B42" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="36" t="s">
+      <c r="C42" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="D42" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="G41" s="23"/>
-    </row>
-    <row r="42" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="35">
+      <c r="G42" s="23"/>
+    </row>
+    <row r="43" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="35">
         <v>45947</v>
       </c>
-      <c r="B42" s="34" t="s">
+      <c r="B43" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="36" t="s">
+      <c r="C43" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D43" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="G42" s="23"/>
-    </row>
-    <row r="43" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="35">
+      <c r="G43" s="23"/>
+    </row>
+    <row r="44" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="35">
         <v>45940</v>
       </c>
-      <c r="B43" s="34" t="s">
+      <c r="B44" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C44" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D44" s="23" t="s">
         <v>101</v>
-      </c>
-      <c r="G43" s="23"/>
-    </row>
-    <row r="44" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="35">
-        <v>45933</v>
-      </c>
-      <c r="B44" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C44" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>104</v>
       </c>
       <c r="G44" s="23"/>
     </row>
     <row r="45" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="35">
+        <v>45933</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="G45" s="23"/>
+    </row>
+    <row r="46" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="35">
         <v>45926</v>
       </c>
-      <c r="B45" s="34" t="s">
+      <c r="B46" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="C45" s="36" t="s">
+      <c r="C46" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D45" s="23" t="s">
+      <c r="D46" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="G45" s="23"/>
-    </row>
-    <row r="46" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="35">
+      <c r="G46" s="23"/>
+    </row>
+    <row r="47" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="35">
         <v>45919</v>
       </c>
-      <c r="B46" s="34" t="s">
+      <c r="B47" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="C47" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D47" s="23" t="s">
         <v>110</v>
-      </c>
-      <c r="G46" s="23"/>
-    </row>
-    <row r="47" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="35">
-        <v>45912</v>
-      </c>
-      <c r="B47" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C47" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>113</v>
       </c>
       <c r="G47" s="23"/>
     </row>
     <row r="48" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="35">
+        <v>45912</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="G48" s="23"/>
+    </row>
+    <row r="49" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="35">
         <v>45905</v>
       </c>
-      <c r="B48" s="34" t="s">
+      <c r="B49" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="36" t="s">
+      <c r="C49" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="D48" s="23" t="s">
+      <c r="D49" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="G48" s="23"/>
-    </row>
-    <row r="49" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="35">
+      <c r="G49" s="23"/>
+    </row>
+    <row r="50" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="35">
         <v>45898</v>
       </c>
-      <c r="B49" s="34" t="s">
+      <c r="B50" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C50" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="D49" s="23" t="s">
+      <c r="D50" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="G49" s="23"/>
-    </row>
-    <row r="50" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="35">
+      <c r="G50" s="23"/>
+    </row>
+    <row r="51" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="35">
         <v>45891</v>
       </c>
-      <c r="B50" s="34" t="s">
+      <c r="B51" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="C50" s="36" t="s">
+      <c r="C51" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D51" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="G50" s="23"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="35">
+      <c r="G51" s="23"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="35">
         <v>45884</v>
       </c>
-      <c r="B51" s="34" t="s">
+      <c r="B52" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="C51" s="34" t="s">
+      <c r="C52" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="D51" s="23" t="s">
+      <c r="D52" s="23" t="s">
         <v>124</v>
-      </c>
-      <c r="G51" s="23"/>
-    </row>
-    <row r="52" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="35">
-        <v>45877</v>
-      </c>
-      <c r="B52" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="C52" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>127</v>
       </c>
       <c r="G52" s="23"/>
     </row>
     <row r="53" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="35">
+        <v>45877</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="G53" s="23"/>
+    </row>
+    <row r="54" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="35">
         <v>45870</v>
       </c>
-      <c r="B53" s="34" t="s">
+      <c r="B54" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="C53" s="36" t="s">
+      <c r="C54" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="D53" s="23" t="s">
+      <c r="D54" s="23" t="s">
         <v>130</v>
-      </c>
-      <c r="G53" s="23"/>
-    </row>
-    <row r="54" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35">
-        <v>45863</v>
-      </c>
-      <c r="B54" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="C54" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>133</v>
       </c>
       <c r="G54" s="23"/>
     </row>
     <row r="55" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="35">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="B55" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G55" s="23"/>
     </row>
     <row r="56" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="35">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C56" s="36" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G56" s="23"/>
     </row>
     <row r="57" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="35">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="B57" s="34" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G57" s="23"/>
     </row>
     <row r="58" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="35">
+        <v>45842</v>
+      </c>
+      <c r="B58" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="C58" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="G58" s="23"/>
+    </row>
+    <row r="59" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="35">
         <v>45835</v>
       </c>
-      <c r="B58" s="34" t="s">
+      <c r="B59" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="C58" s="36" t="s">
+      <c r="C59" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="D58" s="23" t="s">
+      <c r="D59" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="G58" s="23"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C59" s="36"/>
+      <c r="G59" s="23"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C60" s="36"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="D11" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="D12" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="D13" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
-    <hyperlink ref="D14" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
-    <hyperlink ref="D15" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
-    <hyperlink ref="D16" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
-    <hyperlink ref="D18" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
-    <hyperlink ref="D20" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
-    <hyperlink ref="D21" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
-    <hyperlink ref="D22" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
-    <hyperlink ref="D23" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
-    <hyperlink ref="D24" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
-    <hyperlink ref="D25" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
-    <hyperlink ref="D26" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
-    <hyperlink ref="D27" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
-    <hyperlink ref="D28" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
-    <hyperlink ref="D29" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
-    <hyperlink ref="D30" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
-    <hyperlink ref="D31" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
-    <hyperlink ref="D32" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
-    <hyperlink ref="D33" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
-    <hyperlink ref="D34" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
-    <hyperlink ref="D35" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
-    <hyperlink ref="D36" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
-    <hyperlink ref="D37" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
-    <hyperlink ref="D38" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
-    <hyperlink ref="D39" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
-    <hyperlink ref="D40" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
-    <hyperlink ref="D41" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
-    <hyperlink ref="D42" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
-    <hyperlink ref="D43" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
-    <hyperlink ref="D44" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
-    <hyperlink ref="D45" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
-    <hyperlink ref="D46" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
-    <hyperlink ref="D47" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
-    <hyperlink ref="D48" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
-    <hyperlink ref="D49" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
-    <hyperlink ref="D50" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
-    <hyperlink ref="D51" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
-    <hyperlink ref="D52" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
-    <hyperlink ref="D53" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
-    <hyperlink ref="D54" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
-    <hyperlink ref="D55" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
-    <hyperlink ref="D56" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
-    <hyperlink ref="D57" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
-    <hyperlink ref="D58" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
-    <hyperlink ref="D10" r:id="rId48" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
-    <hyperlink ref="D9" r:id="rId49" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
-    <hyperlink ref="D8" r:id="rId50" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
-    <hyperlink ref="D7" r:id="rId51" xr:uid="{8E240BDD-02FF-CA47-B5D9-FD7E9FCA5AEA}"/>
-    <hyperlink ref="D6" r:id="rId52" xr:uid="{77C8CFB5-83B9-D448-AFCE-DD617D9A359D}"/>
-    <hyperlink ref="D5" r:id="rId53" xr:uid="{7282EB94-FBFF-C64E-9C65-3E4E1C662EA7}"/>
-    <hyperlink ref="D4" r:id="rId54" xr:uid="{AC8ED73F-B845-2845-962C-58F7783B2A4D}"/>
-    <hyperlink ref="D3" r:id="rId55" xr:uid="{683CE86C-4345-8043-87A1-967BF156D1E1}"/>
+    <hyperlink ref="D12" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="D13" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="D14" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="D15" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="D16" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="D17" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="D19" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="D21" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
+    <hyperlink ref="D22" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
+    <hyperlink ref="D23" r:id="rId10" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
+    <hyperlink ref="D24" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
+    <hyperlink ref="D25" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
+    <hyperlink ref="D26" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
+    <hyperlink ref="D27" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
+    <hyperlink ref="D28" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
+    <hyperlink ref="D29" r:id="rId16" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
+    <hyperlink ref="D30" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
+    <hyperlink ref="D31" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
+    <hyperlink ref="D32" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
+    <hyperlink ref="D33" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
+    <hyperlink ref="D34" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
+    <hyperlink ref="D35" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
+    <hyperlink ref="D36" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
+    <hyperlink ref="D37" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
+    <hyperlink ref="D38" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
+    <hyperlink ref="D39" r:id="rId26" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
+    <hyperlink ref="D40" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
+    <hyperlink ref="D41" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
+    <hyperlink ref="D42" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
+    <hyperlink ref="D43" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
+    <hyperlink ref="D44" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
+    <hyperlink ref="D45" r:id="rId32" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
+    <hyperlink ref="D46" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
+    <hyperlink ref="D47" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
+    <hyperlink ref="D48" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
+    <hyperlink ref="D49" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
+    <hyperlink ref="D50" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
+    <hyperlink ref="D51" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
+    <hyperlink ref="D52" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
+    <hyperlink ref="D53" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
+    <hyperlink ref="D54" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
+    <hyperlink ref="D55" r:id="rId42" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
+    <hyperlink ref="D56" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
+    <hyperlink ref="D57" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
+    <hyperlink ref="D58" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
+    <hyperlink ref="D59" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
+    <hyperlink ref="D11" r:id="rId47" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
+    <hyperlink ref="D10" r:id="rId48" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
+    <hyperlink ref="D9" r:id="rId49" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
+    <hyperlink ref="D8" r:id="rId50" xr:uid="{8E240BDD-02FF-CA47-B5D9-FD7E9FCA5AEA}"/>
+    <hyperlink ref="D7" r:id="rId51" xr:uid="{77C8CFB5-83B9-D448-AFCE-DD617D9A359D}"/>
+    <hyperlink ref="D6" r:id="rId52" xr:uid="{7282EB94-FBFF-C64E-9C65-3E4E1C662EA7}"/>
+    <hyperlink ref="D5" r:id="rId53" xr:uid="{AC8ED73F-B845-2845-962C-58F7783B2A4D}"/>
+    <hyperlink ref="D4" r:id="rId54" xr:uid="{683CE86C-4345-8043-87A1-967BF156D1E1}"/>
+    <hyperlink ref="D2" r:id="rId55" xr:uid="{4A609F52-301A-7E4F-9D40-745FB09003DC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28C6BCF-F4BB-944C-9E05-2A8D9E64FBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337E53AB-A943-E34A-A270-89CDEC2CA926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4034" uniqueCount="2553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4059" uniqueCount="2573">
   <si>
     <t>date</t>
   </si>
@@ -13414,6 +13414,67 @@
   </si>
   <si>
     <t>Week of August 21, 2026</t>
+  </si>
+  <si>
+    <t>Taehyung and Jungkook feature in No Manners Magazine’s look at how Asian talent is driving Media Impact Value for fashion &amp; beauty brands in 2026.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DcLsWqbtvX8/</t>
+  </si>
+  <si>
+    <t>🐯 Taehyung’s appointment as Champion’s Global Ambassador generated $6.3M in MIV in just 48 hours, with Champion’s overall brand performance increasing 37-fold on announcement day. The article also highlights his influence through CELINE, Cartier, TIRTIR and Snow Peak Apparel.
+🐰 Jungkook’s CHANEL 1957 L’Extrait campaign generated $11.7M MIV, while his Hublot ambassadorship generated $32.3M MIV in one week. His Calvin Klein collaboration also generated $3.4M MIV in 48 hours.</t>
+  </si>
+  <si>
+    <t>https://nomannersmagazine.com/how-asian-talent-is-driving-fashion-and-beauty-brands-media-impact-value-2026-jungkook-v-win-metawin/</t>
+  </si>
+  <si>
+    <t>Japan’s Toyo Keizai highlights the powerful “V Effect” on global brands</t>
+  </si>
+  <si>
+    <t>Japan’s Toyo Keizai has spotlighted BTS V’s growing economic influence, describing him as a global star and brand in his own right whose campaigns can drive consumer behaviour, product sell-outs, social media growth and increased brand sales. The publication also highlighted the impact of V’s ambassador roles with brands including YUNTH and Champion.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DcTENyBtfLf/</t>
+  </si>
+  <si>
+    <t>https://naver.me/xVRIcOYo</t>
+  </si>
+  <si>
+    <t>Jungkook’s ‘GOLDEN’ extends its record as the longest-charting Asian solo album on Spotify</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DcYRSoHNCOQ/</t>
+  </si>
+  <si>
+    <t>BTS Jungkook’s first solo album ‘GOLDEN’ has extended its record on Spotify’s Weekly Top Albums Global chart to 146 consecutive weeks, the longest ever for an Asian solo artist album, while surpassing 7.39 billion cumulative streams.</t>
+  </si>
+  <si>
+    <t>https://naver.me/xfbVEg80</t>
+  </si>
+  <si>
+    <t>V shares a glimpse of his relaxed Toronto days with the members</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Dca4Sf0tuvs/</t>
+  </si>
+  <si>
+    <t>BTS V shared a short, natural video from Toronto showing him spending time with the members in a relaxed outdoor setting, giving fans a glimpse of their everyday moments during the ARIRANG world tour.</t>
+  </si>
+  <si>
+    <t>https://naver.me/GJZPYvn4</t>
+  </si>
+  <si>
+    <t>Jungkook’s “messing around” editing video surpasses 31.4 million views</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Dca4-ZJtmZ6/</t>
+  </si>
+  <si>
+    <t>BTS Jungkook’s editing-practice video, which he jokingly captioned “messing around,” has surpassed 31.4 million views on Instagram, with fans praising his creative editing and production skills and his long-standing reputation as “Director Kook.”</t>
+  </si>
+  <si>
+    <t>https://naver.me/xG09xi2b</t>
   </si>
 </sst>
 </file>
@@ -74924,7 +74985,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="25" bestFit="1" customWidth="1"/>
@@ -74932,7 +74993,7 @@
     <col min="3" max="3" width="57.6640625" style="25" customWidth="1"/>
     <col min="4" max="4" width="40.6640625" style="25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="88.33203125" style="25" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" style="25" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="25" customWidth="1"/>
     <col min="7" max="16384" width="8.83203125" style="25"/>
   </cols>
   <sheetData>
@@ -74958,772 +75019,882 @@
     </row>
     <row r="2" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="31">
-        <v>46249</v>
+        <v>46258</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>2533</v>
+        <v>2569</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2535</v>
+        <v>2570</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>2534</v>
+        <v>2571</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>2536</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="31">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>216</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>2516</v>
+        <v>2565</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>2515</v>
+        <v>2566</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>2517</v>
+        <v>2567</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>2518</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="31">
-        <v>46244</v>
+        <v>46257</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>206</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>2511</v>
+        <v>2561</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>2512</v>
+        <v>2562</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>2513</v>
+        <v>2563</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>2514</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A5" s="31">
-        <v>46238</v>
+        <v>46255</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>216</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>2508</v>
+        <v>2557</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>2507</v>
+        <v>2559</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>2509</v>
+        <v>2558</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A6" s="31">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>2503</v>
+        <v>2553</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2504</v>
+        <v>2554</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>2505</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>2506</v>
+        <v>2555</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>2556</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="31">
-        <v>46232</v>
+        <v>46249</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>216</v>
+        <v>167</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>2500</v>
+        <v>2533</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2499</v>
+        <v>2535</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>2501</v>
+        <v>2534</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>2502</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="31">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>2495</v>
+        <v>2516</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2498</v>
+        <v>2515</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>2496</v>
+        <v>2517</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>2497</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
-        <v>46226</v>
+        <v>46244</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>206</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>2491</v>
+        <v>2511</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2492</v>
+        <v>2512</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>2493</v>
+        <v>2513</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>2494</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
-        <v>46222</v>
+        <v>46238</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>216</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>1967</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>1966</v>
+        <v>2508</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>2507</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>1968</v>
+        <v>2509</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>1969</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="31">
-        <v>46222</v>
+        <v>46238</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>206</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>1965</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>1963</v>
+        <v>2503</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>2504</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>1964</v>
+        <v>2505</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1970</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="31">
-        <v>46219</v>
+        <v>46232</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>216</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>1961</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>1960</v>
+        <v>2500</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>2499</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>1962</v>
+        <v>2501</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>1971</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="31">
-        <v>46219</v>
+        <v>46232</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>206</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>1957</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>1959</v>
+        <v>2495</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>2498</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>1958</v>
+        <v>2496</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="289" x14ac:dyDescent="0.2">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>1954</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>1955</v>
+        <v>2491</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>2492</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>1956</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="238" x14ac:dyDescent="0.2">
+        <v>2493</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
-        <v>46218</v>
+        <v>46222</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>1951</v>
+        <v>1967</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>1950</v>
+        <v>1966</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>1953</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="204" x14ac:dyDescent="0.2">
+        <v>1968</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="31">
-        <v>46218</v>
+        <v>46222</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>1952</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>1948</v>
+        <v>1965</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>1963</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>1949</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>1964</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" s="31">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>1946</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>1945</v>
+        <v>1961</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>1960</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>1947</v>
+        <v>1962</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="31">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>1943</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>1942</v>
+        <v>1957</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>1959</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>1944</v>
+        <v>1958</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="289" x14ac:dyDescent="0.2">
       <c r="A19" s="31">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>216</v>
+        <v>167</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>1939</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>1938</v>
+        <v>1954</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>1955</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>1940</v>
-      </c>
-      <c r="F19" s="29" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>1956</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="238" x14ac:dyDescent="0.2">
       <c r="A20" s="31">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>1936</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>1935</v>
+        <v>1951</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>1950</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="238" x14ac:dyDescent="0.2">
+        <v>1953</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="204" x14ac:dyDescent="0.2">
       <c r="A21" s="31">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>167</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>1933</v>
+        <v>1952</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>1932</v>
+        <v>1948</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>1934</v>
+        <v>1949</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A22" s="31">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B22" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>1947</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A23" s="31">
+        <v>46217</v>
+      </c>
+      <c r="B23" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="C22" s="22" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>1929</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>1931</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A23" s="31">
-        <v>46213</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>206</v>
-      </c>
       <c r="C23" s="22" t="s">
-        <v>1927</v>
+        <v>1943</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>1926</v>
+        <v>1942</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>1928</v>
+        <v>1944</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>1979</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="31">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B24" s="22" t="s">
         <v>216</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>1923</v>
+        <v>1939</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>1924</v>
+        <v>1938</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>1925</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+        <v>1940</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A25" s="31">
-        <v>46208</v>
+        <v>46216</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>1812</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>1815</v>
+        <v>1936</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>1935</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>1813</v>
+        <v>1937</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="238" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>1808</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>1811</v>
+        <v>1933</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>1932</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>1809</v>
-      </c>
-      <c r="F26" s="29" t="s">
-        <v>1810</v>
+        <v>1934</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>1977</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>216</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>1805</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>1800</v>
+        <v>1930</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>1929</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F27" s="30" t="s">
-        <v>1807</v>
+        <v>1931</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>1978</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>206</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A29" s="31">
+        <v>46210</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>1925</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A30" s="31">
+        <v>46208</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A31" s="31">
+        <v>46208</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A32" s="31">
+        <v>46205</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F32" s="30" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A33" s="31">
+        <v>46206</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="C33" s="22" t="s">
         <v>1802</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D33" s="29" t="s">
         <v>1801</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E33" s="22" t="s">
         <v>1803</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F33" s="29" t="s">
         <v>1804</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A29" s="32">
+    <row r="34" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A34" s="32">
         <v>46203</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B34" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C34" s="25" t="s">
         <v>1761</v>
       </c>
-      <c r="D29" s="29" t="s">
+      <c r="D34" s="29" t="s">
         <v>1762</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="E34" s="25" t="s">
         <v>1763</v>
       </c>
-      <c r="F29" s="29" t="s">
+      <c r="F34" s="29" t="s">
         <v>1767</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A30" s="32">
+    <row r="35" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A35" s="32">
         <v>46203</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C35" s="25" t="s">
         <v>1765</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D35" s="25" t="s">
         <v>1764</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="E35" s="25" t="s">
         <v>1766</v>
       </c>
-      <c r="F30" s="29" t="s">
+      <c r="F35" s="29" t="s">
         <v>1768</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A31" s="32">
+    <row r="36" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A36" s="32">
         <v>46202</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B36" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C36" s="25" t="s">
         <v>1770</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="D36" s="29" t="s">
         <v>1769</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="E36" s="25" t="s">
         <v>1772</v>
       </c>
-      <c r="F31" s="29" t="s">
+      <c r="F36" s="29" t="s">
         <v>1771</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A32" s="32">
+    <row r="37" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A37" s="32">
         <v>46202</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C37" s="25" t="s">
         <v>1775</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="D37" s="25" t="s">
         <v>1773</v>
       </c>
-      <c r="E32" s="25" t="s">
+      <c r="E37" s="25" t="s">
         <v>1774</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F37" s="29" t="s">
         <v>1776</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A33" s="32">
+    <row r="38" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A38" s="32">
         <v>46201</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B38" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C38" s="25" t="s">
         <v>1777</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D38" s="29" t="s">
         <v>1779</v>
       </c>
-      <c r="E33" s="25" t="s">
+      <c r="E38" s="25" t="s">
         <v>1778</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F38" s="29" t="s">
         <v>1780</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A34" s="32">
+    <row r="39" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A39" s="32">
         <v>46201</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C39" s="25" t="s">
         <v>1782</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D39" s="29" t="s">
         <v>1781</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="E39" s="25" t="s">
         <v>1783</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F39" s="29" t="s">
         <v>1784</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A35" s="32">
+    <row r="40" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A40" s="32">
         <v>46198</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B40" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C40" s="25" t="s">
         <v>1786</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D40" s="25" t="s">
         <v>1785</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="E40" s="25" t="s">
         <v>1787</v>
       </c>
-      <c r="F35" s="29" t="s">
+      <c r="F40" s="29" t="s">
         <v>1788</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A36" s="32">
+    <row r="41" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A41" s="32">
         <v>46198</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C41" s="25" t="s">
         <v>1790</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D41" s="29" t="s">
         <v>1789</v>
       </c>
-      <c r="E36" s="25" t="s">
+      <c r="E41" s="25" t="s">
         <v>1791</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F41" s="29" t="s">
         <v>1792</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F29" r:id="rId1" xr:uid="{4C165E91-B26F-0A45-88A2-06AA9774DFAE}"/>
-    <hyperlink ref="F30" r:id="rId2" xr:uid="{7642FB96-3502-1243-90D5-20631BBFCC79}"/>
-    <hyperlink ref="D29" r:id="rId3" xr:uid="{1E0F0315-6747-884F-AA49-D6E56727920B}"/>
-    <hyperlink ref="D31" r:id="rId4" xr:uid="{8488153C-110A-4C48-965B-7630C9492F36}"/>
-    <hyperlink ref="F31" r:id="rId5" xr:uid="{BE75DA92-F980-1948-9204-01AC25600C6B}"/>
-    <hyperlink ref="F32" r:id="rId6" xr:uid="{7457B18B-86CB-6147-ADA9-A3CE56A83401}"/>
-    <hyperlink ref="D33" r:id="rId7" xr:uid="{FBAC6F67-55B1-324A-82BF-DD02FC6BBA04}"/>
-    <hyperlink ref="F33" r:id="rId8" xr:uid="{865A0475-BB84-DB47-9559-DC4649F4A676}"/>
-    <hyperlink ref="D34" r:id="rId9" xr:uid="{D9D6577F-5D20-B245-9F68-2D50BDFCA180}"/>
-    <hyperlink ref="F34" r:id="rId10" xr:uid="{21950F61-40D9-5E42-87ED-8402F010D442}"/>
-    <hyperlink ref="F35" r:id="rId11" xr:uid="{990DFC39-986D-3849-99EC-29E4E365D40A}"/>
-    <hyperlink ref="D36" r:id="rId12" xr:uid="{DE7E8DCA-2195-394F-9E1F-C6282B5AFE11}"/>
-    <hyperlink ref="F36" r:id="rId13" xr:uid="{A97FBDD3-5139-A04F-A3D7-E34D3553362F}"/>
-    <hyperlink ref="D27" r:id="rId14" xr:uid="{B5715535-CBF7-2F43-A872-9DF1119833A5}"/>
-    <hyperlink ref="D28" r:id="rId15" xr:uid="{4BD8C645-AD86-B644-BB86-E474C950B5C1}"/>
-    <hyperlink ref="F28" r:id="rId16" xr:uid="{E6DC40BA-2FBD-8741-8B86-BE0CB8B5DF5A}"/>
-    <hyperlink ref="F27" r:id="rId17" xr:uid="{2D25DB01-973D-C442-BAAA-A7898AECF3CB}"/>
-    <hyperlink ref="D26" r:id="rId18" xr:uid="{5EE266C8-30C3-AA49-A280-DD6ACA716BED}"/>
-    <hyperlink ref="F26" r:id="rId19" xr:uid="{1523EF8F-C7CF-B247-84A6-D1068FDF2FC9}"/>
-    <hyperlink ref="F25" r:id="rId20" xr:uid="{5344D85B-DBA1-7F4D-A437-9ADA0A6F25E7}"/>
-    <hyperlink ref="D25" r:id="rId21" xr:uid="{82E8603F-6B68-A849-9DB1-A6D7D62BC5C3}"/>
-    <hyperlink ref="D24" r:id="rId22" xr:uid="{C4B7F07F-C7EF-A445-BA36-79AFD111A13A}"/>
-    <hyperlink ref="D23" r:id="rId23" xr:uid="{28DE8988-3557-EF48-BB75-91D97971DC4D}"/>
-    <hyperlink ref="D22" r:id="rId24" xr:uid="{0B7C9678-BFED-1B4C-9FF2-DCCCE6ED62A7}"/>
-    <hyperlink ref="D21" r:id="rId25" xr:uid="{F69DCD8B-5576-A945-A1C0-850B8C57018F}"/>
-    <hyperlink ref="D20" r:id="rId26" xr:uid="{5CC655C1-5F71-CA47-90F1-336EB32A4376}"/>
-    <hyperlink ref="D19" r:id="rId27" xr:uid="{435469A8-0A82-1B46-ADC7-2BD93F4F0AD8}"/>
-    <hyperlink ref="D18" r:id="rId28" xr:uid="{C3AD3B54-C7D7-D14E-9805-9AEFCD3B56FC}"/>
-    <hyperlink ref="D17" r:id="rId29" xr:uid="{0FC6BD88-2D04-304E-AA6D-D0FC8F78BCA3}"/>
-    <hyperlink ref="D16" r:id="rId30" xr:uid="{9D70D003-ECDB-EC41-8AC7-5169C0795E15}"/>
-    <hyperlink ref="D15" r:id="rId31" xr:uid="{95972599-A68F-6141-8993-0C512EA7EB77}"/>
-    <hyperlink ref="D14" r:id="rId32" xr:uid="{325C9583-A49B-764F-9858-1A1870FCBF90}"/>
-    <hyperlink ref="D13" r:id="rId33" xr:uid="{841ECEF8-4ED6-B84D-8372-B8844DAD23B5}"/>
-    <hyperlink ref="D12" r:id="rId34" xr:uid="{3F93FFDC-C232-DD42-9509-5E6EC6ECC7D3}"/>
-    <hyperlink ref="D11" r:id="rId35" xr:uid="{1C3439D8-0793-DA4B-991C-E5E37FAAC840}"/>
+    <hyperlink ref="F34" r:id="rId1" xr:uid="{4C165E91-B26F-0A45-88A2-06AA9774DFAE}"/>
+    <hyperlink ref="F35" r:id="rId2" xr:uid="{7642FB96-3502-1243-90D5-20631BBFCC79}"/>
+    <hyperlink ref="D34" r:id="rId3" xr:uid="{1E0F0315-6747-884F-AA49-D6E56727920B}"/>
+    <hyperlink ref="D36" r:id="rId4" xr:uid="{8488153C-110A-4C48-965B-7630C9492F36}"/>
+    <hyperlink ref="F36" r:id="rId5" xr:uid="{BE75DA92-F980-1948-9204-01AC25600C6B}"/>
+    <hyperlink ref="F37" r:id="rId6" xr:uid="{7457B18B-86CB-6147-ADA9-A3CE56A83401}"/>
+    <hyperlink ref="D38" r:id="rId7" xr:uid="{FBAC6F67-55B1-324A-82BF-DD02FC6BBA04}"/>
+    <hyperlink ref="F38" r:id="rId8" xr:uid="{865A0475-BB84-DB47-9559-DC4649F4A676}"/>
+    <hyperlink ref="D39" r:id="rId9" xr:uid="{D9D6577F-5D20-B245-9F68-2D50BDFCA180}"/>
+    <hyperlink ref="F39" r:id="rId10" xr:uid="{21950F61-40D9-5E42-87ED-8402F010D442}"/>
+    <hyperlink ref="F40" r:id="rId11" xr:uid="{990DFC39-986D-3849-99EC-29E4E365D40A}"/>
+    <hyperlink ref="D41" r:id="rId12" xr:uid="{DE7E8DCA-2195-394F-9E1F-C6282B5AFE11}"/>
+    <hyperlink ref="F41" r:id="rId13" xr:uid="{A97FBDD3-5139-A04F-A3D7-E34D3553362F}"/>
+    <hyperlink ref="D32" r:id="rId14" xr:uid="{B5715535-CBF7-2F43-A872-9DF1119833A5}"/>
+    <hyperlink ref="D33" r:id="rId15" xr:uid="{4BD8C645-AD86-B644-BB86-E474C950B5C1}"/>
+    <hyperlink ref="F33" r:id="rId16" xr:uid="{E6DC40BA-2FBD-8741-8B86-BE0CB8B5DF5A}"/>
+    <hyperlink ref="F32" r:id="rId17" xr:uid="{2D25DB01-973D-C442-BAAA-A7898AECF3CB}"/>
+    <hyperlink ref="D31" r:id="rId18" xr:uid="{5EE266C8-30C3-AA49-A280-DD6ACA716BED}"/>
+    <hyperlink ref="F31" r:id="rId19" xr:uid="{1523EF8F-C7CF-B247-84A6-D1068FDF2FC9}"/>
+    <hyperlink ref="F30" r:id="rId20" xr:uid="{5344D85B-DBA1-7F4D-A437-9ADA0A6F25E7}"/>
+    <hyperlink ref="D30" r:id="rId21" xr:uid="{82E8603F-6B68-A849-9DB1-A6D7D62BC5C3}"/>
+    <hyperlink ref="D29" r:id="rId22" xr:uid="{C4B7F07F-C7EF-A445-BA36-79AFD111A13A}"/>
+    <hyperlink ref="D28" r:id="rId23" xr:uid="{28DE8988-3557-EF48-BB75-91D97971DC4D}"/>
+    <hyperlink ref="D27" r:id="rId24" xr:uid="{0B7C9678-BFED-1B4C-9FF2-DCCCE6ED62A7}"/>
+    <hyperlink ref="D26" r:id="rId25" xr:uid="{F69DCD8B-5576-A945-A1C0-850B8C57018F}"/>
+    <hyperlink ref="D25" r:id="rId26" xr:uid="{5CC655C1-5F71-CA47-90F1-336EB32A4376}"/>
+    <hyperlink ref="D24" r:id="rId27" xr:uid="{435469A8-0A82-1B46-ADC7-2BD93F4F0AD8}"/>
+    <hyperlink ref="D23" r:id="rId28" xr:uid="{C3AD3B54-C7D7-D14E-9805-9AEFCD3B56FC}"/>
+    <hyperlink ref="D22" r:id="rId29" xr:uid="{0FC6BD88-2D04-304E-AA6D-D0FC8F78BCA3}"/>
+    <hyperlink ref="D21" r:id="rId30" xr:uid="{9D70D003-ECDB-EC41-8AC7-5169C0795E15}"/>
+    <hyperlink ref="D20" r:id="rId31" xr:uid="{95972599-A68F-6141-8993-0C512EA7EB77}"/>
+    <hyperlink ref="D19" r:id="rId32" xr:uid="{325C9583-A49B-764F-9858-1A1870FCBF90}"/>
+    <hyperlink ref="D18" r:id="rId33" xr:uid="{841ECEF8-4ED6-B84D-8372-B8844DAD23B5}"/>
+    <hyperlink ref="D17" r:id="rId34" xr:uid="{3F93FFDC-C232-DD42-9509-5E6EC6ECC7D3}"/>
+    <hyperlink ref="D16" r:id="rId35" xr:uid="{1C3439D8-0793-DA4B-991C-E5E37FAAC840}"/>
     <hyperlink ref="D2" r:id="rId36" xr:uid="{51A6409E-8F94-AF44-B60C-08D0EDDC3758}"/>
     <hyperlink ref="F2" r:id="rId37" xr:uid="{7F3D42E2-43F6-3548-BB2F-32CAD36E6170}"/>
-    <hyperlink ref="F11" r:id="rId38" xr:uid="{BDC3FD63-F436-E94D-A22F-05D357586E92}"/>
-    <hyperlink ref="F12" r:id="rId39" xr:uid="{0D035AE3-AAB0-254A-8010-E546387524A5}"/>
-    <hyperlink ref="F13" r:id="rId40" xr:uid="{2BCDC745-7256-214E-85A3-5FD239BA2A2F}"/>
-    <hyperlink ref="F14" r:id="rId41" xr:uid="{646B607C-75D4-0A47-8DED-0FDED514E2D3}"/>
-    <hyperlink ref="F15" r:id="rId42" xr:uid="{B9D307B7-2704-6E46-A670-B2DF92C7BC6F}"/>
-    <hyperlink ref="F16" r:id="rId43" xr:uid="{AE106E88-F04C-8744-B97B-68010273A3BF}"/>
-    <hyperlink ref="F17" r:id="rId44" xr:uid="{E5B27231-C944-BC4D-8025-6C163578708B}"/>
-    <hyperlink ref="F18" r:id="rId45" xr:uid="{4394F2F6-3518-9346-9D09-3496D3A48ABE}"/>
-    <hyperlink ref="F20" r:id="rId46" xr:uid="{C243C78A-1717-6C4E-9BE0-5AB19A56F3AB}"/>
-    <hyperlink ref="F21" r:id="rId47" xr:uid="{95FB7936-E26F-434D-AF06-44A9337A976E}"/>
-    <hyperlink ref="F22" r:id="rId48" xr:uid="{DFDB01C1-AE39-EB47-8DEA-A691B1A13FFF}"/>
-    <hyperlink ref="F23" r:id="rId49" xr:uid="{D57E7D52-6454-0149-87FF-11C129D8632B}"/>
-    <hyperlink ref="F24" r:id="rId50" xr:uid="{CD3A77F8-468B-EB42-BC45-17DABC164DD2}"/>
-    <hyperlink ref="D10" r:id="rId51" xr:uid="{473EB3CE-A564-1E45-AC13-AF793AC0B477}"/>
-    <hyperlink ref="F10" r:id="rId52" xr:uid="{9674E89D-A51D-CD48-BAD4-0268F5EF0218}"/>
-    <hyperlink ref="D9" r:id="rId53" xr:uid="{2C21E21B-D467-6B40-B99F-10CFF204DF5E}"/>
-    <hyperlink ref="F9" r:id="rId54" xr:uid="{653FC37B-0E60-F24C-9F82-E361CB6F1BEA}"/>
-    <hyperlink ref="D8" r:id="rId55" xr:uid="{D092DE5A-6AF2-2244-9717-800A8A08CED7}"/>
-    <hyperlink ref="F8" r:id="rId56" xr:uid="{54C0ACDA-4A86-524D-8E90-A1EA869C6122}"/>
-    <hyperlink ref="D7" r:id="rId57" xr:uid="{97F64753-0AA1-EE4A-B974-83528256F4F4}"/>
-    <hyperlink ref="F7" r:id="rId58" xr:uid="{A5448C25-A12C-794E-A542-556C39C496AC}"/>
-    <hyperlink ref="D6" r:id="rId59" xr:uid="{77CE2757-4893-874D-99A1-72D0C139E6FF}"/>
-    <hyperlink ref="F6" r:id="rId60" xr:uid="{7453F409-FB26-364F-96CF-B8B3C16C5539}"/>
-    <hyperlink ref="D5" r:id="rId61" xr:uid="{48A4ED37-D659-7A47-AC11-024E77FD1932}"/>
-    <hyperlink ref="F5" r:id="rId62" xr:uid="{227686EA-22C5-4D4C-A4A3-E4AEAB8249BD}"/>
-    <hyperlink ref="D4" r:id="rId63" xr:uid="{4819B73E-4D12-7442-A4E4-9BCA2F43B41E}"/>
-    <hyperlink ref="F4" r:id="rId64" xr:uid="{FEB6F6C5-6B93-0541-8DFC-234A63742636}"/>
-    <hyperlink ref="D3" r:id="rId65" xr:uid="{908F3A4C-B3BF-5143-8411-82FA701D3B47}"/>
-    <hyperlink ref="F3" r:id="rId66" xr:uid="{BE91235B-8F82-0046-9FD0-B9E1CC774D1C}"/>
+    <hyperlink ref="F16" r:id="rId38" xr:uid="{BDC3FD63-F436-E94D-A22F-05D357586E92}"/>
+    <hyperlink ref="F17" r:id="rId39" xr:uid="{0D035AE3-AAB0-254A-8010-E546387524A5}"/>
+    <hyperlink ref="F18" r:id="rId40" xr:uid="{2BCDC745-7256-214E-85A3-5FD239BA2A2F}"/>
+    <hyperlink ref="F19" r:id="rId41" xr:uid="{646B607C-75D4-0A47-8DED-0FDED514E2D3}"/>
+    <hyperlink ref="F20" r:id="rId42" xr:uid="{B9D307B7-2704-6E46-A670-B2DF92C7BC6F}"/>
+    <hyperlink ref="F21" r:id="rId43" xr:uid="{AE106E88-F04C-8744-B97B-68010273A3BF}"/>
+    <hyperlink ref="F22" r:id="rId44" xr:uid="{E5B27231-C944-BC4D-8025-6C163578708B}"/>
+    <hyperlink ref="F23" r:id="rId45" xr:uid="{4394F2F6-3518-9346-9D09-3496D3A48ABE}"/>
+    <hyperlink ref="F25" r:id="rId46" xr:uid="{C243C78A-1717-6C4E-9BE0-5AB19A56F3AB}"/>
+    <hyperlink ref="F26" r:id="rId47" xr:uid="{95FB7936-E26F-434D-AF06-44A9337A976E}"/>
+    <hyperlink ref="F27" r:id="rId48" xr:uid="{DFDB01C1-AE39-EB47-8DEA-A691B1A13FFF}"/>
+    <hyperlink ref="F28" r:id="rId49" xr:uid="{D57E7D52-6454-0149-87FF-11C129D8632B}"/>
+    <hyperlink ref="F29" r:id="rId50" xr:uid="{CD3A77F8-468B-EB42-BC45-17DABC164DD2}"/>
+    <hyperlink ref="D15" r:id="rId51" xr:uid="{473EB3CE-A564-1E45-AC13-AF793AC0B477}"/>
+    <hyperlink ref="F15" r:id="rId52" xr:uid="{9674E89D-A51D-CD48-BAD4-0268F5EF0218}"/>
+    <hyperlink ref="D14" r:id="rId53" xr:uid="{2C21E21B-D467-6B40-B99F-10CFF204DF5E}"/>
+    <hyperlink ref="F14" r:id="rId54" xr:uid="{653FC37B-0E60-F24C-9F82-E361CB6F1BEA}"/>
+    <hyperlink ref="D13" r:id="rId55" xr:uid="{D092DE5A-6AF2-2244-9717-800A8A08CED7}"/>
+    <hyperlink ref="F13" r:id="rId56" xr:uid="{54C0ACDA-4A86-524D-8E90-A1EA869C6122}"/>
+    <hyperlink ref="D12" r:id="rId57" xr:uid="{97F64753-0AA1-EE4A-B974-83528256F4F4}"/>
+    <hyperlink ref="F12" r:id="rId58" xr:uid="{A5448C25-A12C-794E-A542-556C39C496AC}"/>
+    <hyperlink ref="D11" r:id="rId59" xr:uid="{77CE2757-4893-874D-99A1-72D0C139E6FF}"/>
+    <hyperlink ref="F11" r:id="rId60" xr:uid="{7453F409-FB26-364F-96CF-B8B3C16C5539}"/>
+    <hyperlink ref="D10" r:id="rId61" xr:uid="{48A4ED37-D659-7A47-AC11-024E77FD1932}"/>
+    <hyperlink ref="F10" r:id="rId62" xr:uid="{227686EA-22C5-4D4C-A4A3-E4AEAB8249BD}"/>
+    <hyperlink ref="D9" r:id="rId63" xr:uid="{4819B73E-4D12-7442-A4E4-9BCA2F43B41E}"/>
+    <hyperlink ref="F9" r:id="rId64" xr:uid="{FEB6F6C5-6B93-0541-8DFC-234A63742636}"/>
+    <hyperlink ref="D8" r:id="rId65" xr:uid="{908F3A4C-B3BF-5143-8411-82FA701D3B47}"/>
+    <hyperlink ref="F8" r:id="rId66" xr:uid="{BE91235B-8F82-0046-9FD0-B9E1CC774D1C}"/>
+    <hyperlink ref="D7" r:id="rId67" xr:uid="{16DB5697-836B-9D46-83E7-3056E572B29B}"/>
+    <hyperlink ref="F7" r:id="rId68" xr:uid="{CF85B538-39DB-BD47-AE3A-8B073048DFBB}"/>
+    <hyperlink ref="D6" r:id="rId69" xr:uid="{6C5B8EB1-AC9A-904C-907A-569707B74F92}"/>
+    <hyperlink ref="F6" r:id="rId70" xr:uid="{0AF9FAE1-834E-7943-9702-95FC0EB25D0F}"/>
+    <hyperlink ref="D5" r:id="rId71" xr:uid="{D67FD214-5BBB-154A-A06A-D03CEB54BD5C}"/>
+    <hyperlink ref="F5" r:id="rId72" xr:uid="{D237E9DD-C9A8-E740-8277-55420D2AD9DE}"/>
+    <hyperlink ref="D4" r:id="rId73" xr:uid="{5EA863AF-B605-7C4E-931A-904E68BFC36C}"/>
+    <hyperlink ref="F4" r:id="rId74" xr:uid="{3D5A580C-46B7-734E-8E50-64362E621AD2}"/>
+    <hyperlink ref="D3" r:id="rId75" xr:uid="{F593F17C-AE20-1243-820A-652D2D067441}"/>
+    <hyperlink ref="F3" r:id="rId76" xr:uid="{1502675B-8FAC-054C-8E99-CBF9BED0C5AB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekookuniverse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F80349-9C1E-0D45-84FD-311B4E3C4977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BA8F73-EF42-E641-9D42-B8D54B6FBC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32840" yWindow="2720" windowWidth="28900" windowHeight="15860" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35080" yWindow="2720" windowWidth="31140" windowHeight="18160" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TKURadio" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4053" uniqueCount="2573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4071" uniqueCount="2588">
   <si>
     <t>date</t>
   </si>
@@ -13475,6 +13475,53 @@
   </si>
   <si>
     <t>kookies kitchen</t>
+  </si>
+  <si>
+    <t>V hilariously introduces Jungkook as the “dangerous” member</t>
+  </si>
+  <si>
+    <t>BTS V had fans laughing after sharing photos of the members and jokingly warning that Jungkook “might bite” if approached, while playfully describing Jin as “wild,” RM as one he “captured with great difficulty” and J-Hope as “probably harmless.”</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DcgA1HztWgX/</t>
+  </si>
+  <si>
+    <t>https://naver.me/551k00U0</t>
+  </si>
+  <si>
+    <t>Jungkook’s birthday celebrations take over cities around the world</t>
+  </si>
+  <si>
+    <t>BTS Jungkook’s September 1 birthday will be celebrated with fan-led events across LA, Japan and Seoul, including LED trucks, a fireworks display, purple lighting and large-scale birthday advertisements at major venues and transport hubs.</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/Dciek2UNMhT/</t>
+  </si>
+  <si>
+    <t>https://naver.me/5zUbmFvT</t>
+  </si>
+  <si>
+    <t>V’s iconic Dodgers first pitch celebrated by MLB one year later ⚾️</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DcifrGGto3l/</t>
+  </si>
+  <si>
+    <t>MLB celebrated the first anniversary of BTS V’s ceremonial first pitch at Dodger Stadium, sharing footage from the memorable moment and recalling the extraordinary reaction from the crowd, with commentators describing V as a global sensation and an “undeniable megastar.”</t>
+  </si>
+  <si>
+    <t>https://naver.me/GP2UzZXi</t>
+  </si>
+  <si>
+    <t>Another week overflowing with TaeKook and BTS moments! 🥹
+We enjoyed unforgettable concerts in Toronto and Chicago, along with new IG and TikTok videos from both Taehyung and Jungkook, plenty of fun personal moments and memories shared, and exciting content from several of their brand partnerships! ✨
+And with September 1 almost here, Jungkook’s birthday celebrations have already begun around the globe, making this week even more special! 🎂🐰💜</t>
+  </si>
+  <si>
+    <t>Week of August 28, 2026</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Ias8-PmNWb4</t>
   </si>
 </sst>
 </file>
@@ -69582,7 +69629,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A21" s="17">
         <v>45594</v>
       </c>
@@ -69797,7 +69844,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="272" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="238" x14ac:dyDescent="0.2">
       <c r="A34" s="17">
         <v>45430</v>
       </c>
@@ -69814,7 +69861,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="17">
         <v>45422</v>
       </c>
@@ -72611,7 +72658,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="34" bestFit="1" customWidth="1"/>
@@ -72641,934 +72688,950 @@
     </row>
     <row r="2" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A2" s="35">
+        <v>46262</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>2585</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>2587</v>
+      </c>
+      <c r="G2" s="33"/>
+    </row>
+    <row r="3" spans="1:7" ht="85" x14ac:dyDescent="0.2">
+      <c r="A3" s="35">
         <v>46255</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B3" s="34" t="s">
         <v>2549</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C3" s="36" t="s">
         <v>2548</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D3" s="23" t="s">
         <v>2547</v>
       </c>
-      <c r="G2" s="33"/>
-    </row>
-    <row r="3" spans="1:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="A3" s="35">
+      <c r="G3" s="33"/>
+    </row>
+    <row r="4" spans="1:7" ht="136" x14ac:dyDescent="0.2">
+      <c r="A4" s="35">
         <v>46248</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B4" s="34" t="s">
         <v>2534</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C4" s="36" t="s">
         <v>2535</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D4" s="23" t="s">
         <v>2536</v>
       </c>
-      <c r="G3" s="33"/>
-    </row>
-    <row r="4" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A4" s="35">
+      <c r="G4" s="33"/>
+    </row>
+    <row r="5" spans="1:7" ht="102" x14ac:dyDescent="0.2">
+      <c r="A5" s="35">
         <v>46241</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B5" s="34" t="s">
         <v>2487</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C5" s="36" t="s">
         <v>2486</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D5" s="23" t="s">
         <v>2485</v>
       </c>
-      <c r="G4" s="33"/>
-    </row>
-    <row r="5" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="35">
+      <c r="G5" s="33"/>
+    </row>
+    <row r="6" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="35">
         <v>46234</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B6" s="34" t="s">
         <v>2525</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C6" s="36" t="s">
         <v>2453</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D6" s="23" t="s">
         <v>2452</v>
-      </c>
-      <c r="G5" s="33"/>
-    </row>
-    <row r="6" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="35">
-        <v>46227</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>1999</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>2000</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>1998</v>
       </c>
       <c r="G6" s="33"/>
     </row>
     <row r="7" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="35">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>1918</v>
+        <v>1999</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1917</v>
+        <v>2000</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>1919</v>
+        <v>1998</v>
       </c>
       <c r="G7" s="33"/>
     </row>
     <row r="8" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="35">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1913</v>
+        <v>1917</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>1911</v>
+        <v>1919</v>
       </c>
       <c r="G8" s="33"/>
     </row>
     <row r="9" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="35">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>1862</v>
+        <v>1912</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1864</v>
+        <v>1913</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>1863</v>
+        <v>1911</v>
       </c>
       <c r="G9" s="33"/>
     </row>
     <row r="10" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="35">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>1743</v>
+        <v>1862</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1742</v>
+        <v>1864</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>1744</v>
+        <v>1863</v>
       </c>
       <c r="G10" s="33"/>
     </row>
     <row r="11" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="35">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>4</v>
+        <v>1743</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>5</v>
+        <v>1742</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>6</v>
+        <v>1744</v>
       </c>
       <c r="G11" s="33"/>
     </row>
     <row r="12" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="35">
-        <v>46185</v>
+        <v>46192</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G12" s="33"/>
     </row>
     <row r="13" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="35">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G13" s="33"/>
     </row>
     <row r="14" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="35">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G14" s="33"/>
     </row>
     <row r="15" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="35">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G15" s="33"/>
     </row>
     <row r="16" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="35">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G16" s="33"/>
     </row>
     <row r="17" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="35">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G17" s="33"/>
     </row>
     <row r="18" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="35">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G18" s="33"/>
     </row>
     <row r="19" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="35">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G19" s="33"/>
     </row>
     <row r="20" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="35">
-        <v>46129</v>
+        <v>46136</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G20" s="33"/>
     </row>
     <row r="21" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="35">
-        <v>46115</v>
+        <v>46129</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G21" s="33"/>
     </row>
     <row r="22" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="35">
-        <v>46094</v>
+        <v>46115</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G22" s="33"/>
     </row>
     <row r="23" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="35">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G23" s="33"/>
     </row>
     <row r="24" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="35">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G24" s="33"/>
     </row>
     <row r="25" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="35">
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G25" s="33"/>
     </row>
     <row r="26" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="35">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G26" s="33"/>
     </row>
     <row r="27" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="35">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C27" s="36" t="s">
         <v>50</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G27" s="33"/>
     </row>
     <row r="28" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="35">
-        <v>46052</v>
+        <v>46059</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G28" s="33"/>
     </row>
     <row r="29" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="35">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G29" s="33"/>
     </row>
     <row r="30" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="35">
+        <v>46045</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="33"/>
+    </row>
+    <row r="31" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="35">
         <v>46038</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B31" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C31" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D31" s="23" t="s">
         <v>61</v>
-      </c>
-      <c r="G30" s="33"/>
-    </row>
-    <row r="31" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="35">
-        <v>46031</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>64</v>
       </c>
       <c r="G31" s="33"/>
     </row>
     <row r="32" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="35">
+        <v>46031</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="33"/>
+    </row>
+    <row r="33" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="35">
         <v>46024</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="B33" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C33" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D33" s="23" t="s">
         <v>67</v>
-      </c>
-      <c r="G32" s="33"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="35">
-        <v>46017</v>
-      </c>
-      <c r="B33" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>70</v>
       </c>
       <c r="G33" s="33"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="35">
+        <v>46017</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="33"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="35">
         <v>46010</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B35" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C35" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D35" s="23" t="s">
         <v>73</v>
-      </c>
-      <c r="G34" s="33"/>
-    </row>
-    <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="35">
-        <v>46003</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>76</v>
       </c>
       <c r="G35" s="33"/>
     </row>
     <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="35">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="G36" s="23"/>
+        <v>76</v>
+      </c>
+      <c r="G36" s="33"/>
     </row>
     <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="35">
-        <v>45989</v>
+        <v>45996</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G37" s="23"/>
     </row>
     <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="35">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G38" s="23"/>
     </row>
     <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="35">
-        <v>45975</v>
+        <v>45982</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G39" s="23"/>
     </row>
     <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="35">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G40" s="23"/>
     </row>
     <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="35">
+        <v>45968</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G41" s="23"/>
+    </row>
+    <row r="42" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="35">
         <v>45961</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B42" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="36" t="s">
+      <c r="C42" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="23" t="s">
+      <c r="D42" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="G41" s="23"/>
-    </row>
-    <row r="42" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="35">
+      <c r="G42" s="23"/>
+    </row>
+    <row r="43" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="35">
         <v>45954</v>
       </c>
-      <c r="B42" s="34" t="s">
+      <c r="B43" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="36" t="s">
+      <c r="C43" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D43" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="G42" s="23"/>
-    </row>
-    <row r="43" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="35">
+      <c r="G43" s="23"/>
+    </row>
+    <row r="44" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="35">
         <v>45947</v>
       </c>
-      <c r="B43" s="34" t="s">
+      <c r="B44" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C44" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D44" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="G43" s="23"/>
-    </row>
-    <row r="44" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="35">
+      <c r="G44" s="23"/>
+    </row>
+    <row r="45" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="35">
         <v>45940</v>
       </c>
-      <c r="B44" s="34" t="s">
+      <c r="B45" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="36" t="s">
+      <c r="C45" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="23" t="s">
+      <c r="D45" s="23" t="s">
         <v>101</v>
-      </c>
-      <c r="G44" s="23"/>
-    </row>
-    <row r="45" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="35">
-        <v>45933</v>
-      </c>
-      <c r="B45" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C45" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>104</v>
       </c>
       <c r="G45" s="23"/>
     </row>
     <row r="46" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="35">
+        <v>45933</v>
+      </c>
+      <c r="B46" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="23"/>
+    </row>
+    <row r="47" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="35">
         <v>45926</v>
       </c>
-      <c r="B46" s="34" t="s">
+      <c r="B47" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="C47" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D47" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="G46" s="23"/>
-    </row>
-    <row r="47" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="35">
+      <c r="G47" s="23"/>
+    </row>
+    <row r="48" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="35">
         <v>45919</v>
       </c>
-      <c r="B47" s="34" t="s">
+      <c r="B48" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="C47" s="36" t="s">
+      <c r="C48" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="D47" s="23" t="s">
+      <c r="D48" s="23" t="s">
         <v>110</v>
-      </c>
-      <c r="G47" s="23"/>
-    </row>
-    <row r="48" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="35">
-        <v>45912</v>
-      </c>
-      <c r="B48" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>113</v>
       </c>
       <c r="G48" s="23"/>
     </row>
     <row r="49" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="35">
+        <v>45912</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="G49" s="23"/>
+    </row>
+    <row r="50" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="35">
         <v>45905</v>
       </c>
-      <c r="B49" s="34" t="s">
+      <c r="B50" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C50" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="23" t="s">
+      <c r="D50" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="G49" s="23"/>
-    </row>
-    <row r="50" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="35">
+      <c r="G50" s="23"/>
+    </row>
+    <row r="51" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="35">
         <v>45898</v>
       </c>
-      <c r="B50" s="34" t="s">
+      <c r="B51" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="C50" s="36" t="s">
+      <c r="C51" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D51" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="G50" s="23"/>
-    </row>
-    <row r="51" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="35">
+      <c r="G51" s="23"/>
+    </row>
+    <row r="52" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="35">
         <v>45891</v>
       </c>
-      <c r="B51" s="34" t="s">
+      <c r="B52" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="C51" s="36" t="s">
+      <c r="C52" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="D51" s="23" t="s">
+      <c r="D52" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="G51" s="23"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="35">
+      <c r="G52" s="23"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="35">
         <v>45884</v>
       </c>
-      <c r="B52" s="34" t="s">
+      <c r="B53" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="C52" s="34" t="s">
+      <c r="C53" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="D52" s="23" t="s">
+      <c r="D53" s="23" t="s">
         <v>124</v>
-      </c>
-      <c r="G52" s="23"/>
-    </row>
-    <row r="53" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="35">
-        <v>45877</v>
-      </c>
-      <c r="B53" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="C53" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>127</v>
       </c>
       <c r="G53" s="23"/>
     </row>
     <row r="54" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="35">
+        <v>45877</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="G54" s="23"/>
+    </row>
+    <row r="55" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="35">
         <v>45870</v>
       </c>
-      <c r="B54" s="34" t="s">
+      <c r="B55" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="C54" s="36" t="s">
+      <c r="C55" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="D54" s="23" t="s">
+      <c r="D55" s="23" t="s">
         <v>130</v>
-      </c>
-      <c r="G54" s="23"/>
-    </row>
-    <row r="55" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="35">
-        <v>45863</v>
-      </c>
-      <c r="B55" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="C55" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>133</v>
       </c>
       <c r="G55" s="23"/>
     </row>
     <row r="56" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="35">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C56" s="36" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G56" s="23"/>
     </row>
     <row r="57" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="35">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="B57" s="34" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G57" s="23"/>
     </row>
     <row r="58" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="35">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C58" s="36" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G58" s="23"/>
     </row>
     <row r="59" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="35">
+        <v>45842</v>
+      </c>
+      <c r="B59" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="C59" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="G59" s="23"/>
+    </row>
+    <row r="60" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="35">
         <v>45835</v>
       </c>
-      <c r="B59" s="34" t="s">
+      <c r="B60" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="C59" s="36" t="s">
+      <c r="C60" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="D59" s="23" t="s">
+      <c r="D60" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="G59" s="23"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C60" s="36"/>
+      <c r="G60" s="23"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C61" s="36"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D12" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="D13" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="D14" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
-    <hyperlink ref="D15" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
-    <hyperlink ref="D16" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
-    <hyperlink ref="D17" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
-    <hyperlink ref="D19" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
-    <hyperlink ref="D21" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
-    <hyperlink ref="D22" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
-    <hyperlink ref="D23" r:id="rId10" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
-    <hyperlink ref="D24" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
-    <hyperlink ref="D25" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
-    <hyperlink ref="D26" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
-    <hyperlink ref="D27" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
-    <hyperlink ref="D28" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
-    <hyperlink ref="D29" r:id="rId16" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
-    <hyperlink ref="D30" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
-    <hyperlink ref="D31" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
-    <hyperlink ref="D32" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
-    <hyperlink ref="D33" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
-    <hyperlink ref="D34" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
-    <hyperlink ref="D35" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
-    <hyperlink ref="D36" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
-    <hyperlink ref="D37" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
-    <hyperlink ref="D38" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
-    <hyperlink ref="D39" r:id="rId26" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
-    <hyperlink ref="D40" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
-    <hyperlink ref="D41" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
-    <hyperlink ref="D42" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
-    <hyperlink ref="D43" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
-    <hyperlink ref="D44" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
-    <hyperlink ref="D45" r:id="rId32" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
-    <hyperlink ref="D46" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
-    <hyperlink ref="D47" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
-    <hyperlink ref="D48" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
-    <hyperlink ref="D49" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
-    <hyperlink ref="D50" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
-    <hyperlink ref="D51" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
-    <hyperlink ref="D52" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
-    <hyperlink ref="D53" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
-    <hyperlink ref="D54" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
-    <hyperlink ref="D55" r:id="rId42" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
-    <hyperlink ref="D56" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
-    <hyperlink ref="D57" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
-    <hyperlink ref="D58" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
-    <hyperlink ref="D59" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
-    <hyperlink ref="D11" r:id="rId47" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
-    <hyperlink ref="D10" r:id="rId48" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
-    <hyperlink ref="D9" r:id="rId49" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
-    <hyperlink ref="D8" r:id="rId50" xr:uid="{8E240BDD-02FF-CA47-B5D9-FD7E9FCA5AEA}"/>
-    <hyperlink ref="D7" r:id="rId51" xr:uid="{77C8CFB5-83B9-D448-AFCE-DD617D9A359D}"/>
-    <hyperlink ref="D6" r:id="rId52" xr:uid="{7282EB94-FBFF-C64E-9C65-3E4E1C662EA7}"/>
-    <hyperlink ref="D5" r:id="rId53" xr:uid="{AC8ED73F-B845-2845-962C-58F7783B2A4D}"/>
-    <hyperlink ref="D4" r:id="rId54" xr:uid="{683CE86C-4345-8043-87A1-967BF156D1E1}"/>
+    <hyperlink ref="D13" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="D14" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="D15" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="D16" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="D17" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="D18" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="D20" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="D22" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
+    <hyperlink ref="D23" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
+    <hyperlink ref="D24" r:id="rId10" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
+    <hyperlink ref="D25" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
+    <hyperlink ref="D26" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
+    <hyperlink ref="D27" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
+    <hyperlink ref="D28" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
+    <hyperlink ref="D29" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
+    <hyperlink ref="D30" r:id="rId16" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
+    <hyperlink ref="D31" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
+    <hyperlink ref="D32" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
+    <hyperlink ref="D33" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
+    <hyperlink ref="D34" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
+    <hyperlink ref="D35" r:id="rId21" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
+    <hyperlink ref="D36" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
+    <hyperlink ref="D37" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
+    <hyperlink ref="D38" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
+    <hyperlink ref="D39" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
+    <hyperlink ref="D40" r:id="rId26" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
+    <hyperlink ref="D41" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
+    <hyperlink ref="D42" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
+    <hyperlink ref="D43" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
+    <hyperlink ref="D44" r:id="rId30" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
+    <hyperlink ref="D45" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
+    <hyperlink ref="D46" r:id="rId32" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
+    <hyperlink ref="D47" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
+    <hyperlink ref="D48" r:id="rId34" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
+    <hyperlink ref="D49" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
+    <hyperlink ref="D50" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
+    <hyperlink ref="D51" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
+    <hyperlink ref="D52" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
+    <hyperlink ref="D53" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
+    <hyperlink ref="D54" r:id="rId40" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
+    <hyperlink ref="D55" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
+    <hyperlink ref="D56" r:id="rId42" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
+    <hyperlink ref="D57" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
+    <hyperlink ref="D58" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
+    <hyperlink ref="D59" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
+    <hyperlink ref="D60" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
+    <hyperlink ref="D12" r:id="rId47" xr:uid="{F9990143-F9A9-124E-BCC1-1FAB349A9366}"/>
+    <hyperlink ref="D11" r:id="rId48" xr:uid="{EE336F4B-5EFC-034A-9FF6-DB34FC42BBA7}"/>
+    <hyperlink ref="D10" r:id="rId49" xr:uid="{4FE02816-5803-B546-8B3C-00FB300D94B2}"/>
+    <hyperlink ref="D9" r:id="rId50" xr:uid="{8E240BDD-02FF-CA47-B5D9-FD7E9FCA5AEA}"/>
+    <hyperlink ref="D8" r:id="rId51" xr:uid="{77C8CFB5-83B9-D448-AFCE-DD617D9A359D}"/>
+    <hyperlink ref="D7" r:id="rId52" xr:uid="{7282EB94-FBFF-C64E-9C65-3E4E1C662EA7}"/>
+    <hyperlink ref="D6" r:id="rId53" xr:uid="{AC8ED73F-B845-2845-962C-58F7783B2A4D}"/>
+    <hyperlink ref="D5" r:id="rId54" xr:uid="{683CE86C-4345-8043-87A1-967BF156D1E1}"/>
     <hyperlink ref="D2" r:id="rId55" xr:uid="{4A609F52-301A-7E4F-9D40-745FB09003DC}"/>
+    <hyperlink ref="D3" r:id="rId56" xr:uid="{F0A8C1AE-BD5B-7445-868A-F470A7978FBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -74963,7 +75026,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="25" bestFit="1" customWidth="1"/>
@@ -74997,882 +75060,948 @@
     </row>
     <row r="2" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="31">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>2566</v>
+        <v>2581</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2567</v>
+        <v>2582</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>2568</v>
+        <v>2583</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>2569</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="31">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>2562</v>
+        <v>2577</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>2563</v>
+        <v>2579</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>2564</v>
+        <v>2578</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>2565</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="31">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="B4" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>2573</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>2574</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A5" s="31">
+        <v>46258</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>2558</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>2559</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>2560</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>2561</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A5" s="31">
-        <v>46255</v>
-      </c>
-      <c r="B5" s="22" t="s">
+      <c r="C5" s="22" t="s">
+        <v>2566</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>2568</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" s="31">
+        <v>46258</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>2554</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>2556</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>2555</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>2557</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A6" s="31">
-        <v>46251</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>167</v>
-      </c>
       <c r="C6" s="22" t="s">
-        <v>2550</v>
+        <v>2562</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2551</v>
+        <v>2563</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>2552</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>2553</v>
+        <v>2564</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>2565</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="31">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>2530</v>
+        <v>2558</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2532</v>
+        <v>2559</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>2531</v>
+        <v>2560</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="31">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>213</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>2513</v>
+        <v>2554</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2512</v>
+        <v>2556</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>2514</v>
+        <v>2555</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>2515</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>2508</v>
+        <v>2550</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2509</v>
+        <v>2551</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>2510</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>2511</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>2552</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
-        <v>46238</v>
+        <v>46249</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>2505</v>
+        <v>2530</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>2504</v>
+        <v>2532</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>2506</v>
+        <v>2531</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>2507</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="31">
+        <v>46244</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>2512</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>2514</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A12" s="31">
+        <v>46244</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>2508</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>2509</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>2510</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A13" s="31">
         <v>46238</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>2500</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>2501</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>2503</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A12" s="31">
-        <v>46232</v>
-      </c>
-      <c r="B12" s="22" t="s">
+      <c r="B13" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>2497</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>2496</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>2499</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="31">
-        <v>46232</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>203</v>
-      </c>
       <c r="C13" s="22" t="s">
-        <v>2492</v>
+        <v>2505</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>2495</v>
+        <v>2504</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>2493</v>
+        <v>2506</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>2494</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
-        <v>46226</v>
+        <v>46238</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>203</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>2488</v>
+        <v>2500</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>2489</v>
+        <v>2501</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>2490</v>
+        <v>2502</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>2491</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
-        <v>46222</v>
+        <v>46232</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>213</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>1964</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>1963</v>
+        <v>2497</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>2496</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>1965</v>
+        <v>2498</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>1966</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="31">
-        <v>46222</v>
+        <v>46232</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>203</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>1962</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>1960</v>
+        <v>2492</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>2495</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>1961</v>
+        <v>2493</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" s="31">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>1958</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>1957</v>
+        <v>2488</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>2489</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>1959</v>
+        <v>2490</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1968</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="31">
+        <v>46222</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>1965</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A19" s="31">
+        <v>46222</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>1960</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>1961</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A20" s="31">
         <v>46219</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B20" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>1959</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A21" s="31">
+        <v>46219</v>
+      </c>
+      <c r="B21" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C21" s="22" t="s">
         <v>1954</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D21" s="23" t="s">
         <v>1956</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>1955</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>1969</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="289" x14ac:dyDescent="0.2">
-      <c r="A19" s="31">
+    <row r="22" spans="1:6" ht="289" x14ac:dyDescent="0.2">
+      <c r="A22" s="31">
         <v>46218</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B22" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C22" s="22" t="s">
         <v>1951</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D22" s="23" t="s">
         <v>1952</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E22" s="22" t="s">
         <v>1953</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F22" s="11" t="s">
         <v>1970</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="238" x14ac:dyDescent="0.2">
-      <c r="A20" s="31">
+    <row r="23" spans="1:6" ht="238" x14ac:dyDescent="0.2">
+      <c r="A23" s="31">
         <v>46218</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B23" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C23" s="22" t="s">
         <v>1948</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D23" s="23" t="s">
         <v>1947</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>1950</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F23" s="11" t="s">
         <v>1970</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="204" x14ac:dyDescent="0.2">
-      <c r="A21" s="31">
+    <row r="24" spans="1:6" ht="204" x14ac:dyDescent="0.2">
+      <c r="A24" s="31">
         <v>46218</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B24" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C24" s="22" t="s">
         <v>1949</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D24" s="30" t="s">
         <v>1945</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>1946</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F24" s="11" t="s">
         <v>1970</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A22" s="31">
+    <row r="25" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A25" s="31">
         <v>46217</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>1943</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>1942</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>1944</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="31">
-        <v>46217</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>1940</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>1939</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>1941</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A24" s="31">
-        <v>46216</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>1936</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>1935</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F24" s="29" t="s">
-        <v>1938</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="31">
-        <v>46216</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>203</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>1933</v>
+        <v>1943</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>1932</v>
+        <v>1942</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>1934</v>
+        <v>1944</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="238" x14ac:dyDescent="0.2">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>167</v>
+        <v>213</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>1931</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>1974</v>
+        <v>1941</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>1972</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>213</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>1927</v>
+        <v>1936</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>1926</v>
+        <v>1935</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>1928</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+        <v>1937</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>203</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>1924</v>
+        <v>1933</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>1923</v>
+        <v>1932</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>1925</v>
+        <v>1934</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="238" x14ac:dyDescent="0.2">
       <c r="A29" s="31">
-        <v>46210</v>
+        <v>46215</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>1920</v>
+        <v>1930</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>1921</v>
+        <v>1929</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>1922</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+        <v>1931</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A30" s="31">
-        <v>46208</v>
+        <v>46213</v>
       </c>
       <c r="B30" s="22" t="s">
         <v>213</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>1812</v>
+        <v>1927</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>1926</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>1810</v>
+        <v>1928</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>1811</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A31" s="31">
-        <v>46208</v>
+        <v>46213</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>203</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>1805</v>
-      </c>
-      <c r="D31" s="29" t="s">
-        <v>1808</v>
+        <v>1924</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>1923</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F31" s="29" t="s">
-        <v>1807</v>
+        <v>1925</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>1976</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A32" s="31">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B32" s="22" t="s">
         <v>213</v>
       </c>
       <c r="C32" s="22" t="s">
+        <v>1920</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>1921</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>1922</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A33" s="31">
+        <v>46208</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>1812</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>1810</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A34" s="31">
+        <v>46208</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F34" s="29" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A35" s="31">
+        <v>46205</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="22" t="s">
         <v>1802</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="D35" s="29" t="s">
         <v>1797</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E35" s="22" t="s">
         <v>1803</v>
       </c>
-      <c r="F32" s="30" t="s">
+      <c r="F35" s="30" t="s">
         <v>1804</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A33" s="31">
+    <row r="36" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A36" s="31">
         <v>46206</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C36" s="22" t="s">
         <v>1799</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D36" s="29" t="s">
         <v>1798</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E36" s="22" t="s">
         <v>1800</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F36" s="29" t="s">
         <v>1801</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A34" s="32">
+    <row r="37" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A37" s="32">
         <v>46203</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C37" s="25" t="s">
         <v>1758</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D37" s="29" t="s">
         <v>1759</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="E37" s="25" t="s">
         <v>1760</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F37" s="29" t="s">
         <v>1764</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A35" s="32">
+    <row r="38" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A38" s="32">
         <v>46203</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B38" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C38" s="25" t="s">
         <v>1762</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D38" s="25" t="s">
         <v>1761</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="E38" s="25" t="s">
         <v>1763</v>
       </c>
-      <c r="F35" s="29" t="s">
+      <c r="F38" s="29" t="s">
         <v>1765</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A36" s="32">
+    <row r="39" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A39" s="32">
         <v>46202</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C39" s="25" t="s">
         <v>1767</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D39" s="29" t="s">
         <v>1766</v>
       </c>
-      <c r="E36" s="25" t="s">
+      <c r="E39" s="25" t="s">
         <v>1769</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F39" s="29" t="s">
         <v>1768</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A37" s="32">
+    <row r="40" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A40" s="32">
         <v>46202</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B40" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C40" s="25" t="s">
         <v>1772</v>
       </c>
-      <c r="D37" s="25" t="s">
+      <c r="D40" s="25" t="s">
         <v>1770</v>
       </c>
-      <c r="E37" s="25" t="s">
+      <c r="E40" s="25" t="s">
         <v>1771</v>
       </c>
-      <c r="F37" s="29" t="s">
+      <c r="F40" s="29" t="s">
         <v>1773</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A38" s="32">
+    <row r="41" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A41" s="32">
         <v>46201</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C41" s="25" t="s">
         <v>1774</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D41" s="29" t="s">
         <v>1776</v>
       </c>
-      <c r="E38" s="25" t="s">
+      <c r="E41" s="25" t="s">
         <v>1775</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F41" s="29" t="s">
         <v>1777</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A39" s="32">
+    <row r="42" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="A42" s="32">
         <v>46201</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B42" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C42" s="25" t="s">
         <v>1779</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D42" s="29" t="s">
         <v>1778</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E42" s="25" t="s">
         <v>1780</v>
       </c>
-      <c r="F39" s="29" t="s">
+      <c r="F42" s="29" t="s">
         <v>1781</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A40" s="32">
+    <row r="43" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A43" s="32">
         <v>46198</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C43" s="25" t="s">
         <v>1783</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="D43" s="25" t="s">
         <v>1782</v>
       </c>
-      <c r="E40" s="25" t="s">
+      <c r="E43" s="25" t="s">
         <v>1784</v>
       </c>
-      <c r="F40" s="29" t="s">
+      <c r="F43" s="29" t="s">
         <v>1785</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A41" s="32">
+    <row r="44" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A44" s="32">
         <v>46198</v>
       </c>
-      <c r="B41" s="25" t="s">
+      <c r="B44" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C44" s="25" t="s">
         <v>1787</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D44" s="29" t="s">
         <v>1786</v>
       </c>
-      <c r="E41" s="25" t="s">
+      <c r="E44" s="25" t="s">
         <v>1788</v>
       </c>
-      <c r="F41" s="29" t="s">
+      <c r="F44" s="29" t="s">
         <v>1789</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F34" r:id="rId1" xr:uid="{4C165E91-B26F-0A45-88A2-06AA9774DFAE}"/>
-    <hyperlink ref="F35" r:id="rId2" xr:uid="{7642FB96-3502-1243-90D5-20631BBFCC79}"/>
-    <hyperlink ref="D34" r:id="rId3" xr:uid="{1E0F0315-6747-884F-AA49-D6E56727920B}"/>
-    <hyperlink ref="D36" r:id="rId4" xr:uid="{8488153C-110A-4C48-965B-7630C9492F36}"/>
-    <hyperlink ref="F36" r:id="rId5" xr:uid="{BE75DA92-F980-1948-9204-01AC25600C6B}"/>
-    <hyperlink ref="F37" r:id="rId6" xr:uid="{7457B18B-86CB-6147-ADA9-A3CE56A83401}"/>
-    <hyperlink ref="D38" r:id="rId7" xr:uid="{FBAC6F67-55B1-324A-82BF-DD02FC6BBA04}"/>
-    <hyperlink ref="F38" r:id="rId8" xr:uid="{865A0475-BB84-DB47-9559-DC4649F4A676}"/>
-    <hyperlink ref="D39" r:id="rId9" xr:uid="{D9D6577F-5D20-B245-9F68-2D50BDFCA180}"/>
-    <hyperlink ref="F39" r:id="rId10" xr:uid="{21950F61-40D9-5E42-87ED-8402F010D442}"/>
-    <hyperlink ref="F40" r:id="rId11" xr:uid="{990DFC39-986D-3849-99EC-29E4E365D40A}"/>
-    <hyperlink ref="D41" r:id="rId12" xr:uid="{DE7E8DCA-2195-394F-9E1F-C6282B5AFE11}"/>
-    <hyperlink ref="F41" r:id="rId13" xr:uid="{A97FBDD3-5139-A04F-A3D7-E34D3553362F}"/>
-    <hyperlink ref="D32" r:id="rId14" xr:uid="{B5715535-CBF7-2F43-A872-9DF1119833A5}"/>
-    <hyperlink ref="D33" r:id="rId15" xr:uid="{4BD8C645-AD86-B644-BB86-E474C950B5C1}"/>
-    <hyperlink ref="F33" r:id="rId16" xr:uid="{E6DC40BA-2FBD-8741-8B86-BE0CB8B5DF5A}"/>
-    <hyperlink ref="F32" r:id="rId17" xr:uid="{2D25DB01-973D-C442-BAAA-A7898AECF3CB}"/>
-    <hyperlink ref="D31" r:id="rId18" xr:uid="{5EE266C8-30C3-AA49-A280-DD6ACA716BED}"/>
-    <hyperlink ref="F31" r:id="rId19" xr:uid="{1523EF8F-C7CF-B247-84A6-D1068FDF2FC9}"/>
-    <hyperlink ref="F30" r:id="rId20" xr:uid="{5344D85B-DBA1-7F4D-A437-9ADA0A6F25E7}"/>
-    <hyperlink ref="D30" r:id="rId21" xr:uid="{82E8603F-6B68-A849-9DB1-A6D7D62BC5C3}"/>
-    <hyperlink ref="D29" r:id="rId22" xr:uid="{C4B7F07F-C7EF-A445-BA36-79AFD111A13A}"/>
-    <hyperlink ref="D28" r:id="rId23" xr:uid="{28DE8988-3557-EF48-BB75-91D97971DC4D}"/>
-    <hyperlink ref="D27" r:id="rId24" xr:uid="{0B7C9678-BFED-1B4C-9FF2-DCCCE6ED62A7}"/>
-    <hyperlink ref="D26" r:id="rId25" xr:uid="{F69DCD8B-5576-A945-A1C0-850B8C57018F}"/>
-    <hyperlink ref="D25" r:id="rId26" xr:uid="{5CC655C1-5F71-CA47-90F1-336EB32A4376}"/>
-    <hyperlink ref="D24" r:id="rId27" xr:uid="{435469A8-0A82-1B46-ADC7-2BD93F4F0AD8}"/>
-    <hyperlink ref="D23" r:id="rId28" xr:uid="{C3AD3B54-C7D7-D14E-9805-9AEFCD3B56FC}"/>
-    <hyperlink ref="D22" r:id="rId29" xr:uid="{0FC6BD88-2D04-304E-AA6D-D0FC8F78BCA3}"/>
-    <hyperlink ref="D21" r:id="rId30" xr:uid="{9D70D003-ECDB-EC41-8AC7-5169C0795E15}"/>
-    <hyperlink ref="D20" r:id="rId31" xr:uid="{95972599-A68F-6141-8993-0C512EA7EB77}"/>
-    <hyperlink ref="D19" r:id="rId32" xr:uid="{325C9583-A49B-764F-9858-1A1870FCBF90}"/>
-    <hyperlink ref="D18" r:id="rId33" xr:uid="{841ECEF8-4ED6-B84D-8372-B8844DAD23B5}"/>
-    <hyperlink ref="D17" r:id="rId34" xr:uid="{3F93FFDC-C232-DD42-9509-5E6EC6ECC7D3}"/>
-    <hyperlink ref="D16" r:id="rId35" xr:uid="{1C3439D8-0793-DA4B-991C-E5E37FAAC840}"/>
+    <hyperlink ref="F37" r:id="rId1" xr:uid="{4C165E91-B26F-0A45-88A2-06AA9774DFAE}"/>
+    <hyperlink ref="F38" r:id="rId2" xr:uid="{7642FB96-3502-1243-90D5-20631BBFCC79}"/>
+    <hyperlink ref="D37" r:id="rId3" xr:uid="{1E0F0315-6747-884F-AA49-D6E56727920B}"/>
+    <hyperlink ref="D39" r:id="rId4" xr:uid="{8488153C-110A-4C48-965B-7630C9492F36}"/>
+    <hyperlink ref="F39" r:id="rId5" xr:uid="{BE75DA92-F980-1948-9204-01AC25600C6B}"/>
+    <hyperlink ref="F40" r:id="rId6" xr:uid="{7457B18B-86CB-6147-ADA9-A3CE56A83401}"/>
+    <hyperlink ref="D41" r:id="rId7" xr:uid="{FBAC6F67-55B1-324A-82BF-DD02FC6BBA04}"/>
+    <hyperlink ref="F41" r:id="rId8" xr:uid="{865A0475-BB84-DB47-9559-DC4649F4A676}"/>
+    <hyperlink ref="D42" r:id="rId9" xr:uid="{D9D6577F-5D20-B245-9F68-2D50BDFCA180}"/>
+    <hyperlink ref="F42" r:id="rId10" xr:uid="{21950F61-40D9-5E42-87ED-8402F010D442}"/>
+    <hyperlink ref="F43" r:id="rId11" xr:uid="{990DFC39-986D-3849-99EC-29E4E365D40A}"/>
+    <hyperlink ref="D44" r:id="rId12" xr:uid="{DE7E8DCA-2195-394F-9E1F-C6282B5AFE11}"/>
+    <hyperlink ref="F44" r:id="rId13" xr:uid="{A97FBDD3-5139-A04F-A3D7-E34D3553362F}"/>
+    <hyperlink ref="D35" r:id="rId14" xr:uid="{B5715535-CBF7-2F43-A872-9DF1119833A5}"/>
+    <hyperlink ref="D36" r:id="rId15" xr:uid="{4BD8C645-AD86-B644-BB86-E474C950B5C1}"/>
+    <hyperlink ref="F36" r:id="rId16" xr:uid="{E6DC40BA-2FBD-8741-8B86-BE0CB8B5DF5A}"/>
+    <hyperlink ref="F35" r:id="rId17" xr:uid="{2D25DB01-973D-C442-BAAA-A7898AECF3CB}"/>
+    <hyperlink ref="D34" r:id="rId18" xr:uid="{5EE266C8-30C3-AA49-A280-DD6ACA716BED}"/>
+    <hyperlink ref="F34" r:id="rId19" xr:uid="{1523EF8F-C7CF-B247-84A6-D1068FDF2FC9}"/>
+    <hyperlink ref="F33" r:id="rId20" xr:uid="{5344D85B-DBA1-7F4D-A437-9ADA0A6F25E7}"/>
+    <hyperlink ref="D33" r:id="rId21" xr:uid="{82E8603F-6B68-A849-9DB1-A6D7D62BC5C3}"/>
+    <hyperlink ref="D32" r:id="rId22" xr:uid="{C4B7F07F-C7EF-A445-BA36-79AFD111A13A}"/>
+    <hyperlink ref="D31" r:id="rId23" xr:uid="{28DE8988-3557-EF48-BB75-91D97971DC4D}"/>
+    <hyperlink ref="D30" r:id="rId24" xr:uid="{0B7C9678-BFED-1B4C-9FF2-DCCCE6ED62A7}"/>
+    <hyperlink ref="D29" r:id="rId25" xr:uid="{F69DCD8B-5576-A945-A1C0-850B8C57018F}"/>
+    <hyperlink ref="D28" r:id="rId26" xr:uid="{5CC655C1-5F71-CA47-90F1-336EB32A4376}"/>
+    <hyperlink ref="D27" r:id="rId27" xr:uid="{435469A8-0A82-1B46-ADC7-2BD93F4F0AD8}"/>
+    <hyperlink ref="D26" r:id="rId28" xr:uid="{C3AD3B54-C7D7-D14E-9805-9AEFCD3B56FC}"/>
+    <hyperlink ref="D25" r:id="rId29" xr:uid="{0FC6BD88-2D04-304E-AA6D-D0FC8F78BCA3}"/>
+    <hyperlink ref="D24" r:id="rId30" xr:uid="{9D70D003-ECDB-EC41-8AC7-5169C0795E15}"/>
+    <hyperlink ref="D23" r:id="rId31" xr:uid="{95972599-A68F-6141-8993-0C512EA7EB77}"/>
+    <hyperlink ref="D22" r:id="rId32" xr:uid="{325C9583-A49B-764F-9858-1A1870FCBF90}"/>
+    <hyperlink ref="D21" r:id="rId33" xr:uid="{841ECEF8-4ED6-B84D-8372-B8844DAD23B5}"/>
+    <hyperlink ref="D20" r:id="rId34" xr:uid="{3F93FFDC-C232-DD42-9509-5E6EC6ECC7D3}"/>
+    <hyperlink ref="D19" r:id="rId35" xr:uid="{1C3439D8-0793-DA4B-991C-E5E37FAAC840}"/>
     <hyperlink ref="D2" r:id="rId36" xr:uid="{51A6409E-8F94-AF44-B60C-08D0EDDC3758}"/>
     <hyperlink ref="F2" r:id="rId37" xr:uid="{7F3D42E2-43F6-3548-BB2F-32CAD36E6170}"/>
-    <hyperlink ref="F16" r:id="rId38" xr:uid="{BDC3FD63-F436-E94D-A22F-05D357586E92}"/>
-    <hyperlink ref="F17" r:id="rId39" xr:uid="{0D035AE3-AAB0-254A-8010-E546387524A5}"/>
-    <hyperlink ref="F18" r:id="rId40" xr:uid="{2BCDC745-7256-214E-85A3-5FD239BA2A2F}"/>
-    <hyperlink ref="F19" r:id="rId41" xr:uid="{646B607C-75D4-0A47-8DED-0FDED514E2D3}"/>
-    <hyperlink ref="F20" r:id="rId42" xr:uid="{B9D307B7-2704-6E46-A670-B2DF92C7BC6F}"/>
-    <hyperlink ref="F21" r:id="rId43" xr:uid="{AE106E88-F04C-8744-B97B-68010273A3BF}"/>
-    <hyperlink ref="F22" r:id="rId44" xr:uid="{E5B27231-C944-BC4D-8025-6C163578708B}"/>
-    <hyperlink ref="F23" r:id="rId45" xr:uid="{4394F2F6-3518-9346-9D09-3496D3A48ABE}"/>
-    <hyperlink ref="F25" r:id="rId46" xr:uid="{C243C78A-1717-6C4E-9BE0-5AB19A56F3AB}"/>
-    <hyperlink ref="F26" r:id="rId47" xr:uid="{95FB7936-E26F-434D-AF06-44A9337A976E}"/>
-    <hyperlink ref="F27" r:id="rId48" xr:uid="{DFDB01C1-AE39-EB47-8DEA-A691B1A13FFF}"/>
-    <hyperlink ref="F28" r:id="rId49" xr:uid="{D57E7D52-6454-0149-87FF-11C129D8632B}"/>
-    <hyperlink ref="F29" r:id="rId50" xr:uid="{CD3A77F8-468B-EB42-BC45-17DABC164DD2}"/>
-    <hyperlink ref="D15" r:id="rId51" xr:uid="{473EB3CE-A564-1E45-AC13-AF793AC0B477}"/>
-    <hyperlink ref="F15" r:id="rId52" xr:uid="{9674E89D-A51D-CD48-BAD4-0268F5EF0218}"/>
-    <hyperlink ref="D14" r:id="rId53" xr:uid="{2C21E21B-D467-6B40-B99F-10CFF204DF5E}"/>
-    <hyperlink ref="F14" r:id="rId54" xr:uid="{653FC37B-0E60-F24C-9F82-E361CB6F1BEA}"/>
-    <hyperlink ref="D13" r:id="rId55" xr:uid="{D092DE5A-6AF2-2244-9717-800A8A08CED7}"/>
-    <hyperlink ref="F13" r:id="rId56" xr:uid="{54C0ACDA-4A86-524D-8E90-A1EA869C6122}"/>
-    <hyperlink ref="D12" r:id="rId57" xr:uid="{97F64753-0AA1-EE4A-B974-83528256F4F4}"/>
-    <hyperlink ref="F12" r:id="rId58" xr:uid="{A5448C25-A12C-794E-A542-556C39C496AC}"/>
-    <hyperlink ref="D11" r:id="rId59" xr:uid="{77CE2757-4893-874D-99A1-72D0C139E6FF}"/>
-    <hyperlink ref="F11" r:id="rId60" xr:uid="{7453F409-FB26-364F-96CF-B8B3C16C5539}"/>
-    <hyperlink ref="D10" r:id="rId61" xr:uid="{48A4ED37-D659-7A47-AC11-024E77FD1932}"/>
-    <hyperlink ref="F10" r:id="rId62" xr:uid="{227686EA-22C5-4D4C-A4A3-E4AEAB8249BD}"/>
-    <hyperlink ref="D9" r:id="rId63" xr:uid="{4819B73E-4D12-7442-A4E4-9BCA2F43B41E}"/>
-    <hyperlink ref="F9" r:id="rId64" xr:uid="{FEB6F6C5-6B93-0541-8DFC-234A63742636}"/>
-    <hyperlink ref="D8" r:id="rId65" xr:uid="{908F3A4C-B3BF-5143-8411-82FA701D3B47}"/>
-    <hyperlink ref="F8" r:id="rId66" xr:uid="{BE91235B-8F82-0046-9FD0-B9E1CC774D1C}"/>
-    <hyperlink ref="D7" r:id="rId67" xr:uid="{16DB5697-836B-9D46-83E7-3056E572B29B}"/>
-    <hyperlink ref="F7" r:id="rId68" xr:uid="{CF85B538-39DB-BD47-AE3A-8B073048DFBB}"/>
-    <hyperlink ref="D6" r:id="rId69" xr:uid="{6C5B8EB1-AC9A-904C-907A-569707B74F92}"/>
-    <hyperlink ref="F6" r:id="rId70" xr:uid="{0AF9FAE1-834E-7943-9702-95FC0EB25D0F}"/>
-    <hyperlink ref="D5" r:id="rId71" xr:uid="{D67FD214-5BBB-154A-A06A-D03CEB54BD5C}"/>
-    <hyperlink ref="F5" r:id="rId72" xr:uid="{D237E9DD-C9A8-E740-8277-55420D2AD9DE}"/>
-    <hyperlink ref="D4" r:id="rId73" xr:uid="{5EA863AF-B605-7C4E-931A-904E68BFC36C}"/>
-    <hyperlink ref="F4" r:id="rId74" xr:uid="{3D5A580C-46B7-734E-8E50-64362E621AD2}"/>
-    <hyperlink ref="D3" r:id="rId75" xr:uid="{F593F17C-AE20-1243-820A-652D2D067441}"/>
-    <hyperlink ref="F3" r:id="rId76" xr:uid="{1502675B-8FAC-054C-8E99-CBF9BED0C5AB}"/>
+    <hyperlink ref="F19" r:id="rId38" xr:uid="{BDC3FD63-F436-E94D-A22F-05D357586E92}"/>
+    <hyperlink ref="F20" r:id="rId39" xr:uid="{0D035AE3-AAB0-254A-8010-E546387524A5}"/>
+    <hyperlink ref="F21" r:id="rId40" xr:uid="{2BCDC745-7256-214E-85A3-5FD239BA2A2F}"/>
+    <hyperlink ref="F22" r:id="rId41" xr:uid="{646B607C-75D4-0A47-8DED-0FDED514E2D3}"/>
+    <hyperlink ref="F23" r:id="rId42" xr:uid="{B9D307B7-2704-6E46-A670-B2DF92C7BC6F}"/>
+    <hyperlink ref="F24" r:id="rId43" xr:uid="{AE106E88-F04C-8744-B97B-68010273A3BF}"/>
+    <hyperlink ref="F25" r:id="rId44" xr:uid="{E5B27231-C944-BC4D-8025-6C163578708B}"/>
+    <hyperlink ref="F26" r:id="rId45" xr:uid="{4394F2F6-3518-9346-9D09-3496D3A48ABE}"/>
+    <hyperlink ref="F28" r:id="rId46" xr:uid="{C243C78A-1717-6C4E-9BE0-5AB19A56F3AB}"/>
+    <hyperlink ref="F29" r:id="rId47" xr:uid="{95FB7936-E26F-434D-AF06-44A9337A976E}"/>
+    <hyperlink ref="F30" r:id="rId48" xr:uid="{DFDB01C1-AE39-EB47-8DEA-A691B1A13FFF}"/>
+    <hyperlink ref="F31" r:id="rId49" xr:uid="{D57E7D52-6454-0149-87FF-11C129D8632B}"/>
+    <hyperlink ref="F32" r:id="rId50" xr:uid="{CD3A77F8-468B-EB42-BC45-17DABC164DD2}"/>
+    <hyperlink ref="D18" r:id="rId51" xr:uid="{473EB3CE-A564-1E45-AC13-AF793AC0B477}"/>
+    <hyperlink ref="F18" r:id="rId52" xr:uid="{9674E89D-A51D-CD48-BAD4-0268F5EF0218}"/>
+    <hyperlink ref="D17" r:id="rId53" xr:uid="{2C21E21B-D467-6B40-B99F-10CFF204DF5E}"/>
+    <hyperlink ref="F17" r:id="rId54" xr:uid="{653FC37B-0E60-F24C-9F82-E361CB6F1BEA}"/>
+    <hyperlink ref="D16" r:id="rId55" xr:uid="{D092DE5A-6AF2-2244-9717-800A8A08CED7}"/>
+    <hyperlink ref="F16" r:id="rId56" xr:uid="{54C0ACDA-4A86-524D-8E90-A1EA869C6122}"/>
+    <hyperlink ref="D15" r:id="rId57" xr:uid="{97F64753-0AA1-EE4A-B974-83528256F4F4}"/>
+    <hyperlink ref="F15" r:id="rId58" xr:uid="{A5448C25-A12C-794E-A542-556C39C496AC}"/>
+    <hyperlink ref="D14" r:id="rId59" xr:uid="{77CE2757-4893-874D-99A1-72D0C139E6FF}"/>
+    <hyperlink ref="F14" r:id="rId60" xr:uid="{7453F409-FB26-364F-96CF-B8B3C16C5539}"/>
+    <hyperlink ref="D13" r:id="rId61" xr:uid="{48A4ED37-D659-7A47-AC11-024E77FD1932}"/>
+    <hyperlink ref="F13" r:id="rId62" xr:uid="{227686EA-22C5-4D4C-A4A3-E4AEAB8249BD}"/>
+    <hyperlink ref="D12" r:id="rId63" xr:uid="{4819B73E-4D12-7442-A4E4-9BCA2F43B41E}"/>
+    <hyperlink ref="F12" r:id="rId64" xr:uid="{FEB6F6C5-6B93-0541-8DFC-234A63742636}"/>
+    <hyperlink ref="D11" r:id="rId65" xr:uid="{908F3A4C-B3BF-5143-8411-82FA701D3B47}"/>
+    <hyperlink ref="F11" r:id="rId66" xr:uid="{BE91235B-8F82-0046-9FD0-B9E1CC774D1C}"/>
+    <hyperlink ref="D10" r:id="rId67" xr:uid="{16DB5697-836B-9D46-83E7-3056E572B29B}"/>
+    <hyperlink ref="F10" r:id="rId68" xr:uid="{CF85B538-39DB-BD47-AE3A-8B073048DFBB}"/>
+    <hyperlink ref="D9" r:id="rId69" xr:uid="{6C5B8EB1-AC9A-904C-907A-569707B74F92}"/>
+    <hyperlink ref="F9" r:id="rId70" xr:uid="{0AF9FAE1-834E-7943-9702-95FC0EB25D0F}"/>
+    <hyperlink ref="D8" r:id="rId71" xr:uid="{D67FD214-5BBB-154A-A06A-D03CEB54BD5C}"/>
+    <hyperlink ref="F8" r:id="rId72" xr:uid="{D237E9DD-C9A8-E740-8277-55420D2AD9DE}"/>
+    <hyperlink ref="D7" r:id="rId73" xr:uid="{5EA863AF-B605-7C4E-931A-904E68BFC36C}"/>
+    <hyperlink ref="F7" r:id="rId74" xr:uid="{3D5A580C-46B7-734E-8E50-64362E621AD2}"/>
+    <hyperlink ref="D6" r:id="rId75" xr:uid="{F593F17C-AE20-1243-820A-652D2D067441}"/>
+    <hyperlink ref="F6" r:id="rId76" xr:uid="{1502675B-8FAC-054C-8E99-CBF9BED0C5AB}"/>
+    <hyperlink ref="D5" r:id="rId77" xr:uid="{000154E9-7A52-D54C-AF9C-566779ADB529}"/>
+    <hyperlink ref="F5" r:id="rId78" xr:uid="{B8166870-E862-EA41-B8C7-06C12E6A0DBA}"/>
+    <hyperlink ref="D4" r:id="rId79" xr:uid="{077645D6-1EBD-1A48-99C3-9CCA9C04C12A}"/>
+    <hyperlink ref="F4" r:id="rId80" xr:uid="{26722FE0-D6EE-DA4D-8421-2FEDE70D1F71}"/>
+    <hyperlink ref="D3" r:id="rId81" xr:uid="{3E74A20E-4BA7-C54D-8A01-82F290B4A2BA}"/>
+    <hyperlink ref="F3" r:id="rId82" xr:uid="{AD6902CF-54CB-674D-8F44-C1807D93A89E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
